--- a/corretor/diario-template.xlsx
+++ b/corretor/diario-template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NEWPC GAMER\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NEWPC GAMER\Desktop\Parque-Clube\correção provas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{732D7B35-8A2C-44EB-83C3-F55DEF1E258A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B30F2E10-DD23-4382-9A32-4A5D421D68B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="195" windowWidth="22335" windowHeight="15405" tabRatio="963" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3135" yWindow="795" windowWidth="25665" windowHeight="15405" tabRatio="963" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="4º ano D - FREQUÊNCIA - 1º BIM" sheetId="14" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1453" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1432" uniqueCount="123">
   <si>
     <t>Quantidade de Aulas</t>
   </si>
@@ -284,9 +284,6 @@
     </r>
   </si>
   <si>
-    <t>2º BIMESTRE  26/04/2019 a 08/07/2019</t>
-  </si>
-  <si>
     <t>1º BIMESTRE 11/02/2019 a 25/04/2019</t>
   </si>
   <si>
@@ -475,9 +472,6 @@
   </si>
   <si>
     <t>1º BIMESTRE  12/02/2026  a 29/04/2025</t>
-  </si>
-  <si>
-    <t>ALYCE VICTÓRIA FERREIRA SANTO+B9:B27S</t>
   </si>
 </sst>
 </file>
@@ -1238,7 +1232,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="164">
+  <cellXfs count="169">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1403,7 +1397,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1467,11 +1460,41 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1488,50 +1511,41 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1541,6 +1555,30 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="38" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1569,9 +1607,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1584,47 +1619,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="38" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1656,20 +1652,27 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2257,278 +2260,278 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="79" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="80"/>
-      <c r="L1" s="80"/>
-      <c r="M1" s="80"/>
-      <c r="N1" s="80"/>
-      <c r="O1" s="80"/>
-      <c r="P1" s="80"/>
-      <c r="Q1" s="80"/>
-      <c r="R1" s="80"/>
-      <c r="S1" s="80"/>
-      <c r="T1" s="80"/>
-      <c r="U1" s="80"/>
-      <c r="V1" s="80"/>
-      <c r="W1" s="80"/>
-      <c r="X1" s="80"/>
-      <c r="Y1" s="80"/>
-      <c r="Z1" s="80"/>
-      <c r="AA1" s="80"/>
-      <c r="AB1" s="80"/>
-      <c r="AC1" s="80"/>
-      <c r="AD1" s="80"/>
-      <c r="AE1" s="80"/>
-      <c r="AF1" s="80"/>
-      <c r="AG1" s="80"/>
-      <c r="AH1" s="80"/>
-      <c r="AI1" s="80"/>
-      <c r="AJ1" s="80"/>
-      <c r="AK1" s="80"/>
-      <c r="AL1" s="80"/>
-      <c r="AM1" s="80"/>
-      <c r="AN1" s="80"/>
-      <c r="AO1" s="80"/>
-      <c r="AP1" s="80"/>
-      <c r="AQ1" s="80"/>
-      <c r="AR1" s="80"/>
-      <c r="AS1" s="80"/>
-      <c r="AT1" s="80"/>
-      <c r="AU1" s="80"/>
-      <c r="AV1" s="80"/>
-      <c r="AW1" s="80"/>
-      <c r="AX1" s="80"/>
-      <c r="AY1" s="80"/>
-      <c r="AZ1" s="80"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+      <c r="M1" s="79"/>
+      <c r="N1" s="79"/>
+      <c r="O1" s="79"/>
+      <c r="P1" s="79"/>
+      <c r="Q1" s="79"/>
+      <c r="R1" s="79"/>
+      <c r="S1" s="79"/>
+      <c r="T1" s="79"/>
+      <c r="U1" s="79"/>
+      <c r="V1" s="79"/>
+      <c r="W1" s="79"/>
+      <c r="X1" s="79"/>
+      <c r="Y1" s="79"/>
+      <c r="Z1" s="79"/>
+      <c r="AA1" s="79"/>
+      <c r="AB1" s="79"/>
+      <c r="AC1" s="79"/>
+      <c r="AD1" s="79"/>
+      <c r="AE1" s="79"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="79"/>
+      <c r="AH1" s="79"/>
+      <c r="AI1" s="79"/>
+      <c r="AJ1" s="79"/>
+      <c r="AK1" s="79"/>
+      <c r="AL1" s="79"/>
+      <c r="AM1" s="79"/>
+      <c r="AN1" s="79"/>
+      <c r="AO1" s="79"/>
+      <c r="AP1" s="79"/>
+      <c r="AQ1" s="79"/>
+      <c r="AR1" s="79"/>
+      <c r="AS1" s="79"/>
+      <c r="AT1" s="79"/>
+      <c r="AU1" s="79"/>
+      <c r="AV1" s="79"/>
+      <c r="AW1" s="79"/>
+      <c r="AX1" s="79"/>
+      <c r="AY1" s="79"/>
+      <c r="AZ1" s="79"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A2" s="80"/>
-      <c r="B2" s="80"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="80"/>
-      <c r="K2" s="80"/>
-      <c r="L2" s="80"/>
-      <c r="M2" s="80"/>
-      <c r="N2" s="80"/>
-      <c r="O2" s="80"/>
-      <c r="P2" s="80"/>
-      <c r="Q2" s="80"/>
-      <c r="R2" s="80"/>
-      <c r="S2" s="80"/>
-      <c r="T2" s="80"/>
-      <c r="U2" s="80"/>
-      <c r="V2" s="80"/>
-      <c r="W2" s="80"/>
-      <c r="X2" s="80"/>
-      <c r="Y2" s="80"/>
-      <c r="Z2" s="80"/>
-      <c r="AA2" s="80"/>
-      <c r="AB2" s="80"/>
-      <c r="AC2" s="80"/>
-      <c r="AD2" s="80"/>
-      <c r="AE2" s="80"/>
-      <c r="AF2" s="80"/>
-      <c r="AG2" s="80"/>
-      <c r="AH2" s="80"/>
-      <c r="AI2" s="80"/>
-      <c r="AJ2" s="80"/>
-      <c r="AK2" s="80"/>
-      <c r="AL2" s="80"/>
-      <c r="AM2" s="80"/>
-      <c r="AN2" s="80"/>
-      <c r="AO2" s="80"/>
-      <c r="AP2" s="80"/>
-      <c r="AQ2" s="80"/>
-      <c r="AR2" s="80"/>
-      <c r="AS2" s="80"/>
-      <c r="AT2" s="80"/>
-      <c r="AU2" s="80"/>
-      <c r="AV2" s="80"/>
-      <c r="AW2" s="80"/>
-      <c r="AX2" s="80"/>
-      <c r="AY2" s="80"/>
-      <c r="AZ2" s="80"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
+      <c r="L2" s="79"/>
+      <c r="M2" s="79"/>
+      <c r="N2" s="79"/>
+      <c r="O2" s="79"/>
+      <c r="P2" s="79"/>
+      <c r="Q2" s="79"/>
+      <c r="R2" s="79"/>
+      <c r="S2" s="79"/>
+      <c r="T2" s="79"/>
+      <c r="U2" s="79"/>
+      <c r="V2" s="79"/>
+      <c r="W2" s="79"/>
+      <c r="X2" s="79"/>
+      <c r="Y2" s="79"/>
+      <c r="Z2" s="79"/>
+      <c r="AA2" s="79"/>
+      <c r="AB2" s="79"/>
+      <c r="AC2" s="79"/>
+      <c r="AD2" s="79"/>
+      <c r="AE2" s="79"/>
+      <c r="AF2" s="79"/>
+      <c r="AG2" s="79"/>
+      <c r="AH2" s="79"/>
+      <c r="AI2" s="79"/>
+      <c r="AJ2" s="79"/>
+      <c r="AK2" s="79"/>
+      <c r="AL2" s="79"/>
+      <c r="AM2" s="79"/>
+      <c r="AN2" s="79"/>
+      <c r="AO2" s="79"/>
+      <c r="AP2" s="79"/>
+      <c r="AQ2" s="79"/>
+      <c r="AR2" s="79"/>
+      <c r="AS2" s="79"/>
+      <c r="AT2" s="79"/>
+      <c r="AU2" s="79"/>
+      <c r="AV2" s="79"/>
+      <c r="AW2" s="79"/>
+      <c r="AX2" s="79"/>
+      <c r="AY2" s="79"/>
+      <c r="AZ2" s="79"/>
     </row>
     <row r="3" spans="1:54" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="80"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="80"/>
-      <c r="K3" s="80"/>
-      <c r="L3" s="80"/>
-      <c r="M3" s="80"/>
-      <c r="N3" s="80"/>
-      <c r="O3" s="80"/>
-      <c r="P3" s="80"/>
-      <c r="Q3" s="80"/>
-      <c r="R3" s="80"/>
-      <c r="S3" s="80"/>
-      <c r="T3" s="80"/>
-      <c r="U3" s="80"/>
-      <c r="V3" s="80"/>
-      <c r="W3" s="80"/>
-      <c r="X3" s="80"/>
-      <c r="Y3" s="80"/>
-      <c r="Z3" s="80"/>
-      <c r="AA3" s="80"/>
-      <c r="AB3" s="80"/>
-      <c r="AC3" s="80"/>
-      <c r="AD3" s="80"/>
-      <c r="AE3" s="80"/>
-      <c r="AF3" s="80"/>
-      <c r="AG3" s="80"/>
-      <c r="AH3" s="80"/>
-      <c r="AI3" s="80"/>
-      <c r="AJ3" s="80"/>
-      <c r="AK3" s="80"/>
-      <c r="AL3" s="80"/>
-      <c r="AM3" s="80"/>
-      <c r="AN3" s="80"/>
-      <c r="AO3" s="80"/>
-      <c r="AP3" s="80"/>
-      <c r="AQ3" s="80"/>
-      <c r="AR3" s="80"/>
-      <c r="AS3" s="80"/>
-      <c r="AT3" s="80"/>
-      <c r="AU3" s="80"/>
-      <c r="AV3" s="80"/>
-      <c r="AW3" s="80"/>
-      <c r="AX3" s="80"/>
-      <c r="AY3" s="80"/>
-      <c r="AZ3" s="80"/>
+      <c r="A3" s="79"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
+      <c r="I3" s="79"/>
+      <c r="J3" s="79"/>
+      <c r="K3" s="79"/>
+      <c r="L3" s="79"/>
+      <c r="M3" s="79"/>
+      <c r="N3" s="79"/>
+      <c r="O3" s="79"/>
+      <c r="P3" s="79"/>
+      <c r="Q3" s="79"/>
+      <c r="R3" s="79"/>
+      <c r="S3" s="79"/>
+      <c r="T3" s="79"/>
+      <c r="U3" s="79"/>
+      <c r="V3" s="79"/>
+      <c r="W3" s="79"/>
+      <c r="X3" s="79"/>
+      <c r="Y3" s="79"/>
+      <c r="Z3" s="79"/>
+      <c r="AA3" s="79"/>
+      <c r="AB3" s="79"/>
+      <c r="AC3" s="79"/>
+      <c r="AD3" s="79"/>
+      <c r="AE3" s="79"/>
+      <c r="AF3" s="79"/>
+      <c r="AG3" s="79"/>
+      <c r="AH3" s="79"/>
+      <c r="AI3" s="79"/>
+      <c r="AJ3" s="79"/>
+      <c r="AK3" s="79"/>
+      <c r="AL3" s="79"/>
+      <c r="AM3" s="79"/>
+      <c r="AN3" s="79"/>
+      <c r="AO3" s="79"/>
+      <c r="AP3" s="79"/>
+      <c r="AQ3" s="79"/>
+      <c r="AR3" s="79"/>
+      <c r="AS3" s="79"/>
+      <c r="AT3" s="79"/>
+      <c r="AU3" s="79"/>
+      <c r="AV3" s="79"/>
+      <c r="AW3" s="79"/>
+      <c r="AX3" s="79"/>
+      <c r="AY3" s="79"/>
+      <c r="AZ3" s="79"/>
     </row>
     <row r="4" spans="1:54" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="80"/>
-      <c r="B4" s="80"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="80"/>
-      <c r="I4" s="80"/>
-      <c r="J4" s="80"/>
-      <c r="K4" s="80"/>
-      <c r="L4" s="80"/>
-      <c r="M4" s="80"/>
-      <c r="N4" s="80"/>
-      <c r="O4" s="80"/>
-      <c r="P4" s="80"/>
-      <c r="Q4" s="80"/>
-      <c r="R4" s="80"/>
-      <c r="S4" s="80"/>
-      <c r="T4" s="80"/>
-      <c r="U4" s="80"/>
-      <c r="V4" s="80"/>
-      <c r="W4" s="80"/>
-      <c r="X4" s="80"/>
-      <c r="Y4" s="80"/>
-      <c r="Z4" s="80"/>
-      <c r="AA4" s="80"/>
-      <c r="AB4" s="80"/>
-      <c r="AC4" s="80"/>
-      <c r="AD4" s="80"/>
-      <c r="AE4" s="80"/>
-      <c r="AF4" s="80"/>
-      <c r="AG4" s="80"/>
-      <c r="AH4" s="80"/>
-      <c r="AI4" s="80"/>
-      <c r="AJ4" s="80"/>
-      <c r="AK4" s="80"/>
-      <c r="AL4" s="80"/>
-      <c r="AM4" s="80"/>
-      <c r="AN4" s="80"/>
-      <c r="AO4" s="80"/>
-      <c r="AP4" s="80"/>
-      <c r="AQ4" s="80"/>
-      <c r="AR4" s="80"/>
-      <c r="AS4" s="80"/>
-      <c r="AT4" s="80"/>
-      <c r="AU4" s="80"/>
-      <c r="AV4" s="80"/>
-      <c r="AW4" s="80"/>
-      <c r="AX4" s="80"/>
-      <c r="AY4" s="80"/>
-      <c r="AZ4" s="80"/>
+      <c r="A4" s="79"/>
+      <c r="B4" s="79"/>
+      <c r="C4" s="79"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="79"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="79"/>
+      <c r="H4" s="79"/>
+      <c r="I4" s="79"/>
+      <c r="J4" s="79"/>
+      <c r="K4" s="79"/>
+      <c r="L4" s="79"/>
+      <c r="M4" s="79"/>
+      <c r="N4" s="79"/>
+      <c r="O4" s="79"/>
+      <c r="P4" s="79"/>
+      <c r="Q4" s="79"/>
+      <c r="R4" s="79"/>
+      <c r="S4" s="79"/>
+      <c r="T4" s="79"/>
+      <c r="U4" s="79"/>
+      <c r="V4" s="79"/>
+      <c r="W4" s="79"/>
+      <c r="X4" s="79"/>
+      <c r="Y4" s="79"/>
+      <c r="Z4" s="79"/>
+      <c r="AA4" s="79"/>
+      <c r="AB4" s="79"/>
+      <c r="AC4" s="79"/>
+      <c r="AD4" s="79"/>
+      <c r="AE4" s="79"/>
+      <c r="AF4" s="79"/>
+      <c r="AG4" s="79"/>
+      <c r="AH4" s="79"/>
+      <c r="AI4" s="79"/>
+      <c r="AJ4" s="79"/>
+      <c r="AK4" s="79"/>
+      <c r="AL4" s="79"/>
+      <c r="AM4" s="79"/>
+      <c r="AN4" s="79"/>
+      <c r="AO4" s="79"/>
+      <c r="AP4" s="79"/>
+      <c r="AQ4" s="79"/>
+      <c r="AR4" s="79"/>
+      <c r="AS4" s="79"/>
+      <c r="AT4" s="79"/>
+      <c r="AU4" s="79"/>
+      <c r="AV4" s="79"/>
+      <c r="AW4" s="79"/>
+      <c r="AX4" s="79"/>
+      <c r="AY4" s="79"/>
+      <c r="AZ4" s="79"/>
     </row>
     <row r="5" spans="1:54" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="81" t="s">
-        <v>99</v>
-      </c>
-      <c r="B5" s="81"/>
-      <c r="C5" s="81"/>
-      <c r="D5" s="81"/>
-      <c r="E5" s="81"/>
-      <c r="F5" s="81"/>
-      <c r="G5" s="81"/>
-      <c r="H5" s="81"/>
-      <c r="I5" s="81"/>
-      <c r="J5" s="81"/>
-      <c r="K5" s="81"/>
-      <c r="L5" s="81"/>
-      <c r="M5" s="81"/>
-      <c r="N5" s="81"/>
-      <c r="O5" s="81"/>
-      <c r="P5" s="81"/>
-      <c r="Q5" s="81"/>
-      <c r="R5" s="81"/>
-      <c r="S5" s="81"/>
-      <c r="T5" s="81"/>
-      <c r="U5" s="81"/>
-      <c r="V5" s="81"/>
-      <c r="W5" s="81"/>
-      <c r="X5" s="81"/>
-      <c r="Y5" s="81"/>
-      <c r="Z5" s="81"/>
-      <c r="AA5" s="81"/>
-      <c r="AB5" s="81"/>
-      <c r="AC5" s="81"/>
-      <c r="AD5" s="81"/>
-      <c r="AE5" s="81"/>
-      <c r="AF5" s="81"/>
-      <c r="AG5" s="81"/>
-      <c r="AH5" s="81"/>
-      <c r="AI5" s="81"/>
-      <c r="AJ5" s="81"/>
-      <c r="AK5" s="81"/>
-      <c r="AL5" s="81"/>
-      <c r="AM5" s="81"/>
-      <c r="AN5" s="81"/>
-      <c r="AO5" s="81"/>
-      <c r="AP5" s="81"/>
-      <c r="AQ5" s="81"/>
-      <c r="AR5" s="81"/>
-      <c r="AS5" s="81"/>
-      <c r="AT5" s="81"/>
-      <c r="AU5" s="81"/>
-      <c r="AV5" s="81"/>
-      <c r="AW5" s="81"/>
-      <c r="AX5" s="81"/>
-      <c r="AY5" s="81"/>
-      <c r="AZ5" s="81"/>
+      <c r="A5" s="80" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" s="80"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="80"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="80"/>
+      <c r="J5" s="80"/>
+      <c r="K5" s="80"/>
+      <c r="L5" s="80"/>
+      <c r="M5" s="80"/>
+      <c r="N5" s="80"/>
+      <c r="O5" s="80"/>
+      <c r="P5" s="80"/>
+      <c r="Q5" s="80"/>
+      <c r="R5" s="80"/>
+      <c r="S5" s="80"/>
+      <c r="T5" s="80"/>
+      <c r="U5" s="80"/>
+      <c r="V5" s="80"/>
+      <c r="W5" s="80"/>
+      <c r="X5" s="80"/>
+      <c r="Y5" s="80"/>
+      <c r="Z5" s="80"/>
+      <c r="AA5" s="80"/>
+      <c r="AB5" s="80"/>
+      <c r="AC5" s="80"/>
+      <c r="AD5" s="80"/>
+      <c r="AE5" s="80"/>
+      <c r="AF5" s="80"/>
+      <c r="AG5" s="80"/>
+      <c r="AH5" s="80"/>
+      <c r="AI5" s="80"/>
+      <c r="AJ5" s="80"/>
+      <c r="AK5" s="80"/>
+      <c r="AL5" s="80"/>
+      <c r="AM5" s="80"/>
+      <c r="AN5" s="80"/>
+      <c r="AO5" s="80"/>
+      <c r="AP5" s="80"/>
+      <c r="AQ5" s="80"/>
+      <c r="AR5" s="80"/>
+      <c r="AS5" s="80"/>
+      <c r="AT5" s="80"/>
+      <c r="AU5" s="80"/>
+      <c r="AV5" s="80"/>
+      <c r="AW5" s="80"/>
+      <c r="AX5" s="80"/>
+      <c r="AY5" s="80"/>
+      <c r="AZ5" s="80"/>
     </row>
     <row r="6" spans="1:54" s="3" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
@@ -2536,215 +2539,115 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="4"/>
-      <c r="D6" s="82"/>
-      <c r="E6" s="82"/>
-      <c r="F6" s="82"/>
-      <c r="G6" s="82"/>
-      <c r="H6" s="82"/>
-      <c r="I6" s="82"/>
-      <c r="J6" s="82"/>
-      <c r="K6" s="82"/>
-      <c r="L6" s="82"/>
-      <c r="M6" s="82"/>
-      <c r="N6" s="82"/>
-      <c r="O6" s="82"/>
-      <c r="P6" s="82"/>
-      <c r="Q6" s="83" t="s">
+      <c r="D6" s="81"/>
+      <c r="E6" s="81"/>
+      <c r="F6" s="81"/>
+      <c r="G6" s="81"/>
+      <c r="H6" s="81"/>
+      <c r="I6" s="81"/>
+      <c r="J6" s="81"/>
+      <c r="K6" s="81"/>
+      <c r="L6" s="81"/>
+      <c r="M6" s="81"/>
+      <c r="N6" s="81"/>
+      <c r="O6" s="81"/>
+      <c r="P6" s="81"/>
+      <c r="Q6" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="83"/>
-      <c r="S6" s="83"/>
-      <c r="T6" s="83"/>
-      <c r="U6" s="83"/>
-      <c r="V6" s="83"/>
-      <c r="W6" s="83"/>
-      <c r="X6" s="83"/>
-      <c r="Y6" s="83"/>
-      <c r="Z6" s="83"/>
-      <c r="AA6" s="83"/>
-      <c r="AB6" s="83"/>
-      <c r="AC6" s="83"/>
-      <c r="AD6" s="82">
+      <c r="R6" s="82"/>
+      <c r="S6" s="82"/>
+      <c r="T6" s="82"/>
+      <c r="U6" s="82"/>
+      <c r="V6" s="82"/>
+      <c r="W6" s="82"/>
+      <c r="X6" s="82"/>
+      <c r="Y6" s="82"/>
+      <c r="Z6" s="82"/>
+      <c r="AA6" s="82"/>
+      <c r="AB6" s="82"/>
+      <c r="AC6" s="82"/>
+      <c r="AD6" s="81">
         <v>50</v>
       </c>
-      <c r="AE6" s="82"/>
+      <c r="AE6" s="81"/>
       <c r="AF6" s="5"/>
-      <c r="AG6" s="82" t="s">
+      <c r="AG6" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="AH6" s="82"/>
-      <c r="AI6" s="82"/>
-      <c r="AJ6" s="82"/>
-      <c r="AK6" s="82"/>
-      <c r="AL6" s="82"/>
-      <c r="AM6" s="82"/>
-      <c r="AN6" s="82"/>
-      <c r="AO6" s="82"/>
-      <c r="AP6" s="82"/>
-      <c r="AQ6" s="82"/>
-      <c r="AR6" s="82"/>
-      <c r="AS6" s="82"/>
+      <c r="AH6" s="81"/>
+      <c r="AI6" s="81"/>
+      <c r="AJ6" s="81"/>
+      <c r="AK6" s="81"/>
+      <c r="AL6" s="81"/>
+      <c r="AM6" s="81"/>
+      <c r="AN6" s="81"/>
+      <c r="AO6" s="81"/>
+      <c r="AP6" s="81"/>
+      <c r="AQ6" s="81"/>
+      <c r="AR6" s="81"/>
+      <c r="AS6" s="81"/>
       <c r="AT6" s="4"/>
       <c r="AU6" s="4"/>
       <c r="AV6" s="4"/>
     </row>
     <row r="7" spans="1:54" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="50"/>
-      <c r="B7" s="75" t="s">
-        <v>123</v>
-      </c>
-      <c r="C7" s="76">
-        <v>45698</v>
-      </c>
-      <c r="D7" s="76">
-        <v>45699</v>
-      </c>
-      <c r="E7" s="76">
-        <v>45700</v>
-      </c>
-      <c r="F7" s="76">
-        <v>45701</v>
-      </c>
-      <c r="G7" s="76">
-        <v>45702</v>
-      </c>
-      <c r="H7" s="76">
-        <v>45705</v>
-      </c>
-      <c r="I7" s="76">
-        <v>45706</v>
-      </c>
-      <c r="J7" s="76">
-        <v>45707</v>
-      </c>
-      <c r="K7" s="76">
-        <v>45708</v>
-      </c>
-      <c r="L7" s="76">
-        <v>45709</v>
-      </c>
-      <c r="M7" s="76">
-        <v>45712</v>
-      </c>
-      <c r="N7" s="76">
-        <v>45713</v>
-      </c>
-      <c r="O7" s="76">
-        <v>45714</v>
-      </c>
-      <c r="P7" s="76">
-        <v>45715</v>
-      </c>
-      <c r="Q7" s="76">
-        <v>45716</v>
-      </c>
-      <c r="R7" s="76">
-        <v>45722</v>
-      </c>
-      <c r="S7" s="76">
-        <v>45723</v>
-      </c>
-      <c r="T7" s="76">
-        <v>45726</v>
-      </c>
-      <c r="U7" s="76">
-        <v>45727</v>
-      </c>
-      <c r="V7" s="76">
-        <v>45728</v>
-      </c>
-      <c r="W7" s="76">
-        <v>45729</v>
-      </c>
-      <c r="X7" s="76">
-        <v>45730</v>
-      </c>
-      <c r="Y7" s="76">
-        <v>45733</v>
-      </c>
-      <c r="Z7" s="76">
-        <v>45734</v>
-      </c>
-      <c r="AA7" s="76">
-        <v>45735</v>
-      </c>
-      <c r="AB7" s="76">
-        <v>45736</v>
-      </c>
-      <c r="AC7" s="76">
-        <v>45737</v>
-      </c>
-      <c r="AD7" s="76">
-        <v>45740</v>
-      </c>
-      <c r="AE7" s="76">
-        <v>45741</v>
-      </c>
-      <c r="AF7" s="76">
-        <v>45742</v>
-      </c>
-      <c r="AG7" s="76">
-        <v>45743</v>
-      </c>
-      <c r="AH7" s="76">
-        <v>45744</v>
-      </c>
-      <c r="AI7" s="76">
-        <v>45747</v>
-      </c>
-      <c r="AJ7" s="76">
-        <v>45748</v>
-      </c>
-      <c r="AK7" s="76">
-        <v>45749</v>
-      </c>
-      <c r="AL7" s="76">
-        <v>45750</v>
-      </c>
-      <c r="AM7" s="76">
-        <v>45751</v>
-      </c>
-      <c r="AN7" s="76">
-        <v>45754</v>
-      </c>
-      <c r="AO7" s="76">
-        <v>45755</v>
-      </c>
-      <c r="AP7" s="76">
-        <v>45756</v>
-      </c>
-      <c r="AQ7" s="76">
-        <v>45757</v>
-      </c>
-      <c r="AR7" s="76">
-        <v>45758</v>
-      </c>
-      <c r="AS7" s="76">
-        <v>45761</v>
-      </c>
-      <c r="AT7" s="76">
-        <v>45762</v>
-      </c>
-      <c r="AU7" s="76">
-        <v>45763</v>
-      </c>
-      <c r="AV7" s="76">
-        <v>45764</v>
-      </c>
-      <c r="AW7" s="76">
-        <v>45769</v>
-      </c>
-      <c r="AX7" s="76">
-        <v>45770</v>
-      </c>
-      <c r="AY7" s="76">
-        <v>45771</v>
-      </c>
-      <c r="AZ7" s="76">
-        <v>45772</v>
-      </c>
-      <c r="BA7" s="77"/>
-      <c r="BB7" s="78" t="s">
+      <c r="B7" s="74" t="s">
+        <v>122</v>
+      </c>
+      <c r="C7" s="75"/>
+      <c r="D7" s="75"/>
+      <c r="E7" s="75"/>
+      <c r="F7" s="75"/>
+      <c r="G7" s="75"/>
+      <c r="H7" s="75"/>
+      <c r="I7" s="75"/>
+      <c r="J7" s="75"/>
+      <c r="K7" s="75"/>
+      <c r="L7" s="75"/>
+      <c r="M7" s="75"/>
+      <c r="N7" s="75"/>
+      <c r="O7" s="75"/>
+      <c r="P7" s="75"/>
+      <c r="Q7" s="75"/>
+      <c r="R7" s="75"/>
+      <c r="S7" s="75"/>
+      <c r="T7" s="75"/>
+      <c r="U7" s="75"/>
+      <c r="V7" s="75"/>
+      <c r="W7" s="75"/>
+      <c r="X7" s="75"/>
+      <c r="Y7" s="75"/>
+      <c r="Z7" s="75"/>
+      <c r="AA7" s="75"/>
+      <c r="AB7" s="75"/>
+      <c r="AC7" s="75"/>
+      <c r="AD7" s="75"/>
+      <c r="AE7" s="75"/>
+      <c r="AF7" s="75"/>
+      <c r="AG7" s="75"/>
+      <c r="AH7" s="75"/>
+      <c r="AI7" s="75"/>
+      <c r="AJ7" s="75"/>
+      <c r="AK7" s="75"/>
+      <c r="AL7" s="75"/>
+      <c r="AM7" s="75"/>
+      <c r="AN7" s="75"/>
+      <c r="AO7" s="75"/>
+      <c r="AP7" s="75"/>
+      <c r="AQ7" s="75"/>
+      <c r="AR7" s="75"/>
+      <c r="AS7" s="75"/>
+      <c r="AT7" s="75"/>
+      <c r="AU7" s="75"/>
+      <c r="AV7" s="75"/>
+      <c r="AW7" s="75"/>
+      <c r="AX7" s="75"/>
+      <c r="AY7" s="75"/>
+      <c r="AZ7" s="75"/>
+      <c r="BA7" s="76"/>
+      <c r="BB7" s="77" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2908,15 +2811,13 @@
       <c r="BA8" s="1">
         <v>51</v>
       </c>
-      <c r="BB8" s="79"/>
+      <c r="BB8" s="78"/>
     </row>
     <row r="9" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A9" s="54">
         <v>1</v>
       </c>
-      <c r="B9" s="56" t="s">
-        <v>124</v>
-      </c>
+      <c r="B9" s="163"/>
       <c r="C9" s="49" t="s">
         <v>30</v>
       </c>
@@ -3076,7 +2977,7 @@
       <c r="A10" s="52">
         <v>2</v>
       </c>
-      <c r="B10" s="56"/>
+      <c r="B10" s="163"/>
       <c r="C10" s="49" t="s">
         <v>30</v>
       </c>
@@ -3236,7 +3137,7 @@
       <c r="A11" s="52">
         <v>3</v>
       </c>
-      <c r="B11" s="56"/>
+      <c r="B11" s="163"/>
       <c r="C11" s="49" t="s">
         <v>30</v>
       </c>
@@ -3396,7 +3297,7 @@
       <c r="A12" s="52">
         <v>4</v>
       </c>
-      <c r="B12" s="74"/>
+      <c r="B12" s="163"/>
       <c r="C12" s="49" t="s">
         <v>30</v>
       </c>
@@ -3556,7 +3457,7 @@
       <c r="A13" s="52">
         <v>5</v>
       </c>
-      <c r="B13" s="56"/>
+      <c r="B13" s="163"/>
       <c r="C13" s="49" t="s">
         <v>30</v>
       </c>
@@ -3716,7 +3617,7 @@
       <c r="A14" s="52">
         <v>6</v>
       </c>
-      <c r="B14" s="56"/>
+      <c r="B14" s="163"/>
       <c r="C14" s="49" t="s">
         <v>30</v>
       </c>
@@ -3876,7 +3777,7 @@
       <c r="A15" s="52">
         <v>7</v>
       </c>
-      <c r="B15" s="56"/>
+      <c r="B15" s="163"/>
       <c r="C15" s="49" t="s">
         <v>30</v>
       </c>
@@ -4036,7 +3937,7 @@
       <c r="A16" s="52">
         <v>8</v>
       </c>
-      <c r="B16" s="56"/>
+      <c r="B16" s="163"/>
       <c r="C16" s="49" t="s">
         <v>30</v>
       </c>
@@ -4196,7 +4097,7 @@
       <c r="A17" s="52">
         <v>9</v>
       </c>
-      <c r="B17" s="56"/>
+      <c r="B17" s="163"/>
       <c r="C17" s="49" t="s">
         <v>30</v>
       </c>
@@ -4356,7 +4257,7 @@
       <c r="A18" s="52">
         <v>10</v>
       </c>
-      <c r="B18" s="56"/>
+      <c r="B18" s="163"/>
       <c r="C18" s="49" t="s">
         <v>30</v>
       </c>
@@ -4516,7 +4417,7 @@
       <c r="A19" s="52">
         <v>11</v>
       </c>
-      <c r="B19" s="56"/>
+      <c r="B19" s="163"/>
       <c r="C19" s="49" t="s">
         <v>30</v>
       </c>
@@ -4676,7 +4577,7 @@
       <c r="A20" s="52">
         <v>12</v>
       </c>
-      <c r="B20" s="56"/>
+      <c r="B20" s="163"/>
       <c r="C20" s="49" t="s">
         <v>30</v>
       </c>
@@ -4836,7 +4737,7 @@
       <c r="A21" s="52">
         <v>13</v>
       </c>
-      <c r="B21" s="74"/>
+      <c r="B21" s="163"/>
       <c r="C21" s="49" t="s">
         <v>30</v>
       </c>
@@ -4996,7 +4897,7 @@
       <c r="A22" s="52">
         <v>14</v>
       </c>
-      <c r="B22" s="56"/>
+      <c r="B22" s="163"/>
       <c r="C22" s="49" t="s">
         <v>30</v>
       </c>
@@ -5156,7 +5057,7 @@
       <c r="A23" s="52">
         <v>15</v>
       </c>
-      <c r="B23" s="56"/>
+      <c r="B23" s="163"/>
       <c r="C23" s="49" t="s">
         <v>30</v>
       </c>
@@ -5316,7 +5217,7 @@
       <c r="A24" s="52">
         <v>16</v>
       </c>
-      <c r="B24" s="56"/>
+      <c r="B24" s="163"/>
       <c r="C24" s="49" t="s">
         <v>30</v>
       </c>
@@ -5476,7 +5377,7 @@
       <c r="A25" s="52">
         <v>17</v>
       </c>
-      <c r="B25" s="56"/>
+      <c r="B25" s="163"/>
       <c r="C25" s="49" t="s">
         <v>30</v>
       </c>
@@ -5636,7 +5537,7 @@
       <c r="A26" s="52">
         <v>18</v>
       </c>
-      <c r="B26" s="74"/>
+      <c r="B26" s="163"/>
       <c r="C26" s="49" t="s">
         <v>30</v>
       </c>
@@ -5796,7 +5697,7 @@
       <c r="A27" s="52">
         <v>19</v>
       </c>
-      <c r="B27" s="55"/>
+      <c r="B27" s="164"/>
       <c r="C27" s="49" t="s">
         <v>30</v>
       </c>
@@ -5956,7 +5857,7 @@
       <c r="A28" s="52">
         <v>20</v>
       </c>
-      <c r="B28" s="19"/>
+      <c r="B28" s="165"/>
       <c r="C28" s="49" t="s">
         <v>30</v>
       </c>
@@ -6112,172 +6013,70 @@
       </c>
       <c r="BB28" s="56"/>
     </row>
-    <row r="29" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="30" spans="1:54" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="166"/>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A30" s="50"/>
-      <c r="B30" s="75" t="s">
-        <v>65</v>
-      </c>
-      <c r="C30" s="76">
-        <v>45698</v>
-      </c>
-      <c r="D30" s="76">
-        <v>45699</v>
-      </c>
-      <c r="E30" s="76">
-        <v>45700</v>
-      </c>
-      <c r="F30" s="76">
-        <v>45701</v>
-      </c>
-      <c r="G30" s="76">
-        <v>45702</v>
-      </c>
-      <c r="H30" s="76">
-        <v>45705</v>
-      </c>
-      <c r="I30" s="76">
-        <v>45706</v>
-      </c>
-      <c r="J30" s="76">
-        <v>45707</v>
-      </c>
-      <c r="K30" s="76">
-        <v>45708</v>
-      </c>
-      <c r="L30" s="76">
-        <v>45709</v>
-      </c>
-      <c r="M30" s="76">
-        <v>45712</v>
-      </c>
-      <c r="N30" s="76">
-        <v>45713</v>
-      </c>
-      <c r="O30" s="76">
-        <v>45714</v>
-      </c>
-      <c r="P30" s="76">
-        <v>45715</v>
-      </c>
-      <c r="Q30" s="76">
-        <v>45716</v>
-      </c>
-      <c r="R30" s="76">
-        <v>45722</v>
-      </c>
-      <c r="S30" s="76">
-        <v>45723</v>
-      </c>
-      <c r="T30" s="76">
-        <v>45726</v>
-      </c>
-      <c r="U30" s="76">
-        <v>45727</v>
-      </c>
-      <c r="V30" s="76">
-        <v>45728</v>
-      </c>
-      <c r="W30" s="76">
-        <v>45729</v>
-      </c>
-      <c r="X30" s="76">
-        <v>45730</v>
-      </c>
-      <c r="Y30" s="76">
-        <v>45733</v>
-      </c>
-      <c r="Z30" s="76">
-        <v>45734</v>
-      </c>
-      <c r="AA30" s="76">
-        <v>45735</v>
-      </c>
-      <c r="AB30" s="76">
-        <v>45736</v>
-      </c>
-      <c r="AC30" s="76">
-        <v>45737</v>
-      </c>
-      <c r="AD30" s="76">
-        <v>45740</v>
-      </c>
-      <c r="AE30" s="76">
-        <v>45741</v>
-      </c>
-      <c r="AF30" s="76">
-        <v>45742</v>
-      </c>
-      <c r="AG30" s="76">
-        <v>45743</v>
-      </c>
-      <c r="AH30" s="76">
-        <v>45744</v>
-      </c>
-      <c r="AI30" s="76">
-        <v>45747</v>
-      </c>
-      <c r="AJ30" s="76">
-        <v>45748</v>
-      </c>
-      <c r="AK30" s="76">
-        <v>45749</v>
-      </c>
-      <c r="AL30" s="76">
-        <v>45750</v>
-      </c>
-      <c r="AM30" s="76">
-        <v>45751</v>
-      </c>
-      <c r="AN30" s="76">
-        <v>45754</v>
-      </c>
-      <c r="AO30" s="76">
-        <v>45755</v>
-      </c>
-      <c r="AP30" s="76">
-        <v>45756</v>
-      </c>
-      <c r="AQ30" s="76">
-        <v>45757</v>
-      </c>
-      <c r="AR30" s="76">
-        <v>45758</v>
-      </c>
-      <c r="AS30" s="76">
-        <v>45761</v>
-      </c>
-      <c r="AT30" s="76">
-        <v>45762</v>
-      </c>
-      <c r="AU30" s="76">
-        <v>45763</v>
-      </c>
-      <c r="AV30" s="76">
-        <v>45764</v>
-      </c>
-      <c r="AW30" s="76">
-        <v>45769</v>
-      </c>
-      <c r="AX30" s="76">
-        <v>45770</v>
-      </c>
-      <c r="AY30" s="76">
-        <v>45771</v>
-      </c>
-      <c r="AZ30" s="76">
-        <v>45772</v>
-      </c>
-      <c r="BA30" s="77"/>
-      <c r="BB30" s="78"/>
+      <c r="B30" s="167"/>
+      <c r="C30" s="75"/>
+      <c r="D30" s="75"/>
+      <c r="E30" s="75"/>
+      <c r="F30" s="75"/>
+      <c r="G30" s="75"/>
+      <c r="H30" s="75"/>
+      <c r="I30" s="75"/>
+      <c r="J30" s="75"/>
+      <c r="K30" s="75"/>
+      <c r="L30" s="75"/>
+      <c r="M30" s="75"/>
+      <c r="N30" s="75"/>
+      <c r="O30" s="75"/>
+      <c r="P30" s="75"/>
+      <c r="Q30" s="75"/>
+      <c r="R30" s="75"/>
+      <c r="S30" s="75"/>
+      <c r="T30" s="75"/>
+      <c r="U30" s="75"/>
+      <c r="V30" s="75"/>
+      <c r="W30" s="75"/>
+      <c r="X30" s="75"/>
+      <c r="Y30" s="75"/>
+      <c r="Z30" s="75"/>
+      <c r="AA30" s="75"/>
+      <c r="AB30" s="75"/>
+      <c r="AC30" s="75"/>
+      <c r="AD30" s="75"/>
+      <c r="AE30" s="75"/>
+      <c r="AF30" s="75"/>
+      <c r="AG30" s="75"/>
+      <c r="AH30" s="75"/>
+      <c r="AI30" s="75"/>
+      <c r="AJ30" s="75"/>
+      <c r="AK30" s="75"/>
+      <c r="AL30" s="75"/>
+      <c r="AM30" s="75"/>
+      <c r="AN30" s="75"/>
+      <c r="AO30" s="75"/>
+      <c r="AP30" s="75"/>
+      <c r="AQ30" s="75"/>
+      <c r="AR30" s="75"/>
+      <c r="AS30" s="75"/>
+      <c r="AT30" s="75"/>
+      <c r="AU30" s="75"/>
+      <c r="AV30" s="75"/>
+      <c r="AW30" s="75"/>
+      <c r="AX30" s="75"/>
+      <c r="AY30" s="75"/>
+      <c r="AZ30" s="75"/>
+      <c r="BA30" s="76"/>
+      <c r="BB30" s="77"/>
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A31" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="B31" s="53" t="s">
-        <v>0</v>
-      </c>
+      <c r="B31" s="168"/>
       <c r="C31" s="48">
         <v>1</v>
       </c>
@@ -6431,15 +6230,13 @@
       <c r="BA31" s="1">
         <v>51</v>
       </c>
-      <c r="BB31" s="79"/>
+      <c r="BB31" s="78"/>
     </row>
     <row r="32" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A32" s="54">
         <v>1</v>
       </c>
-      <c r="B32" s="56" t="s">
-        <v>84</v>
-      </c>
+      <c r="B32" s="163"/>
       <c r="C32" s="49"/>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
@@ -6497,9 +6294,7 @@
       <c r="A33" s="52">
         <v>2</v>
       </c>
-      <c r="B33" s="56" t="s">
-        <v>96</v>
-      </c>
+      <c r="B33" s="163"/>
       <c r="C33" s="49"/>
       <c r="D33" s="6"/>
       <c r="E33" s="6"/>
@@ -6557,9 +6352,7 @@
       <c r="A34" s="52">
         <v>3</v>
       </c>
-      <c r="B34" s="56" t="s">
-        <v>85</v>
-      </c>
+      <c r="B34" s="163"/>
       <c r="C34" s="49"/>
       <c r="D34" s="6"/>
       <c r="E34" s="6"/>
@@ -6617,9 +6410,7 @@
       <c r="A35" s="52">
         <v>4</v>
       </c>
-      <c r="B35" s="74" t="s">
-        <v>83</v>
-      </c>
+      <c r="B35" s="163"/>
       <c r="C35" s="49"/>
       <c r="D35" s="6"/>
       <c r="E35" s="6"/>
@@ -6677,9 +6468,7 @@
       <c r="A36" s="52">
         <v>5</v>
       </c>
-      <c r="B36" s="56" t="s">
-        <v>86</v>
-      </c>
+      <c r="B36" s="163"/>
       <c r="C36" s="49"/>
       <c r="D36" s="6"/>
       <c r="E36" s="6"/>
@@ -6737,9 +6526,7 @@
       <c r="A37" s="52">
         <v>6</v>
       </c>
-      <c r="B37" s="56" t="s">
-        <v>87</v>
-      </c>
+      <c r="B37" s="163"/>
       <c r="C37" s="49"/>
       <c r="D37" s="6"/>
       <c r="E37" s="6"/>
@@ -6797,9 +6584,7 @@
       <c r="A38" s="52">
         <v>7</v>
       </c>
-      <c r="B38" s="56" t="s">
-        <v>88</v>
-      </c>
+      <c r="B38" s="163"/>
       <c r="C38" s="49"/>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
@@ -6857,9 +6642,7 @@
       <c r="A39" s="52">
         <v>8</v>
       </c>
-      <c r="B39" s="56" t="s">
-        <v>97</v>
-      </c>
+      <c r="B39" s="163"/>
       <c r="C39" s="49"/>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
@@ -6917,9 +6700,7 @@
       <c r="A40" s="52">
         <v>9</v>
       </c>
-      <c r="B40" s="56" t="s">
-        <v>89</v>
-      </c>
+      <c r="B40" s="163"/>
       <c r="C40" s="49"/>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
@@ -6977,9 +6758,7 @@
       <c r="A41" s="52">
         <v>10</v>
       </c>
-      <c r="B41" s="56" t="s">
-        <v>90</v>
-      </c>
+      <c r="B41" s="163"/>
       <c r="C41" s="49"/>
       <c r="D41" s="6"/>
       <c r="E41" s="6"/>
@@ -7037,9 +6816,7 @@
       <c r="A42" s="52">
         <v>11</v>
       </c>
-      <c r="B42" s="56" t="s">
-        <v>91</v>
-      </c>
+      <c r="B42" s="163"/>
       <c r="C42" s="49"/>
       <c r="D42" s="6"/>
       <c r="E42" s="6"/>
@@ -7097,9 +6874,7 @@
       <c r="A43" s="52">
         <v>12</v>
       </c>
-      <c r="B43" s="56" t="s">
-        <v>92</v>
-      </c>
+      <c r="B43" s="163"/>
       <c r="C43" s="49"/>
       <c r="D43" s="6"/>
       <c r="E43" s="6"/>
@@ -7157,9 +6932,7 @@
       <c r="A44" s="52">
         <v>13</v>
       </c>
-      <c r="B44" s="74" t="s">
-        <v>81</v>
-      </c>
+      <c r="B44" s="163"/>
       <c r="C44" s="49"/>
       <c r="D44" s="6"/>
       <c r="E44" s="6"/>
@@ -7217,9 +6990,7 @@
       <c r="A45" s="52">
         <v>14</v>
       </c>
-      <c r="B45" s="56" t="s">
-        <v>93</v>
-      </c>
+      <c r="B45" s="163"/>
       <c r="C45" s="49"/>
       <c r="D45" s="6"/>
       <c r="E45" s="6"/>
@@ -7277,9 +7048,7 @@
       <c r="A46" s="52">
         <v>15</v>
       </c>
-      <c r="B46" s="56" t="s">
-        <v>98</v>
-      </c>
+      <c r="B46" s="163"/>
       <c r="C46" s="49"/>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
@@ -7337,9 +7106,7 @@
       <c r="A47" s="52">
         <v>16</v>
       </c>
-      <c r="B47" s="56" t="s">
-        <v>94</v>
-      </c>
+      <c r="B47" s="163"/>
       <c r="C47" s="49"/>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
@@ -7397,9 +7164,7 @@
       <c r="A48" s="52">
         <v>17</v>
       </c>
-      <c r="B48" s="56" t="s">
-        <v>95</v>
-      </c>
+      <c r="B48" s="163"/>
       <c r="C48" s="49"/>
       <c r="D48" s="6"/>
       <c r="E48" s="6"/>
@@ -7457,9 +7222,7 @@
       <c r="A49" s="52">
         <v>18</v>
       </c>
-      <c r="B49" s="74" t="s">
-        <v>82</v>
-      </c>
+      <c r="B49" s="163"/>
       <c r="C49" s="49"/>
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
@@ -7548,10 +7311,10 @@
   <sheetData>
     <row r="2" spans="1:3" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="B2" s="17" t="s">
         <v>121</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>122</v>
       </c>
       <c r="C2" s="17"/>
     </row>
@@ -7560,7 +7323,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C3" s="17">
         <v>1</v>
@@ -7571,7 +7334,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C4" s="17"/>
     </row>
@@ -7580,7 +7343,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C5" s="17"/>
     </row>
@@ -7589,7 +7352,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C6" s="17"/>
     </row>
@@ -7598,7 +7361,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C7" s="17"/>
     </row>
@@ -7607,7 +7370,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C8" s="17"/>
     </row>
@@ -7616,7 +7379,7 @@
         <v>11</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C9" s="17"/>
     </row>
@@ -7625,7 +7388,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C10" s="17"/>
     </row>
@@ -7634,7 +7397,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C11" s="17"/>
     </row>
@@ -7643,7 +7406,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C12" s="17"/>
     </row>
@@ -7652,7 +7415,7 @@
         <v>5</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C13" s="17"/>
     </row>
@@ -7661,7 +7424,7 @@
         <v>1</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C14" s="17"/>
     </row>
@@ -7670,7 +7433,7 @@
         <v>2</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C15" s="17"/>
     </row>
@@ -7679,7 +7442,7 @@
         <v>2</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C16" s="17"/>
     </row>
@@ -7688,7 +7451,7 @@
         <v>2</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C17" s="17"/>
     </row>
@@ -7697,7 +7460,7 @@
         <v>2</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C18" s="17"/>
     </row>
@@ -7706,7 +7469,7 @@
         <v>2</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C19" s="17"/>
     </row>
@@ -7715,7 +7478,7 @@
         <v>1</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C20" s="17"/>
     </row>
@@ -7724,7 +7487,7 @@
         <v>1</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C21" s="17"/>
     </row>
@@ -7733,7 +7496,7 @@
         <v>1</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C22" s="17"/>
     </row>
@@ -7744,14 +7507,14 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="17"/>
-      <c r="B24" s="163" t="s">
-        <v>120</v>
+      <c r="B24" s="162" t="s">
+        <v>119</v>
       </c>
       <c r="C24" s="17"/>
     </row>
     <row r="25" spans="1:3" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="17"/>
-      <c r="B25" s="163"/>
+      <c r="B25" s="162"/>
       <c r="C25" s="17"/>
     </row>
   </sheetData>
@@ -7778,278 +7541,278 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:53" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="79" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="80"/>
-      <c r="L1" s="80"/>
-      <c r="M1" s="80"/>
-      <c r="N1" s="80"/>
-      <c r="O1" s="80"/>
-      <c r="P1" s="80"/>
-      <c r="Q1" s="80"/>
-      <c r="R1" s="80"/>
-      <c r="S1" s="80"/>
-      <c r="T1" s="80"/>
-      <c r="U1" s="80"/>
-      <c r="V1" s="80"/>
-      <c r="W1" s="80"/>
-      <c r="X1" s="80"/>
-      <c r="Y1" s="80"/>
-      <c r="Z1" s="80"/>
-      <c r="AA1" s="80"/>
-      <c r="AB1" s="80"/>
-      <c r="AC1" s="80"/>
-      <c r="AD1" s="80"/>
-      <c r="AE1" s="80"/>
-      <c r="AF1" s="80"/>
-      <c r="AG1" s="80"/>
-      <c r="AH1" s="80"/>
-      <c r="AI1" s="80"/>
-      <c r="AJ1" s="80"/>
-      <c r="AK1" s="80"/>
-      <c r="AL1" s="80"/>
-      <c r="AM1" s="80"/>
-      <c r="AN1" s="80"/>
-      <c r="AO1" s="80"/>
-      <c r="AP1" s="80"/>
-      <c r="AQ1" s="80"/>
-      <c r="AR1" s="80"/>
-      <c r="AS1" s="80"/>
-      <c r="AT1" s="80"/>
-      <c r="AU1" s="80"/>
-      <c r="AV1" s="80"/>
-      <c r="AW1" s="80"/>
-      <c r="AX1" s="80"/>
-      <c r="AY1" s="80"/>
-      <c r="AZ1" s="80"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+      <c r="M1" s="79"/>
+      <c r="N1" s="79"/>
+      <c r="O1" s="79"/>
+      <c r="P1" s="79"/>
+      <c r="Q1" s="79"/>
+      <c r="R1" s="79"/>
+      <c r="S1" s="79"/>
+      <c r="T1" s="79"/>
+      <c r="U1" s="79"/>
+      <c r="V1" s="79"/>
+      <c r="W1" s="79"/>
+      <c r="X1" s="79"/>
+      <c r="Y1" s="79"/>
+      <c r="Z1" s="79"/>
+      <c r="AA1" s="79"/>
+      <c r="AB1" s="79"/>
+      <c r="AC1" s="79"/>
+      <c r="AD1" s="79"/>
+      <c r="AE1" s="79"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="79"/>
+      <c r="AH1" s="79"/>
+      <c r="AI1" s="79"/>
+      <c r="AJ1" s="79"/>
+      <c r="AK1" s="79"/>
+      <c r="AL1" s="79"/>
+      <c r="AM1" s="79"/>
+      <c r="AN1" s="79"/>
+      <c r="AO1" s="79"/>
+      <c r="AP1" s="79"/>
+      <c r="AQ1" s="79"/>
+      <c r="AR1" s="79"/>
+      <c r="AS1" s="79"/>
+      <c r="AT1" s="79"/>
+      <c r="AU1" s="79"/>
+      <c r="AV1" s="79"/>
+      <c r="AW1" s="79"/>
+      <c r="AX1" s="79"/>
+      <c r="AY1" s="79"/>
+      <c r="AZ1" s="79"/>
     </row>
     <row r="2" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A2" s="80"/>
-      <c r="B2" s="80"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="80"/>
-      <c r="K2" s="80"/>
-      <c r="L2" s="80"/>
-      <c r="M2" s="80"/>
-      <c r="N2" s="80"/>
-      <c r="O2" s="80"/>
-      <c r="P2" s="80"/>
-      <c r="Q2" s="80"/>
-      <c r="R2" s="80"/>
-      <c r="S2" s="80"/>
-      <c r="T2" s="80"/>
-      <c r="U2" s="80"/>
-      <c r="V2" s="80"/>
-      <c r="W2" s="80"/>
-      <c r="X2" s="80"/>
-      <c r="Y2" s="80"/>
-      <c r="Z2" s="80"/>
-      <c r="AA2" s="80"/>
-      <c r="AB2" s="80"/>
-      <c r="AC2" s="80"/>
-      <c r="AD2" s="80"/>
-      <c r="AE2" s="80"/>
-      <c r="AF2" s="80"/>
-      <c r="AG2" s="80"/>
-      <c r="AH2" s="80"/>
-      <c r="AI2" s="80"/>
-      <c r="AJ2" s="80"/>
-      <c r="AK2" s="80"/>
-      <c r="AL2" s="80"/>
-      <c r="AM2" s="80"/>
-      <c r="AN2" s="80"/>
-      <c r="AO2" s="80"/>
-      <c r="AP2" s="80"/>
-      <c r="AQ2" s="80"/>
-      <c r="AR2" s="80"/>
-      <c r="AS2" s="80"/>
-      <c r="AT2" s="80"/>
-      <c r="AU2" s="80"/>
-      <c r="AV2" s="80"/>
-      <c r="AW2" s="80"/>
-      <c r="AX2" s="80"/>
-      <c r="AY2" s="80"/>
-      <c r="AZ2" s="80"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
+      <c r="L2" s="79"/>
+      <c r="M2" s="79"/>
+      <c r="N2" s="79"/>
+      <c r="O2" s="79"/>
+      <c r="P2" s="79"/>
+      <c r="Q2" s="79"/>
+      <c r="R2" s="79"/>
+      <c r="S2" s="79"/>
+      <c r="T2" s="79"/>
+      <c r="U2" s="79"/>
+      <c r="V2" s="79"/>
+      <c r="W2" s="79"/>
+      <c r="X2" s="79"/>
+      <c r="Y2" s="79"/>
+      <c r="Z2" s="79"/>
+      <c r="AA2" s="79"/>
+      <c r="AB2" s="79"/>
+      <c r="AC2" s="79"/>
+      <c r="AD2" s="79"/>
+      <c r="AE2" s="79"/>
+      <c r="AF2" s="79"/>
+      <c r="AG2" s="79"/>
+      <c r="AH2" s="79"/>
+      <c r="AI2" s="79"/>
+      <c r="AJ2" s="79"/>
+      <c r="AK2" s="79"/>
+      <c r="AL2" s="79"/>
+      <c r="AM2" s="79"/>
+      <c r="AN2" s="79"/>
+      <c r="AO2" s="79"/>
+      <c r="AP2" s="79"/>
+      <c r="AQ2" s="79"/>
+      <c r="AR2" s="79"/>
+      <c r="AS2" s="79"/>
+      <c r="AT2" s="79"/>
+      <c r="AU2" s="79"/>
+      <c r="AV2" s="79"/>
+      <c r="AW2" s="79"/>
+      <c r="AX2" s="79"/>
+      <c r="AY2" s="79"/>
+      <c r="AZ2" s="79"/>
     </row>
     <row r="3" spans="1:53" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="80"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="80"/>
-      <c r="K3" s="80"/>
-      <c r="L3" s="80"/>
-      <c r="M3" s="80"/>
-      <c r="N3" s="80"/>
-      <c r="O3" s="80"/>
-      <c r="P3" s="80"/>
-      <c r="Q3" s="80"/>
-      <c r="R3" s="80"/>
-      <c r="S3" s="80"/>
-      <c r="T3" s="80"/>
-      <c r="U3" s="80"/>
-      <c r="V3" s="80"/>
-      <c r="W3" s="80"/>
-      <c r="X3" s="80"/>
-      <c r="Y3" s="80"/>
-      <c r="Z3" s="80"/>
-      <c r="AA3" s="80"/>
-      <c r="AB3" s="80"/>
-      <c r="AC3" s="80"/>
-      <c r="AD3" s="80"/>
-      <c r="AE3" s="80"/>
-      <c r="AF3" s="80"/>
-      <c r="AG3" s="80"/>
-      <c r="AH3" s="80"/>
-      <c r="AI3" s="80"/>
-      <c r="AJ3" s="80"/>
-      <c r="AK3" s="80"/>
-      <c r="AL3" s="80"/>
-      <c r="AM3" s="80"/>
-      <c r="AN3" s="80"/>
-      <c r="AO3" s="80"/>
-      <c r="AP3" s="80"/>
-      <c r="AQ3" s="80"/>
-      <c r="AR3" s="80"/>
-      <c r="AS3" s="80"/>
-      <c r="AT3" s="80"/>
-      <c r="AU3" s="80"/>
-      <c r="AV3" s="80"/>
-      <c r="AW3" s="80"/>
-      <c r="AX3" s="80"/>
-      <c r="AY3" s="80"/>
-      <c r="AZ3" s="80"/>
+      <c r="A3" s="79"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
+      <c r="I3" s="79"/>
+      <c r="J3" s="79"/>
+      <c r="K3" s="79"/>
+      <c r="L3" s="79"/>
+      <c r="M3" s="79"/>
+      <c r="N3" s="79"/>
+      <c r="O3" s="79"/>
+      <c r="P3" s="79"/>
+      <c r="Q3" s="79"/>
+      <c r="R3" s="79"/>
+      <c r="S3" s="79"/>
+      <c r="T3" s="79"/>
+      <c r="U3" s="79"/>
+      <c r="V3" s="79"/>
+      <c r="W3" s="79"/>
+      <c r="X3" s="79"/>
+      <c r="Y3" s="79"/>
+      <c r="Z3" s="79"/>
+      <c r="AA3" s="79"/>
+      <c r="AB3" s="79"/>
+      <c r="AC3" s="79"/>
+      <c r="AD3" s="79"/>
+      <c r="AE3" s="79"/>
+      <c r="AF3" s="79"/>
+      <c r="AG3" s="79"/>
+      <c r="AH3" s="79"/>
+      <c r="AI3" s="79"/>
+      <c r="AJ3" s="79"/>
+      <c r="AK3" s="79"/>
+      <c r="AL3" s="79"/>
+      <c r="AM3" s="79"/>
+      <c r="AN3" s="79"/>
+      <c r="AO3" s="79"/>
+      <c r="AP3" s="79"/>
+      <c r="AQ3" s="79"/>
+      <c r="AR3" s="79"/>
+      <c r="AS3" s="79"/>
+      <c r="AT3" s="79"/>
+      <c r="AU3" s="79"/>
+      <c r="AV3" s="79"/>
+      <c r="AW3" s="79"/>
+      <c r="AX3" s="79"/>
+      <c r="AY3" s="79"/>
+      <c r="AZ3" s="79"/>
     </row>
     <row r="4" spans="1:53" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="80"/>
-      <c r="B4" s="80"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="80"/>
-      <c r="I4" s="80"/>
-      <c r="J4" s="80"/>
-      <c r="K4" s="80"/>
-      <c r="L4" s="80"/>
-      <c r="M4" s="80"/>
-      <c r="N4" s="80"/>
-      <c r="O4" s="80"/>
-      <c r="P4" s="80"/>
-      <c r="Q4" s="80"/>
-      <c r="R4" s="80"/>
-      <c r="S4" s="80"/>
-      <c r="T4" s="80"/>
-      <c r="U4" s="80"/>
-      <c r="V4" s="80"/>
-      <c r="W4" s="80"/>
-      <c r="X4" s="80"/>
-      <c r="Y4" s="80"/>
-      <c r="Z4" s="80"/>
-      <c r="AA4" s="80"/>
-      <c r="AB4" s="80"/>
-      <c r="AC4" s="80"/>
-      <c r="AD4" s="80"/>
-      <c r="AE4" s="80"/>
-      <c r="AF4" s="80"/>
-      <c r="AG4" s="80"/>
-      <c r="AH4" s="80"/>
-      <c r="AI4" s="80"/>
-      <c r="AJ4" s="80"/>
-      <c r="AK4" s="80"/>
-      <c r="AL4" s="80"/>
-      <c r="AM4" s="80"/>
-      <c r="AN4" s="80"/>
-      <c r="AO4" s="80"/>
-      <c r="AP4" s="80"/>
-      <c r="AQ4" s="80"/>
-      <c r="AR4" s="80"/>
-      <c r="AS4" s="80"/>
-      <c r="AT4" s="80"/>
-      <c r="AU4" s="80"/>
-      <c r="AV4" s="80"/>
-      <c r="AW4" s="80"/>
-      <c r="AX4" s="80"/>
-      <c r="AY4" s="80"/>
-      <c r="AZ4" s="80"/>
+      <c r="A4" s="79"/>
+      <c r="B4" s="79"/>
+      <c r="C4" s="79"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="79"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="79"/>
+      <c r="H4" s="79"/>
+      <c r="I4" s="79"/>
+      <c r="J4" s="79"/>
+      <c r="K4" s="79"/>
+      <c r="L4" s="79"/>
+      <c r="M4" s="79"/>
+      <c r="N4" s="79"/>
+      <c r="O4" s="79"/>
+      <c r="P4" s="79"/>
+      <c r="Q4" s="79"/>
+      <c r="R4" s="79"/>
+      <c r="S4" s="79"/>
+      <c r="T4" s="79"/>
+      <c r="U4" s="79"/>
+      <c r="V4" s="79"/>
+      <c r="W4" s="79"/>
+      <c r="X4" s="79"/>
+      <c r="Y4" s="79"/>
+      <c r="Z4" s="79"/>
+      <c r="AA4" s="79"/>
+      <c r="AB4" s="79"/>
+      <c r="AC4" s="79"/>
+      <c r="AD4" s="79"/>
+      <c r="AE4" s="79"/>
+      <c r="AF4" s="79"/>
+      <c r="AG4" s="79"/>
+      <c r="AH4" s="79"/>
+      <c r="AI4" s="79"/>
+      <c r="AJ4" s="79"/>
+      <c r="AK4" s="79"/>
+      <c r="AL4" s="79"/>
+      <c r="AM4" s="79"/>
+      <c r="AN4" s="79"/>
+      <c r="AO4" s="79"/>
+      <c r="AP4" s="79"/>
+      <c r="AQ4" s="79"/>
+      <c r="AR4" s="79"/>
+      <c r="AS4" s="79"/>
+      <c r="AT4" s="79"/>
+      <c r="AU4" s="79"/>
+      <c r="AV4" s="79"/>
+      <c r="AW4" s="79"/>
+      <c r="AX4" s="79"/>
+      <c r="AY4" s="79"/>
+      <c r="AZ4" s="79"/>
     </row>
     <row r="5" spans="1:53" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="84" t="s">
-        <v>67</v>
-      </c>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
-      <c r="K5" s="84"/>
-      <c r="L5" s="84"/>
-      <c r="M5" s="84"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="84"/>
-      <c r="U5" s="84"/>
-      <c r="V5" s="84"/>
-      <c r="W5" s="84"/>
-      <c r="X5" s="84"/>
-      <c r="Y5" s="84"/>
-      <c r="Z5" s="84"/>
-      <c r="AA5" s="84"/>
-      <c r="AB5" s="84"/>
-      <c r="AC5" s="84"/>
-      <c r="AD5" s="84"/>
-      <c r="AE5" s="84"/>
-      <c r="AF5" s="84"/>
-      <c r="AG5" s="84"/>
-      <c r="AH5" s="84"/>
-      <c r="AI5" s="84"/>
-      <c r="AJ5" s="84"/>
-      <c r="AK5" s="84"/>
-      <c r="AL5" s="84"/>
-      <c r="AM5" s="84"/>
-      <c r="AN5" s="84"/>
-      <c r="AO5" s="84"/>
-      <c r="AP5" s="84"/>
-      <c r="AQ5" s="84"/>
-      <c r="AR5" s="84"/>
-      <c r="AS5" s="84"/>
-      <c r="AT5" s="84"/>
-      <c r="AU5" s="84"/>
-      <c r="AV5" s="84"/>
-      <c r="AW5" s="84"/>
-      <c r="AX5" s="84"/>
-      <c r="AY5" s="84"/>
-      <c r="AZ5" s="84"/>
+      <c r="A5" s="83" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5" s="83"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="83"/>
+      <c r="E5" s="83"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="83"/>
+      <c r="H5" s="83"/>
+      <c r="I5" s="83"/>
+      <c r="J5" s="83"/>
+      <c r="K5" s="83"/>
+      <c r="L5" s="83"/>
+      <c r="M5" s="83"/>
+      <c r="N5" s="83"/>
+      <c r="O5" s="83"/>
+      <c r="P5" s="83"/>
+      <c r="Q5" s="83"/>
+      <c r="R5" s="83"/>
+      <c r="S5" s="83"/>
+      <c r="T5" s="83"/>
+      <c r="U5" s="83"/>
+      <c r="V5" s="83"/>
+      <c r="W5" s="83"/>
+      <c r="X5" s="83"/>
+      <c r="Y5" s="83"/>
+      <c r="Z5" s="83"/>
+      <c r="AA5" s="83"/>
+      <c r="AB5" s="83"/>
+      <c r="AC5" s="83"/>
+      <c r="AD5" s="83"/>
+      <c r="AE5" s="83"/>
+      <c r="AF5" s="83"/>
+      <c r="AG5" s="83"/>
+      <c r="AH5" s="83"/>
+      <c r="AI5" s="83"/>
+      <c r="AJ5" s="83"/>
+      <c r="AK5" s="83"/>
+      <c r="AL5" s="83"/>
+      <c r="AM5" s="83"/>
+      <c r="AN5" s="83"/>
+      <c r="AO5" s="83"/>
+      <c r="AP5" s="83"/>
+      <c r="AQ5" s="83"/>
+      <c r="AR5" s="83"/>
+      <c r="AS5" s="83"/>
+      <c r="AT5" s="83"/>
+      <c r="AU5" s="83"/>
+      <c r="AV5" s="83"/>
+      <c r="AW5" s="83"/>
+      <c r="AX5" s="83"/>
+      <c r="AY5" s="83"/>
+      <c r="AZ5" s="83"/>
     </row>
     <row r="6" spans="1:53" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
@@ -8057,19 +7820,19 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="4"/>
-      <c r="D6" s="82"/>
-      <c r="E6" s="82"/>
-      <c r="F6" s="82"/>
-      <c r="G6" s="82"/>
-      <c r="H6" s="82"/>
-      <c r="I6" s="82"/>
-      <c r="J6" s="82"/>
-      <c r="K6" s="82"/>
-      <c r="L6" s="82"/>
-      <c r="M6" s="82"/>
-      <c r="N6" s="82"/>
-      <c r="O6" s="82"/>
-      <c r="P6" s="82"/>
+      <c r="D6" s="81"/>
+      <c r="E6" s="81"/>
+      <c r="F6" s="81"/>
+      <c r="G6" s="81"/>
+      <c r="H6" s="81"/>
+      <c r="I6" s="81"/>
+      <c r="J6" s="81"/>
+      <c r="K6" s="81"/>
+      <c r="L6" s="81"/>
+      <c r="M6" s="81"/>
+      <c r="N6" s="81"/>
+      <c r="O6" s="81"/>
+      <c r="P6" s="81"/>
       <c r="Q6" s="5" t="s">
         <v>63</v>
       </c>
@@ -8105,20 +7868,20 @@
       <c r="AU6" s="4"/>
       <c r="AV6" s="4"/>
     </row>
-    <row r="7" spans="1:53" s="85" customFormat="1" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="1:53" s="84" customFormat="1" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="1:53" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="50"/>
       <c r="B8" s="51" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D8" s="59" t="s">
+        <v>78</v>
+      </c>
+      <c r="E8" s="59" t="s">
         <v>79</v>
-      </c>
-      <c r="E8" s="59" t="s">
-        <v>80</v>
       </c>
       <c r="F8" s="59"/>
       <c r="G8" s="59"/>
@@ -8341,10 +8104,10 @@
         <v>46</v>
       </c>
       <c r="D10" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E10" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F10" s="67"/>
       <c r="G10" s="67"/>
@@ -8406,10 +8169,10 @@
         <v>50</v>
       </c>
       <c r="D11" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E11" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F11" s="67"/>
       <c r="G11" s="67"/>
@@ -8471,10 +8234,10 @@
         <v>40</v>
       </c>
       <c r="D12" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E12" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F12" s="67"/>
       <c r="G12" s="67"/>
@@ -8536,10 +8299,10 @@
         <v>49</v>
       </c>
       <c r="D13" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E13" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F13" s="67"/>
       <c r="G13" s="67"/>
@@ -8601,10 +8364,10 @@
         <v>39</v>
       </c>
       <c r="D14" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E14" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F14" s="67"/>
       <c r="G14" s="67"/>
@@ -8665,7 +8428,7 @@
       <c r="C15" s="66"/>
       <c r="D15" s="67"/>
       <c r="E15" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F15" s="67"/>
       <c r="G15" s="67"/>
@@ -8727,10 +8490,10 @@
         <v>48</v>
       </c>
       <c r="D16" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E16" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F16" s="67"/>
       <c r="G16" s="67"/>
@@ -8852,7 +8615,7 @@
       <c r="C18" s="66"/>
       <c r="D18" s="72"/>
       <c r="E18" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F18" s="67"/>
       <c r="G18" s="67"/>
@@ -8914,10 +8677,10 @@
         <v>50</v>
       </c>
       <c r="D19" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E19" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F19" s="67"/>
       <c r="G19" s="67"/>
@@ -9038,10 +8801,10 @@
         <v>46</v>
       </c>
       <c r="D21" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E21" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F21" s="67"/>
       <c r="G21" s="67"/>
@@ -9103,10 +8866,10 @@
         <v>50</v>
       </c>
       <c r="D22" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E22" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F22" s="67"/>
       <c r="G22" s="67"/>
@@ -9168,10 +8931,10 @@
         <v>50</v>
       </c>
       <c r="D23" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E23" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F23" s="67"/>
       <c r="G23" s="67"/>
@@ -9234,7 +8997,7 @@
       </c>
       <c r="D24" s="72"/>
       <c r="E24" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F24" s="67"/>
       <c r="G24" s="67"/>
@@ -9357,7 +9120,7 @@
         <v>49</v>
       </c>
       <c r="D26" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E26" s="72"/>
       <c r="F26" s="67"/>
@@ -9419,7 +9182,7 @@
       <c r="C27" s="66"/>
       <c r="D27" s="72"/>
       <c r="E27" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F27" s="67"/>
       <c r="G27" s="67"/>
@@ -9479,7 +9242,7 @@
       </c>
       <c r="C28" s="66"/>
       <c r="D28" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E28" s="67"/>
       <c r="F28" s="67"/>
@@ -9542,10 +9305,10 @@
         <v>20</v>
       </c>
       <c r="D29" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E29" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F29" s="67"/>
       <c r="G29" s="67"/>
@@ -9608,7 +9371,7 @@
       </c>
       <c r="D30" s="72"/>
       <c r="E30" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F30" s="67"/>
       <c r="G30" s="67"/>
@@ -9670,10 +9433,10 @@
         <v>40</v>
       </c>
       <c r="D31" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E31" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F31" s="67"/>
       <c r="G31" s="67"/>
@@ -9733,10 +9496,10 @@
       </c>
       <c r="C32" s="66"/>
       <c r="D32" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E32" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F32" s="67"/>
       <c r="G32" s="67"/>
@@ -9799,7 +9562,7 @@
       </c>
       <c r="D33" s="72"/>
       <c r="E33" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F33" s="67"/>
       <c r="G33" s="67"/>
@@ -9861,10 +9624,10 @@
         <v>49</v>
       </c>
       <c r="D34" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E34" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F34" s="67"/>
       <c r="G34" s="67"/>
@@ -9924,10 +9687,10 @@
       </c>
       <c r="C35" s="66"/>
       <c r="D35" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E35" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F35" s="67"/>
       <c r="G35" s="67"/>
@@ -9989,10 +9752,10 @@
         <v>24</v>
       </c>
       <c r="D36" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E36" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F36" s="67"/>
       <c r="G36" s="67"/>
@@ -10052,10 +9815,10 @@
       </c>
       <c r="C37" s="66"/>
       <c r="D37" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E37" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F37" s="67"/>
       <c r="G37" s="67"/>
@@ -10178,10 +9941,10 @@
         <v>42</v>
       </c>
       <c r="D39" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E39" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F39" s="67"/>
       <c r="G39" s="67"/>
@@ -10693,15 +10456,15 @@
     </row>
     <row r="4" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12"/>
-      <c r="B4" s="95" t="s">
+      <c r="B4" s="94" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="95"/>
-      <c r="D4" s="95"/>
-      <c r="E4" s="95"/>
-      <c r="F4" s="95"/>
-      <c r="G4" s="95"/>
-      <c r="H4" s="95"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="94"/>
+      <c r="G4" s="94"/>
+      <c r="H4" s="94"/>
       <c r="J4" s="13"/>
     </row>
     <row r="5" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10721,59 +10484,59 @@
     </row>
     <row r="7" spans="1:10" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12"/>
-      <c r="B7" s="95" t="s">
+      <c r="B7" s="94" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="95"/>
-      <c r="D7" s="95"/>
-      <c r="E7" s="95"/>
-      <c r="F7" s="95"/>
-      <c r="G7" s="95"/>
-      <c r="H7" s="95"/>
+      <c r="C7" s="94"/>
+      <c r="D7" s="94"/>
+      <c r="E7" s="94"/>
+      <c r="F7" s="94"/>
+      <c r="G7" s="94"/>
+      <c r="H7" s="94"/>
       <c r="J7" s="13"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="12"/>
-      <c r="B8" s="86"/>
-      <c r="C8" s="87"/>
-      <c r="D8" s="87"/>
-      <c r="E8" s="87"/>
-      <c r="F8" s="87"/>
-      <c r="G8" s="87"/>
-      <c r="H8" s="88"/>
+      <c r="B8" s="85"/>
+      <c r="C8" s="86"/>
+      <c r="D8" s="86"/>
+      <c r="E8" s="86"/>
+      <c r="F8" s="86"/>
+      <c r="G8" s="86"/>
+      <c r="H8" s="87"/>
       <c r="J8" s="13"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="12"/>
-      <c r="B9" s="89"/>
-      <c r="C9" s="90"/>
-      <c r="D9" s="90"/>
-      <c r="E9" s="90"/>
-      <c r="F9" s="90"/>
-      <c r="G9" s="90"/>
-      <c r="H9" s="91"/>
+      <c r="B9" s="88"/>
+      <c r="C9" s="89"/>
+      <c r="D9" s="89"/>
+      <c r="E9" s="89"/>
+      <c r="F9" s="89"/>
+      <c r="G9" s="89"/>
+      <c r="H9" s="90"/>
       <c r="J9" s="13"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="12"/>
-      <c r="B10" s="89"/>
-      <c r="C10" s="90"/>
-      <c r="D10" s="90"/>
-      <c r="E10" s="90"/>
-      <c r="F10" s="90"/>
-      <c r="G10" s="90"/>
-      <c r="H10" s="91"/>
+      <c r="B10" s="88"/>
+      <c r="C10" s="89"/>
+      <c r="D10" s="89"/>
+      <c r="E10" s="89"/>
+      <c r="F10" s="89"/>
+      <c r="G10" s="89"/>
+      <c r="H10" s="90"/>
       <c r="J10" s="13"/>
     </row>
     <row r="11" spans="1:10" ht="72" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="12"/>
-      <c r="B11" s="92"/>
-      <c r="C11" s="93"/>
-      <c r="D11" s="93"/>
-      <c r="E11" s="93"/>
-      <c r="F11" s="93"/>
-      <c r="G11" s="93"/>
-      <c r="H11" s="94"/>
+      <c r="B11" s="91"/>
+      <c r="C11" s="92"/>
+      <c r="D11" s="92"/>
+      <c r="E11" s="92"/>
+      <c r="F11" s="92"/>
+      <c r="G11" s="92"/>
+      <c r="H11" s="93"/>
       <c r="J11" s="13"/>
     </row>
     <row r="12" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -11193,135 +10956,135 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="107" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="108"/>
+      <c r="G1" s="108"/>
       <c r="H1" s="27"/>
       <c r="I1" s="34"/>
-      <c r="J1" s="98" t="s">
+      <c r="J1" s="107" t="s">
         <v>47</v>
       </c>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="100"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="109"/>
     </row>
     <row r="2" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="101" t="s">
+      <c r="A2" s="110" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="102"/>
-      <c r="C2" s="102"/>
-      <c r="D2" s="102"/>
-      <c r="E2" s="102"/>
-      <c r="F2" s="96" t="s">
+      <c r="B2" s="111"/>
+      <c r="C2" s="111"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="111"/>
+      <c r="F2" s="112" t="s">
         <v>55</v>
       </c>
-      <c r="G2" s="97"/>
+      <c r="G2" s="113"/>
       <c r="H2" s="29"/>
-      <c r="J2" s="101" t="s">
+      <c r="J2" s="110" t="s">
         <v>48</v>
       </c>
-      <c r="K2" s="102"/>
-      <c r="L2" s="102"/>
-      <c r="M2" s="102"/>
-      <c r="N2" s="102"/>
-      <c r="O2" s="103" t="s">
+      <c r="K2" s="111"/>
+      <c r="L2" s="111"/>
+      <c r="M2" s="111"/>
+      <c r="N2" s="111"/>
+      <c r="O2" s="114" t="s">
         <v>55</v>
       </c>
-      <c r="P2" s="104"/>
+      <c r="P2" s="115"/>
     </row>
     <row r="3" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="105" t="s">
+      <c r="A3" s="95" t="s">
         <v>54</v>
       </c>
-      <c r="B3" s="106"/>
-      <c r="C3" s="106"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="106"/>
+      <c r="B3" s="96"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="96"/>
+      <c r="G3" s="96"/>
       <c r="H3" s="29"/>
-      <c r="J3" s="105" t="s">
+      <c r="J3" s="95" t="s">
         <v>54</v>
       </c>
-      <c r="K3" s="106"/>
-      <c r="L3" s="106"/>
-      <c r="M3" s="106"/>
-      <c r="N3" s="106"/>
-      <c r="O3" s="106"/>
-      <c r="P3" s="107"/>
+      <c r="K3" s="96"/>
+      <c r="L3" s="96"/>
+      <c r="M3" s="96"/>
+      <c r="N3" s="96"/>
+      <c r="O3" s="96"/>
+      <c r="P3" s="97"/>
     </row>
     <row r="4" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="105" t="s">
+      <c r="A4" s="95" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="106"/>
-      <c r="C4" s="106"/>
-      <c r="D4" s="106"/>
-      <c r="E4" s="106"/>
-      <c r="F4" s="106"/>
-      <c r="G4" s="106"/>
+      <c r="B4" s="96"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="96"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="96"/>
+      <c r="G4" s="96"/>
       <c r="H4" s="29"/>
-      <c r="J4" s="105" t="s">
+      <c r="J4" s="95" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="106"/>
-      <c r="L4" s="106"/>
-      <c r="M4" s="106"/>
-      <c r="N4" s="106"/>
-      <c r="O4" s="106"/>
-      <c r="P4" s="107"/>
+      <c r="K4" s="96"/>
+      <c r="L4" s="96"/>
+      <c r="M4" s="96"/>
+      <c r="N4" s="96"/>
+      <c r="O4" s="96"/>
+      <c r="P4" s="97"/>
     </row>
     <row r="5" spans="1:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="108" t="s">
+      <c r="A5" s="104" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="109"/>
-      <c r="C5" s="109"/>
-      <c r="D5" s="109"/>
-      <c r="E5" s="109"/>
-      <c r="F5" s="109"/>
-      <c r="G5" s="109"/>
+      <c r="B5" s="105"/>
+      <c r="C5" s="105"/>
+      <c r="D5" s="105"/>
+      <c r="E5" s="105"/>
+      <c r="F5" s="105"/>
+      <c r="G5" s="105"/>
       <c r="H5" s="29"/>
-      <c r="J5" s="108" t="s">
+      <c r="J5" s="104" t="s">
         <v>53</v>
       </c>
-      <c r="K5" s="109"/>
-      <c r="L5" s="109"/>
-      <c r="M5" s="109"/>
-      <c r="N5" s="109"/>
-      <c r="O5" s="109"/>
-      <c r="P5" s="110"/>
+      <c r="K5" s="105"/>
+      <c r="L5" s="105"/>
+      <c r="M5" s="105"/>
+      <c r="N5" s="105"/>
+      <c r="O5" s="105"/>
+      <c r="P5" s="106"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="105" t="s">
+      <c r="A6" s="95" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="106"/>
-      <c r="C6" s="106"/>
-      <c r="D6" s="106"/>
-      <c r="E6" s="106"/>
-      <c r="F6" s="106"/>
-      <c r="G6" s="106"/>
+      <c r="B6" s="96"/>
+      <c r="C6" s="96"/>
+      <c r="D6" s="96"/>
+      <c r="E6" s="96"/>
+      <c r="F6" s="96"/>
+      <c r="G6" s="96"/>
       <c r="H6" s="29"/>
-      <c r="J6" s="105" t="s">
+      <c r="J6" s="95" t="s">
         <v>50</v>
       </c>
-      <c r="K6" s="106"/>
-      <c r="L6" s="106"/>
-      <c r="M6" s="106"/>
-      <c r="N6" s="106"/>
-      <c r="O6" s="106"/>
-      <c r="P6" s="107"/>
+      <c r="K6" s="96"/>
+      <c r="L6" s="96"/>
+      <c r="M6" s="96"/>
+      <c r="N6" s="96"/>
+      <c r="O6" s="96"/>
+      <c r="P6" s="97"/>
     </row>
     <row r="7" spans="1:16" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="28"/>
@@ -11330,46 +11093,46 @@
       <c r="P7" s="29"/>
     </row>
     <row r="8" spans="1:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="113" t="s">
+      <c r="A8" s="98" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="114"/>
-      <c r="C8" s="114"/>
-      <c r="D8" s="114"/>
-      <c r="E8" s="114"/>
-      <c r="F8" s="114"/>
-      <c r="G8" s="114"/>
+      <c r="B8" s="99"/>
+      <c r="C8" s="99"/>
+      <c r="D8" s="99"/>
+      <c r="E8" s="99"/>
+      <c r="F8" s="99"/>
+      <c r="G8" s="99"/>
       <c r="H8" s="29"/>
-      <c r="J8" s="113" t="s">
+      <c r="J8" s="98" t="s">
         <v>51</v>
       </c>
-      <c r="K8" s="114"/>
-      <c r="L8" s="114"/>
-      <c r="M8" s="114"/>
-      <c r="N8" s="114"/>
-      <c r="O8" s="114"/>
-      <c r="P8" s="115"/>
+      <c r="K8" s="99"/>
+      <c r="L8" s="99"/>
+      <c r="M8" s="99"/>
+      <c r="N8" s="99"/>
+      <c r="O8" s="99"/>
+      <c r="P8" s="100"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="111" t="s">
+      <c r="A9" s="101" t="s">
         <v>57</v>
       </c>
-      <c r="B9" s="112"/>
-      <c r="C9" s="112"/>
-      <c r="D9" s="112"/>
-      <c r="E9" s="112"/>
-      <c r="F9" s="112"/>
-      <c r="G9" s="112"/>
+      <c r="B9" s="102"/>
+      <c r="C9" s="102"/>
+      <c r="D9" s="102"/>
+      <c r="E9" s="102"/>
+      <c r="F9" s="102"/>
+      <c r="G9" s="102"/>
       <c r="H9" s="29"/>
-      <c r="J9" s="111" t="s">
+      <c r="J9" s="101" t="s">
         <v>57</v>
       </c>
-      <c r="K9" s="112"/>
-      <c r="L9" s="112"/>
-      <c r="M9" s="112"/>
-      <c r="N9" s="112"/>
-      <c r="O9" s="112"/>
-      <c r="P9" s="116"/>
+      <c r="K9" s="102"/>
+      <c r="L9" s="102"/>
+      <c r="M9" s="102"/>
+      <c r="N9" s="102"/>
+      <c r="O9" s="102"/>
+      <c r="P9" s="103"/>
     </row>
     <row r="10" spans="1:16" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="30"/>
@@ -11390,135 +11153,135 @@
       <c r="P10" s="33"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="98" t="s">
+      <c r="A11" s="107" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="99"/>
-      <c r="C11" s="99"/>
-      <c r="D11" s="99"/>
-      <c r="E11" s="99"/>
-      <c r="F11" s="99"/>
-      <c r="G11" s="99"/>
+      <c r="B11" s="108"/>
+      <c r="C11" s="108"/>
+      <c r="D11" s="108"/>
+      <c r="E11" s="108"/>
+      <c r="F11" s="108"/>
+      <c r="G11" s="108"/>
       <c r="H11" s="27"/>
       <c r="I11" s="34"/>
-      <c r="J11" s="98" t="s">
+      <c r="J11" s="107" t="s">
         <v>47</v>
       </c>
-      <c r="K11" s="99"/>
-      <c r="L11" s="99"/>
-      <c r="M11" s="99"/>
-      <c r="N11" s="99"/>
-      <c r="O11" s="99"/>
-      <c r="P11" s="100"/>
+      <c r="K11" s="108"/>
+      <c r="L11" s="108"/>
+      <c r="M11" s="108"/>
+      <c r="N11" s="108"/>
+      <c r="O11" s="108"/>
+      <c r="P11" s="109"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="101" t="s">
+      <c r="A12" s="110" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="102"/>
-      <c r="C12" s="102"/>
-      <c r="D12" s="102"/>
-      <c r="E12" s="102"/>
-      <c r="F12" s="96" t="s">
+      <c r="B12" s="111"/>
+      <c r="C12" s="111"/>
+      <c r="D12" s="111"/>
+      <c r="E12" s="111"/>
+      <c r="F12" s="112" t="s">
         <v>55</v>
       </c>
-      <c r="G12" s="97"/>
+      <c r="G12" s="113"/>
       <c r="H12" s="29"/>
-      <c r="J12" s="101" t="s">
+      <c r="J12" s="110" t="s">
         <v>48</v>
       </c>
-      <c r="K12" s="102"/>
-      <c r="L12" s="102"/>
-      <c r="M12" s="102"/>
-      <c r="N12" s="102"/>
-      <c r="O12" s="103" t="s">
+      <c r="K12" s="111"/>
+      <c r="L12" s="111"/>
+      <c r="M12" s="111"/>
+      <c r="N12" s="111"/>
+      <c r="O12" s="114" t="s">
         <v>55</v>
       </c>
-      <c r="P12" s="104"/>
+      <c r="P12" s="115"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="105" t="s">
+      <c r="A13" s="95" t="s">
         <v>54</v>
       </c>
-      <c r="B13" s="106"/>
-      <c r="C13" s="106"/>
-      <c r="D13" s="106"/>
-      <c r="E13" s="106"/>
-      <c r="F13" s="106"/>
-      <c r="G13" s="106"/>
+      <c r="B13" s="96"/>
+      <c r="C13" s="96"/>
+      <c r="D13" s="96"/>
+      <c r="E13" s="96"/>
+      <c r="F13" s="96"/>
+      <c r="G13" s="96"/>
       <c r="H13" s="29"/>
-      <c r="J13" s="105" t="s">
+      <c r="J13" s="95" t="s">
         <v>54</v>
       </c>
-      <c r="K13" s="106"/>
-      <c r="L13" s="106"/>
-      <c r="M13" s="106"/>
-      <c r="N13" s="106"/>
-      <c r="O13" s="106"/>
-      <c r="P13" s="107"/>
+      <c r="K13" s="96"/>
+      <c r="L13" s="96"/>
+      <c r="M13" s="96"/>
+      <c r="N13" s="96"/>
+      <c r="O13" s="96"/>
+      <c r="P13" s="97"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="105" t="s">
+      <c r="A14" s="95" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="106"/>
-      <c r="C14" s="106"/>
-      <c r="D14" s="106"/>
-      <c r="E14" s="106"/>
-      <c r="F14" s="106"/>
-      <c r="G14" s="106"/>
+      <c r="B14" s="96"/>
+      <c r="C14" s="96"/>
+      <c r="D14" s="96"/>
+      <c r="E14" s="96"/>
+      <c r="F14" s="96"/>
+      <c r="G14" s="96"/>
       <c r="H14" s="29"/>
-      <c r="J14" s="105" t="s">
+      <c r="J14" s="95" t="s">
         <v>49</v>
       </c>
-      <c r="K14" s="106"/>
-      <c r="L14" s="106"/>
-      <c r="M14" s="106"/>
-      <c r="N14" s="106"/>
-      <c r="O14" s="106"/>
-      <c r="P14" s="107"/>
+      <c r="K14" s="96"/>
+      <c r="L14" s="96"/>
+      <c r="M14" s="96"/>
+      <c r="N14" s="96"/>
+      <c r="O14" s="96"/>
+      <c r="P14" s="97"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" s="108" t="s">
+      <c r="A15" s="104" t="s">
         <v>53</v>
       </c>
-      <c r="B15" s="109"/>
-      <c r="C15" s="109"/>
-      <c r="D15" s="109"/>
-      <c r="E15" s="109"/>
-      <c r="F15" s="109"/>
-      <c r="G15" s="109"/>
+      <c r="B15" s="105"/>
+      <c r="C15" s="105"/>
+      <c r="D15" s="105"/>
+      <c r="E15" s="105"/>
+      <c r="F15" s="105"/>
+      <c r="G15" s="105"/>
       <c r="H15" s="29"/>
-      <c r="J15" s="108" t="s">
+      <c r="J15" s="104" t="s">
         <v>53</v>
       </c>
-      <c r="K15" s="109"/>
-      <c r="L15" s="109"/>
-      <c r="M15" s="109"/>
-      <c r="N15" s="109"/>
-      <c r="O15" s="109"/>
-      <c r="P15" s="110"/>
+      <c r="K15" s="105"/>
+      <c r="L15" s="105"/>
+      <c r="M15" s="105"/>
+      <c r="N15" s="105"/>
+      <c r="O15" s="105"/>
+      <c r="P15" s="106"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" s="105" t="s">
+      <c r="A16" s="95" t="s">
         <v>50</v>
       </c>
-      <c r="B16" s="106"/>
-      <c r="C16" s="106"/>
-      <c r="D16" s="106"/>
-      <c r="E16" s="106"/>
-      <c r="F16" s="106"/>
-      <c r="G16" s="106"/>
+      <c r="B16" s="96"/>
+      <c r="C16" s="96"/>
+      <c r="D16" s="96"/>
+      <c r="E16" s="96"/>
+      <c r="F16" s="96"/>
+      <c r="G16" s="96"/>
       <c r="H16" s="29"/>
-      <c r="J16" s="105" t="s">
+      <c r="J16" s="95" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="106"/>
-      <c r="L16" s="106"/>
-      <c r="M16" s="106"/>
-      <c r="N16" s="106"/>
-      <c r="O16" s="106"/>
-      <c r="P16" s="107"/>
+      <c r="K16" s="96"/>
+      <c r="L16" s="96"/>
+      <c r="M16" s="96"/>
+      <c r="N16" s="96"/>
+      <c r="O16" s="96"/>
+      <c r="P16" s="97"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="28"/>
@@ -11527,46 +11290,46 @@
       <c r="P17" s="29"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="113" t="s">
+      <c r="A18" s="98" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="114"/>
-      <c r="C18" s="114"/>
-      <c r="D18" s="114"/>
-      <c r="E18" s="114"/>
-      <c r="F18" s="114"/>
-      <c r="G18" s="114"/>
+      <c r="B18" s="99"/>
+      <c r="C18" s="99"/>
+      <c r="D18" s="99"/>
+      <c r="E18" s="99"/>
+      <c r="F18" s="99"/>
+      <c r="G18" s="99"/>
       <c r="H18" s="29"/>
-      <c r="J18" s="113" t="s">
+      <c r="J18" s="98" t="s">
         <v>51</v>
       </c>
-      <c r="K18" s="114"/>
-      <c r="L18" s="114"/>
-      <c r="M18" s="114"/>
-      <c r="N18" s="114"/>
-      <c r="O18" s="114"/>
-      <c r="P18" s="115"/>
+      <c r="K18" s="99"/>
+      <c r="L18" s="99"/>
+      <c r="M18" s="99"/>
+      <c r="N18" s="99"/>
+      <c r="O18" s="99"/>
+      <c r="P18" s="100"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="111" t="s">
+      <c r="A19" s="101" t="s">
         <v>57</v>
       </c>
-      <c r="B19" s="112"/>
-      <c r="C19" s="112"/>
-      <c r="D19" s="112"/>
-      <c r="E19" s="112"/>
-      <c r="F19" s="112"/>
-      <c r="G19" s="112"/>
+      <c r="B19" s="102"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102"/>
       <c r="H19" s="29"/>
-      <c r="J19" s="111" t="s">
+      <c r="J19" s="101" t="s">
         <v>57</v>
       </c>
-      <c r="K19" s="112"/>
-      <c r="L19" s="112"/>
-      <c r="M19" s="112"/>
-      <c r="N19" s="112"/>
-      <c r="O19" s="112"/>
-      <c r="P19" s="116"/>
+      <c r="K19" s="102"/>
+      <c r="L19" s="102"/>
+      <c r="M19" s="102"/>
+      <c r="N19" s="102"/>
+      <c r="O19" s="102"/>
+      <c r="P19" s="103"/>
     </row>
     <row r="20" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="30"/>
@@ -11587,135 +11350,135 @@
       <c r="P20" s="33"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="98" t="s">
+      <c r="A21" s="107" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="99"/>
-      <c r="C21" s="99"/>
-      <c r="D21" s="99"/>
-      <c r="E21" s="99"/>
-      <c r="F21" s="99"/>
-      <c r="G21" s="99"/>
+      <c r="B21" s="108"/>
+      <c r="C21" s="108"/>
+      <c r="D21" s="108"/>
+      <c r="E21" s="108"/>
+      <c r="F21" s="108"/>
+      <c r="G21" s="108"/>
       <c r="H21" s="27"/>
       <c r="I21" s="34"/>
-      <c r="J21" s="98" t="s">
+      <c r="J21" s="107" t="s">
         <v>47</v>
       </c>
-      <c r="K21" s="99"/>
-      <c r="L21" s="99"/>
-      <c r="M21" s="99"/>
-      <c r="N21" s="99"/>
-      <c r="O21" s="99"/>
-      <c r="P21" s="100"/>
+      <c r="K21" s="108"/>
+      <c r="L21" s="108"/>
+      <c r="M21" s="108"/>
+      <c r="N21" s="108"/>
+      <c r="O21" s="108"/>
+      <c r="P21" s="109"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" s="101" t="s">
+      <c r="A22" s="110" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="102"/>
-      <c r="C22" s="102"/>
-      <c r="D22" s="102"/>
-      <c r="E22" s="102"/>
-      <c r="F22" s="96" t="s">
+      <c r="B22" s="111"/>
+      <c r="C22" s="111"/>
+      <c r="D22" s="111"/>
+      <c r="E22" s="111"/>
+      <c r="F22" s="112" t="s">
         <v>55</v>
       </c>
-      <c r="G22" s="97"/>
+      <c r="G22" s="113"/>
       <c r="H22" s="29"/>
-      <c r="J22" s="101" t="s">
+      <c r="J22" s="110" t="s">
         <v>48</v>
       </c>
-      <c r="K22" s="102"/>
-      <c r="L22" s="102"/>
-      <c r="M22" s="102"/>
-      <c r="N22" s="102"/>
-      <c r="O22" s="103" t="s">
+      <c r="K22" s="111"/>
+      <c r="L22" s="111"/>
+      <c r="M22" s="111"/>
+      <c r="N22" s="111"/>
+      <c r="O22" s="114" t="s">
         <v>55</v>
       </c>
-      <c r="P22" s="104"/>
+      <c r="P22" s="115"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" s="105" t="s">
+      <c r="A23" s="95" t="s">
         <v>54</v>
       </c>
-      <c r="B23" s="106"/>
-      <c r="C23" s="106"/>
-      <c r="D23" s="106"/>
-      <c r="E23" s="106"/>
-      <c r="F23" s="106"/>
-      <c r="G23" s="106"/>
+      <c r="B23" s="96"/>
+      <c r="C23" s="96"/>
+      <c r="D23" s="96"/>
+      <c r="E23" s="96"/>
+      <c r="F23" s="96"/>
+      <c r="G23" s="96"/>
       <c r="H23" s="29"/>
-      <c r="J23" s="105" t="s">
+      <c r="J23" s="95" t="s">
         <v>54</v>
       </c>
-      <c r="K23" s="106"/>
-      <c r="L23" s="106"/>
-      <c r="M23" s="106"/>
-      <c r="N23" s="106"/>
-      <c r="O23" s="106"/>
-      <c r="P23" s="107"/>
+      <c r="K23" s="96"/>
+      <c r="L23" s="96"/>
+      <c r="M23" s="96"/>
+      <c r="N23" s="96"/>
+      <c r="O23" s="96"/>
+      <c r="P23" s="97"/>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" s="105" t="s">
+      <c r="A24" s="95" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="106"/>
-      <c r="C24" s="106"/>
-      <c r="D24" s="106"/>
-      <c r="E24" s="106"/>
-      <c r="F24" s="106"/>
-      <c r="G24" s="106"/>
+      <c r="B24" s="96"/>
+      <c r="C24" s="96"/>
+      <c r="D24" s="96"/>
+      <c r="E24" s="96"/>
+      <c r="F24" s="96"/>
+      <c r="G24" s="96"/>
       <c r="H24" s="29"/>
-      <c r="J24" s="105" t="s">
+      <c r="J24" s="95" t="s">
         <v>49</v>
       </c>
-      <c r="K24" s="106"/>
-      <c r="L24" s="106"/>
-      <c r="M24" s="106"/>
-      <c r="N24" s="106"/>
-      <c r="O24" s="106"/>
-      <c r="P24" s="107"/>
+      <c r="K24" s="96"/>
+      <c r="L24" s="96"/>
+      <c r="M24" s="96"/>
+      <c r="N24" s="96"/>
+      <c r="O24" s="96"/>
+      <c r="P24" s="97"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" s="108" t="s">
+      <c r="A25" s="104" t="s">
         <v>53</v>
       </c>
-      <c r="B25" s="109"/>
-      <c r="C25" s="109"/>
-      <c r="D25" s="109"/>
-      <c r="E25" s="109"/>
-      <c r="F25" s="109"/>
-      <c r="G25" s="109"/>
+      <c r="B25" s="105"/>
+      <c r="C25" s="105"/>
+      <c r="D25" s="105"/>
+      <c r="E25" s="105"/>
+      <c r="F25" s="105"/>
+      <c r="G25" s="105"/>
       <c r="H25" s="29"/>
-      <c r="J25" s="108" t="s">
+      <c r="J25" s="104" t="s">
         <v>53</v>
       </c>
-      <c r="K25" s="109"/>
-      <c r="L25" s="109"/>
-      <c r="M25" s="109"/>
-      <c r="N25" s="109"/>
-      <c r="O25" s="109"/>
-      <c r="P25" s="110"/>
+      <c r="K25" s="105"/>
+      <c r="L25" s="105"/>
+      <c r="M25" s="105"/>
+      <c r="N25" s="105"/>
+      <c r="O25" s="105"/>
+      <c r="P25" s="106"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" s="105" t="s">
+      <c r="A26" s="95" t="s">
         <v>50</v>
       </c>
-      <c r="B26" s="106"/>
-      <c r="C26" s="106"/>
-      <c r="D26" s="106"/>
-      <c r="E26" s="106"/>
-      <c r="F26" s="106"/>
-      <c r="G26" s="106"/>
+      <c r="B26" s="96"/>
+      <c r="C26" s="96"/>
+      <c r="D26" s="96"/>
+      <c r="E26" s="96"/>
+      <c r="F26" s="96"/>
+      <c r="G26" s="96"/>
       <c r="H26" s="29"/>
-      <c r="J26" s="105" t="s">
+      <c r="J26" s="95" t="s">
         <v>50</v>
       </c>
-      <c r="K26" s="106"/>
-      <c r="L26" s="106"/>
-      <c r="M26" s="106"/>
-      <c r="N26" s="106"/>
-      <c r="O26" s="106"/>
-      <c r="P26" s="107"/>
+      <c r="K26" s="96"/>
+      <c r="L26" s="96"/>
+      <c r="M26" s="96"/>
+      <c r="N26" s="96"/>
+      <c r="O26" s="96"/>
+      <c r="P26" s="97"/>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="28"/>
@@ -11724,46 +11487,46 @@
       <c r="P27" s="29"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" s="113" t="s">
+      <c r="A28" s="98" t="s">
         <v>51</v>
       </c>
-      <c r="B28" s="114"/>
-      <c r="C28" s="114"/>
-      <c r="D28" s="114"/>
-      <c r="E28" s="114"/>
-      <c r="F28" s="114"/>
-      <c r="G28" s="114"/>
+      <c r="B28" s="99"/>
+      <c r="C28" s="99"/>
+      <c r="D28" s="99"/>
+      <c r="E28" s="99"/>
+      <c r="F28" s="99"/>
+      <c r="G28" s="99"/>
       <c r="H28" s="29"/>
-      <c r="J28" s="113" t="s">
+      <c r="J28" s="98" t="s">
         <v>51</v>
       </c>
-      <c r="K28" s="114"/>
-      <c r="L28" s="114"/>
-      <c r="M28" s="114"/>
-      <c r="N28" s="114"/>
-      <c r="O28" s="114"/>
-      <c r="P28" s="115"/>
+      <c r="K28" s="99"/>
+      <c r="L28" s="99"/>
+      <c r="M28" s="99"/>
+      <c r="N28" s="99"/>
+      <c r="O28" s="99"/>
+      <c r="P28" s="100"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" s="111" t="s">
+      <c r="A29" s="101" t="s">
         <v>57</v>
       </c>
-      <c r="B29" s="112"/>
-      <c r="C29" s="112"/>
-      <c r="D29" s="112"/>
-      <c r="E29" s="112"/>
-      <c r="F29" s="112"/>
-      <c r="G29" s="112"/>
+      <c r="B29" s="102"/>
+      <c r="C29" s="102"/>
+      <c r="D29" s="102"/>
+      <c r="E29" s="102"/>
+      <c r="F29" s="102"/>
+      <c r="G29" s="102"/>
       <c r="H29" s="29"/>
-      <c r="J29" s="111" t="s">
+      <c r="J29" s="101" t="s">
         <v>57</v>
       </c>
-      <c r="K29" s="112"/>
-      <c r="L29" s="112"/>
-      <c r="M29" s="112"/>
-      <c r="N29" s="112"/>
-      <c r="O29" s="112"/>
-      <c r="P29" s="116"/>
+      <c r="K29" s="102"/>
+      <c r="L29" s="102"/>
+      <c r="M29" s="102"/>
+      <c r="N29" s="102"/>
+      <c r="O29" s="102"/>
+      <c r="P29" s="103"/>
     </row>
     <row r="30" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="30"/>
@@ -11784,135 +11547,135 @@
       <c r="P30" s="33"/>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31" s="98" t="s">
+      <c r="A31" s="107" t="s">
         <v>47</v>
       </c>
-      <c r="B31" s="99"/>
-      <c r="C31" s="99"/>
-      <c r="D31" s="99"/>
-      <c r="E31" s="99"/>
-      <c r="F31" s="99"/>
-      <c r="G31" s="99"/>
+      <c r="B31" s="108"/>
+      <c r="C31" s="108"/>
+      <c r="D31" s="108"/>
+      <c r="E31" s="108"/>
+      <c r="F31" s="108"/>
+      <c r="G31" s="108"/>
       <c r="H31" s="27"/>
       <c r="I31" s="34"/>
-      <c r="J31" s="98" t="s">
+      <c r="J31" s="107" t="s">
         <v>47</v>
       </c>
-      <c r="K31" s="99"/>
-      <c r="L31" s="99"/>
-      <c r="M31" s="99"/>
-      <c r="N31" s="99"/>
-      <c r="O31" s="99"/>
-      <c r="P31" s="100"/>
+      <c r="K31" s="108"/>
+      <c r="L31" s="108"/>
+      <c r="M31" s="108"/>
+      <c r="N31" s="108"/>
+      <c r="O31" s="108"/>
+      <c r="P31" s="109"/>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" s="101" t="s">
+      <c r="A32" s="110" t="s">
         <v>48</v>
       </c>
-      <c r="B32" s="102"/>
-      <c r="C32" s="102"/>
-      <c r="D32" s="102"/>
-      <c r="E32" s="102"/>
-      <c r="F32" s="96" t="s">
+      <c r="B32" s="111"/>
+      <c r="C32" s="111"/>
+      <c r="D32" s="111"/>
+      <c r="E32" s="111"/>
+      <c r="F32" s="112" t="s">
         <v>55</v>
       </c>
-      <c r="G32" s="97"/>
+      <c r="G32" s="113"/>
       <c r="H32" s="29"/>
-      <c r="J32" s="101" t="s">
+      <c r="J32" s="110" t="s">
         <v>48</v>
       </c>
-      <c r="K32" s="102"/>
-      <c r="L32" s="102"/>
-      <c r="M32" s="102"/>
-      <c r="N32" s="102"/>
-      <c r="O32" s="103" t="s">
+      <c r="K32" s="111"/>
+      <c r="L32" s="111"/>
+      <c r="M32" s="111"/>
+      <c r="N32" s="111"/>
+      <c r="O32" s="114" t="s">
         <v>55</v>
       </c>
-      <c r="P32" s="104"/>
+      <c r="P32" s="115"/>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" s="105" t="s">
+      <c r="A33" s="95" t="s">
         <v>54</v>
       </c>
-      <c r="B33" s="106"/>
-      <c r="C33" s="106"/>
-      <c r="D33" s="106"/>
-      <c r="E33" s="106"/>
-      <c r="F33" s="106"/>
-      <c r="G33" s="106"/>
+      <c r="B33" s="96"/>
+      <c r="C33" s="96"/>
+      <c r="D33" s="96"/>
+      <c r="E33" s="96"/>
+      <c r="F33" s="96"/>
+      <c r="G33" s="96"/>
       <c r="H33" s="29"/>
-      <c r="J33" s="105" t="s">
+      <c r="J33" s="95" t="s">
         <v>54</v>
       </c>
-      <c r="K33" s="106"/>
-      <c r="L33" s="106"/>
-      <c r="M33" s="106"/>
-      <c r="N33" s="106"/>
-      <c r="O33" s="106"/>
-      <c r="P33" s="107"/>
+      <c r="K33" s="96"/>
+      <c r="L33" s="96"/>
+      <c r="M33" s="96"/>
+      <c r="N33" s="96"/>
+      <c r="O33" s="96"/>
+      <c r="P33" s="97"/>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34" s="105" t="s">
+      <c r="A34" s="95" t="s">
         <v>49</v>
       </c>
-      <c r="B34" s="106"/>
-      <c r="C34" s="106"/>
-      <c r="D34" s="106"/>
-      <c r="E34" s="106"/>
-      <c r="F34" s="106"/>
-      <c r="G34" s="106"/>
+      <c r="B34" s="96"/>
+      <c r="C34" s="96"/>
+      <c r="D34" s="96"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="96"/>
+      <c r="G34" s="96"/>
       <c r="H34" s="29"/>
-      <c r="J34" s="105" t="s">
+      <c r="J34" s="95" t="s">
         <v>49</v>
       </c>
-      <c r="K34" s="106"/>
-      <c r="L34" s="106"/>
-      <c r="M34" s="106"/>
-      <c r="N34" s="106"/>
-      <c r="O34" s="106"/>
-      <c r="P34" s="107"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="96"/>
+      <c r="M34" s="96"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="96"/>
+      <c r="P34" s="97"/>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A35" s="108" t="s">
+      <c r="A35" s="104" t="s">
         <v>53</v>
       </c>
-      <c r="B35" s="109"/>
-      <c r="C35" s="109"/>
-      <c r="D35" s="109"/>
-      <c r="E35" s="109"/>
-      <c r="F35" s="109"/>
-      <c r="G35" s="109"/>
+      <c r="B35" s="105"/>
+      <c r="C35" s="105"/>
+      <c r="D35" s="105"/>
+      <c r="E35" s="105"/>
+      <c r="F35" s="105"/>
+      <c r="G35" s="105"/>
       <c r="H35" s="29"/>
-      <c r="J35" s="108" t="s">
+      <c r="J35" s="104" t="s">
         <v>53</v>
       </c>
-      <c r="K35" s="109"/>
-      <c r="L35" s="109"/>
-      <c r="M35" s="109"/>
-      <c r="N35" s="109"/>
-      <c r="O35" s="109"/>
-      <c r="P35" s="110"/>
+      <c r="K35" s="105"/>
+      <c r="L35" s="105"/>
+      <c r="M35" s="105"/>
+      <c r="N35" s="105"/>
+      <c r="O35" s="105"/>
+      <c r="P35" s="106"/>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A36" s="105" t="s">
+      <c r="A36" s="95" t="s">
         <v>50</v>
       </c>
-      <c r="B36" s="106"/>
-      <c r="C36" s="106"/>
-      <c r="D36" s="106"/>
-      <c r="E36" s="106"/>
-      <c r="F36" s="106"/>
-      <c r="G36" s="106"/>
+      <c r="B36" s="96"/>
+      <c r="C36" s="96"/>
+      <c r="D36" s="96"/>
+      <c r="E36" s="96"/>
+      <c r="F36" s="96"/>
+      <c r="G36" s="96"/>
       <c r="H36" s="29"/>
-      <c r="J36" s="105" t="s">
+      <c r="J36" s="95" t="s">
         <v>50</v>
       </c>
-      <c r="K36" s="106"/>
-      <c r="L36" s="106"/>
-      <c r="M36" s="106"/>
-      <c r="N36" s="106"/>
-      <c r="O36" s="106"/>
-      <c r="P36" s="107"/>
+      <c r="K36" s="96"/>
+      <c r="L36" s="96"/>
+      <c r="M36" s="96"/>
+      <c r="N36" s="96"/>
+      <c r="O36" s="96"/>
+      <c r="P36" s="97"/>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="28"/>
@@ -11921,46 +11684,46 @@
       <c r="P37" s="29"/>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A38" s="113" t="s">
+      <c r="A38" s="98" t="s">
         <v>51</v>
       </c>
-      <c r="B38" s="114"/>
-      <c r="C38" s="114"/>
-      <c r="D38" s="114"/>
-      <c r="E38" s="114"/>
-      <c r="F38" s="114"/>
-      <c r="G38" s="114"/>
+      <c r="B38" s="99"/>
+      <c r="C38" s="99"/>
+      <c r="D38" s="99"/>
+      <c r="E38" s="99"/>
+      <c r="F38" s="99"/>
+      <c r="G38" s="99"/>
       <c r="H38" s="29"/>
-      <c r="J38" s="113" t="s">
+      <c r="J38" s="98" t="s">
         <v>51</v>
       </c>
-      <c r="K38" s="114"/>
-      <c r="L38" s="114"/>
-      <c r="M38" s="114"/>
-      <c r="N38" s="114"/>
-      <c r="O38" s="114"/>
-      <c r="P38" s="115"/>
+      <c r="K38" s="99"/>
+      <c r="L38" s="99"/>
+      <c r="M38" s="99"/>
+      <c r="N38" s="99"/>
+      <c r="O38" s="99"/>
+      <c r="P38" s="100"/>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" s="111" t="s">
+      <c r="A39" s="101" t="s">
         <v>57</v>
       </c>
-      <c r="B39" s="112"/>
-      <c r="C39" s="112"/>
-      <c r="D39" s="112"/>
-      <c r="E39" s="112"/>
-      <c r="F39" s="112"/>
-      <c r="G39" s="112"/>
+      <c r="B39" s="102"/>
+      <c r="C39" s="102"/>
+      <c r="D39" s="102"/>
+      <c r="E39" s="102"/>
+      <c r="F39" s="102"/>
+      <c r="G39" s="102"/>
       <c r="H39" s="29"/>
-      <c r="J39" s="111" t="s">
+      <c r="J39" s="101" t="s">
         <v>52</v>
       </c>
-      <c r="K39" s="112"/>
-      <c r="L39" s="112"/>
-      <c r="M39" s="112"/>
-      <c r="N39" s="112"/>
-      <c r="O39" s="112"/>
-      <c r="P39" s="116"/>
+      <c r="K39" s="102"/>
+      <c r="L39" s="102"/>
+      <c r="M39" s="102"/>
+      <c r="N39" s="102"/>
+      <c r="O39" s="102"/>
+      <c r="P39" s="103"/>
     </row>
     <row r="40" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="30"/>
@@ -11981,135 +11744,135 @@
       <c r="P40" s="33"/>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A41" s="98" t="s">
+      <c r="A41" s="107" t="s">
         <v>47</v>
       </c>
-      <c r="B41" s="99"/>
-      <c r="C41" s="99"/>
-      <c r="D41" s="99"/>
-      <c r="E41" s="99"/>
-      <c r="F41" s="99"/>
-      <c r="G41" s="99"/>
+      <c r="B41" s="108"/>
+      <c r="C41" s="108"/>
+      <c r="D41" s="108"/>
+      <c r="E41" s="108"/>
+      <c r="F41" s="108"/>
+      <c r="G41" s="108"/>
       <c r="H41" s="27"/>
       <c r="I41" s="34"/>
-      <c r="J41" s="98" t="s">
+      <c r="J41" s="107" t="s">
         <v>47</v>
       </c>
-      <c r="K41" s="99"/>
-      <c r="L41" s="99"/>
-      <c r="M41" s="99"/>
-      <c r="N41" s="99"/>
-      <c r="O41" s="99"/>
-      <c r="P41" s="100"/>
+      <c r="K41" s="108"/>
+      <c r="L41" s="108"/>
+      <c r="M41" s="108"/>
+      <c r="N41" s="108"/>
+      <c r="O41" s="108"/>
+      <c r="P41" s="109"/>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42" s="101" t="s">
+      <c r="A42" s="110" t="s">
         <v>48</v>
       </c>
-      <c r="B42" s="102"/>
-      <c r="C42" s="102"/>
-      <c r="D42" s="102"/>
-      <c r="E42" s="102"/>
-      <c r="F42" s="96" t="s">
+      <c r="B42" s="111"/>
+      <c r="C42" s="111"/>
+      <c r="D42" s="111"/>
+      <c r="E42" s="111"/>
+      <c r="F42" s="112" t="s">
         <v>55</v>
       </c>
-      <c r="G42" s="97"/>
+      <c r="G42" s="113"/>
       <c r="H42" s="29"/>
-      <c r="J42" s="101" t="s">
+      <c r="J42" s="110" t="s">
         <v>48</v>
       </c>
-      <c r="K42" s="102"/>
-      <c r="L42" s="102"/>
-      <c r="M42" s="102"/>
-      <c r="N42" s="102"/>
-      <c r="O42" s="103" t="s">
+      <c r="K42" s="111"/>
+      <c r="L42" s="111"/>
+      <c r="M42" s="111"/>
+      <c r="N42" s="111"/>
+      <c r="O42" s="114" t="s">
         <v>55</v>
       </c>
-      <c r="P42" s="104"/>
+      <c r="P42" s="115"/>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43" s="105" t="s">
+      <c r="A43" s="95" t="s">
         <v>54</v>
       </c>
-      <c r="B43" s="106"/>
-      <c r="C43" s="106"/>
-      <c r="D43" s="106"/>
-      <c r="E43" s="106"/>
-      <c r="F43" s="106"/>
-      <c r="G43" s="106"/>
+      <c r="B43" s="96"/>
+      <c r="C43" s="96"/>
+      <c r="D43" s="96"/>
+      <c r="E43" s="96"/>
+      <c r="F43" s="96"/>
+      <c r="G43" s="96"/>
       <c r="H43" s="29"/>
-      <c r="J43" s="105" t="s">
+      <c r="J43" s="95" t="s">
         <v>54</v>
       </c>
-      <c r="K43" s="106"/>
-      <c r="L43" s="106"/>
-      <c r="M43" s="106"/>
-      <c r="N43" s="106"/>
-      <c r="O43" s="106"/>
-      <c r="P43" s="107"/>
+      <c r="K43" s="96"/>
+      <c r="L43" s="96"/>
+      <c r="M43" s="96"/>
+      <c r="N43" s="96"/>
+      <c r="O43" s="96"/>
+      <c r="P43" s="97"/>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44" s="105" t="s">
+      <c r="A44" s="95" t="s">
         <v>49</v>
       </c>
-      <c r="B44" s="106"/>
-      <c r="C44" s="106"/>
-      <c r="D44" s="106"/>
-      <c r="E44" s="106"/>
-      <c r="F44" s="106"/>
-      <c r="G44" s="106"/>
+      <c r="B44" s="96"/>
+      <c r="C44" s="96"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
+      <c r="F44" s="96"/>
+      <c r="G44" s="96"/>
       <c r="H44" s="29"/>
-      <c r="J44" s="105" t="s">
+      <c r="J44" s="95" t="s">
         <v>49</v>
       </c>
-      <c r="K44" s="106"/>
-      <c r="L44" s="106"/>
-      <c r="M44" s="106"/>
-      <c r="N44" s="106"/>
-      <c r="O44" s="106"/>
-      <c r="P44" s="107"/>
+      <c r="K44" s="96"/>
+      <c r="L44" s="96"/>
+      <c r="M44" s="96"/>
+      <c r="N44" s="96"/>
+      <c r="O44" s="96"/>
+      <c r="P44" s="97"/>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A45" s="108" t="s">
+      <c r="A45" s="104" t="s">
         <v>53</v>
       </c>
-      <c r="B45" s="109"/>
-      <c r="C45" s="109"/>
-      <c r="D45" s="109"/>
-      <c r="E45" s="109"/>
-      <c r="F45" s="109"/>
-      <c r="G45" s="109"/>
+      <c r="B45" s="105"/>
+      <c r="C45" s="105"/>
+      <c r="D45" s="105"/>
+      <c r="E45" s="105"/>
+      <c r="F45" s="105"/>
+      <c r="G45" s="105"/>
       <c r="H45" s="29"/>
-      <c r="J45" s="108" t="s">
+      <c r="J45" s="104" t="s">
         <v>53</v>
       </c>
-      <c r="K45" s="109"/>
-      <c r="L45" s="109"/>
-      <c r="M45" s="109"/>
-      <c r="N45" s="109"/>
-      <c r="O45" s="109"/>
-      <c r="P45" s="110"/>
+      <c r="K45" s="105"/>
+      <c r="L45" s="105"/>
+      <c r="M45" s="105"/>
+      <c r="N45" s="105"/>
+      <c r="O45" s="105"/>
+      <c r="P45" s="106"/>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A46" s="105" t="s">
+      <c r="A46" s="95" t="s">
         <v>50</v>
       </c>
-      <c r="B46" s="106"/>
-      <c r="C46" s="106"/>
-      <c r="D46" s="106"/>
-      <c r="E46" s="106"/>
-      <c r="F46" s="106"/>
-      <c r="G46" s="106"/>
+      <c r="B46" s="96"/>
+      <c r="C46" s="96"/>
+      <c r="D46" s="96"/>
+      <c r="E46" s="96"/>
+      <c r="F46" s="96"/>
+      <c r="G46" s="96"/>
       <c r="H46" s="29"/>
-      <c r="J46" s="105" t="s">
+      <c r="J46" s="95" t="s">
         <v>50</v>
       </c>
-      <c r="K46" s="106"/>
-      <c r="L46" s="106"/>
-      <c r="M46" s="106"/>
-      <c r="N46" s="106"/>
-      <c r="O46" s="106"/>
-      <c r="P46" s="107"/>
+      <c r="K46" s="96"/>
+      <c r="L46" s="96"/>
+      <c r="M46" s="96"/>
+      <c r="N46" s="96"/>
+      <c r="O46" s="96"/>
+      <c r="P46" s="97"/>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" s="28"/>
@@ -12118,46 +11881,46 @@
       <c r="P47" s="29"/>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A48" s="113" t="s">
+      <c r="A48" s="98" t="s">
         <v>51</v>
       </c>
-      <c r="B48" s="114"/>
-      <c r="C48" s="114"/>
-      <c r="D48" s="114"/>
-      <c r="E48" s="114"/>
-      <c r="F48" s="114"/>
-      <c r="G48" s="114"/>
+      <c r="B48" s="99"/>
+      <c r="C48" s="99"/>
+      <c r="D48" s="99"/>
+      <c r="E48" s="99"/>
+      <c r="F48" s="99"/>
+      <c r="G48" s="99"/>
       <c r="H48" s="29"/>
-      <c r="J48" s="113" t="s">
+      <c r="J48" s="98" t="s">
         <v>51</v>
       </c>
-      <c r="K48" s="114"/>
-      <c r="L48" s="114"/>
-      <c r="M48" s="114"/>
-      <c r="N48" s="114"/>
-      <c r="O48" s="114"/>
-      <c r="P48" s="115"/>
+      <c r="K48" s="99"/>
+      <c r="L48" s="99"/>
+      <c r="M48" s="99"/>
+      <c r="N48" s="99"/>
+      <c r="O48" s="99"/>
+      <c r="P48" s="100"/>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A49" s="111" t="s">
+      <c r="A49" s="101" t="s">
         <v>57</v>
       </c>
-      <c r="B49" s="112"/>
-      <c r="C49" s="112"/>
-      <c r="D49" s="112"/>
-      <c r="E49" s="112"/>
-      <c r="F49" s="112"/>
-      <c r="G49" s="112"/>
+      <c r="B49" s="102"/>
+      <c r="C49" s="102"/>
+      <c r="D49" s="102"/>
+      <c r="E49" s="102"/>
+      <c r="F49" s="102"/>
+      <c r="G49" s="102"/>
       <c r="H49" s="29"/>
-      <c r="J49" s="111" t="s">
+      <c r="J49" s="101" t="s">
         <v>57</v>
       </c>
-      <c r="K49" s="112"/>
-      <c r="L49" s="112"/>
-      <c r="M49" s="112"/>
-      <c r="N49" s="112"/>
-      <c r="O49" s="112"/>
-      <c r="P49" s="116"/>
+      <c r="K49" s="102"/>
+      <c r="L49" s="102"/>
+      <c r="M49" s="102"/>
+      <c r="N49" s="102"/>
+      <c r="O49" s="102"/>
+      <c r="P49" s="103"/>
     </row>
     <row r="50" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="30"/>
@@ -12178,135 +11941,135 @@
       <c r="P50" s="33"/>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A51" s="98" t="s">
+      <c r="A51" s="107" t="s">
         <v>47</v>
       </c>
-      <c r="B51" s="99"/>
-      <c r="C51" s="99"/>
-      <c r="D51" s="99"/>
-      <c r="E51" s="99"/>
-      <c r="F51" s="99"/>
-      <c r="G51" s="99"/>
+      <c r="B51" s="108"/>
+      <c r="C51" s="108"/>
+      <c r="D51" s="108"/>
+      <c r="E51" s="108"/>
+      <c r="F51" s="108"/>
+      <c r="G51" s="108"/>
       <c r="H51" s="27"/>
       <c r="I51" s="34"/>
-      <c r="J51" s="98" t="s">
+      <c r="J51" s="107" t="s">
         <v>47</v>
       </c>
-      <c r="K51" s="99"/>
-      <c r="L51" s="99"/>
-      <c r="M51" s="99"/>
-      <c r="N51" s="99"/>
-      <c r="O51" s="99"/>
-      <c r="P51" s="100"/>
+      <c r="K51" s="108"/>
+      <c r="L51" s="108"/>
+      <c r="M51" s="108"/>
+      <c r="N51" s="108"/>
+      <c r="O51" s="108"/>
+      <c r="P51" s="109"/>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A52" s="101" t="s">
+      <c r="A52" s="110" t="s">
         <v>48</v>
       </c>
-      <c r="B52" s="102"/>
-      <c r="C52" s="102"/>
-      <c r="D52" s="102"/>
-      <c r="E52" s="102"/>
-      <c r="F52" s="96" t="s">
+      <c r="B52" s="111"/>
+      <c r="C52" s="111"/>
+      <c r="D52" s="111"/>
+      <c r="E52" s="111"/>
+      <c r="F52" s="112" t="s">
         <v>55</v>
       </c>
-      <c r="G52" s="97"/>
+      <c r="G52" s="113"/>
       <c r="H52" s="29"/>
-      <c r="J52" s="101" t="s">
+      <c r="J52" s="110" t="s">
         <v>48</v>
       </c>
-      <c r="K52" s="102"/>
-      <c r="L52" s="102"/>
-      <c r="M52" s="102"/>
-      <c r="N52" s="102"/>
-      <c r="O52" s="103" t="s">
+      <c r="K52" s="111"/>
+      <c r="L52" s="111"/>
+      <c r="M52" s="111"/>
+      <c r="N52" s="111"/>
+      <c r="O52" s="114" t="s">
         <v>55</v>
       </c>
-      <c r="P52" s="104"/>
+      <c r="P52" s="115"/>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A53" s="105" t="s">
+      <c r="A53" s="95" t="s">
         <v>54</v>
       </c>
-      <c r="B53" s="106"/>
-      <c r="C53" s="106"/>
-      <c r="D53" s="106"/>
-      <c r="E53" s="106"/>
-      <c r="F53" s="106"/>
-      <c r="G53" s="106"/>
+      <c r="B53" s="96"/>
+      <c r="C53" s="96"/>
+      <c r="D53" s="96"/>
+      <c r="E53" s="96"/>
+      <c r="F53" s="96"/>
+      <c r="G53" s="96"/>
       <c r="H53" s="29"/>
-      <c r="J53" s="105" t="s">
+      <c r="J53" s="95" t="s">
         <v>54</v>
       </c>
-      <c r="K53" s="106"/>
-      <c r="L53" s="106"/>
-      <c r="M53" s="106"/>
-      <c r="N53" s="106"/>
-      <c r="O53" s="106"/>
-      <c r="P53" s="107"/>
+      <c r="K53" s="96"/>
+      <c r="L53" s="96"/>
+      <c r="M53" s="96"/>
+      <c r="N53" s="96"/>
+      <c r="O53" s="96"/>
+      <c r="P53" s="97"/>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A54" s="105" t="s">
+      <c r="A54" s="95" t="s">
         <v>49</v>
       </c>
-      <c r="B54" s="106"/>
-      <c r="C54" s="106"/>
-      <c r="D54" s="106"/>
-      <c r="E54" s="106"/>
-      <c r="F54" s="106"/>
-      <c r="G54" s="106"/>
+      <c r="B54" s="96"/>
+      <c r="C54" s="96"/>
+      <c r="D54" s="96"/>
+      <c r="E54" s="96"/>
+      <c r="F54" s="96"/>
+      <c r="G54" s="96"/>
       <c r="H54" s="29"/>
-      <c r="J54" s="105" t="s">
+      <c r="J54" s="95" t="s">
         <v>49</v>
       </c>
-      <c r="K54" s="106"/>
-      <c r="L54" s="106"/>
-      <c r="M54" s="106"/>
-      <c r="N54" s="106"/>
-      <c r="O54" s="106"/>
-      <c r="P54" s="107"/>
+      <c r="K54" s="96"/>
+      <c r="L54" s="96"/>
+      <c r="M54" s="96"/>
+      <c r="N54" s="96"/>
+      <c r="O54" s="96"/>
+      <c r="P54" s="97"/>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A55" s="108" t="s">
+      <c r="A55" s="104" t="s">
         <v>53</v>
       </c>
-      <c r="B55" s="109"/>
-      <c r="C55" s="109"/>
-      <c r="D55" s="109"/>
-      <c r="E55" s="109"/>
-      <c r="F55" s="109"/>
-      <c r="G55" s="109"/>
+      <c r="B55" s="105"/>
+      <c r="C55" s="105"/>
+      <c r="D55" s="105"/>
+      <c r="E55" s="105"/>
+      <c r="F55" s="105"/>
+      <c r="G55" s="105"/>
       <c r="H55" s="29"/>
-      <c r="J55" s="108" t="s">
+      <c r="J55" s="104" t="s">
         <v>53</v>
       </c>
-      <c r="K55" s="109"/>
-      <c r="L55" s="109"/>
-      <c r="M55" s="109"/>
-      <c r="N55" s="109"/>
-      <c r="O55" s="109"/>
-      <c r="P55" s="110"/>
+      <c r="K55" s="105"/>
+      <c r="L55" s="105"/>
+      <c r="M55" s="105"/>
+      <c r="N55" s="105"/>
+      <c r="O55" s="105"/>
+      <c r="P55" s="106"/>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A56" s="105" t="s">
+      <c r="A56" s="95" t="s">
         <v>50</v>
       </c>
-      <c r="B56" s="106"/>
-      <c r="C56" s="106"/>
-      <c r="D56" s="106"/>
-      <c r="E56" s="106"/>
-      <c r="F56" s="106"/>
-      <c r="G56" s="106"/>
+      <c r="B56" s="96"/>
+      <c r="C56" s="96"/>
+      <c r="D56" s="96"/>
+      <c r="E56" s="96"/>
+      <c r="F56" s="96"/>
+      <c r="G56" s="96"/>
       <c r="H56" s="29"/>
-      <c r="J56" s="105" t="s">
+      <c r="J56" s="95" t="s">
         <v>50</v>
       </c>
-      <c r="K56" s="106"/>
-      <c r="L56" s="106"/>
-      <c r="M56" s="106"/>
-      <c r="N56" s="106"/>
-      <c r="O56" s="106"/>
-      <c r="P56" s="107"/>
+      <c r="K56" s="96"/>
+      <c r="L56" s="96"/>
+      <c r="M56" s="96"/>
+      <c r="N56" s="96"/>
+      <c r="O56" s="96"/>
+      <c r="P56" s="97"/>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57" s="28"/>
@@ -12315,46 +12078,46 @@
       <c r="P57" s="29"/>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A58" s="113" t="s">
+      <c r="A58" s="98" t="s">
         <v>51</v>
       </c>
-      <c r="B58" s="114"/>
-      <c r="C58" s="114"/>
-      <c r="D58" s="114"/>
-      <c r="E58" s="114"/>
-      <c r="F58" s="114"/>
-      <c r="G58" s="114"/>
+      <c r="B58" s="99"/>
+      <c r="C58" s="99"/>
+      <c r="D58" s="99"/>
+      <c r="E58" s="99"/>
+      <c r="F58" s="99"/>
+      <c r="G58" s="99"/>
       <c r="H58" s="29"/>
-      <c r="J58" s="113" t="s">
+      <c r="J58" s="98" t="s">
         <v>51</v>
       </c>
-      <c r="K58" s="114"/>
-      <c r="L58" s="114"/>
-      <c r="M58" s="114"/>
-      <c r="N58" s="114"/>
-      <c r="O58" s="114"/>
-      <c r="P58" s="115"/>
+      <c r="K58" s="99"/>
+      <c r="L58" s="99"/>
+      <c r="M58" s="99"/>
+      <c r="N58" s="99"/>
+      <c r="O58" s="99"/>
+      <c r="P58" s="100"/>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A59" s="111" t="s">
+      <c r="A59" s="101" t="s">
         <v>57</v>
       </c>
-      <c r="B59" s="112"/>
-      <c r="C59" s="112"/>
-      <c r="D59" s="112"/>
-      <c r="E59" s="112"/>
-      <c r="F59" s="112"/>
-      <c r="G59" s="112"/>
+      <c r="B59" s="102"/>
+      <c r="C59" s="102"/>
+      <c r="D59" s="102"/>
+      <c r="E59" s="102"/>
+      <c r="F59" s="102"/>
+      <c r="G59" s="102"/>
       <c r="H59" s="29"/>
-      <c r="J59" s="111" t="s">
+      <c r="J59" s="101" t="s">
         <v>57</v>
       </c>
-      <c r="K59" s="112"/>
-      <c r="L59" s="112"/>
-      <c r="M59" s="112"/>
-      <c r="N59" s="112"/>
-      <c r="O59" s="112"/>
-      <c r="P59" s="116"/>
+      <c r="K59" s="102"/>
+      <c r="L59" s="102"/>
+      <c r="M59" s="102"/>
+      <c r="N59" s="102"/>
+      <c r="O59" s="102"/>
+      <c r="P59" s="103"/>
     </row>
     <row r="60" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="30"/>
@@ -12375,135 +12138,135 @@
       <c r="P60" s="33"/>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A61" s="98" t="s">
+      <c r="A61" s="107" t="s">
         <v>47</v>
       </c>
-      <c r="B61" s="99"/>
-      <c r="C61" s="99"/>
-      <c r="D61" s="99"/>
-      <c r="E61" s="99"/>
-      <c r="F61" s="99"/>
-      <c r="G61" s="99"/>
+      <c r="B61" s="108"/>
+      <c r="C61" s="108"/>
+      <c r="D61" s="108"/>
+      <c r="E61" s="108"/>
+      <c r="F61" s="108"/>
+      <c r="G61" s="108"/>
       <c r="H61" s="27"/>
       <c r="I61" s="34"/>
-      <c r="J61" s="98" t="s">
+      <c r="J61" s="107" t="s">
         <v>47</v>
       </c>
-      <c r="K61" s="99"/>
-      <c r="L61" s="99"/>
-      <c r="M61" s="99"/>
-      <c r="N61" s="99"/>
-      <c r="O61" s="99"/>
-      <c r="P61" s="100"/>
+      <c r="K61" s="108"/>
+      <c r="L61" s="108"/>
+      <c r="M61" s="108"/>
+      <c r="N61" s="108"/>
+      <c r="O61" s="108"/>
+      <c r="P61" s="109"/>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A62" s="101" t="s">
+      <c r="A62" s="110" t="s">
         <v>48</v>
       </c>
-      <c r="B62" s="102"/>
-      <c r="C62" s="102"/>
-      <c r="D62" s="102"/>
-      <c r="E62" s="102"/>
-      <c r="F62" s="96" t="s">
+      <c r="B62" s="111"/>
+      <c r="C62" s="111"/>
+      <c r="D62" s="111"/>
+      <c r="E62" s="111"/>
+      <c r="F62" s="112" t="s">
         <v>55</v>
       </c>
-      <c r="G62" s="97"/>
+      <c r="G62" s="113"/>
       <c r="H62" s="29"/>
-      <c r="J62" s="101" t="s">
+      <c r="J62" s="110" t="s">
         <v>48</v>
       </c>
-      <c r="K62" s="102"/>
-      <c r="L62" s="102"/>
-      <c r="M62" s="102"/>
-      <c r="N62" s="102"/>
-      <c r="O62" s="103" t="s">
+      <c r="K62" s="111"/>
+      <c r="L62" s="111"/>
+      <c r="M62" s="111"/>
+      <c r="N62" s="111"/>
+      <c r="O62" s="114" t="s">
         <v>55</v>
       </c>
-      <c r="P62" s="104"/>
+      <c r="P62" s="115"/>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A63" s="105" t="s">
+      <c r="A63" s="95" t="s">
         <v>54</v>
       </c>
-      <c r="B63" s="106"/>
-      <c r="C63" s="106"/>
-      <c r="D63" s="106"/>
-      <c r="E63" s="106"/>
-      <c r="F63" s="106"/>
-      <c r="G63" s="106"/>
+      <c r="B63" s="96"/>
+      <c r="C63" s="96"/>
+      <c r="D63" s="96"/>
+      <c r="E63" s="96"/>
+      <c r="F63" s="96"/>
+      <c r="G63" s="96"/>
       <c r="H63" s="29"/>
-      <c r="J63" s="105" t="s">
+      <c r="J63" s="95" t="s">
         <v>54</v>
       </c>
-      <c r="K63" s="106"/>
-      <c r="L63" s="106"/>
-      <c r="M63" s="106"/>
-      <c r="N63" s="106"/>
-      <c r="O63" s="106"/>
-      <c r="P63" s="107"/>
+      <c r="K63" s="96"/>
+      <c r="L63" s="96"/>
+      <c r="M63" s="96"/>
+      <c r="N63" s="96"/>
+      <c r="O63" s="96"/>
+      <c r="P63" s="97"/>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A64" s="105" t="s">
+      <c r="A64" s="95" t="s">
         <v>49</v>
       </c>
-      <c r="B64" s="106"/>
-      <c r="C64" s="106"/>
-      <c r="D64" s="106"/>
-      <c r="E64" s="106"/>
-      <c r="F64" s="106"/>
-      <c r="G64" s="106"/>
+      <c r="B64" s="96"/>
+      <c r="C64" s="96"/>
+      <c r="D64" s="96"/>
+      <c r="E64" s="96"/>
+      <c r="F64" s="96"/>
+      <c r="G64" s="96"/>
       <c r="H64" s="29"/>
-      <c r="J64" s="105" t="s">
+      <c r="J64" s="95" t="s">
         <v>49</v>
       </c>
-      <c r="K64" s="106"/>
-      <c r="L64" s="106"/>
-      <c r="M64" s="106"/>
-      <c r="N64" s="106"/>
-      <c r="O64" s="106"/>
-      <c r="P64" s="107"/>
+      <c r="K64" s="96"/>
+      <c r="L64" s="96"/>
+      <c r="M64" s="96"/>
+      <c r="N64" s="96"/>
+      <c r="O64" s="96"/>
+      <c r="P64" s="97"/>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A65" s="108" t="s">
+      <c r="A65" s="104" t="s">
         <v>53</v>
       </c>
-      <c r="B65" s="109"/>
-      <c r="C65" s="109"/>
-      <c r="D65" s="109"/>
-      <c r="E65" s="109"/>
-      <c r="F65" s="109"/>
-      <c r="G65" s="109"/>
+      <c r="B65" s="105"/>
+      <c r="C65" s="105"/>
+      <c r="D65" s="105"/>
+      <c r="E65" s="105"/>
+      <c r="F65" s="105"/>
+      <c r="G65" s="105"/>
       <c r="H65" s="29"/>
-      <c r="J65" s="108" t="s">
+      <c r="J65" s="104" t="s">
         <v>53</v>
       </c>
-      <c r="K65" s="109"/>
-      <c r="L65" s="109"/>
-      <c r="M65" s="109"/>
-      <c r="N65" s="109"/>
-      <c r="O65" s="109"/>
-      <c r="P65" s="110"/>
+      <c r="K65" s="105"/>
+      <c r="L65" s="105"/>
+      <c r="M65" s="105"/>
+      <c r="N65" s="105"/>
+      <c r="O65" s="105"/>
+      <c r="P65" s="106"/>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A66" s="105" t="s">
+      <c r="A66" s="95" t="s">
         <v>50</v>
       </c>
-      <c r="B66" s="106"/>
-      <c r="C66" s="106"/>
-      <c r="D66" s="106"/>
-      <c r="E66" s="106"/>
-      <c r="F66" s="106"/>
-      <c r="G66" s="106"/>
+      <c r="B66" s="96"/>
+      <c r="C66" s="96"/>
+      <c r="D66" s="96"/>
+      <c r="E66" s="96"/>
+      <c r="F66" s="96"/>
+      <c r="G66" s="96"/>
       <c r="H66" s="29"/>
-      <c r="J66" s="105" t="s">
+      <c r="J66" s="95" t="s">
         <v>50</v>
       </c>
-      <c r="K66" s="106"/>
-      <c r="L66" s="106"/>
-      <c r="M66" s="106"/>
-      <c r="N66" s="106"/>
-      <c r="O66" s="106"/>
-      <c r="P66" s="107"/>
+      <c r="K66" s="96"/>
+      <c r="L66" s="96"/>
+      <c r="M66" s="96"/>
+      <c r="N66" s="96"/>
+      <c r="O66" s="96"/>
+      <c r="P66" s="97"/>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" s="28"/>
@@ -12512,46 +12275,46 @@
       <c r="P67" s="29"/>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A68" s="113" t="s">
+      <c r="A68" s="98" t="s">
         <v>51</v>
       </c>
-      <c r="B68" s="114"/>
-      <c r="C68" s="114"/>
-      <c r="D68" s="114"/>
-      <c r="E68" s="114"/>
-      <c r="F68" s="114"/>
-      <c r="G68" s="114"/>
+      <c r="B68" s="99"/>
+      <c r="C68" s="99"/>
+      <c r="D68" s="99"/>
+      <c r="E68" s="99"/>
+      <c r="F68" s="99"/>
+      <c r="G68" s="99"/>
       <c r="H68" s="29"/>
-      <c r="J68" s="113" t="s">
+      <c r="J68" s="98" t="s">
         <v>51</v>
       </c>
-      <c r="K68" s="114"/>
-      <c r="L68" s="114"/>
-      <c r="M68" s="114"/>
-      <c r="N68" s="114"/>
-      <c r="O68" s="114"/>
-      <c r="P68" s="115"/>
+      <c r="K68" s="99"/>
+      <c r="L68" s="99"/>
+      <c r="M68" s="99"/>
+      <c r="N68" s="99"/>
+      <c r="O68" s="99"/>
+      <c r="P68" s="100"/>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A69" s="111" t="s">
+      <c r="A69" s="101" t="s">
         <v>56</v>
       </c>
-      <c r="B69" s="112"/>
-      <c r="C69" s="112"/>
-      <c r="D69" s="112"/>
-      <c r="E69" s="112"/>
-      <c r="F69" s="112"/>
-      <c r="G69" s="112"/>
+      <c r="B69" s="102"/>
+      <c r="C69" s="102"/>
+      <c r="D69" s="102"/>
+      <c r="E69" s="102"/>
+      <c r="F69" s="102"/>
+      <c r="G69" s="102"/>
       <c r="H69" s="29"/>
-      <c r="J69" s="111" t="s">
+      <c r="J69" s="101" t="s">
         <v>57</v>
       </c>
-      <c r="K69" s="112"/>
-      <c r="L69" s="112"/>
-      <c r="M69" s="112"/>
-      <c r="N69" s="112"/>
-      <c r="O69" s="112"/>
-      <c r="P69" s="116"/>
+      <c r="K69" s="102"/>
+      <c r="L69" s="102"/>
+      <c r="M69" s="102"/>
+      <c r="N69" s="102"/>
+      <c r="O69" s="102"/>
+      <c r="P69" s="103"/>
     </row>
     <row r="70" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="30"/>
@@ -12573,116 +12336,6 @@
     </row>
   </sheetData>
   <mergeCells count="126">
-    <mergeCell ref="A66:G66"/>
-    <mergeCell ref="J66:P66"/>
-    <mergeCell ref="A68:G68"/>
-    <mergeCell ref="J68:P68"/>
-    <mergeCell ref="A69:G69"/>
-    <mergeCell ref="J69:P69"/>
-    <mergeCell ref="A63:G63"/>
-    <mergeCell ref="J63:P63"/>
-    <mergeCell ref="A64:G64"/>
-    <mergeCell ref="J64:P64"/>
-    <mergeCell ref="A65:G65"/>
-    <mergeCell ref="J65:P65"/>
-    <mergeCell ref="A61:G61"/>
-    <mergeCell ref="J61:P61"/>
-    <mergeCell ref="A62:E62"/>
-    <mergeCell ref="F62:G62"/>
-    <mergeCell ref="J62:N62"/>
-    <mergeCell ref="O62:P62"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="J56:P56"/>
-    <mergeCell ref="A58:G58"/>
-    <mergeCell ref="J58:P58"/>
-    <mergeCell ref="A59:G59"/>
-    <mergeCell ref="J59:P59"/>
-    <mergeCell ref="A53:G53"/>
-    <mergeCell ref="J53:P53"/>
-    <mergeCell ref="A54:G54"/>
-    <mergeCell ref="J54:P54"/>
-    <mergeCell ref="A55:G55"/>
-    <mergeCell ref="J55:P55"/>
-    <mergeCell ref="A51:G51"/>
-    <mergeCell ref="J51:P51"/>
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="J52:N52"/>
-    <mergeCell ref="O52:P52"/>
-    <mergeCell ref="A46:G46"/>
-    <mergeCell ref="J46:P46"/>
-    <mergeCell ref="A48:G48"/>
-    <mergeCell ref="J48:P48"/>
-    <mergeCell ref="A49:G49"/>
-    <mergeCell ref="J49:P49"/>
-    <mergeCell ref="A43:G43"/>
-    <mergeCell ref="J43:P43"/>
-    <mergeCell ref="A44:G44"/>
-    <mergeCell ref="J44:P44"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="J45:P45"/>
-    <mergeCell ref="A41:G41"/>
-    <mergeCell ref="J41:P41"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="J42:N42"/>
-    <mergeCell ref="O42:P42"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="J36:P36"/>
-    <mergeCell ref="A38:G38"/>
-    <mergeCell ref="J38:P38"/>
-    <mergeCell ref="A39:G39"/>
-    <mergeCell ref="J39:P39"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="J33:P33"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="J34:P34"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="J35:P35"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="A32:E32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="J32:N32"/>
-    <mergeCell ref="O32:P32"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="J22:N22"/>
-    <mergeCell ref="O22:P22"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="J12:N12"/>
-    <mergeCell ref="O12:P12"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="J2:N2"/>
@@ -12699,6 +12352,116 @@
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="J12:N12"/>
+    <mergeCell ref="O12:P12"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="J22:N22"/>
+    <mergeCell ref="O22:P22"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="J33:P33"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="J34:P34"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="J35:P35"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="J32:N32"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="J41:P41"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="J42:N42"/>
+    <mergeCell ref="O42:P42"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="J36:P36"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="J38:P38"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="J39:P39"/>
+    <mergeCell ref="A46:G46"/>
+    <mergeCell ref="J46:P46"/>
+    <mergeCell ref="A48:G48"/>
+    <mergeCell ref="J48:P48"/>
+    <mergeCell ref="A49:G49"/>
+    <mergeCell ref="J49:P49"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="J43:P43"/>
+    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="J44:P44"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="J45:P45"/>
+    <mergeCell ref="A53:G53"/>
+    <mergeCell ref="J53:P53"/>
+    <mergeCell ref="A54:G54"/>
+    <mergeCell ref="J54:P54"/>
+    <mergeCell ref="A55:G55"/>
+    <mergeCell ref="J55:P55"/>
+    <mergeCell ref="A51:G51"/>
+    <mergeCell ref="J51:P51"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="J52:N52"/>
+    <mergeCell ref="O52:P52"/>
+    <mergeCell ref="A61:G61"/>
+    <mergeCell ref="J61:P61"/>
+    <mergeCell ref="A62:E62"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="J62:N62"/>
+    <mergeCell ref="O62:P62"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="J56:P56"/>
+    <mergeCell ref="A58:G58"/>
+    <mergeCell ref="J58:P58"/>
+    <mergeCell ref="A59:G59"/>
+    <mergeCell ref="J59:P59"/>
+    <mergeCell ref="A66:G66"/>
+    <mergeCell ref="J66:P66"/>
+    <mergeCell ref="A68:G68"/>
+    <mergeCell ref="J68:P68"/>
+    <mergeCell ref="A69:G69"/>
+    <mergeCell ref="J69:P69"/>
+    <mergeCell ref="A63:G63"/>
+    <mergeCell ref="J63:P63"/>
+    <mergeCell ref="A64:G64"/>
+    <mergeCell ref="J64:P64"/>
+    <mergeCell ref="A65:G65"/>
+    <mergeCell ref="J65:P65"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="70" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -12723,61 +12486,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
     </row>
     <row r="2" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="117"/>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
-      <c r="E2" s="117"/>
-      <c r="F2" s="117"/>
-      <c r="G2" s="117"/>
-      <c r="H2" s="117"/>
-      <c r="I2" s="117"/>
-      <c r="J2" s="117"/>
-      <c r="K2" s="117"/>
+      <c r="B2" s="134"/>
+      <c r="C2" s="134"/>
+      <c r="D2" s="134"/>
+      <c r="E2" s="134"/>
+      <c r="F2" s="134"/>
+      <c r="G2" s="134"/>
+      <c r="H2" s="134"/>
+      <c r="I2" s="134"/>
+      <c r="J2" s="134"/>
+      <c r="K2" s="134"/>
     </row>
     <row r="3" spans="2:11" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="117"/>
-      <c r="C3" s="117"/>
-      <c r="D3" s="117"/>
-      <c r="E3" s="117"/>
-      <c r="F3" s="117"/>
-      <c r="G3" s="117"/>
-      <c r="H3" s="117"/>
-      <c r="I3" s="117"/>
-      <c r="J3" s="117"/>
-      <c r="K3" s="117"/>
+      <c r="B3" s="134"/>
+      <c r="C3" s="134"/>
+      <c r="D3" s="134"/>
+      <c r="E3" s="134"/>
+      <c r="F3" s="134"/>
+      <c r="G3" s="134"/>
+      <c r="H3" s="134"/>
+      <c r="I3" s="134"/>
+      <c r="J3" s="134"/>
+      <c r="K3" s="134"/>
     </row>
     <row r="4" spans="2:11" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="117"/>
-      <c r="C4" s="117"/>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="117"/>
+      <c r="B4" s="134"/>
+      <c r="C4" s="134"/>
+      <c r="D4" s="134"/>
+      <c r="E4" s="134"/>
+      <c r="F4" s="134"/>
+      <c r="G4" s="134"/>
+      <c r="H4" s="134"/>
+      <c r="I4" s="134"/>
+      <c r="J4" s="134"/>
+      <c r="K4" s="134"/>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B5" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="135">
+      <c r="C5" s="132">
         <v>43509</v>
       </c>
-      <c r="D5" s="136"/>
+      <c r="D5" s="133"/>
       <c r="E5" s="40" t="s">
         <v>1</v>
       </c>
@@ -12787,10 +12550,10 @@
       <c r="G5" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="H5" s="135">
+      <c r="H5" s="132">
         <v>43516</v>
       </c>
-      <c r="I5" s="136"/>
+      <c r="I5" s="133"/>
       <c r="J5" s="40" t="s">
         <v>1</v>
       </c>
@@ -12799,129 +12562,129 @@
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B6" s="118" t="s">
+      <c r="B6" s="124" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="119"/>
-      <c r="D6" s="119"/>
-      <c r="E6" s="120"/>
-      <c r="F6" s="120"/>
-      <c r="G6" s="119" t="s">
+      <c r="C6" s="125"/>
+      <c r="D6" s="125"/>
+      <c r="E6" s="126"/>
+      <c r="F6" s="126"/>
+      <c r="G6" s="125" t="s">
         <v>59</v>
       </c>
-      <c r="H6" s="119"/>
-      <c r="I6" s="119"/>
-      <c r="J6" s="120"/>
-      <c r="K6" s="130"/>
+      <c r="H6" s="125"/>
+      <c r="I6" s="125"/>
+      <c r="J6" s="126"/>
+      <c r="K6" s="127"/>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B7" s="121" t="s">
+      <c r="B7" s="135" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="122"/>
-      <c r="D7" s="122"/>
-      <c r="E7" s="122"/>
-      <c r="F7" s="123"/>
-      <c r="G7" s="131" t="s">
+      <c r="C7" s="136"/>
+      <c r="D7" s="136"/>
+      <c r="E7" s="136"/>
+      <c r="F7" s="137"/>
+      <c r="G7" s="144" t="s">
         <v>62</v>
       </c>
-      <c r="H7" s="131"/>
-      <c r="I7" s="131"/>
-      <c r="J7" s="131"/>
-      <c r="K7" s="132"/>
+      <c r="H7" s="144"/>
+      <c r="I7" s="144"/>
+      <c r="J7" s="144"/>
+      <c r="K7" s="145"/>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B8" s="124"/>
-      <c r="C8" s="125"/>
-      <c r="D8" s="125"/>
-      <c r="E8" s="125"/>
-      <c r="F8" s="126"/>
-      <c r="G8" s="131"/>
-      <c r="H8" s="131"/>
-      <c r="I8" s="131"/>
-      <c r="J8" s="131"/>
-      <c r="K8" s="132"/>
+      <c r="B8" s="138"/>
+      <c r="C8" s="139"/>
+      <c r="D8" s="139"/>
+      <c r="E8" s="139"/>
+      <c r="F8" s="140"/>
+      <c r="G8" s="144"/>
+      <c r="H8" s="144"/>
+      <c r="I8" s="144"/>
+      <c r="J8" s="144"/>
+      <c r="K8" s="145"/>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B9" s="124"/>
-      <c r="C9" s="125"/>
-      <c r="D9" s="125"/>
-      <c r="E9" s="125"/>
-      <c r="F9" s="126"/>
-      <c r="G9" s="131"/>
-      <c r="H9" s="131"/>
-      <c r="I9" s="131"/>
-      <c r="J9" s="131"/>
-      <c r="K9" s="132"/>
+      <c r="B9" s="138"/>
+      <c r="C9" s="139"/>
+      <c r="D9" s="139"/>
+      <c r="E9" s="139"/>
+      <c r="F9" s="140"/>
+      <c r="G9" s="144"/>
+      <c r="H9" s="144"/>
+      <c r="I9" s="144"/>
+      <c r="J9" s="144"/>
+      <c r="K9" s="145"/>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B10" s="124"/>
-      <c r="C10" s="125"/>
-      <c r="D10" s="125"/>
-      <c r="E10" s="125"/>
-      <c r="F10" s="126"/>
-      <c r="G10" s="131"/>
-      <c r="H10" s="131"/>
-      <c r="I10" s="131"/>
-      <c r="J10" s="131"/>
-      <c r="K10" s="132"/>
+      <c r="B10" s="138"/>
+      <c r="C10" s="139"/>
+      <c r="D10" s="139"/>
+      <c r="E10" s="139"/>
+      <c r="F10" s="140"/>
+      <c r="G10" s="144"/>
+      <c r="H10" s="144"/>
+      <c r="I10" s="144"/>
+      <c r="J10" s="144"/>
+      <c r="K10" s="145"/>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B11" s="124"/>
-      <c r="C11" s="125"/>
-      <c r="D11" s="125"/>
-      <c r="E11" s="125"/>
-      <c r="F11" s="126"/>
-      <c r="G11" s="131"/>
-      <c r="H11" s="131"/>
-      <c r="I11" s="131"/>
-      <c r="J11" s="131"/>
-      <c r="K11" s="132"/>
+      <c r="B11" s="138"/>
+      <c r="C11" s="139"/>
+      <c r="D11" s="139"/>
+      <c r="E11" s="139"/>
+      <c r="F11" s="140"/>
+      <c r="G11" s="144"/>
+      <c r="H11" s="144"/>
+      <c r="I11" s="144"/>
+      <c r="J11" s="144"/>
+      <c r="K11" s="145"/>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B12" s="124"/>
-      <c r="C12" s="125"/>
-      <c r="D12" s="125"/>
-      <c r="E12" s="125"/>
-      <c r="F12" s="126"/>
-      <c r="G12" s="131"/>
-      <c r="H12" s="131"/>
-      <c r="I12" s="131"/>
-      <c r="J12" s="131"/>
-      <c r="K12" s="132"/>
+      <c r="B12" s="138"/>
+      <c r="C12" s="139"/>
+      <c r="D12" s="139"/>
+      <c r="E12" s="139"/>
+      <c r="F12" s="140"/>
+      <c r="G12" s="144"/>
+      <c r="H12" s="144"/>
+      <c r="I12" s="144"/>
+      <c r="J12" s="144"/>
+      <c r="K12" s="145"/>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B13" s="124"/>
-      <c r="C13" s="125"/>
-      <c r="D13" s="125"/>
-      <c r="E13" s="125"/>
-      <c r="F13" s="126"/>
-      <c r="G13" s="131"/>
-      <c r="H13" s="131"/>
-      <c r="I13" s="131"/>
-      <c r="J13" s="131"/>
-      <c r="K13" s="132"/>
+      <c r="B13" s="138"/>
+      <c r="C13" s="139"/>
+      <c r="D13" s="139"/>
+      <c r="E13" s="139"/>
+      <c r="F13" s="140"/>
+      <c r="G13" s="144"/>
+      <c r="H13" s="144"/>
+      <c r="I13" s="144"/>
+      <c r="J13" s="144"/>
+      <c r="K13" s="145"/>
     </row>
     <row r="14" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="127"/>
-      <c r="C14" s="128"/>
-      <c r="D14" s="128"/>
-      <c r="E14" s="128"/>
-      <c r="F14" s="129"/>
-      <c r="G14" s="131"/>
-      <c r="H14" s="131"/>
-      <c r="I14" s="131"/>
-      <c r="J14" s="133"/>
-      <c r="K14" s="134"/>
+      <c r="B14" s="141"/>
+      <c r="C14" s="142"/>
+      <c r="D14" s="142"/>
+      <c r="E14" s="142"/>
+      <c r="F14" s="143"/>
+      <c r="G14" s="144"/>
+      <c r="H14" s="144"/>
+      <c r="I14" s="144"/>
+      <c r="J14" s="146"/>
+      <c r="K14" s="147"/>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" s="44" t="s">
         <v>58</v>
       </c>
-      <c r="C15" s="137">
+      <c r="C15" s="130">
         <v>43523</v>
       </c>
-      <c r="D15" s="138"/>
+      <c r="D15" s="131"/>
       <c r="E15" s="35" t="s">
         <v>1</v>
       </c>
@@ -12931,10 +12694,10 @@
       <c r="G15" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="H15" s="139">
+      <c r="H15" s="122">
         <v>43530</v>
       </c>
-      <c r="I15" s="140"/>
+      <c r="I15" s="123"/>
       <c r="J15" s="35" t="s">
         <v>1</v>
       </c>
@@ -12943,127 +12706,127 @@
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B16" s="118" t="s">
+      <c r="B16" s="124" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="119"/>
-      <c r="D16" s="119"/>
-      <c r="E16" s="120"/>
-      <c r="F16" s="120"/>
-      <c r="G16" s="119" t="s">
+      <c r="C16" s="125"/>
+      <c r="D16" s="125"/>
+      <c r="E16" s="126"/>
+      <c r="F16" s="126"/>
+      <c r="G16" s="125" t="s">
         <v>59</v>
       </c>
-      <c r="H16" s="119"/>
-      <c r="I16" s="119"/>
-      <c r="J16" s="120"/>
-      <c r="K16" s="130"/>
+      <c r="H16" s="125"/>
+      <c r="I16" s="125"/>
+      <c r="J16" s="126"/>
+      <c r="K16" s="127"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B17" s="144" t="s">
+      <c r="B17" s="128" t="s">
         <v>60</v>
       </c>
-      <c r="C17" s="145"/>
-      <c r="D17" s="145"/>
-      <c r="E17" s="145"/>
-      <c r="F17" s="145"/>
-      <c r="G17" s="142"/>
-      <c r="H17" s="142"/>
-      <c r="I17" s="142"/>
-      <c r="J17" s="142"/>
-      <c r="K17" s="143"/>
+      <c r="C17" s="129"/>
+      <c r="D17" s="129"/>
+      <c r="E17" s="129"/>
+      <c r="F17" s="129"/>
+      <c r="G17" s="117"/>
+      <c r="H17" s="117"/>
+      <c r="I17" s="117"/>
+      <c r="J17" s="117"/>
+      <c r="K17" s="120"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B18" s="144"/>
-      <c r="C18" s="145"/>
-      <c r="D18" s="145"/>
-      <c r="E18" s="145"/>
-      <c r="F18" s="145"/>
-      <c r="G18" s="142"/>
-      <c r="H18" s="142"/>
-      <c r="I18" s="142"/>
-      <c r="J18" s="142"/>
-      <c r="K18" s="143"/>
+      <c r="B18" s="128"/>
+      <c r="C18" s="129"/>
+      <c r="D18" s="129"/>
+      <c r="E18" s="129"/>
+      <c r="F18" s="129"/>
+      <c r="G18" s="117"/>
+      <c r="H18" s="117"/>
+      <c r="I18" s="117"/>
+      <c r="J18" s="117"/>
+      <c r="K18" s="120"/>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B19" s="144"/>
-      <c r="C19" s="145"/>
-      <c r="D19" s="145"/>
-      <c r="E19" s="145"/>
-      <c r="F19" s="145"/>
-      <c r="G19" s="142"/>
-      <c r="H19" s="142"/>
-      <c r="I19" s="142"/>
-      <c r="J19" s="142"/>
-      <c r="K19" s="143"/>
+      <c r="B19" s="128"/>
+      <c r="C19" s="129"/>
+      <c r="D19" s="129"/>
+      <c r="E19" s="129"/>
+      <c r="F19" s="129"/>
+      <c r="G19" s="117"/>
+      <c r="H19" s="117"/>
+      <c r="I19" s="117"/>
+      <c r="J19" s="117"/>
+      <c r="K19" s="120"/>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B20" s="144"/>
-      <c r="C20" s="145"/>
-      <c r="D20" s="145"/>
-      <c r="E20" s="145"/>
-      <c r="F20" s="145"/>
-      <c r="G20" s="142"/>
-      <c r="H20" s="142"/>
-      <c r="I20" s="142"/>
-      <c r="J20" s="142"/>
-      <c r="K20" s="143"/>
+      <c r="B20" s="128"/>
+      <c r="C20" s="129"/>
+      <c r="D20" s="129"/>
+      <c r="E20" s="129"/>
+      <c r="F20" s="129"/>
+      <c r="G20" s="117"/>
+      <c r="H20" s="117"/>
+      <c r="I20" s="117"/>
+      <c r="J20" s="117"/>
+      <c r="K20" s="120"/>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B21" s="144"/>
-      <c r="C21" s="145"/>
-      <c r="D21" s="145"/>
-      <c r="E21" s="145"/>
-      <c r="F21" s="145"/>
-      <c r="G21" s="142"/>
-      <c r="H21" s="142"/>
-      <c r="I21" s="142"/>
-      <c r="J21" s="142"/>
-      <c r="K21" s="143"/>
+      <c r="B21" s="128"/>
+      <c r="C21" s="129"/>
+      <c r="D21" s="129"/>
+      <c r="E21" s="129"/>
+      <c r="F21" s="129"/>
+      <c r="G21" s="117"/>
+      <c r="H21" s="117"/>
+      <c r="I21" s="117"/>
+      <c r="J21" s="117"/>
+      <c r="K21" s="120"/>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B22" s="144"/>
-      <c r="C22" s="145"/>
-      <c r="D22" s="145"/>
-      <c r="E22" s="145"/>
-      <c r="F22" s="145"/>
-      <c r="G22" s="142"/>
-      <c r="H22" s="142"/>
-      <c r="I22" s="142"/>
-      <c r="J22" s="142"/>
-      <c r="K22" s="143"/>
+      <c r="B22" s="128"/>
+      <c r="C22" s="129"/>
+      <c r="D22" s="129"/>
+      <c r="E22" s="129"/>
+      <c r="F22" s="129"/>
+      <c r="G22" s="117"/>
+      <c r="H22" s="117"/>
+      <c r="I22" s="117"/>
+      <c r="J22" s="117"/>
+      <c r="K22" s="120"/>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B23" s="144"/>
-      <c r="C23" s="145"/>
-      <c r="D23" s="145"/>
-      <c r="E23" s="145"/>
-      <c r="F23" s="145"/>
-      <c r="G23" s="142"/>
-      <c r="H23" s="142"/>
-      <c r="I23" s="142"/>
-      <c r="J23" s="142"/>
-      <c r="K23" s="143"/>
+      <c r="B23" s="128"/>
+      <c r="C23" s="129"/>
+      <c r="D23" s="129"/>
+      <c r="E23" s="129"/>
+      <c r="F23" s="129"/>
+      <c r="G23" s="117"/>
+      <c r="H23" s="117"/>
+      <c r="I23" s="117"/>
+      <c r="J23" s="117"/>
+      <c r="K23" s="120"/>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B24" s="144"/>
-      <c r="C24" s="145"/>
-      <c r="D24" s="145"/>
-      <c r="E24" s="145"/>
-      <c r="F24" s="145"/>
-      <c r="G24" s="142"/>
-      <c r="H24" s="142"/>
-      <c r="I24" s="142"/>
-      <c r="J24" s="142"/>
-      <c r="K24" s="143"/>
+      <c r="B24" s="128"/>
+      <c r="C24" s="129"/>
+      <c r="D24" s="129"/>
+      <c r="E24" s="129"/>
+      <c r="F24" s="129"/>
+      <c r="G24" s="117"/>
+      <c r="H24" s="117"/>
+      <c r="I24" s="117"/>
+      <c r="J24" s="117"/>
+      <c r="K24" s="120"/>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B25" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="C25" s="139">
+      <c r="C25" s="122">
         <v>43537</v>
       </c>
-      <c r="D25" s="140"/>
+      <c r="D25" s="123"/>
       <c r="E25" s="35" t="s">
         <v>1</v>
       </c>
@@ -13073,10 +12836,10 @@
       <c r="G25" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="H25" s="139">
+      <c r="H25" s="122">
         <v>43544</v>
       </c>
-      <c r="I25" s="140"/>
+      <c r="I25" s="123"/>
       <c r="J25" s="35" t="s">
         <v>1</v>
       </c>
@@ -13085,125 +12848,125 @@
       </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B26" s="118" t="s">
+      <c r="B26" s="124" t="s">
         <v>59</v>
       </c>
-      <c r="C26" s="119"/>
-      <c r="D26" s="119"/>
-      <c r="E26" s="120"/>
-      <c r="F26" s="120"/>
-      <c r="G26" s="119" t="s">
+      <c r="C26" s="125"/>
+      <c r="D26" s="125"/>
+      <c r="E26" s="126"/>
+      <c r="F26" s="126"/>
+      <c r="G26" s="125" t="s">
         <v>59</v>
       </c>
-      <c r="H26" s="119"/>
-      <c r="I26" s="119"/>
-      <c r="J26" s="120"/>
-      <c r="K26" s="130"/>
+      <c r="H26" s="125"/>
+      <c r="I26" s="125"/>
+      <c r="J26" s="126"/>
+      <c r="K26" s="127"/>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B27" s="141"/>
-      <c r="C27" s="142"/>
-      <c r="D27" s="142"/>
-      <c r="E27" s="142"/>
-      <c r="F27" s="142"/>
-      <c r="G27" s="142"/>
-      <c r="H27" s="142"/>
-      <c r="I27" s="142"/>
-      <c r="J27" s="142"/>
-      <c r="K27" s="143"/>
+      <c r="B27" s="116"/>
+      <c r="C27" s="117"/>
+      <c r="D27" s="117"/>
+      <c r="E27" s="117"/>
+      <c r="F27" s="117"/>
+      <c r="G27" s="117"/>
+      <c r="H27" s="117"/>
+      <c r="I27" s="117"/>
+      <c r="J27" s="117"/>
+      <c r="K27" s="120"/>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B28" s="141"/>
-      <c r="C28" s="142"/>
-      <c r="D28" s="142"/>
-      <c r="E28" s="142"/>
-      <c r="F28" s="142"/>
-      <c r="G28" s="142"/>
-      <c r="H28" s="142"/>
-      <c r="I28" s="142"/>
-      <c r="J28" s="142"/>
-      <c r="K28" s="143"/>
+      <c r="B28" s="116"/>
+      <c r="C28" s="117"/>
+      <c r="D28" s="117"/>
+      <c r="E28" s="117"/>
+      <c r="F28" s="117"/>
+      <c r="G28" s="117"/>
+      <c r="H28" s="117"/>
+      <c r="I28" s="117"/>
+      <c r="J28" s="117"/>
+      <c r="K28" s="120"/>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B29" s="141"/>
-      <c r="C29" s="142"/>
-      <c r="D29" s="142"/>
-      <c r="E29" s="142"/>
-      <c r="F29" s="142"/>
-      <c r="G29" s="142"/>
-      <c r="H29" s="142"/>
-      <c r="I29" s="142"/>
-      <c r="J29" s="142"/>
-      <c r="K29" s="143"/>
+      <c r="B29" s="116"/>
+      <c r="C29" s="117"/>
+      <c r="D29" s="117"/>
+      <c r="E29" s="117"/>
+      <c r="F29" s="117"/>
+      <c r="G29" s="117"/>
+      <c r="H29" s="117"/>
+      <c r="I29" s="117"/>
+      <c r="J29" s="117"/>
+      <c r="K29" s="120"/>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B30" s="141"/>
-      <c r="C30" s="142"/>
-      <c r="D30" s="142"/>
-      <c r="E30" s="142"/>
-      <c r="F30" s="142"/>
-      <c r="G30" s="142"/>
-      <c r="H30" s="142"/>
-      <c r="I30" s="142"/>
-      <c r="J30" s="142"/>
-      <c r="K30" s="143"/>
+      <c r="B30" s="116"/>
+      <c r="C30" s="117"/>
+      <c r="D30" s="117"/>
+      <c r="E30" s="117"/>
+      <c r="F30" s="117"/>
+      <c r="G30" s="117"/>
+      <c r="H30" s="117"/>
+      <c r="I30" s="117"/>
+      <c r="J30" s="117"/>
+      <c r="K30" s="120"/>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B31" s="141"/>
-      <c r="C31" s="142"/>
-      <c r="D31" s="142"/>
-      <c r="E31" s="142"/>
-      <c r="F31" s="142"/>
-      <c r="G31" s="142"/>
-      <c r="H31" s="142"/>
-      <c r="I31" s="142"/>
-      <c r="J31" s="142"/>
-      <c r="K31" s="143"/>
+      <c r="B31" s="116"/>
+      <c r="C31" s="117"/>
+      <c r="D31" s="117"/>
+      <c r="E31" s="117"/>
+      <c r="F31" s="117"/>
+      <c r="G31" s="117"/>
+      <c r="H31" s="117"/>
+      <c r="I31" s="117"/>
+      <c r="J31" s="117"/>
+      <c r="K31" s="120"/>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B32" s="141"/>
-      <c r="C32" s="142"/>
-      <c r="D32" s="142"/>
-      <c r="E32" s="142"/>
-      <c r="F32" s="142"/>
-      <c r="G32" s="142"/>
-      <c r="H32" s="142"/>
-      <c r="I32" s="142"/>
-      <c r="J32" s="142"/>
-      <c r="K32" s="143"/>
+      <c r="B32" s="116"/>
+      <c r="C32" s="117"/>
+      <c r="D32" s="117"/>
+      <c r="E32" s="117"/>
+      <c r="F32" s="117"/>
+      <c r="G32" s="117"/>
+      <c r="H32" s="117"/>
+      <c r="I32" s="117"/>
+      <c r="J32" s="117"/>
+      <c r="K32" s="120"/>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B33" s="141"/>
-      <c r="C33" s="142"/>
-      <c r="D33" s="142"/>
-      <c r="E33" s="142"/>
-      <c r="F33" s="142"/>
-      <c r="G33" s="142"/>
-      <c r="H33" s="142"/>
-      <c r="I33" s="142"/>
-      <c r="J33" s="142"/>
-      <c r="K33" s="143"/>
+      <c r="B33" s="116"/>
+      <c r="C33" s="117"/>
+      <c r="D33" s="117"/>
+      <c r="E33" s="117"/>
+      <c r="F33" s="117"/>
+      <c r="G33" s="117"/>
+      <c r="H33" s="117"/>
+      <c r="I33" s="117"/>
+      <c r="J33" s="117"/>
+      <c r="K33" s="120"/>
     </row>
     <row r="34" spans="2:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="141"/>
-      <c r="C34" s="142"/>
-      <c r="D34" s="142"/>
-      <c r="E34" s="142"/>
-      <c r="F34" s="142"/>
-      <c r="G34" s="142"/>
-      <c r="H34" s="142"/>
-      <c r="I34" s="142"/>
-      <c r="J34" s="142"/>
-      <c r="K34" s="143"/>
+      <c r="B34" s="116"/>
+      <c r="C34" s="117"/>
+      <c r="D34" s="117"/>
+      <c r="E34" s="117"/>
+      <c r="F34" s="117"/>
+      <c r="G34" s="117"/>
+      <c r="H34" s="117"/>
+      <c r="I34" s="117"/>
+      <c r="J34" s="117"/>
+      <c r="K34" s="120"/>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="C35" s="139">
+      <c r="C35" s="122">
         <v>43551</v>
       </c>
-      <c r="D35" s="140"/>
+      <c r="D35" s="123"/>
       <c r="E35" s="35" t="s">
         <v>1</v>
       </c>
@@ -13213,10 +12976,10 @@
       <c r="G35" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="H35" s="139">
+      <c r="H35" s="122">
         <v>43558</v>
       </c>
-      <c r="I35" s="140"/>
+      <c r="I35" s="123"/>
       <c r="J35" s="35" t="s">
         <v>1</v>
       </c>
@@ -13225,126 +12988,126 @@
       </c>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B36" s="118" t="s">
+      <c r="B36" s="124" t="s">
         <v>59</v>
       </c>
-      <c r="C36" s="119"/>
-      <c r="D36" s="119"/>
-      <c r="E36" s="120"/>
-      <c r="F36" s="120"/>
-      <c r="G36" s="119" t="s">
+      <c r="C36" s="125"/>
+      <c r="D36" s="125"/>
+      <c r="E36" s="126"/>
+      <c r="F36" s="126"/>
+      <c r="G36" s="125" t="s">
         <v>59</v>
       </c>
-      <c r="H36" s="119"/>
-      <c r="I36" s="119"/>
-      <c r="J36" s="120"/>
-      <c r="K36" s="130"/>
+      <c r="H36" s="125"/>
+      <c r="I36" s="125"/>
+      <c r="J36" s="126"/>
+      <c r="K36" s="127"/>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B37" s="141"/>
-      <c r="C37" s="142"/>
-      <c r="D37" s="142"/>
-      <c r="E37" s="142"/>
-      <c r="F37" s="142"/>
-      <c r="G37" s="142"/>
-      <c r="H37" s="142"/>
-      <c r="I37" s="142"/>
-      <c r="J37" s="142"/>
-      <c r="K37" s="143"/>
+      <c r="B37" s="116"/>
+      <c r="C37" s="117"/>
+      <c r="D37" s="117"/>
+      <c r="E37" s="117"/>
+      <c r="F37" s="117"/>
+      <c r="G37" s="117"/>
+      <c r="H37" s="117"/>
+      <c r="I37" s="117"/>
+      <c r="J37" s="117"/>
+      <c r="K37" s="120"/>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B38" s="141"/>
-      <c r="C38" s="142"/>
-      <c r="D38" s="142"/>
-      <c r="E38" s="142"/>
-      <c r="F38" s="142"/>
-      <c r="G38" s="142"/>
-      <c r="H38" s="142"/>
-      <c r="I38" s="142"/>
-      <c r="J38" s="142"/>
-      <c r="K38" s="143"/>
+      <c r="B38" s="116"/>
+      <c r="C38" s="117"/>
+      <c r="D38" s="117"/>
+      <c r="E38" s="117"/>
+      <c r="F38" s="117"/>
+      <c r="G38" s="117"/>
+      <c r="H38" s="117"/>
+      <c r="I38" s="117"/>
+      <c r="J38" s="117"/>
+      <c r="K38" s="120"/>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B39" s="141"/>
-      <c r="C39" s="142"/>
-      <c r="D39" s="142"/>
-      <c r="E39" s="142"/>
-      <c r="F39" s="142"/>
-      <c r="G39" s="142"/>
-      <c r="H39" s="142"/>
-      <c r="I39" s="142"/>
-      <c r="J39" s="142"/>
-      <c r="K39" s="143"/>
+      <c r="B39" s="116"/>
+      <c r="C39" s="117"/>
+      <c r="D39" s="117"/>
+      <c r="E39" s="117"/>
+      <c r="F39" s="117"/>
+      <c r="G39" s="117"/>
+      <c r="H39" s="117"/>
+      <c r="I39" s="117"/>
+      <c r="J39" s="117"/>
+      <c r="K39" s="120"/>
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B40" s="141"/>
-      <c r="C40" s="142"/>
-      <c r="D40" s="142"/>
-      <c r="E40" s="142"/>
-      <c r="F40" s="142"/>
-      <c r="G40" s="142"/>
-      <c r="H40" s="142"/>
-      <c r="I40" s="142"/>
-      <c r="J40" s="142"/>
-      <c r="K40" s="143"/>
+      <c r="B40" s="116"/>
+      <c r="C40" s="117"/>
+      <c r="D40" s="117"/>
+      <c r="E40" s="117"/>
+      <c r="F40" s="117"/>
+      <c r="G40" s="117"/>
+      <c r="H40" s="117"/>
+      <c r="I40" s="117"/>
+      <c r="J40" s="117"/>
+      <c r="K40" s="120"/>
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B41" s="141"/>
-      <c r="C41" s="142"/>
-      <c r="D41" s="142"/>
-      <c r="E41" s="142"/>
-      <c r="F41" s="142"/>
-      <c r="G41" s="142"/>
-      <c r="H41" s="142"/>
-      <c r="I41" s="142"/>
-      <c r="J41" s="142"/>
-      <c r="K41" s="143"/>
+      <c r="B41" s="116"/>
+      <c r="C41" s="117"/>
+      <c r="D41" s="117"/>
+      <c r="E41" s="117"/>
+      <c r="F41" s="117"/>
+      <c r="G41" s="117"/>
+      <c r="H41" s="117"/>
+      <c r="I41" s="117"/>
+      <c r="J41" s="117"/>
+      <c r="K41" s="120"/>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B42" s="141"/>
-      <c r="C42" s="142"/>
-      <c r="D42" s="142"/>
-      <c r="E42" s="142"/>
-      <c r="F42" s="142"/>
-      <c r="G42" s="142"/>
-      <c r="H42" s="142"/>
-      <c r="I42" s="142"/>
-      <c r="J42" s="142"/>
-      <c r="K42" s="143"/>
+      <c r="B42" s="116"/>
+      <c r="C42" s="117"/>
+      <c r="D42" s="117"/>
+      <c r="E42" s="117"/>
+      <c r="F42" s="117"/>
+      <c r="G42" s="117"/>
+      <c r="H42" s="117"/>
+      <c r="I42" s="117"/>
+      <c r="J42" s="117"/>
+      <c r="K42" s="120"/>
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B43" s="141"/>
-      <c r="C43" s="142"/>
-      <c r="D43" s="142"/>
-      <c r="E43" s="142"/>
-      <c r="F43" s="142"/>
-      <c r="G43" s="142"/>
-      <c r="H43" s="142"/>
-      <c r="I43" s="142"/>
-      <c r="J43" s="142"/>
-      <c r="K43" s="143"/>
+      <c r="B43" s="116"/>
+      <c r="C43" s="117"/>
+      <c r="D43" s="117"/>
+      <c r="E43" s="117"/>
+      <c r="F43" s="117"/>
+      <c r="G43" s="117"/>
+      <c r="H43" s="117"/>
+      <c r="I43" s="117"/>
+      <c r="J43" s="117"/>
+      <c r="K43" s="120"/>
     </row>
     <row r="44" spans="2:11" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="146"/>
-      <c r="C44" s="147"/>
-      <c r="D44" s="147"/>
-      <c r="E44" s="147"/>
-      <c r="F44" s="147"/>
-      <c r="G44" s="147"/>
-      <c r="H44" s="147"/>
-      <c r="I44" s="147"/>
-      <c r="J44" s="147"/>
-      <c r="K44" s="148"/>
+      <c r="B44" s="118"/>
+      <c r="C44" s="119"/>
+      <c r="D44" s="119"/>
+      <c r="E44" s="119"/>
+      <c r="F44" s="119"/>
+      <c r="G44" s="119"/>
+      <c r="H44" s="119"/>
+      <c r="I44" s="119"/>
+      <c r="J44" s="119"/>
+      <c r="K44" s="121"/>
     </row>
     <row r="45" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B46" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="C46" s="135">
+      <c r="C46" s="132">
         <v>43782</v>
       </c>
-      <c r="D46" s="136"/>
+      <c r="D46" s="133"/>
       <c r="E46" s="40" t="s">
         <v>1</v>
       </c>
@@ -13354,10 +13117,10 @@
       <c r="G46" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="H46" s="135">
+      <c r="H46" s="132">
         <v>43789</v>
       </c>
-      <c r="I46" s="136"/>
+      <c r="I46" s="133"/>
       <c r="J46" s="40" t="s">
         <v>1</v>
       </c>
@@ -13366,125 +13129,125 @@
       </c>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B47" s="118" t="s">
+      <c r="B47" s="124" t="s">
         <v>59</v>
       </c>
-      <c r="C47" s="119"/>
-      <c r="D47" s="119"/>
-      <c r="E47" s="120"/>
-      <c r="F47" s="120"/>
-      <c r="G47" s="119" t="s">
+      <c r="C47" s="125"/>
+      <c r="D47" s="125"/>
+      <c r="E47" s="126"/>
+      <c r="F47" s="126"/>
+      <c r="G47" s="125" t="s">
         <v>59</v>
       </c>
-      <c r="H47" s="119"/>
-      <c r="I47" s="119"/>
-      <c r="J47" s="120"/>
-      <c r="K47" s="130"/>
+      <c r="H47" s="125"/>
+      <c r="I47" s="125"/>
+      <c r="J47" s="126"/>
+      <c r="K47" s="127"/>
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B48" s="141"/>
-      <c r="C48" s="142"/>
-      <c r="D48" s="142"/>
-      <c r="E48" s="142"/>
-      <c r="F48" s="142"/>
-      <c r="G48" s="142"/>
-      <c r="H48" s="142"/>
-      <c r="I48" s="142"/>
-      <c r="J48" s="142"/>
-      <c r="K48" s="143"/>
+      <c r="B48" s="116"/>
+      <c r="C48" s="117"/>
+      <c r="D48" s="117"/>
+      <c r="E48" s="117"/>
+      <c r="F48" s="117"/>
+      <c r="G48" s="117"/>
+      <c r="H48" s="117"/>
+      <c r="I48" s="117"/>
+      <c r="J48" s="117"/>
+      <c r="K48" s="120"/>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B49" s="141"/>
-      <c r="C49" s="142"/>
-      <c r="D49" s="142"/>
-      <c r="E49" s="142"/>
-      <c r="F49" s="142"/>
-      <c r="G49" s="142"/>
-      <c r="H49" s="142"/>
-      <c r="I49" s="142"/>
-      <c r="J49" s="142"/>
-      <c r="K49" s="143"/>
+      <c r="B49" s="116"/>
+      <c r="C49" s="117"/>
+      <c r="D49" s="117"/>
+      <c r="E49" s="117"/>
+      <c r="F49" s="117"/>
+      <c r="G49" s="117"/>
+      <c r="H49" s="117"/>
+      <c r="I49" s="117"/>
+      <c r="J49" s="117"/>
+      <c r="K49" s="120"/>
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B50" s="141"/>
-      <c r="C50" s="142"/>
-      <c r="D50" s="142"/>
-      <c r="E50" s="142"/>
-      <c r="F50" s="142"/>
-      <c r="G50" s="142"/>
-      <c r="H50" s="142"/>
-      <c r="I50" s="142"/>
-      <c r="J50" s="142"/>
-      <c r="K50" s="143"/>
+      <c r="B50" s="116"/>
+      <c r="C50" s="117"/>
+      <c r="D50" s="117"/>
+      <c r="E50" s="117"/>
+      <c r="F50" s="117"/>
+      <c r="G50" s="117"/>
+      <c r="H50" s="117"/>
+      <c r="I50" s="117"/>
+      <c r="J50" s="117"/>
+      <c r="K50" s="120"/>
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B51" s="141"/>
-      <c r="C51" s="142"/>
-      <c r="D51" s="142"/>
-      <c r="E51" s="142"/>
-      <c r="F51" s="142"/>
-      <c r="G51" s="142"/>
-      <c r="H51" s="142"/>
-      <c r="I51" s="142"/>
-      <c r="J51" s="142"/>
-      <c r="K51" s="143"/>
+      <c r="B51" s="116"/>
+      <c r="C51" s="117"/>
+      <c r="D51" s="117"/>
+      <c r="E51" s="117"/>
+      <c r="F51" s="117"/>
+      <c r="G51" s="117"/>
+      <c r="H51" s="117"/>
+      <c r="I51" s="117"/>
+      <c r="J51" s="117"/>
+      <c r="K51" s="120"/>
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B52" s="141"/>
-      <c r="C52" s="142"/>
-      <c r="D52" s="142"/>
-      <c r="E52" s="142"/>
-      <c r="F52" s="142"/>
-      <c r="G52" s="142"/>
-      <c r="H52" s="142"/>
-      <c r="I52" s="142"/>
-      <c r="J52" s="142"/>
-      <c r="K52" s="143"/>
+      <c r="B52" s="116"/>
+      <c r="C52" s="117"/>
+      <c r="D52" s="117"/>
+      <c r="E52" s="117"/>
+      <c r="F52" s="117"/>
+      <c r="G52" s="117"/>
+      <c r="H52" s="117"/>
+      <c r="I52" s="117"/>
+      <c r="J52" s="117"/>
+      <c r="K52" s="120"/>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B53" s="141"/>
-      <c r="C53" s="142"/>
-      <c r="D53" s="142"/>
-      <c r="E53" s="142"/>
-      <c r="F53" s="142"/>
-      <c r="G53" s="142"/>
-      <c r="H53" s="142"/>
-      <c r="I53" s="142"/>
-      <c r="J53" s="142"/>
-      <c r="K53" s="143"/>
+      <c r="B53" s="116"/>
+      <c r="C53" s="117"/>
+      <c r="D53" s="117"/>
+      <c r="E53" s="117"/>
+      <c r="F53" s="117"/>
+      <c r="G53" s="117"/>
+      <c r="H53" s="117"/>
+      <c r="I53" s="117"/>
+      <c r="J53" s="117"/>
+      <c r="K53" s="120"/>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B54" s="141"/>
-      <c r="C54" s="142"/>
-      <c r="D54" s="142"/>
-      <c r="E54" s="142"/>
-      <c r="F54" s="142"/>
-      <c r="G54" s="142"/>
-      <c r="H54" s="142"/>
-      <c r="I54" s="142"/>
-      <c r="J54" s="142"/>
-      <c r="K54" s="143"/>
+      <c r="B54" s="116"/>
+      <c r="C54" s="117"/>
+      <c r="D54" s="117"/>
+      <c r="E54" s="117"/>
+      <c r="F54" s="117"/>
+      <c r="G54" s="117"/>
+      <c r="H54" s="117"/>
+      <c r="I54" s="117"/>
+      <c r="J54" s="117"/>
+      <c r="K54" s="120"/>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B55" s="141"/>
-      <c r="C55" s="142"/>
-      <c r="D55" s="142"/>
-      <c r="E55" s="142"/>
-      <c r="F55" s="142"/>
-      <c r="G55" s="142"/>
-      <c r="H55" s="142"/>
-      <c r="I55" s="142"/>
-      <c r="J55" s="142"/>
-      <c r="K55" s="143"/>
+      <c r="B55" s="116"/>
+      <c r="C55" s="117"/>
+      <c r="D55" s="117"/>
+      <c r="E55" s="117"/>
+      <c r="F55" s="117"/>
+      <c r="G55" s="117"/>
+      <c r="H55" s="117"/>
+      <c r="I55" s="117"/>
+      <c r="J55" s="117"/>
+      <c r="K55" s="120"/>
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B56" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="C56" s="139">
+      <c r="C56" s="122">
         <v>43796</v>
       </c>
-      <c r="D56" s="140"/>
+      <c r="D56" s="123"/>
       <c r="E56" s="35" t="s">
         <v>1</v>
       </c>
@@ -13494,10 +13257,10 @@
       <c r="G56" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="H56" s="139">
+      <c r="H56" s="122">
         <v>43803</v>
       </c>
-      <c r="I56" s="140"/>
+      <c r="I56" s="123"/>
       <c r="J56" s="35" t="s">
         <v>1</v>
       </c>
@@ -13506,125 +13269,125 @@
       </c>
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B57" s="118" t="s">
+      <c r="B57" s="124" t="s">
         <v>59</v>
       </c>
-      <c r="C57" s="119"/>
-      <c r="D57" s="119"/>
-      <c r="E57" s="120"/>
-      <c r="F57" s="120"/>
-      <c r="G57" s="119" t="s">
+      <c r="C57" s="125"/>
+      <c r="D57" s="125"/>
+      <c r="E57" s="126"/>
+      <c r="F57" s="126"/>
+      <c r="G57" s="125" t="s">
         <v>59</v>
       </c>
-      <c r="H57" s="119"/>
-      <c r="I57" s="119"/>
-      <c r="J57" s="120"/>
-      <c r="K57" s="130"/>
+      <c r="H57" s="125"/>
+      <c r="I57" s="125"/>
+      <c r="J57" s="126"/>
+      <c r="K57" s="127"/>
     </row>
     <row r="58" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="141"/>
-      <c r="C58" s="142"/>
-      <c r="D58" s="142"/>
-      <c r="E58" s="142"/>
-      <c r="F58" s="142"/>
-      <c r="G58" s="142"/>
-      <c r="H58" s="142"/>
-      <c r="I58" s="142"/>
-      <c r="J58" s="142"/>
-      <c r="K58" s="143"/>
+      <c r="B58" s="116"/>
+      <c r="C58" s="117"/>
+      <c r="D58" s="117"/>
+      <c r="E58" s="117"/>
+      <c r="F58" s="117"/>
+      <c r="G58" s="117"/>
+      <c r="H58" s="117"/>
+      <c r="I58" s="117"/>
+      <c r="J58" s="117"/>
+      <c r="K58" s="120"/>
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B59" s="141"/>
-      <c r="C59" s="142"/>
-      <c r="D59" s="142"/>
-      <c r="E59" s="142"/>
-      <c r="F59" s="142"/>
-      <c r="G59" s="142"/>
-      <c r="H59" s="142"/>
-      <c r="I59" s="142"/>
-      <c r="J59" s="142"/>
-      <c r="K59" s="143"/>
+      <c r="B59" s="116"/>
+      <c r="C59" s="117"/>
+      <c r="D59" s="117"/>
+      <c r="E59" s="117"/>
+      <c r="F59" s="117"/>
+      <c r="G59" s="117"/>
+      <c r="H59" s="117"/>
+      <c r="I59" s="117"/>
+      <c r="J59" s="117"/>
+      <c r="K59" s="120"/>
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B60" s="141"/>
-      <c r="C60" s="142"/>
-      <c r="D60" s="142"/>
-      <c r="E60" s="142"/>
-      <c r="F60" s="142"/>
-      <c r="G60" s="142"/>
-      <c r="H60" s="142"/>
-      <c r="I60" s="142"/>
-      <c r="J60" s="142"/>
-      <c r="K60" s="143"/>
+      <c r="B60" s="116"/>
+      <c r="C60" s="117"/>
+      <c r="D60" s="117"/>
+      <c r="E60" s="117"/>
+      <c r="F60" s="117"/>
+      <c r="G60" s="117"/>
+      <c r="H60" s="117"/>
+      <c r="I60" s="117"/>
+      <c r="J60" s="117"/>
+      <c r="K60" s="120"/>
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B61" s="141"/>
-      <c r="C61" s="142"/>
-      <c r="D61" s="142"/>
-      <c r="E61" s="142"/>
-      <c r="F61" s="142"/>
-      <c r="G61" s="142"/>
-      <c r="H61" s="142"/>
-      <c r="I61" s="142"/>
-      <c r="J61" s="142"/>
-      <c r="K61" s="143"/>
+      <c r="B61" s="116"/>
+      <c r="C61" s="117"/>
+      <c r="D61" s="117"/>
+      <c r="E61" s="117"/>
+      <c r="F61" s="117"/>
+      <c r="G61" s="117"/>
+      <c r="H61" s="117"/>
+      <c r="I61" s="117"/>
+      <c r="J61" s="117"/>
+      <c r="K61" s="120"/>
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B62" s="141"/>
-      <c r="C62" s="142"/>
-      <c r="D62" s="142"/>
-      <c r="E62" s="142"/>
-      <c r="F62" s="142"/>
-      <c r="G62" s="142"/>
-      <c r="H62" s="142"/>
-      <c r="I62" s="142"/>
-      <c r="J62" s="142"/>
-      <c r="K62" s="143"/>
+      <c r="B62" s="116"/>
+      <c r="C62" s="117"/>
+      <c r="D62" s="117"/>
+      <c r="E62" s="117"/>
+      <c r="F62" s="117"/>
+      <c r="G62" s="117"/>
+      <c r="H62" s="117"/>
+      <c r="I62" s="117"/>
+      <c r="J62" s="117"/>
+      <c r="K62" s="120"/>
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B63" s="141"/>
-      <c r="C63" s="142"/>
-      <c r="D63" s="142"/>
-      <c r="E63" s="142"/>
-      <c r="F63" s="142"/>
-      <c r="G63" s="142"/>
-      <c r="H63" s="142"/>
-      <c r="I63" s="142"/>
-      <c r="J63" s="142"/>
-      <c r="K63" s="143"/>
+      <c r="B63" s="116"/>
+      <c r="C63" s="117"/>
+      <c r="D63" s="117"/>
+      <c r="E63" s="117"/>
+      <c r="F63" s="117"/>
+      <c r="G63" s="117"/>
+      <c r="H63" s="117"/>
+      <c r="I63" s="117"/>
+      <c r="J63" s="117"/>
+      <c r="K63" s="120"/>
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B64" s="141"/>
-      <c r="C64" s="142"/>
-      <c r="D64" s="142"/>
-      <c r="E64" s="142"/>
-      <c r="F64" s="142"/>
-      <c r="G64" s="142"/>
-      <c r="H64" s="142"/>
-      <c r="I64" s="142"/>
-      <c r="J64" s="142"/>
-      <c r="K64" s="143"/>
+      <c r="B64" s="116"/>
+      <c r="C64" s="117"/>
+      <c r="D64" s="117"/>
+      <c r="E64" s="117"/>
+      <c r="F64" s="117"/>
+      <c r="G64" s="117"/>
+      <c r="H64" s="117"/>
+      <c r="I64" s="117"/>
+      <c r="J64" s="117"/>
+      <c r="K64" s="120"/>
     </row>
     <row r="65" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B65" s="141"/>
-      <c r="C65" s="142"/>
-      <c r="D65" s="142"/>
-      <c r="E65" s="142"/>
-      <c r="F65" s="142"/>
-      <c r="G65" s="142"/>
-      <c r="H65" s="142"/>
-      <c r="I65" s="142"/>
-      <c r="J65" s="142"/>
-      <c r="K65" s="143"/>
+      <c r="B65" s="116"/>
+      <c r="C65" s="117"/>
+      <c r="D65" s="117"/>
+      <c r="E65" s="117"/>
+      <c r="F65" s="117"/>
+      <c r="G65" s="117"/>
+      <c r="H65" s="117"/>
+      <c r="I65" s="117"/>
+      <c r="J65" s="117"/>
+      <c r="K65" s="120"/>
     </row>
     <row r="66" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B66" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="C66" s="139">
+      <c r="C66" s="122">
         <v>43810</v>
       </c>
-      <c r="D66" s="140"/>
+      <c r="D66" s="123"/>
       <c r="E66" s="35" t="s">
         <v>1</v>
       </c>
@@ -13634,10 +13397,10 @@
       <c r="G66" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="H66" s="139">
+      <c r="H66" s="122">
         <v>43817</v>
       </c>
-      <c r="I66" s="140"/>
+      <c r="I66" s="123"/>
       <c r="J66" s="35" t="s">
         <v>1</v>
       </c>
@@ -13646,125 +13409,125 @@
       </c>
     </row>
     <row r="67" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B67" s="118" t="s">
+      <c r="B67" s="124" t="s">
         <v>59</v>
       </c>
-      <c r="C67" s="119"/>
-      <c r="D67" s="119"/>
-      <c r="E67" s="120"/>
-      <c r="F67" s="120"/>
-      <c r="G67" s="119" t="s">
+      <c r="C67" s="125"/>
+      <c r="D67" s="125"/>
+      <c r="E67" s="126"/>
+      <c r="F67" s="126"/>
+      <c r="G67" s="125" t="s">
         <v>59</v>
       </c>
-      <c r="H67" s="119"/>
-      <c r="I67" s="119"/>
-      <c r="J67" s="120"/>
-      <c r="K67" s="130"/>
+      <c r="H67" s="125"/>
+      <c r="I67" s="125"/>
+      <c r="J67" s="126"/>
+      <c r="K67" s="127"/>
     </row>
     <row r="68" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B68" s="141"/>
-      <c r="C68" s="142"/>
-      <c r="D68" s="142"/>
-      <c r="E68" s="142"/>
-      <c r="F68" s="142"/>
-      <c r="G68" s="142"/>
-      <c r="H68" s="142"/>
-      <c r="I68" s="142"/>
-      <c r="J68" s="142"/>
-      <c r="K68" s="143"/>
+      <c r="B68" s="116"/>
+      <c r="C68" s="117"/>
+      <c r="D68" s="117"/>
+      <c r="E68" s="117"/>
+      <c r="F68" s="117"/>
+      <c r="G68" s="117"/>
+      <c r="H68" s="117"/>
+      <c r="I68" s="117"/>
+      <c r="J68" s="117"/>
+      <c r="K68" s="120"/>
     </row>
     <row r="69" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B69" s="141"/>
-      <c r="C69" s="142"/>
-      <c r="D69" s="142"/>
-      <c r="E69" s="142"/>
-      <c r="F69" s="142"/>
-      <c r="G69" s="142"/>
-      <c r="H69" s="142"/>
-      <c r="I69" s="142"/>
-      <c r="J69" s="142"/>
-      <c r="K69" s="143"/>
+      <c r="B69" s="116"/>
+      <c r="C69" s="117"/>
+      <c r="D69" s="117"/>
+      <c r="E69" s="117"/>
+      <c r="F69" s="117"/>
+      <c r="G69" s="117"/>
+      <c r="H69" s="117"/>
+      <c r="I69" s="117"/>
+      <c r="J69" s="117"/>
+      <c r="K69" s="120"/>
     </row>
     <row r="70" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B70" s="141"/>
-      <c r="C70" s="142"/>
-      <c r="D70" s="142"/>
-      <c r="E70" s="142"/>
-      <c r="F70" s="142"/>
-      <c r="G70" s="142"/>
-      <c r="H70" s="142"/>
-      <c r="I70" s="142"/>
-      <c r="J70" s="142"/>
-      <c r="K70" s="143"/>
+      <c r="B70" s="116"/>
+      <c r="C70" s="117"/>
+      <c r="D70" s="117"/>
+      <c r="E70" s="117"/>
+      <c r="F70" s="117"/>
+      <c r="G70" s="117"/>
+      <c r="H70" s="117"/>
+      <c r="I70" s="117"/>
+      <c r="J70" s="117"/>
+      <c r="K70" s="120"/>
     </row>
     <row r="71" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B71" s="141"/>
-      <c r="C71" s="142"/>
-      <c r="D71" s="142"/>
-      <c r="E71" s="142"/>
-      <c r="F71" s="142"/>
-      <c r="G71" s="142"/>
-      <c r="H71" s="142"/>
-      <c r="I71" s="142"/>
-      <c r="J71" s="142"/>
-      <c r="K71" s="143"/>
+      <c r="B71" s="116"/>
+      <c r="C71" s="117"/>
+      <c r="D71" s="117"/>
+      <c r="E71" s="117"/>
+      <c r="F71" s="117"/>
+      <c r="G71" s="117"/>
+      <c r="H71" s="117"/>
+      <c r="I71" s="117"/>
+      <c r="J71" s="117"/>
+      <c r="K71" s="120"/>
     </row>
     <row r="72" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B72" s="141"/>
-      <c r="C72" s="142"/>
-      <c r="D72" s="142"/>
-      <c r="E72" s="142"/>
-      <c r="F72" s="142"/>
-      <c r="G72" s="142"/>
-      <c r="H72" s="142"/>
-      <c r="I72" s="142"/>
-      <c r="J72" s="142"/>
-      <c r="K72" s="143"/>
+      <c r="B72" s="116"/>
+      <c r="C72" s="117"/>
+      <c r="D72" s="117"/>
+      <c r="E72" s="117"/>
+      <c r="F72" s="117"/>
+      <c r="G72" s="117"/>
+      <c r="H72" s="117"/>
+      <c r="I72" s="117"/>
+      <c r="J72" s="117"/>
+      <c r="K72" s="120"/>
     </row>
     <row r="73" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B73" s="141"/>
-      <c r="C73" s="142"/>
-      <c r="D73" s="142"/>
-      <c r="E73" s="142"/>
-      <c r="F73" s="142"/>
-      <c r="G73" s="142"/>
-      <c r="H73" s="142"/>
-      <c r="I73" s="142"/>
-      <c r="J73" s="142"/>
-      <c r="K73" s="143"/>
+      <c r="B73" s="116"/>
+      <c r="C73" s="117"/>
+      <c r="D73" s="117"/>
+      <c r="E73" s="117"/>
+      <c r="F73" s="117"/>
+      <c r="G73" s="117"/>
+      <c r="H73" s="117"/>
+      <c r="I73" s="117"/>
+      <c r="J73" s="117"/>
+      <c r="K73" s="120"/>
     </row>
     <row r="74" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B74" s="141"/>
-      <c r="C74" s="142"/>
-      <c r="D74" s="142"/>
-      <c r="E74" s="142"/>
-      <c r="F74" s="142"/>
-      <c r="G74" s="142"/>
-      <c r="H74" s="142"/>
-      <c r="I74" s="142"/>
-      <c r="J74" s="142"/>
-      <c r="K74" s="143"/>
+      <c r="B74" s="116"/>
+      <c r="C74" s="117"/>
+      <c r="D74" s="117"/>
+      <c r="E74" s="117"/>
+      <c r="F74" s="117"/>
+      <c r="G74" s="117"/>
+      <c r="H74" s="117"/>
+      <c r="I74" s="117"/>
+      <c r="J74" s="117"/>
+      <c r="K74" s="120"/>
     </row>
     <row r="75" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B75" s="141"/>
-      <c r="C75" s="142"/>
-      <c r="D75" s="142"/>
-      <c r="E75" s="142"/>
-      <c r="F75" s="142"/>
-      <c r="G75" s="142"/>
-      <c r="H75" s="142"/>
-      <c r="I75" s="142"/>
-      <c r="J75" s="142"/>
-      <c r="K75" s="143"/>
+      <c r="B75" s="116"/>
+      <c r="C75" s="117"/>
+      <c r="D75" s="117"/>
+      <c r="E75" s="117"/>
+      <c r="F75" s="117"/>
+      <c r="G75" s="117"/>
+      <c r="H75" s="117"/>
+      <c r="I75" s="117"/>
+      <c r="J75" s="117"/>
+      <c r="K75" s="120"/>
     </row>
     <row r="76" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B76" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="C76" s="139">
+      <c r="C76" s="122">
         <v>43747</v>
       </c>
-      <c r="D76" s="140"/>
+      <c r="D76" s="123"/>
       <c r="E76" s="35" t="s">
         <v>1</v>
       </c>
@@ -13774,10 +13537,10 @@
       <c r="G76" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="H76" s="139">
+      <c r="H76" s="122">
         <v>43761</v>
       </c>
-      <c r="I76" s="140"/>
+      <c r="I76" s="123"/>
       <c r="J76" s="35" t="s">
         <v>1</v>
       </c>
@@ -13786,125 +13549,125 @@
       </c>
     </row>
     <row r="77" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B77" s="118" t="s">
+      <c r="B77" s="124" t="s">
         <v>59</v>
       </c>
-      <c r="C77" s="119"/>
-      <c r="D77" s="119"/>
-      <c r="E77" s="120"/>
-      <c r="F77" s="120"/>
-      <c r="G77" s="119" t="s">
+      <c r="C77" s="125"/>
+      <c r="D77" s="125"/>
+      <c r="E77" s="126"/>
+      <c r="F77" s="126"/>
+      <c r="G77" s="125" t="s">
         <v>59</v>
       </c>
-      <c r="H77" s="119"/>
-      <c r="I77" s="119"/>
-      <c r="J77" s="120"/>
-      <c r="K77" s="130"/>
+      <c r="H77" s="125"/>
+      <c r="I77" s="125"/>
+      <c r="J77" s="126"/>
+      <c r="K77" s="127"/>
     </row>
     <row r="78" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B78" s="141"/>
-      <c r="C78" s="142"/>
-      <c r="D78" s="142"/>
-      <c r="E78" s="142"/>
-      <c r="F78" s="142"/>
-      <c r="G78" s="142"/>
-      <c r="H78" s="142"/>
-      <c r="I78" s="142"/>
-      <c r="J78" s="142"/>
-      <c r="K78" s="143"/>
+      <c r="B78" s="116"/>
+      <c r="C78" s="117"/>
+      <c r="D78" s="117"/>
+      <c r="E78" s="117"/>
+      <c r="F78" s="117"/>
+      <c r="G78" s="117"/>
+      <c r="H78" s="117"/>
+      <c r="I78" s="117"/>
+      <c r="J78" s="117"/>
+      <c r="K78" s="120"/>
     </row>
     <row r="79" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B79" s="141"/>
-      <c r="C79" s="142"/>
-      <c r="D79" s="142"/>
-      <c r="E79" s="142"/>
-      <c r="F79" s="142"/>
-      <c r="G79" s="142"/>
-      <c r="H79" s="142"/>
-      <c r="I79" s="142"/>
-      <c r="J79" s="142"/>
-      <c r="K79" s="143"/>
+      <c r="B79" s="116"/>
+      <c r="C79" s="117"/>
+      <c r="D79" s="117"/>
+      <c r="E79" s="117"/>
+      <c r="F79" s="117"/>
+      <c r="G79" s="117"/>
+      <c r="H79" s="117"/>
+      <c r="I79" s="117"/>
+      <c r="J79" s="117"/>
+      <c r="K79" s="120"/>
     </row>
     <row r="80" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B80" s="141"/>
-      <c r="C80" s="142"/>
-      <c r="D80" s="142"/>
-      <c r="E80" s="142"/>
-      <c r="F80" s="142"/>
-      <c r="G80" s="142"/>
-      <c r="H80" s="142"/>
-      <c r="I80" s="142"/>
-      <c r="J80" s="142"/>
-      <c r="K80" s="143"/>
+      <c r="B80" s="116"/>
+      <c r="C80" s="117"/>
+      <c r="D80" s="117"/>
+      <c r="E80" s="117"/>
+      <c r="F80" s="117"/>
+      <c r="G80" s="117"/>
+      <c r="H80" s="117"/>
+      <c r="I80" s="117"/>
+      <c r="J80" s="117"/>
+      <c r="K80" s="120"/>
     </row>
     <row r="81" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B81" s="141"/>
-      <c r="C81" s="142"/>
-      <c r="D81" s="142"/>
-      <c r="E81" s="142"/>
-      <c r="F81" s="142"/>
-      <c r="G81" s="142"/>
-      <c r="H81" s="142"/>
-      <c r="I81" s="142"/>
-      <c r="J81" s="142"/>
-      <c r="K81" s="143"/>
+      <c r="B81" s="116"/>
+      <c r="C81" s="117"/>
+      <c r="D81" s="117"/>
+      <c r="E81" s="117"/>
+      <c r="F81" s="117"/>
+      <c r="G81" s="117"/>
+      <c r="H81" s="117"/>
+      <c r="I81" s="117"/>
+      <c r="J81" s="117"/>
+      <c r="K81" s="120"/>
     </row>
     <row r="82" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B82" s="141"/>
-      <c r="C82" s="142"/>
-      <c r="D82" s="142"/>
-      <c r="E82" s="142"/>
-      <c r="F82" s="142"/>
-      <c r="G82" s="142"/>
-      <c r="H82" s="142"/>
-      <c r="I82" s="142"/>
-      <c r="J82" s="142"/>
-      <c r="K82" s="143"/>
+      <c r="B82" s="116"/>
+      <c r="C82" s="117"/>
+      <c r="D82" s="117"/>
+      <c r="E82" s="117"/>
+      <c r="F82" s="117"/>
+      <c r="G82" s="117"/>
+      <c r="H82" s="117"/>
+      <c r="I82" s="117"/>
+      <c r="J82" s="117"/>
+      <c r="K82" s="120"/>
     </row>
     <row r="83" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B83" s="141"/>
-      <c r="C83" s="142"/>
-      <c r="D83" s="142"/>
-      <c r="E83" s="142"/>
-      <c r="F83" s="142"/>
-      <c r="G83" s="142"/>
-      <c r="H83" s="142"/>
-      <c r="I83" s="142"/>
-      <c r="J83" s="142"/>
-      <c r="K83" s="143"/>
+      <c r="B83" s="116"/>
+      <c r="C83" s="117"/>
+      <c r="D83" s="117"/>
+      <c r="E83" s="117"/>
+      <c r="F83" s="117"/>
+      <c r="G83" s="117"/>
+      <c r="H83" s="117"/>
+      <c r="I83" s="117"/>
+      <c r="J83" s="117"/>
+      <c r="K83" s="120"/>
     </row>
     <row r="84" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B84" s="141"/>
-      <c r="C84" s="142"/>
-      <c r="D84" s="142"/>
-      <c r="E84" s="142"/>
-      <c r="F84" s="142"/>
-      <c r="G84" s="142"/>
-      <c r="H84" s="142"/>
-      <c r="I84" s="142"/>
-      <c r="J84" s="142"/>
-      <c r="K84" s="143"/>
+      <c r="B84" s="116"/>
+      <c r="C84" s="117"/>
+      <c r="D84" s="117"/>
+      <c r="E84" s="117"/>
+      <c r="F84" s="117"/>
+      <c r="G84" s="117"/>
+      <c r="H84" s="117"/>
+      <c r="I84" s="117"/>
+      <c r="J84" s="117"/>
+      <c r="K84" s="120"/>
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B85" s="141"/>
-      <c r="C85" s="142"/>
-      <c r="D85" s="142"/>
-      <c r="E85" s="142"/>
-      <c r="F85" s="142"/>
-      <c r="G85" s="142"/>
-      <c r="H85" s="142"/>
-      <c r="I85" s="142"/>
-      <c r="J85" s="142"/>
-      <c r="K85" s="143"/>
+      <c r="B85" s="116"/>
+      <c r="C85" s="117"/>
+      <c r="D85" s="117"/>
+      <c r="E85" s="117"/>
+      <c r="F85" s="117"/>
+      <c r="G85" s="117"/>
+      <c r="H85" s="117"/>
+      <c r="I85" s="117"/>
+      <c r="J85" s="117"/>
+      <c r="K85" s="120"/>
     </row>
     <row r="86" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B86" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="C86" s="139">
+      <c r="C86" s="122">
         <v>43768</v>
       </c>
-      <c r="D86" s="140"/>
+      <c r="D86" s="123"/>
       <c r="E86" s="35" t="s">
         <v>1</v>
       </c>
@@ -13914,10 +13677,10 @@
       <c r="G86" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="H86" s="139">
+      <c r="H86" s="122">
         <v>43775</v>
       </c>
-      <c r="I86" s="140"/>
+      <c r="I86" s="123"/>
       <c r="J86" s="35" t="s">
         <v>1</v>
       </c>
@@ -13926,139 +13689,141 @@
       </c>
     </row>
     <row r="87" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B87" s="118" t="s">
+      <c r="B87" s="124" t="s">
         <v>59</v>
       </c>
-      <c r="C87" s="119"/>
-      <c r="D87" s="119"/>
-      <c r="E87" s="120"/>
-      <c r="F87" s="120"/>
-      <c r="G87" s="119" t="s">
+      <c r="C87" s="125"/>
+      <c r="D87" s="125"/>
+      <c r="E87" s="126"/>
+      <c r="F87" s="126"/>
+      <c r="G87" s="125" t="s">
         <v>59</v>
       </c>
-      <c r="H87" s="119"/>
-      <c r="I87" s="119"/>
-      <c r="J87" s="120"/>
-      <c r="K87" s="130"/>
+      <c r="H87" s="125"/>
+      <c r="I87" s="125"/>
+      <c r="J87" s="126"/>
+      <c r="K87" s="127"/>
     </row>
     <row r="88" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B88" s="141"/>
-      <c r="C88" s="142"/>
-      <c r="D88" s="142"/>
-      <c r="E88" s="142"/>
-      <c r="F88" s="142"/>
-      <c r="G88" s="142"/>
-      <c r="H88" s="142"/>
-      <c r="I88" s="142"/>
-      <c r="J88" s="142"/>
-      <c r="K88" s="143"/>
+      <c r="B88" s="116"/>
+      <c r="C88" s="117"/>
+      <c r="D88" s="117"/>
+      <c r="E88" s="117"/>
+      <c r="F88" s="117"/>
+      <c r="G88" s="117"/>
+      <c r="H88" s="117"/>
+      <c r="I88" s="117"/>
+      <c r="J88" s="117"/>
+      <c r="K88" s="120"/>
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B89" s="141"/>
-      <c r="C89" s="142"/>
-      <c r="D89" s="142"/>
-      <c r="E89" s="142"/>
-      <c r="F89" s="142"/>
-      <c r="G89" s="142"/>
-      <c r="H89" s="142"/>
-      <c r="I89" s="142"/>
-      <c r="J89" s="142"/>
-      <c r="K89" s="143"/>
+      <c r="B89" s="116"/>
+      <c r="C89" s="117"/>
+      <c r="D89" s="117"/>
+      <c r="E89" s="117"/>
+      <c r="F89" s="117"/>
+      <c r="G89" s="117"/>
+      <c r="H89" s="117"/>
+      <c r="I89" s="117"/>
+      <c r="J89" s="117"/>
+      <c r="K89" s="120"/>
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B90" s="141"/>
-      <c r="C90" s="142"/>
-      <c r="D90" s="142"/>
-      <c r="E90" s="142"/>
-      <c r="F90" s="142"/>
-      <c r="G90" s="142"/>
-      <c r="H90" s="142"/>
-      <c r="I90" s="142"/>
-      <c r="J90" s="142"/>
-      <c r="K90" s="143"/>
+      <c r="B90" s="116"/>
+      <c r="C90" s="117"/>
+      <c r="D90" s="117"/>
+      <c r="E90" s="117"/>
+      <c r="F90" s="117"/>
+      <c r="G90" s="117"/>
+      <c r="H90" s="117"/>
+      <c r="I90" s="117"/>
+      <c r="J90" s="117"/>
+      <c r="K90" s="120"/>
     </row>
     <row r="91" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B91" s="141"/>
-      <c r="C91" s="142"/>
-      <c r="D91" s="142"/>
-      <c r="E91" s="142"/>
-      <c r="F91" s="142"/>
-      <c r="G91" s="142"/>
-      <c r="H91" s="142"/>
-      <c r="I91" s="142"/>
-      <c r="J91" s="142"/>
-      <c r="K91" s="143"/>
+      <c r="B91" s="116"/>
+      <c r="C91" s="117"/>
+      <c r="D91" s="117"/>
+      <c r="E91" s="117"/>
+      <c r="F91" s="117"/>
+      <c r="G91" s="117"/>
+      <c r="H91" s="117"/>
+      <c r="I91" s="117"/>
+      <c r="J91" s="117"/>
+      <c r="K91" s="120"/>
     </row>
     <row r="92" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B92" s="141"/>
-      <c r="C92" s="142"/>
-      <c r="D92" s="142"/>
-      <c r="E92" s="142"/>
-      <c r="F92" s="142"/>
-      <c r="G92" s="142"/>
-      <c r="H92" s="142"/>
-      <c r="I92" s="142"/>
-      <c r="J92" s="142"/>
-      <c r="K92" s="143"/>
+      <c r="B92" s="116"/>
+      <c r="C92" s="117"/>
+      <c r="D92" s="117"/>
+      <c r="E92" s="117"/>
+      <c r="F92" s="117"/>
+      <c r="G92" s="117"/>
+      <c r="H92" s="117"/>
+      <c r="I92" s="117"/>
+      <c r="J92" s="117"/>
+      <c r="K92" s="120"/>
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B93" s="141"/>
-      <c r="C93" s="142"/>
-      <c r="D93" s="142"/>
-      <c r="E93" s="142"/>
-      <c r="F93" s="142"/>
-      <c r="G93" s="142"/>
-      <c r="H93" s="142"/>
-      <c r="I93" s="142"/>
-      <c r="J93" s="142"/>
-      <c r="K93" s="143"/>
+      <c r="B93" s="116"/>
+      <c r="C93" s="117"/>
+      <c r="D93" s="117"/>
+      <c r="E93" s="117"/>
+      <c r="F93" s="117"/>
+      <c r="G93" s="117"/>
+      <c r="H93" s="117"/>
+      <c r="I93" s="117"/>
+      <c r="J93" s="117"/>
+      <c r="K93" s="120"/>
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B94" s="141"/>
-      <c r="C94" s="142"/>
-      <c r="D94" s="142"/>
-      <c r="E94" s="142"/>
-      <c r="F94" s="142"/>
-      <c r="G94" s="142"/>
-      <c r="H94" s="142"/>
-      <c r="I94" s="142"/>
-      <c r="J94" s="142"/>
-      <c r="K94" s="143"/>
+      <c r="B94" s="116"/>
+      <c r="C94" s="117"/>
+      <c r="D94" s="117"/>
+      <c r="E94" s="117"/>
+      <c r="F94" s="117"/>
+      <c r="G94" s="117"/>
+      <c r="H94" s="117"/>
+      <c r="I94" s="117"/>
+      <c r="J94" s="117"/>
+      <c r="K94" s="120"/>
     </row>
     <row r="95" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B95" s="146"/>
-      <c r="C95" s="147"/>
-      <c r="D95" s="147"/>
-      <c r="E95" s="147"/>
-      <c r="F95" s="147"/>
-      <c r="G95" s="147"/>
-      <c r="H95" s="147"/>
-      <c r="I95" s="147"/>
-      <c r="J95" s="147"/>
-      <c r="K95" s="148"/>
+      <c r="B95" s="118"/>
+      <c r="C95" s="119"/>
+      <c r="D95" s="119"/>
+      <c r="E95" s="119"/>
+      <c r="F95" s="119"/>
+      <c r="G95" s="119"/>
+      <c r="H95" s="119"/>
+      <c r="I95" s="119"/>
+      <c r="J95" s="119"/>
+      <c r="K95" s="121"/>
     </row>
   </sheetData>
   <mergeCells count="56">
-    <mergeCell ref="B88:F95"/>
-    <mergeCell ref="G88:K95"/>
-    <mergeCell ref="B78:F85"/>
-    <mergeCell ref="G78:K85"/>
-    <mergeCell ref="C86:D86"/>
-    <mergeCell ref="H86:I86"/>
-    <mergeCell ref="B87:F87"/>
-    <mergeCell ref="G87:K87"/>
-    <mergeCell ref="B68:F75"/>
-    <mergeCell ref="G68:K75"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="H76:I76"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="G77:K77"/>
-    <mergeCell ref="B58:F65"/>
-    <mergeCell ref="G58:K65"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="H66:I66"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="G67:K67"/>
+    <mergeCell ref="B1:K3"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B7:F14"/>
+    <mergeCell ref="G6:K6"/>
+    <mergeCell ref="G7:K14"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="B4:K4"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="H56:I56"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="G47:K47"/>
+    <mergeCell ref="B27:F34"/>
+    <mergeCell ref="G27:K34"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="G36:K36"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="H35:I35"/>
     <mergeCell ref="B57:F57"/>
     <mergeCell ref="G57:K57"/>
     <mergeCell ref="B16:F16"/>
@@ -14073,28 +13838,26 @@
     <mergeCell ref="G48:K55"/>
     <mergeCell ref="B37:F44"/>
     <mergeCell ref="G37:K44"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="H56:I56"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="G47:K47"/>
-    <mergeCell ref="B27:F34"/>
-    <mergeCell ref="G27:K34"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="G36:K36"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="B1:K3"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B7:F14"/>
-    <mergeCell ref="G6:K6"/>
-    <mergeCell ref="G7:K14"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="B4:K4"/>
+    <mergeCell ref="B58:F65"/>
+    <mergeCell ref="G58:K65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="H66:I66"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="G67:K67"/>
+    <mergeCell ref="B68:F75"/>
+    <mergeCell ref="G68:K75"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="H76:I76"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="G77:K77"/>
+    <mergeCell ref="B88:F95"/>
+    <mergeCell ref="G88:K95"/>
+    <mergeCell ref="B78:F85"/>
+    <mergeCell ref="G78:K85"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="H86:I86"/>
+    <mergeCell ref="B87:F87"/>
+    <mergeCell ref="G87:K87"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -14115,7 +13878,7 @@
   <sheetData>
     <row r="1" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="149" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C1" s="149"/>
       <c r="D1" s="149"/>
@@ -14143,7 +13906,7 @@
     </row>
     <row r="3" spans="2:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="150" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C3" s="151"/>
       <c r="D3" s="151"/>
@@ -14171,51 +13934,51 @@
     </row>
     <row r="5" spans="2:13" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="154" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C5" s="155"/>
-      <c r="D5" s="159"/>
-      <c r="E5" s="159"/>
-      <c r="F5" s="159"/>
-      <c r="G5" s="159"/>
-      <c r="H5" s="159"/>
-      <c r="I5" s="159"/>
-      <c r="J5" s="142"/>
-      <c r="K5" s="142"/>
-      <c r="L5" s="142"/>
-      <c r="M5" s="142"/>
+      <c r="D5" s="148"/>
+      <c r="E5" s="148"/>
+      <c r="F5" s="148"/>
+      <c r="G5" s="148"/>
+      <c r="H5" s="148"/>
+      <c r="I5" s="148"/>
+      <c r="J5" s="117"/>
+      <c r="K5" s="117"/>
+      <c r="L5" s="117"/>
+      <c r="M5" s="117"/>
     </row>
     <row r="6" spans="2:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="156" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C6" s="157"/>
-      <c r="D6" s="159"/>
-      <c r="E6" s="159"/>
-      <c r="F6" s="159"/>
-      <c r="G6" s="159"/>
-      <c r="H6" s="159"/>
-      <c r="I6" s="159"/>
-      <c r="J6" s="142"/>
-      <c r="K6" s="142"/>
-      <c r="L6" s="142"/>
-      <c r="M6" s="142"/>
+      <c r="D6" s="148"/>
+      <c r="E6" s="148"/>
+      <c r="F6" s="148"/>
+      <c r="G6" s="148"/>
+      <c r="H6" s="148"/>
+      <c r="I6" s="148"/>
+      <c r="J6" s="117"/>
+      <c r="K6" s="117"/>
+      <c r="L6" s="117"/>
+      <c r="M6" s="117"/>
     </row>
     <row r="7" spans="2:13" s="62" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="152" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C7" s="153"/>
-      <c r="D7" s="159"/>
-      <c r="E7" s="159"/>
-      <c r="F7" s="159"/>
-      <c r="G7" s="159"/>
-      <c r="H7" s="159"/>
-      <c r="I7" s="159"/>
-      <c r="J7" s="142"/>
-      <c r="K7" s="142"/>
-      <c r="L7" s="142"/>
-      <c r="M7" s="142"/>
+      <c r="D7" s="148"/>
+      <c r="E7" s="148"/>
+      <c r="F7" s="148"/>
+      <c r="G7" s="148"/>
+      <c r="H7" s="148"/>
+      <c r="I7" s="148"/>
+      <c r="J7" s="117"/>
+      <c r="K7" s="117"/>
+      <c r="L7" s="117"/>
+      <c r="M7" s="117"/>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B8" s="2">
@@ -14887,6 +14650,14 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B1:L2"/>
+    <mergeCell ref="B3:L3"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B4:L4"/>
+    <mergeCell ref="K5:K7"/>
+    <mergeCell ref="L5:L7"/>
     <mergeCell ref="M5:M7"/>
     <mergeCell ref="E5:E7"/>
     <mergeCell ref="D5:D7"/>
@@ -14895,14 +14666,6 @@
     <mergeCell ref="H5:H7"/>
     <mergeCell ref="I5:I7"/>
     <mergeCell ref="J5:J7"/>
-    <mergeCell ref="B1:L2"/>
-    <mergeCell ref="B3:L3"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B4:L4"/>
-    <mergeCell ref="K5:K7"/>
-    <mergeCell ref="L5:L7"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="90" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -14916,569 +14679,602 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:12" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="160" t="s">
-        <v>76</v>
-      </c>
-      <c r="B2" s="160"/>
-      <c r="C2" s="160"/>
-      <c r="D2" s="160"/>
-      <c r="E2" s="160"/>
-      <c r="F2" s="160"/>
-      <c r="G2" s="160"/>
-      <c r="H2" s="160"/>
-      <c r="I2" s="160"/>
-      <c r="J2" s="160"/>
-      <c r="K2" s="160"/>
-      <c r="L2" s="160"/>
+      <c r="A2" s="161" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="161"/>
+      <c r="C2" s="161"/>
+      <c r="D2" s="161"/>
+      <c r="E2" s="161"/>
+      <c r="F2" s="161"/>
+      <c r="G2" s="161"/>
+      <c r="H2" s="161"/>
+      <c r="I2" s="161"/>
+      <c r="J2" s="161"/>
+      <c r="K2" s="161"/>
+      <c r="L2" s="161"/>
     </row>
     <row r="3" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="161" t="s">
+      <c r="A5" s="159" t="s">
+        <v>72</v>
+      </c>
+      <c r="B5" s="159"/>
+      <c r="C5" s="159"/>
+      <c r="D5" s="117" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="161"/>
-      <c r="C5" s="161"/>
-      <c r="D5" s="142" t="s">
+      <c r="E5" s="117"/>
+      <c r="F5" s="117"/>
+      <c r="G5" s="117"/>
+      <c r="H5" s="117"/>
+      <c r="I5" s="117"/>
+      <c r="J5" s="117"/>
+      <c r="K5" s="117"/>
+      <c r="L5" s="117"/>
+    </row>
+    <row r="6" spans="1:12" s="62" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="159"/>
+      <c r="B6" s="159"/>
+      <c r="C6" s="159"/>
+      <c r="D6" s="160" t="s">
         <v>74</v>
       </c>
-      <c r="E5" s="142"/>
-      <c r="F5" s="142"/>
-      <c r="G5" s="142"/>
-      <c r="H5" s="142"/>
-      <c r="I5" s="142"/>
-      <c r="J5" s="142"/>
-      <c r="K5" s="142"/>
-      <c r="L5" s="142"/>
-    </row>
-    <row r="6" spans="1:12" s="62" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="161"/>
-      <c r="B6" s="161"/>
-      <c r="C6" s="161"/>
-      <c r="D6" s="162" t="s">
-        <v>75</v>
-      </c>
-      <c r="E6" s="162"/>
-      <c r="F6" s="162"/>
-      <c r="G6" s="162"/>
-      <c r="H6" s="162"/>
-      <c r="I6" s="162"/>
-      <c r="J6" s="162"/>
-      <c r="K6" s="162"/>
-      <c r="L6" s="162"/>
+      <c r="E6" s="160"/>
+      <c r="F6" s="160"/>
+      <c r="G6" s="160"/>
+      <c r="H6" s="160"/>
+      <c r="I6" s="160"/>
+      <c r="J6" s="160"/>
+      <c r="K6" s="160"/>
+      <c r="L6" s="160"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="161" t="s">
+      <c r="A8" s="159" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" s="159"/>
+      <c r="C8" s="159"/>
+      <c r="D8" s="117" t="s">
         <v>73</v>
       </c>
-      <c r="B8" s="161"/>
-      <c r="C8" s="161"/>
-      <c r="D8" s="142" t="s">
+      <c r="E8" s="117"/>
+      <c r="F8" s="117"/>
+      <c r="G8" s="117"/>
+      <c r="H8" s="117"/>
+      <c r="I8" s="117"/>
+      <c r="J8" s="117"/>
+      <c r="K8" s="117"/>
+      <c r="L8" s="117"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="159"/>
+      <c r="B9" s="159"/>
+      <c r="C9" s="159"/>
+      <c r="D9" s="160" t="s">
         <v>74</v>
       </c>
-      <c r="E8" s="142"/>
-      <c r="F8" s="142"/>
-      <c r="G8" s="142"/>
-      <c r="H8" s="142"/>
-      <c r="I8" s="142"/>
-      <c r="J8" s="142"/>
-      <c r="K8" s="142"/>
-      <c r="L8" s="142"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="161"/>
-      <c r="B9" s="161"/>
-      <c r="C9" s="161"/>
-      <c r="D9" s="162" t="s">
-        <v>75</v>
-      </c>
-      <c r="E9" s="162"/>
-      <c r="F9" s="162"/>
-      <c r="G9" s="162"/>
-      <c r="H9" s="162"/>
-      <c r="I9" s="162"/>
-      <c r="J9" s="162"/>
-      <c r="K9" s="162"/>
-      <c r="L9" s="162"/>
+      <c r="E9" s="160"/>
+      <c r="F9" s="160"/>
+      <c r="G9" s="160"/>
+      <c r="H9" s="160"/>
+      <c r="I9" s="160"/>
+      <c r="J9" s="160"/>
+      <c r="K9" s="160"/>
+      <c r="L9" s="160"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="161" t="s">
+      <c r="A11" s="159" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" s="159"/>
+      <c r="C11" s="159"/>
+      <c r="D11" s="117" t="s">
         <v>73</v>
       </c>
-      <c r="B11" s="161"/>
-      <c r="C11" s="161"/>
-      <c r="D11" s="142" t="s">
+      <c r="E11" s="117"/>
+      <c r="F11" s="117"/>
+      <c r="G11" s="117"/>
+      <c r="H11" s="117"/>
+      <c r="I11" s="117"/>
+      <c r="J11" s="117"/>
+      <c r="K11" s="117"/>
+      <c r="L11" s="117"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="159"/>
+      <c r="B12" s="159"/>
+      <c r="C12" s="159"/>
+      <c r="D12" s="160" t="s">
         <v>74</v>
       </c>
-      <c r="E11" s="142"/>
-      <c r="F11" s="142"/>
-      <c r="G11" s="142"/>
-      <c r="H11" s="142"/>
-      <c r="I11" s="142"/>
-      <c r="J11" s="142"/>
-      <c r="K11" s="142"/>
-      <c r="L11" s="142"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="161"/>
-      <c r="B12" s="161"/>
-      <c r="C12" s="161"/>
-      <c r="D12" s="162" t="s">
-        <v>75</v>
-      </c>
-      <c r="E12" s="162"/>
-      <c r="F12" s="162"/>
-      <c r="G12" s="162"/>
-      <c r="H12" s="162"/>
-      <c r="I12" s="162"/>
-      <c r="J12" s="162"/>
-      <c r="K12" s="162"/>
-      <c r="L12" s="162"/>
+      <c r="E12" s="160"/>
+      <c r="F12" s="160"/>
+      <c r="G12" s="160"/>
+      <c r="H12" s="160"/>
+      <c r="I12" s="160"/>
+      <c r="J12" s="160"/>
+      <c r="K12" s="160"/>
+      <c r="L12" s="160"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="161" t="s">
+      <c r="A14" s="159" t="s">
+        <v>72</v>
+      </c>
+      <c r="B14" s="159"/>
+      <c r="C14" s="159"/>
+      <c r="D14" s="117" t="s">
         <v>73</v>
       </c>
-      <c r="B14" s="161"/>
-      <c r="C14" s="161"/>
-      <c r="D14" s="142" t="s">
+      <c r="E14" s="117"/>
+      <c r="F14" s="117"/>
+      <c r="G14" s="117"/>
+      <c r="H14" s="117"/>
+      <c r="I14" s="117"/>
+      <c r="J14" s="117"/>
+      <c r="K14" s="117"/>
+      <c r="L14" s="117"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="159"/>
+      <c r="B15" s="159"/>
+      <c r="C15" s="159"/>
+      <c r="D15" s="160" t="s">
         <v>74</v>
       </c>
-      <c r="E14" s="142"/>
-      <c r="F14" s="142"/>
-      <c r="G14" s="142"/>
-      <c r="H14" s="142"/>
-      <c r="I14" s="142"/>
-      <c r="J14" s="142"/>
-      <c r="K14" s="142"/>
-      <c r="L14" s="142"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="161"/>
-      <c r="B15" s="161"/>
-      <c r="C15" s="161"/>
-      <c r="D15" s="162" t="s">
-        <v>75</v>
-      </c>
-      <c r="E15" s="162"/>
-      <c r="F15" s="162"/>
-      <c r="G15" s="162"/>
-      <c r="H15" s="162"/>
-      <c r="I15" s="162"/>
-      <c r="J15" s="162"/>
-      <c r="K15" s="162"/>
-      <c r="L15" s="162"/>
+      <c r="E15" s="160"/>
+      <c r="F15" s="160"/>
+      <c r="G15" s="160"/>
+      <c r="H15" s="160"/>
+      <c r="I15" s="160"/>
+      <c r="J15" s="160"/>
+      <c r="K15" s="160"/>
+      <c r="L15" s="160"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="161" t="s">
+      <c r="A17" s="159" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" s="159"/>
+      <c r="C17" s="159"/>
+      <c r="D17" s="117" t="s">
         <v>73</v>
       </c>
-      <c r="B17" s="161"/>
-      <c r="C17" s="161"/>
-      <c r="D17" s="142" t="s">
+      <c r="E17" s="117"/>
+      <c r="F17" s="117"/>
+      <c r="G17" s="117"/>
+      <c r="H17" s="117"/>
+      <c r="I17" s="117"/>
+      <c r="J17" s="117"/>
+      <c r="K17" s="117"/>
+      <c r="L17" s="117"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="159"/>
+      <c r="B18" s="159"/>
+      <c r="C18" s="159"/>
+      <c r="D18" s="160" t="s">
         <v>74</v>
       </c>
-      <c r="E17" s="142"/>
-      <c r="F17" s="142"/>
-      <c r="G17" s="142"/>
-      <c r="H17" s="142"/>
-      <c r="I17" s="142"/>
-      <c r="J17" s="142"/>
-      <c r="K17" s="142"/>
-      <c r="L17" s="142"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="161"/>
-      <c r="B18" s="161"/>
-      <c r="C18" s="161"/>
-      <c r="D18" s="162" t="s">
-        <v>75</v>
-      </c>
-      <c r="E18" s="162"/>
-      <c r="F18" s="162"/>
-      <c r="G18" s="162"/>
-      <c r="H18" s="162"/>
-      <c r="I18" s="162"/>
-      <c r="J18" s="162"/>
-      <c r="K18" s="162"/>
-      <c r="L18" s="162"/>
+      <c r="E18" s="160"/>
+      <c r="F18" s="160"/>
+      <c r="G18" s="160"/>
+      <c r="H18" s="160"/>
+      <c r="I18" s="160"/>
+      <c r="J18" s="160"/>
+      <c r="K18" s="160"/>
+      <c r="L18" s="160"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="161" t="s">
+      <c r="A20" s="159" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" s="159"/>
+      <c r="C20" s="159"/>
+      <c r="D20" s="117" t="s">
         <v>73</v>
       </c>
-      <c r="B20" s="161"/>
-      <c r="C20" s="161"/>
-      <c r="D20" s="142" t="s">
+      <c r="E20" s="117"/>
+      <c r="F20" s="117"/>
+      <c r="G20" s="117"/>
+      <c r="H20" s="117"/>
+      <c r="I20" s="117"/>
+      <c r="J20" s="117"/>
+      <c r="K20" s="117"/>
+      <c r="L20" s="117"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="159"/>
+      <c r="B21" s="159"/>
+      <c r="C21" s="159"/>
+      <c r="D21" s="160" t="s">
         <v>74</v>
       </c>
-      <c r="E20" s="142"/>
-      <c r="F20" s="142"/>
-      <c r="G20" s="142"/>
-      <c r="H20" s="142"/>
-      <c r="I20" s="142"/>
-      <c r="J20" s="142"/>
-      <c r="K20" s="142"/>
-      <c r="L20" s="142"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="161"/>
-      <c r="B21" s="161"/>
-      <c r="C21" s="161"/>
-      <c r="D21" s="162" t="s">
-        <v>75</v>
-      </c>
-      <c r="E21" s="162"/>
-      <c r="F21" s="162"/>
-      <c r="G21" s="162"/>
-      <c r="H21" s="162"/>
-      <c r="I21" s="162"/>
-      <c r="J21" s="162"/>
-      <c r="K21" s="162"/>
-      <c r="L21" s="162"/>
+      <c r="E21" s="160"/>
+      <c r="F21" s="160"/>
+      <c r="G21" s="160"/>
+      <c r="H21" s="160"/>
+      <c r="I21" s="160"/>
+      <c r="J21" s="160"/>
+      <c r="K21" s="160"/>
+      <c r="L21" s="160"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="161" t="s">
+      <c r="A23" s="159" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" s="159"/>
+      <c r="C23" s="159"/>
+      <c r="D23" s="117" t="s">
         <v>73</v>
       </c>
-      <c r="B23" s="161"/>
-      <c r="C23" s="161"/>
-      <c r="D23" s="142" t="s">
+      <c r="E23" s="117"/>
+      <c r="F23" s="117"/>
+      <c r="G23" s="117"/>
+      <c r="H23" s="117"/>
+      <c r="I23" s="117"/>
+      <c r="J23" s="117"/>
+      <c r="K23" s="117"/>
+      <c r="L23" s="117"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="159"/>
+      <c r="B24" s="159"/>
+      <c r="C24" s="159"/>
+      <c r="D24" s="160" t="s">
         <v>74</v>
       </c>
-      <c r="E23" s="142"/>
-      <c r="F23" s="142"/>
-      <c r="G23" s="142"/>
-      <c r="H23" s="142"/>
-      <c r="I23" s="142"/>
-      <c r="J23" s="142"/>
-      <c r="K23" s="142"/>
-      <c r="L23" s="142"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="161"/>
-      <c r="B24" s="161"/>
-      <c r="C24" s="161"/>
-      <c r="D24" s="162" t="s">
-        <v>75</v>
-      </c>
-      <c r="E24" s="162"/>
-      <c r="F24" s="162"/>
-      <c r="G24" s="162"/>
-      <c r="H24" s="162"/>
-      <c r="I24" s="162"/>
-      <c r="J24" s="162"/>
-      <c r="K24" s="162"/>
-      <c r="L24" s="162"/>
+      <c r="E24" s="160"/>
+      <c r="F24" s="160"/>
+      <c r="G24" s="160"/>
+      <c r="H24" s="160"/>
+      <c r="I24" s="160"/>
+      <c r="J24" s="160"/>
+      <c r="K24" s="160"/>
+      <c r="L24" s="160"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="161" t="s">
+      <c r="A26" s="159" t="s">
+        <v>72</v>
+      </c>
+      <c r="B26" s="159"/>
+      <c r="C26" s="159"/>
+      <c r="D26" s="117" t="s">
         <v>73</v>
       </c>
-      <c r="B26" s="161"/>
-      <c r="C26" s="161"/>
-      <c r="D26" s="142" t="s">
+      <c r="E26" s="117"/>
+      <c r="F26" s="117"/>
+      <c r="G26" s="117"/>
+      <c r="H26" s="117"/>
+      <c r="I26" s="117"/>
+      <c r="J26" s="117"/>
+      <c r="K26" s="117"/>
+      <c r="L26" s="117"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="159"/>
+      <c r="B27" s="159"/>
+      <c r="C27" s="159"/>
+      <c r="D27" s="160" t="s">
         <v>74</v>
       </c>
-      <c r="E26" s="142"/>
-      <c r="F26" s="142"/>
-      <c r="G26" s="142"/>
-      <c r="H26" s="142"/>
-      <c r="I26" s="142"/>
-      <c r="J26" s="142"/>
-      <c r="K26" s="142"/>
-      <c r="L26" s="142"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="161"/>
-      <c r="B27" s="161"/>
-      <c r="C27" s="161"/>
-      <c r="D27" s="162" t="s">
-        <v>75</v>
-      </c>
-      <c r="E27" s="162"/>
-      <c r="F27" s="162"/>
-      <c r="G27" s="162"/>
-      <c r="H27" s="162"/>
-      <c r="I27" s="162"/>
-      <c r="J27" s="162"/>
-      <c r="K27" s="162"/>
-      <c r="L27" s="162"/>
+      <c r="E27" s="160"/>
+      <c r="F27" s="160"/>
+      <c r="G27" s="160"/>
+      <c r="H27" s="160"/>
+      <c r="I27" s="160"/>
+      <c r="J27" s="160"/>
+      <c r="K27" s="160"/>
+      <c r="L27" s="160"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="161" t="s">
+      <c r="A29" s="159" t="s">
+        <v>72</v>
+      </c>
+      <c r="B29" s="159"/>
+      <c r="C29" s="159"/>
+      <c r="D29" s="117" t="s">
         <v>73</v>
       </c>
-      <c r="B29" s="161"/>
-      <c r="C29" s="161"/>
-      <c r="D29" s="142" t="s">
+      <c r="E29" s="117"/>
+      <c r="F29" s="117"/>
+      <c r="G29" s="117"/>
+      <c r="H29" s="117"/>
+      <c r="I29" s="117"/>
+      <c r="J29" s="117"/>
+      <c r="K29" s="117"/>
+      <c r="L29" s="117"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="159"/>
+      <c r="B30" s="159"/>
+      <c r="C30" s="159"/>
+      <c r="D30" s="160" t="s">
         <v>74</v>
       </c>
-      <c r="E29" s="142"/>
-      <c r="F29" s="142"/>
-      <c r="G29" s="142"/>
-      <c r="H29" s="142"/>
-      <c r="I29" s="142"/>
-      <c r="J29" s="142"/>
-      <c r="K29" s="142"/>
-      <c r="L29" s="142"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="161"/>
-      <c r="B30" s="161"/>
-      <c r="C30" s="161"/>
-      <c r="D30" s="162" t="s">
-        <v>75</v>
-      </c>
-      <c r="E30" s="162"/>
-      <c r="F30" s="162"/>
-      <c r="G30" s="162"/>
-      <c r="H30" s="162"/>
-      <c r="I30" s="162"/>
-      <c r="J30" s="162"/>
-      <c r="K30" s="162"/>
-      <c r="L30" s="162"/>
+      <c r="E30" s="160"/>
+      <c r="F30" s="160"/>
+      <c r="G30" s="160"/>
+      <c r="H30" s="160"/>
+      <c r="I30" s="160"/>
+      <c r="J30" s="160"/>
+      <c r="K30" s="160"/>
+      <c r="L30" s="160"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="161" t="s">
+      <c r="A32" s="159" t="s">
+        <v>72</v>
+      </c>
+      <c r="B32" s="159"/>
+      <c r="C32" s="159"/>
+      <c r="D32" s="117" t="s">
         <v>73</v>
       </c>
-      <c r="B32" s="161"/>
-      <c r="C32" s="161"/>
-      <c r="D32" s="142" t="s">
+      <c r="E32" s="117"/>
+      <c r="F32" s="117"/>
+      <c r="G32" s="117"/>
+      <c r="H32" s="117"/>
+      <c r="I32" s="117"/>
+      <c r="J32" s="117"/>
+      <c r="K32" s="117"/>
+      <c r="L32" s="117"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="159"/>
+      <c r="B33" s="159"/>
+      <c r="C33" s="159"/>
+      <c r="D33" s="160" t="s">
         <v>74</v>
       </c>
-      <c r="E32" s="142"/>
-      <c r="F32" s="142"/>
-      <c r="G32" s="142"/>
-      <c r="H32" s="142"/>
-      <c r="I32" s="142"/>
-      <c r="J32" s="142"/>
-      <c r="K32" s="142"/>
-      <c r="L32" s="142"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="161"/>
-      <c r="B33" s="161"/>
-      <c r="C33" s="161"/>
-      <c r="D33" s="162" t="s">
-        <v>75</v>
-      </c>
-      <c r="E33" s="162"/>
-      <c r="F33" s="162"/>
-      <c r="G33" s="162"/>
-      <c r="H33" s="162"/>
-      <c r="I33" s="162"/>
-      <c r="J33" s="162"/>
-      <c r="K33" s="162"/>
-      <c r="L33" s="162"/>
+      <c r="E33" s="160"/>
+      <c r="F33" s="160"/>
+      <c r="G33" s="160"/>
+      <c r="H33" s="160"/>
+      <c r="I33" s="160"/>
+      <c r="J33" s="160"/>
+      <c r="K33" s="160"/>
+      <c r="L33" s="160"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="161" t="s">
+      <c r="A35" s="159" t="s">
+        <v>72</v>
+      </c>
+      <c r="B35" s="159"/>
+      <c r="C35" s="159"/>
+      <c r="D35" s="117" t="s">
         <v>73</v>
       </c>
-      <c r="B35" s="161"/>
-      <c r="C35" s="161"/>
-      <c r="D35" s="142" t="s">
+      <c r="E35" s="117"/>
+      <c r="F35" s="117"/>
+      <c r="G35" s="117"/>
+      <c r="H35" s="117"/>
+      <c r="I35" s="117"/>
+      <c r="J35" s="117"/>
+      <c r="K35" s="117"/>
+      <c r="L35" s="117"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" s="159"/>
+      <c r="B36" s="159"/>
+      <c r="C36" s="159"/>
+      <c r="D36" s="160" t="s">
         <v>74</v>
       </c>
-      <c r="E35" s="142"/>
-      <c r="F35" s="142"/>
-      <c r="G35" s="142"/>
-      <c r="H35" s="142"/>
-      <c r="I35" s="142"/>
-      <c r="J35" s="142"/>
-      <c r="K35" s="142"/>
-      <c r="L35" s="142"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="161"/>
-      <c r="B36" s="161"/>
-      <c r="C36" s="161"/>
-      <c r="D36" s="162" t="s">
-        <v>75</v>
-      </c>
-      <c r="E36" s="162"/>
-      <c r="F36" s="162"/>
-      <c r="G36" s="162"/>
-      <c r="H36" s="162"/>
-      <c r="I36" s="162"/>
-      <c r="J36" s="162"/>
-      <c r="K36" s="162"/>
-      <c r="L36" s="162"/>
+      <c r="E36" s="160"/>
+      <c r="F36" s="160"/>
+      <c r="G36" s="160"/>
+      <c r="H36" s="160"/>
+      <c r="I36" s="160"/>
+      <c r="J36" s="160"/>
+      <c r="K36" s="160"/>
+      <c r="L36" s="160"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" s="161" t="s">
+      <c r="A38" s="159" t="s">
+        <v>72</v>
+      </c>
+      <c r="B38" s="159"/>
+      <c r="C38" s="159"/>
+      <c r="D38" s="117" t="s">
         <v>73</v>
       </c>
-      <c r="B38" s="161"/>
-      <c r="C38" s="161"/>
-      <c r="D38" s="142" t="s">
+      <c r="E38" s="117"/>
+      <c r="F38" s="117"/>
+      <c r="G38" s="117"/>
+      <c r="H38" s="117"/>
+      <c r="I38" s="117"/>
+      <c r="J38" s="117"/>
+      <c r="K38" s="117"/>
+      <c r="L38" s="117"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" s="159"/>
+      <c r="B39" s="159"/>
+      <c r="C39" s="159"/>
+      <c r="D39" s="160" t="s">
         <v>74</v>
       </c>
-      <c r="E38" s="142"/>
-      <c r="F38" s="142"/>
-      <c r="G38" s="142"/>
-      <c r="H38" s="142"/>
-      <c r="I38" s="142"/>
-      <c r="J38" s="142"/>
-      <c r="K38" s="142"/>
-      <c r="L38" s="142"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="161"/>
-      <c r="B39" s="161"/>
-      <c r="C39" s="161"/>
-      <c r="D39" s="162" t="s">
-        <v>75</v>
-      </c>
-      <c r="E39" s="162"/>
-      <c r="F39" s="162"/>
-      <c r="G39" s="162"/>
-      <c r="H39" s="162"/>
-      <c r="I39" s="162"/>
-      <c r="J39" s="162"/>
-      <c r="K39" s="162"/>
-      <c r="L39" s="162"/>
+      <c r="E39" s="160"/>
+      <c r="F39" s="160"/>
+      <c r="G39" s="160"/>
+      <c r="H39" s="160"/>
+      <c r="I39" s="160"/>
+      <c r="J39" s="160"/>
+      <c r="K39" s="160"/>
+      <c r="L39" s="160"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41" s="161" t="s">
+      <c r="A41" s="159" t="s">
+        <v>72</v>
+      </c>
+      <c r="B41" s="159"/>
+      <c r="C41" s="159"/>
+      <c r="D41" s="117" t="s">
         <v>73</v>
       </c>
-      <c r="B41" s="161"/>
-      <c r="C41" s="161"/>
-      <c r="D41" s="142" t="s">
+      <c r="E41" s="117"/>
+      <c r="F41" s="117"/>
+      <c r="G41" s="117"/>
+      <c r="H41" s="117"/>
+      <c r="I41" s="117"/>
+      <c r="J41" s="117"/>
+      <c r="K41" s="117"/>
+      <c r="L41" s="117"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A42" s="159"/>
+      <c r="B42" s="159"/>
+      <c r="C42" s="159"/>
+      <c r="D42" s="160" t="s">
         <v>74</v>
       </c>
-      <c r="E41" s="142"/>
-      <c r="F41" s="142"/>
-      <c r="G41" s="142"/>
-      <c r="H41" s="142"/>
-      <c r="I41" s="142"/>
-      <c r="J41" s="142"/>
-      <c r="K41" s="142"/>
-      <c r="L41" s="142"/>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="161"/>
-      <c r="B42" s="161"/>
-      <c r="C42" s="161"/>
-      <c r="D42" s="162" t="s">
-        <v>75</v>
-      </c>
-      <c r="E42" s="162"/>
-      <c r="F42" s="162"/>
-      <c r="G42" s="162"/>
-      <c r="H42" s="162"/>
-      <c r="I42" s="162"/>
-      <c r="J42" s="162"/>
-      <c r="K42" s="162"/>
-      <c r="L42" s="162"/>
+      <c r="E42" s="160"/>
+      <c r="F42" s="160"/>
+      <c r="G42" s="160"/>
+      <c r="H42" s="160"/>
+      <c r="I42" s="160"/>
+      <c r="J42" s="160"/>
+      <c r="K42" s="160"/>
+      <c r="L42" s="160"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A44" s="161" t="s">
+      <c r="A44" s="159" t="s">
+        <v>72</v>
+      </c>
+      <c r="B44" s="159"/>
+      <c r="C44" s="159"/>
+      <c r="D44" s="117" t="s">
         <v>73</v>
       </c>
-      <c r="B44" s="161"/>
-      <c r="C44" s="161"/>
-      <c r="D44" s="142" t="s">
+      <c r="E44" s="117"/>
+      <c r="F44" s="117"/>
+      <c r="G44" s="117"/>
+      <c r="H44" s="117"/>
+      <c r="I44" s="117"/>
+      <c r="J44" s="117"/>
+      <c r="K44" s="117"/>
+      <c r="L44" s="117"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A45" s="159"/>
+      <c r="B45" s="159"/>
+      <c r="C45" s="159"/>
+      <c r="D45" s="160" t="s">
         <v>74</v>
       </c>
-      <c r="E44" s="142"/>
-      <c r="F44" s="142"/>
-      <c r="G44" s="142"/>
-      <c r="H44" s="142"/>
-      <c r="I44" s="142"/>
-      <c r="J44" s="142"/>
-      <c r="K44" s="142"/>
-      <c r="L44" s="142"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45" s="161"/>
-      <c r="B45" s="161"/>
-      <c r="C45" s="161"/>
-      <c r="D45" s="162" t="s">
-        <v>75</v>
-      </c>
-      <c r="E45" s="162"/>
-      <c r="F45" s="162"/>
-      <c r="G45" s="162"/>
-      <c r="H45" s="162"/>
-      <c r="I45" s="162"/>
-      <c r="J45" s="162"/>
-      <c r="K45" s="162"/>
-      <c r="L45" s="162"/>
+      <c r="E45" s="160"/>
+      <c r="F45" s="160"/>
+      <c r="G45" s="160"/>
+      <c r="H45" s="160"/>
+      <c r="I45" s="160"/>
+      <c r="J45" s="160"/>
+      <c r="K45" s="160"/>
+      <c r="L45" s="160"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="161" t="s">
+      <c r="A47" s="159" t="s">
+        <v>72</v>
+      </c>
+      <c r="B47" s="159"/>
+      <c r="C47" s="159"/>
+      <c r="D47" s="117" t="s">
         <v>73</v>
       </c>
-      <c r="B47" s="161"/>
-      <c r="C47" s="161"/>
-      <c r="D47" s="142" t="s">
+      <c r="E47" s="117"/>
+      <c r="F47" s="117"/>
+      <c r="G47" s="117"/>
+      <c r="H47" s="117"/>
+      <c r="I47" s="117"/>
+      <c r="J47" s="117"/>
+      <c r="K47" s="117"/>
+      <c r="L47" s="117"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A48" s="159"/>
+      <c r="B48" s="159"/>
+      <c r="C48" s="159"/>
+      <c r="D48" s="160" t="s">
         <v>74</v>
       </c>
-      <c r="E47" s="142"/>
-      <c r="F47" s="142"/>
-      <c r="G47" s="142"/>
-      <c r="H47" s="142"/>
-      <c r="I47" s="142"/>
-      <c r="J47" s="142"/>
-      <c r="K47" s="142"/>
-      <c r="L47" s="142"/>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48" s="161"/>
-      <c r="B48" s="161"/>
-      <c r="C48" s="161"/>
-      <c r="D48" s="162" t="s">
-        <v>75</v>
-      </c>
-      <c r="E48" s="162"/>
-      <c r="F48" s="162"/>
-      <c r="G48" s="162"/>
-      <c r="H48" s="162"/>
-      <c r="I48" s="162"/>
-      <c r="J48" s="162"/>
-      <c r="K48" s="162"/>
-      <c r="L48" s="162"/>
+      <c r="E48" s="160"/>
+      <c r="F48" s="160"/>
+      <c r="G48" s="160"/>
+      <c r="H48" s="160"/>
+      <c r="I48" s="160"/>
+      <c r="J48" s="160"/>
+      <c r="K48" s="160"/>
+      <c r="L48" s="160"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50" s="161" t="s">
+      <c r="A50" s="159" t="s">
+        <v>72</v>
+      </c>
+      <c r="B50" s="159"/>
+      <c r="C50" s="159"/>
+      <c r="D50" s="117" t="s">
         <v>73</v>
       </c>
-      <c r="B50" s="161"/>
-      <c r="C50" s="161"/>
-      <c r="D50" s="142" t="s">
+      <c r="E50" s="117"/>
+      <c r="F50" s="117"/>
+      <c r="G50" s="117"/>
+      <c r="H50" s="117"/>
+      <c r="I50" s="117"/>
+      <c r="J50" s="117"/>
+      <c r="K50" s="117"/>
+      <c r="L50" s="117"/>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51" s="159"/>
+      <c r="B51" s="159"/>
+      <c r="C51" s="159"/>
+      <c r="D51" s="160" t="s">
         <v>74</v>
       </c>
-      <c r="E50" s="142"/>
-      <c r="F50" s="142"/>
-      <c r="G50" s="142"/>
-      <c r="H50" s="142"/>
-      <c r="I50" s="142"/>
-      <c r="J50" s="142"/>
-      <c r="K50" s="142"/>
-      <c r="L50" s="142"/>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A51" s="161"/>
-      <c r="B51" s="161"/>
-      <c r="C51" s="161"/>
-      <c r="D51" s="162" t="s">
-        <v>75</v>
-      </c>
-      <c r="E51" s="162"/>
-      <c r="F51" s="162"/>
-      <c r="G51" s="162"/>
-      <c r="H51" s="162"/>
-      <c r="I51" s="162"/>
-      <c r="J51" s="162"/>
-      <c r="K51" s="162"/>
-      <c r="L51" s="162"/>
+      <c r="E51" s="160"/>
+      <c r="F51" s="160"/>
+      <c r="G51" s="160"/>
+      <c r="H51" s="160"/>
+      <c r="I51" s="160"/>
+      <c r="J51" s="160"/>
+      <c r="K51" s="160"/>
+      <c r="L51" s="160"/>
     </row>
   </sheetData>
   <mergeCells count="49">
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="D5:L5"/>
+    <mergeCell ref="D8:L8"/>
+    <mergeCell ref="D17:L17"/>
+    <mergeCell ref="D20:L20"/>
+    <mergeCell ref="A14:C15"/>
+    <mergeCell ref="D15:L15"/>
+    <mergeCell ref="A17:C18"/>
+    <mergeCell ref="D18:L18"/>
+    <mergeCell ref="D14:L14"/>
+    <mergeCell ref="D6:L6"/>
+    <mergeCell ref="A5:C6"/>
+    <mergeCell ref="A8:C9"/>
+    <mergeCell ref="D9:L9"/>
+    <mergeCell ref="A11:C12"/>
+    <mergeCell ref="D12:L12"/>
+    <mergeCell ref="D23:L23"/>
+    <mergeCell ref="D26:L26"/>
+    <mergeCell ref="A20:C21"/>
+    <mergeCell ref="D21:L21"/>
+    <mergeCell ref="A23:C24"/>
+    <mergeCell ref="D24:L24"/>
+    <mergeCell ref="D29:L29"/>
+    <mergeCell ref="D32:L32"/>
+    <mergeCell ref="A26:C27"/>
+    <mergeCell ref="D27:L27"/>
+    <mergeCell ref="A29:C30"/>
+    <mergeCell ref="D30:L30"/>
+    <mergeCell ref="D38:L38"/>
+    <mergeCell ref="A32:C33"/>
+    <mergeCell ref="D33:L33"/>
+    <mergeCell ref="A35:C36"/>
+    <mergeCell ref="D36:L36"/>
     <mergeCell ref="A50:C51"/>
     <mergeCell ref="D50:L50"/>
     <mergeCell ref="D51:L51"/>
@@ -15495,39 +15291,6 @@
     <mergeCell ref="A41:C42"/>
     <mergeCell ref="D42:L42"/>
     <mergeCell ref="D35:L35"/>
-    <mergeCell ref="D38:L38"/>
-    <mergeCell ref="A32:C33"/>
-    <mergeCell ref="D33:L33"/>
-    <mergeCell ref="A35:C36"/>
-    <mergeCell ref="D36:L36"/>
-    <mergeCell ref="D29:L29"/>
-    <mergeCell ref="D32:L32"/>
-    <mergeCell ref="A26:C27"/>
-    <mergeCell ref="D27:L27"/>
-    <mergeCell ref="A29:C30"/>
-    <mergeCell ref="D30:L30"/>
-    <mergeCell ref="D23:L23"/>
-    <mergeCell ref="D26:L26"/>
-    <mergeCell ref="A20:C21"/>
-    <mergeCell ref="D21:L21"/>
-    <mergeCell ref="A23:C24"/>
-    <mergeCell ref="D24:L24"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="D5:L5"/>
-    <mergeCell ref="D8:L8"/>
-    <mergeCell ref="D17:L17"/>
-    <mergeCell ref="D20:L20"/>
-    <mergeCell ref="A14:C15"/>
-    <mergeCell ref="D15:L15"/>
-    <mergeCell ref="A17:C18"/>
-    <mergeCell ref="D18:L18"/>
-    <mergeCell ref="D14:L14"/>
-    <mergeCell ref="D6:L6"/>
-    <mergeCell ref="A5:C6"/>
-    <mergeCell ref="A8:C9"/>
-    <mergeCell ref="D9:L9"/>
-    <mergeCell ref="A11:C12"/>
-    <mergeCell ref="D12:L12"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="90" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -15545,92 +15308,92 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="73" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="73" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="73" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/corretor/diario-template.xlsx
+++ b/corretor/diario-template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NEWPC GAMER\Desktop\Parque-Clube\correção provas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NEWPC GAMER\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B30F2E10-DD23-4382-9A32-4A5D421D68B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{732D7B35-8A2C-44EB-83C3-F55DEF1E258A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3135" yWindow="795" windowWidth="25665" windowHeight="15405" tabRatio="963" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="195" windowWidth="22335" windowHeight="15405" tabRatio="963" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="4º ano D - FREQUÊNCIA - 1º BIM" sheetId="14" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1432" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1453" uniqueCount="125">
   <si>
     <t>Quantidade de Aulas</t>
   </si>
@@ -284,6 +284,9 @@
     </r>
   </si>
   <si>
+    <t>2º BIMESTRE  26/04/2019 a 08/07/2019</t>
+  </si>
+  <si>
     <t>1º BIMESTRE 11/02/2019 a 25/04/2019</t>
   </si>
   <si>
@@ -472,6 +475,9 @@
   </si>
   <si>
     <t>1º BIMESTRE  12/02/2026  a 29/04/2025</t>
+  </si>
+  <si>
+    <t>ALYCE VICTÓRIA FERREIRA SANTO+B9:B27S</t>
   </si>
 </sst>
 </file>
@@ -1232,7 +1238,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="169">
+  <cellXfs count="164">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1397,6 +1403,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1460,41 +1467,11 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1511,41 +1488,50 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1555,30 +1541,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="38" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1607,6 +1569,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1619,8 +1584,47 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="38" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1652,27 +1656,20 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2260,278 +2257,278 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="80" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="79"/>
-      <c r="O1" s="79"/>
-      <c r="P1" s="79"/>
-      <c r="Q1" s="79"/>
-      <c r="R1" s="79"/>
-      <c r="S1" s="79"/>
-      <c r="T1" s="79"/>
-      <c r="U1" s="79"/>
-      <c r="V1" s="79"/>
-      <c r="W1" s="79"/>
-      <c r="X1" s="79"/>
-      <c r="Y1" s="79"/>
-      <c r="Z1" s="79"/>
-      <c r="AA1" s="79"/>
-      <c r="AB1" s="79"/>
-      <c r="AC1" s="79"/>
-      <c r="AD1" s="79"/>
-      <c r="AE1" s="79"/>
-      <c r="AF1" s="79"/>
-      <c r="AG1" s="79"/>
-      <c r="AH1" s="79"/>
-      <c r="AI1" s="79"/>
-      <c r="AJ1" s="79"/>
-      <c r="AK1" s="79"/>
-      <c r="AL1" s="79"/>
-      <c r="AM1" s="79"/>
-      <c r="AN1" s="79"/>
-      <c r="AO1" s="79"/>
-      <c r="AP1" s="79"/>
-      <c r="AQ1" s="79"/>
-      <c r="AR1" s="79"/>
-      <c r="AS1" s="79"/>
-      <c r="AT1" s="79"/>
-      <c r="AU1" s="79"/>
-      <c r="AV1" s="79"/>
-      <c r="AW1" s="79"/>
-      <c r="AX1" s="79"/>
-      <c r="AY1" s="79"/>
-      <c r="AZ1" s="79"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="80"/>
+      <c r="L1" s="80"/>
+      <c r="M1" s="80"/>
+      <c r="N1" s="80"/>
+      <c r="O1" s="80"/>
+      <c r="P1" s="80"/>
+      <c r="Q1" s="80"/>
+      <c r="R1" s="80"/>
+      <c r="S1" s="80"/>
+      <c r="T1" s="80"/>
+      <c r="U1" s="80"/>
+      <c r="V1" s="80"/>
+      <c r="W1" s="80"/>
+      <c r="X1" s="80"/>
+      <c r="Y1" s="80"/>
+      <c r="Z1" s="80"/>
+      <c r="AA1" s="80"/>
+      <c r="AB1" s="80"/>
+      <c r="AC1" s="80"/>
+      <c r="AD1" s="80"/>
+      <c r="AE1" s="80"/>
+      <c r="AF1" s="80"/>
+      <c r="AG1" s="80"/>
+      <c r="AH1" s="80"/>
+      <c r="AI1" s="80"/>
+      <c r="AJ1" s="80"/>
+      <c r="AK1" s="80"/>
+      <c r="AL1" s="80"/>
+      <c r="AM1" s="80"/>
+      <c r="AN1" s="80"/>
+      <c r="AO1" s="80"/>
+      <c r="AP1" s="80"/>
+      <c r="AQ1" s="80"/>
+      <c r="AR1" s="80"/>
+      <c r="AS1" s="80"/>
+      <c r="AT1" s="80"/>
+      <c r="AU1" s="80"/>
+      <c r="AV1" s="80"/>
+      <c r="AW1" s="80"/>
+      <c r="AX1" s="80"/>
+      <c r="AY1" s="80"/>
+      <c r="AZ1" s="80"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
-      <c r="M2" s="79"/>
-      <c r="N2" s="79"/>
-      <c r="O2" s="79"/>
-      <c r="P2" s="79"/>
-      <c r="Q2" s="79"/>
-      <c r="R2" s="79"/>
-      <c r="S2" s="79"/>
-      <c r="T2" s="79"/>
-      <c r="U2" s="79"/>
-      <c r="V2" s="79"/>
-      <c r="W2" s="79"/>
-      <c r="X2" s="79"/>
-      <c r="Y2" s="79"/>
-      <c r="Z2" s="79"/>
-      <c r="AA2" s="79"/>
-      <c r="AB2" s="79"/>
-      <c r="AC2" s="79"/>
-      <c r="AD2" s="79"/>
-      <c r="AE2" s="79"/>
-      <c r="AF2" s="79"/>
-      <c r="AG2" s="79"/>
-      <c r="AH2" s="79"/>
-      <c r="AI2" s="79"/>
-      <c r="AJ2" s="79"/>
-      <c r="AK2" s="79"/>
-      <c r="AL2" s="79"/>
-      <c r="AM2" s="79"/>
-      <c r="AN2" s="79"/>
-      <c r="AO2" s="79"/>
-      <c r="AP2" s="79"/>
-      <c r="AQ2" s="79"/>
-      <c r="AR2" s="79"/>
-      <c r="AS2" s="79"/>
-      <c r="AT2" s="79"/>
-      <c r="AU2" s="79"/>
-      <c r="AV2" s="79"/>
-      <c r="AW2" s="79"/>
-      <c r="AX2" s="79"/>
-      <c r="AY2" s="79"/>
-      <c r="AZ2" s="79"/>
+      <c r="A2" s="80"/>
+      <c r="B2" s="80"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="80"/>
+      <c r="K2" s="80"/>
+      <c r="L2" s="80"/>
+      <c r="M2" s="80"/>
+      <c r="N2" s="80"/>
+      <c r="O2" s="80"/>
+      <c r="P2" s="80"/>
+      <c r="Q2" s="80"/>
+      <c r="R2" s="80"/>
+      <c r="S2" s="80"/>
+      <c r="T2" s="80"/>
+      <c r="U2" s="80"/>
+      <c r="V2" s="80"/>
+      <c r="W2" s="80"/>
+      <c r="X2" s="80"/>
+      <c r="Y2" s="80"/>
+      <c r="Z2" s="80"/>
+      <c r="AA2" s="80"/>
+      <c r="AB2" s="80"/>
+      <c r="AC2" s="80"/>
+      <c r="AD2" s="80"/>
+      <c r="AE2" s="80"/>
+      <c r="AF2" s="80"/>
+      <c r="AG2" s="80"/>
+      <c r="AH2" s="80"/>
+      <c r="AI2" s="80"/>
+      <c r="AJ2" s="80"/>
+      <c r="AK2" s="80"/>
+      <c r="AL2" s="80"/>
+      <c r="AM2" s="80"/>
+      <c r="AN2" s="80"/>
+      <c r="AO2" s="80"/>
+      <c r="AP2" s="80"/>
+      <c r="AQ2" s="80"/>
+      <c r="AR2" s="80"/>
+      <c r="AS2" s="80"/>
+      <c r="AT2" s="80"/>
+      <c r="AU2" s="80"/>
+      <c r="AV2" s="80"/>
+      <c r="AW2" s="80"/>
+      <c r="AX2" s="80"/>
+      <c r="AY2" s="80"/>
+      <c r="AZ2" s="80"/>
     </row>
     <row r="3" spans="1:54" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="79"/>
-      <c r="B3" s="79"/>
-      <c r="C3" s="79"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="79"/>
-      <c r="J3" s="79"/>
-      <c r="K3" s="79"/>
-      <c r="L3" s="79"/>
-      <c r="M3" s="79"/>
-      <c r="N3" s="79"/>
-      <c r="O3" s="79"/>
-      <c r="P3" s="79"/>
-      <c r="Q3" s="79"/>
-      <c r="R3" s="79"/>
-      <c r="S3" s="79"/>
-      <c r="T3" s="79"/>
-      <c r="U3" s="79"/>
-      <c r="V3" s="79"/>
-      <c r="W3" s="79"/>
-      <c r="X3" s="79"/>
-      <c r="Y3" s="79"/>
-      <c r="Z3" s="79"/>
-      <c r="AA3" s="79"/>
-      <c r="AB3" s="79"/>
-      <c r="AC3" s="79"/>
-      <c r="AD3" s="79"/>
-      <c r="AE3" s="79"/>
-      <c r="AF3" s="79"/>
-      <c r="AG3" s="79"/>
-      <c r="AH3" s="79"/>
-      <c r="AI3" s="79"/>
-      <c r="AJ3" s="79"/>
-      <c r="AK3" s="79"/>
-      <c r="AL3" s="79"/>
-      <c r="AM3" s="79"/>
-      <c r="AN3" s="79"/>
-      <c r="AO3" s="79"/>
-      <c r="AP3" s="79"/>
-      <c r="AQ3" s="79"/>
-      <c r="AR3" s="79"/>
-      <c r="AS3" s="79"/>
-      <c r="AT3" s="79"/>
-      <c r="AU3" s="79"/>
-      <c r="AV3" s="79"/>
-      <c r="AW3" s="79"/>
-      <c r="AX3" s="79"/>
-      <c r="AY3" s="79"/>
-      <c r="AZ3" s="79"/>
+      <c r="A3" s="80"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="80"/>
+      <c r="K3" s="80"/>
+      <c r="L3" s="80"/>
+      <c r="M3" s="80"/>
+      <c r="N3" s="80"/>
+      <c r="O3" s="80"/>
+      <c r="P3" s="80"/>
+      <c r="Q3" s="80"/>
+      <c r="R3" s="80"/>
+      <c r="S3" s="80"/>
+      <c r="T3" s="80"/>
+      <c r="U3" s="80"/>
+      <c r="V3" s="80"/>
+      <c r="W3" s="80"/>
+      <c r="X3" s="80"/>
+      <c r="Y3" s="80"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
+      <c r="AB3" s="80"/>
+      <c r="AC3" s="80"/>
+      <c r="AD3" s="80"/>
+      <c r="AE3" s="80"/>
+      <c r="AF3" s="80"/>
+      <c r="AG3" s="80"/>
+      <c r="AH3" s="80"/>
+      <c r="AI3" s="80"/>
+      <c r="AJ3" s="80"/>
+      <c r="AK3" s="80"/>
+      <c r="AL3" s="80"/>
+      <c r="AM3" s="80"/>
+      <c r="AN3" s="80"/>
+      <c r="AO3" s="80"/>
+      <c r="AP3" s="80"/>
+      <c r="AQ3" s="80"/>
+      <c r="AR3" s="80"/>
+      <c r="AS3" s="80"/>
+      <c r="AT3" s="80"/>
+      <c r="AU3" s="80"/>
+      <c r="AV3" s="80"/>
+      <c r="AW3" s="80"/>
+      <c r="AX3" s="80"/>
+      <c r="AY3" s="80"/>
+      <c r="AZ3" s="80"/>
     </row>
     <row r="4" spans="1:54" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="79"/>
-      <c r="B4" s="79"/>
-      <c r="C4" s="79"/>
-      <c r="D4" s="79"/>
-      <c r="E4" s="79"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="79"/>
-      <c r="H4" s="79"/>
-      <c r="I4" s="79"/>
-      <c r="J4" s="79"/>
-      <c r="K4" s="79"/>
-      <c r="L4" s="79"/>
-      <c r="M4" s="79"/>
-      <c r="N4" s="79"/>
-      <c r="O4" s="79"/>
-      <c r="P4" s="79"/>
-      <c r="Q4" s="79"/>
-      <c r="R4" s="79"/>
-      <c r="S4" s="79"/>
-      <c r="T4" s="79"/>
-      <c r="U4" s="79"/>
-      <c r="V4" s="79"/>
-      <c r="W4" s="79"/>
-      <c r="X4" s="79"/>
-      <c r="Y4" s="79"/>
-      <c r="Z4" s="79"/>
-      <c r="AA4" s="79"/>
-      <c r="AB4" s="79"/>
-      <c r="AC4" s="79"/>
-      <c r="AD4" s="79"/>
-      <c r="AE4" s="79"/>
-      <c r="AF4" s="79"/>
-      <c r="AG4" s="79"/>
-      <c r="AH4" s="79"/>
-      <c r="AI4" s="79"/>
-      <c r="AJ4" s="79"/>
-      <c r="AK4" s="79"/>
-      <c r="AL4" s="79"/>
-      <c r="AM4" s="79"/>
-      <c r="AN4" s="79"/>
-      <c r="AO4" s="79"/>
-      <c r="AP4" s="79"/>
-      <c r="AQ4" s="79"/>
-      <c r="AR4" s="79"/>
-      <c r="AS4" s="79"/>
-      <c r="AT4" s="79"/>
-      <c r="AU4" s="79"/>
-      <c r="AV4" s="79"/>
-      <c r="AW4" s="79"/>
-      <c r="AX4" s="79"/>
-      <c r="AY4" s="79"/>
-      <c r="AZ4" s="79"/>
+      <c r="A4" s="80"/>
+      <c r="B4" s="80"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="80"/>
+      <c r="I4" s="80"/>
+      <c r="J4" s="80"/>
+      <c r="K4" s="80"/>
+      <c r="L4" s="80"/>
+      <c r="M4" s="80"/>
+      <c r="N4" s="80"/>
+      <c r="O4" s="80"/>
+      <c r="P4" s="80"/>
+      <c r="Q4" s="80"/>
+      <c r="R4" s="80"/>
+      <c r="S4" s="80"/>
+      <c r="T4" s="80"/>
+      <c r="U4" s="80"/>
+      <c r="V4" s="80"/>
+      <c r="W4" s="80"/>
+      <c r="X4" s="80"/>
+      <c r="Y4" s="80"/>
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="80"/>
+      <c r="AB4" s="80"/>
+      <c r="AC4" s="80"/>
+      <c r="AD4" s="80"/>
+      <c r="AE4" s="80"/>
+      <c r="AF4" s="80"/>
+      <c r="AG4" s="80"/>
+      <c r="AH4" s="80"/>
+      <c r="AI4" s="80"/>
+      <c r="AJ4" s="80"/>
+      <c r="AK4" s="80"/>
+      <c r="AL4" s="80"/>
+      <c r="AM4" s="80"/>
+      <c r="AN4" s="80"/>
+      <c r="AO4" s="80"/>
+      <c r="AP4" s="80"/>
+      <c r="AQ4" s="80"/>
+      <c r="AR4" s="80"/>
+      <c r="AS4" s="80"/>
+      <c r="AT4" s="80"/>
+      <c r="AU4" s="80"/>
+      <c r="AV4" s="80"/>
+      <c r="AW4" s="80"/>
+      <c r="AX4" s="80"/>
+      <c r="AY4" s="80"/>
+      <c r="AZ4" s="80"/>
     </row>
     <row r="5" spans="1:54" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="80" t="s">
-        <v>98</v>
-      </c>
-      <c r="B5" s="80"/>
-      <c r="C5" s="80"/>
-      <c r="D5" s="80"/>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="80"/>
-      <c r="K5" s="80"/>
-      <c r="L5" s="80"/>
-      <c r="M5" s="80"/>
-      <c r="N5" s="80"/>
-      <c r="O5" s="80"/>
-      <c r="P5" s="80"/>
-      <c r="Q5" s="80"/>
-      <c r="R5" s="80"/>
-      <c r="S5" s="80"/>
-      <c r="T5" s="80"/>
-      <c r="U5" s="80"/>
-      <c r="V5" s="80"/>
-      <c r="W5" s="80"/>
-      <c r="X5" s="80"/>
-      <c r="Y5" s="80"/>
-      <c r="Z5" s="80"/>
-      <c r="AA5" s="80"/>
-      <c r="AB5" s="80"/>
-      <c r="AC5" s="80"/>
-      <c r="AD5" s="80"/>
-      <c r="AE5" s="80"/>
-      <c r="AF5" s="80"/>
-      <c r="AG5" s="80"/>
-      <c r="AH5" s="80"/>
-      <c r="AI5" s="80"/>
-      <c r="AJ5" s="80"/>
-      <c r="AK5" s="80"/>
-      <c r="AL5" s="80"/>
-      <c r="AM5" s="80"/>
-      <c r="AN5" s="80"/>
-      <c r="AO5" s="80"/>
-      <c r="AP5" s="80"/>
-      <c r="AQ5" s="80"/>
-      <c r="AR5" s="80"/>
-      <c r="AS5" s="80"/>
-      <c r="AT5" s="80"/>
-      <c r="AU5" s="80"/>
-      <c r="AV5" s="80"/>
-      <c r="AW5" s="80"/>
-      <c r="AX5" s="80"/>
-      <c r="AY5" s="80"/>
-      <c r="AZ5" s="80"/>
+      <c r="A5" s="81" t="s">
+        <v>99</v>
+      </c>
+      <c r="B5" s="81"/>
+      <c r="C5" s="81"/>
+      <c r="D5" s="81"/>
+      <c r="E5" s="81"/>
+      <c r="F5" s="81"/>
+      <c r="G5" s="81"/>
+      <c r="H5" s="81"/>
+      <c r="I5" s="81"/>
+      <c r="J5" s="81"/>
+      <c r="K5" s="81"/>
+      <c r="L5" s="81"/>
+      <c r="M5" s="81"/>
+      <c r="N5" s="81"/>
+      <c r="O5" s="81"/>
+      <c r="P5" s="81"/>
+      <c r="Q5" s="81"/>
+      <c r="R5" s="81"/>
+      <c r="S5" s="81"/>
+      <c r="T5" s="81"/>
+      <c r="U5" s="81"/>
+      <c r="V5" s="81"/>
+      <c r="W5" s="81"/>
+      <c r="X5" s="81"/>
+      <c r="Y5" s="81"/>
+      <c r="Z5" s="81"/>
+      <c r="AA5" s="81"/>
+      <c r="AB5" s="81"/>
+      <c r="AC5" s="81"/>
+      <c r="AD5" s="81"/>
+      <c r="AE5" s="81"/>
+      <c r="AF5" s="81"/>
+      <c r="AG5" s="81"/>
+      <c r="AH5" s="81"/>
+      <c r="AI5" s="81"/>
+      <c r="AJ5" s="81"/>
+      <c r="AK5" s="81"/>
+      <c r="AL5" s="81"/>
+      <c r="AM5" s="81"/>
+      <c r="AN5" s="81"/>
+      <c r="AO5" s="81"/>
+      <c r="AP5" s="81"/>
+      <c r="AQ5" s="81"/>
+      <c r="AR5" s="81"/>
+      <c r="AS5" s="81"/>
+      <c r="AT5" s="81"/>
+      <c r="AU5" s="81"/>
+      <c r="AV5" s="81"/>
+      <c r="AW5" s="81"/>
+      <c r="AX5" s="81"/>
+      <c r="AY5" s="81"/>
+      <c r="AZ5" s="81"/>
     </row>
     <row r="6" spans="1:54" s="3" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
@@ -2539,115 +2536,215 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="4"/>
-      <c r="D6" s="81"/>
-      <c r="E6" s="81"/>
-      <c r="F6" s="81"/>
-      <c r="G6" s="81"/>
-      <c r="H6" s="81"/>
-      <c r="I6" s="81"/>
-      <c r="J6" s="81"/>
-      <c r="K6" s="81"/>
-      <c r="L6" s="81"/>
-      <c r="M6" s="81"/>
-      <c r="N6" s="81"/>
-      <c r="O6" s="81"/>
-      <c r="P6" s="81"/>
-      <c r="Q6" s="82" t="s">
+      <c r="D6" s="82"/>
+      <c r="E6" s="82"/>
+      <c r="F6" s="82"/>
+      <c r="G6" s="82"/>
+      <c r="H6" s="82"/>
+      <c r="I6" s="82"/>
+      <c r="J6" s="82"/>
+      <c r="K6" s="82"/>
+      <c r="L6" s="82"/>
+      <c r="M6" s="82"/>
+      <c r="N6" s="82"/>
+      <c r="O6" s="82"/>
+      <c r="P6" s="82"/>
+      <c r="Q6" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="82"/>
-      <c r="S6" s="82"/>
-      <c r="T6" s="82"/>
-      <c r="U6" s="82"/>
-      <c r="V6" s="82"/>
-      <c r="W6" s="82"/>
-      <c r="X6" s="82"/>
-      <c r="Y6" s="82"/>
-      <c r="Z6" s="82"/>
-      <c r="AA6" s="82"/>
-      <c r="AB6" s="82"/>
-      <c r="AC6" s="82"/>
-      <c r="AD6" s="81">
+      <c r="R6" s="83"/>
+      <c r="S6" s="83"/>
+      <c r="T6" s="83"/>
+      <c r="U6" s="83"/>
+      <c r="V6" s="83"/>
+      <c r="W6" s="83"/>
+      <c r="X6" s="83"/>
+      <c r="Y6" s="83"/>
+      <c r="Z6" s="83"/>
+      <c r="AA6" s="83"/>
+      <c r="AB6" s="83"/>
+      <c r="AC6" s="83"/>
+      <c r="AD6" s="82">
         <v>50</v>
       </c>
-      <c r="AE6" s="81"/>
+      <c r="AE6" s="82"/>
       <c r="AF6" s="5"/>
-      <c r="AG6" s="81" t="s">
+      <c r="AG6" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="AH6" s="81"/>
-      <c r="AI6" s="81"/>
-      <c r="AJ6" s="81"/>
-      <c r="AK6" s="81"/>
-      <c r="AL6" s="81"/>
-      <c r="AM6" s="81"/>
-      <c r="AN6" s="81"/>
-      <c r="AO6" s="81"/>
-      <c r="AP6" s="81"/>
-      <c r="AQ6" s="81"/>
-      <c r="AR6" s="81"/>
-      <c r="AS6" s="81"/>
+      <c r="AH6" s="82"/>
+      <c r="AI6" s="82"/>
+      <c r="AJ6" s="82"/>
+      <c r="AK6" s="82"/>
+      <c r="AL6" s="82"/>
+      <c r="AM6" s="82"/>
+      <c r="AN6" s="82"/>
+      <c r="AO6" s="82"/>
+      <c r="AP6" s="82"/>
+      <c r="AQ6" s="82"/>
+      <c r="AR6" s="82"/>
+      <c r="AS6" s="82"/>
       <c r="AT6" s="4"/>
       <c r="AU6" s="4"/>
       <c r="AV6" s="4"/>
     </row>
     <row r="7" spans="1:54" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="50"/>
-      <c r="B7" s="74" t="s">
-        <v>122</v>
-      </c>
-      <c r="C7" s="75"/>
-      <c r="D7" s="75"/>
-      <c r="E7" s="75"/>
-      <c r="F7" s="75"/>
-      <c r="G7" s="75"/>
-      <c r="H7" s="75"/>
-      <c r="I7" s="75"/>
-      <c r="J7" s="75"/>
-      <c r="K7" s="75"/>
-      <c r="L7" s="75"/>
-      <c r="M7" s="75"/>
-      <c r="N7" s="75"/>
-      <c r="O7" s="75"/>
-      <c r="P7" s="75"/>
-      <c r="Q7" s="75"/>
-      <c r="R7" s="75"/>
-      <c r="S7" s="75"/>
-      <c r="T7" s="75"/>
-      <c r="U7" s="75"/>
-      <c r="V7" s="75"/>
-      <c r="W7" s="75"/>
-      <c r="X7" s="75"/>
-      <c r="Y7" s="75"/>
-      <c r="Z7" s="75"/>
-      <c r="AA7" s="75"/>
-      <c r="AB7" s="75"/>
-      <c r="AC7" s="75"/>
-      <c r="AD7" s="75"/>
-      <c r="AE7" s="75"/>
-      <c r="AF7" s="75"/>
-      <c r="AG7" s="75"/>
-      <c r="AH7" s="75"/>
-      <c r="AI7" s="75"/>
-      <c r="AJ7" s="75"/>
-      <c r="AK7" s="75"/>
-      <c r="AL7" s="75"/>
-      <c r="AM7" s="75"/>
-      <c r="AN7" s="75"/>
-      <c r="AO7" s="75"/>
-      <c r="AP7" s="75"/>
-      <c r="AQ7" s="75"/>
-      <c r="AR7" s="75"/>
-      <c r="AS7" s="75"/>
-      <c r="AT7" s="75"/>
-      <c r="AU7" s="75"/>
-      <c r="AV7" s="75"/>
-      <c r="AW7" s="75"/>
-      <c r="AX7" s="75"/>
-      <c r="AY7" s="75"/>
-      <c r="AZ7" s="75"/>
-      <c r="BA7" s="76"/>
-      <c r="BB7" s="77" t="s">
+      <c r="B7" s="75" t="s">
+        <v>123</v>
+      </c>
+      <c r="C7" s="76">
+        <v>45698</v>
+      </c>
+      <c r="D7" s="76">
+        <v>45699</v>
+      </c>
+      <c r="E7" s="76">
+        <v>45700</v>
+      </c>
+      <c r="F7" s="76">
+        <v>45701</v>
+      </c>
+      <c r="G7" s="76">
+        <v>45702</v>
+      </c>
+      <c r="H7" s="76">
+        <v>45705</v>
+      </c>
+      <c r="I7" s="76">
+        <v>45706</v>
+      </c>
+      <c r="J7" s="76">
+        <v>45707</v>
+      </c>
+      <c r="K7" s="76">
+        <v>45708</v>
+      </c>
+      <c r="L7" s="76">
+        <v>45709</v>
+      </c>
+      <c r="M7" s="76">
+        <v>45712</v>
+      </c>
+      <c r="N7" s="76">
+        <v>45713</v>
+      </c>
+      <c r="O7" s="76">
+        <v>45714</v>
+      </c>
+      <c r="P7" s="76">
+        <v>45715</v>
+      </c>
+      <c r="Q7" s="76">
+        <v>45716</v>
+      </c>
+      <c r="R7" s="76">
+        <v>45722</v>
+      </c>
+      <c r="S7" s="76">
+        <v>45723</v>
+      </c>
+      <c r="T7" s="76">
+        <v>45726</v>
+      </c>
+      <c r="U7" s="76">
+        <v>45727</v>
+      </c>
+      <c r="V7" s="76">
+        <v>45728</v>
+      </c>
+      <c r="W7" s="76">
+        <v>45729</v>
+      </c>
+      <c r="X7" s="76">
+        <v>45730</v>
+      </c>
+      <c r="Y7" s="76">
+        <v>45733</v>
+      </c>
+      <c r="Z7" s="76">
+        <v>45734</v>
+      </c>
+      <c r="AA7" s="76">
+        <v>45735</v>
+      </c>
+      <c r="AB7" s="76">
+        <v>45736</v>
+      </c>
+      <c r="AC7" s="76">
+        <v>45737</v>
+      </c>
+      <c r="AD7" s="76">
+        <v>45740</v>
+      </c>
+      <c r="AE7" s="76">
+        <v>45741</v>
+      </c>
+      <c r="AF7" s="76">
+        <v>45742</v>
+      </c>
+      <c r="AG7" s="76">
+        <v>45743</v>
+      </c>
+      <c r="AH7" s="76">
+        <v>45744</v>
+      </c>
+      <c r="AI7" s="76">
+        <v>45747</v>
+      </c>
+      <c r="AJ7" s="76">
+        <v>45748</v>
+      </c>
+      <c r="AK7" s="76">
+        <v>45749</v>
+      </c>
+      <c r="AL7" s="76">
+        <v>45750</v>
+      </c>
+      <c r="AM7" s="76">
+        <v>45751</v>
+      </c>
+      <c r="AN7" s="76">
+        <v>45754</v>
+      </c>
+      <c r="AO7" s="76">
+        <v>45755</v>
+      </c>
+      <c r="AP7" s="76">
+        <v>45756</v>
+      </c>
+      <c r="AQ7" s="76">
+        <v>45757</v>
+      </c>
+      <c r="AR7" s="76">
+        <v>45758</v>
+      </c>
+      <c r="AS7" s="76">
+        <v>45761</v>
+      </c>
+      <c r="AT7" s="76">
+        <v>45762</v>
+      </c>
+      <c r="AU7" s="76">
+        <v>45763</v>
+      </c>
+      <c r="AV7" s="76">
+        <v>45764</v>
+      </c>
+      <c r="AW7" s="76">
+        <v>45769</v>
+      </c>
+      <c r="AX7" s="76">
+        <v>45770</v>
+      </c>
+      <c r="AY7" s="76">
+        <v>45771</v>
+      </c>
+      <c r="AZ7" s="76">
+        <v>45772</v>
+      </c>
+      <c r="BA7" s="77"/>
+      <c r="BB7" s="78" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2811,13 +2908,15 @@
       <c r="BA8" s="1">
         <v>51</v>
       </c>
-      <c r="BB8" s="78"/>
+      <c r="BB8" s="79"/>
     </row>
     <row r="9" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A9" s="54">
         <v>1</v>
       </c>
-      <c r="B9" s="163"/>
+      <c r="B9" s="56" t="s">
+        <v>124</v>
+      </c>
       <c r="C9" s="49" t="s">
         <v>30</v>
       </c>
@@ -2977,7 +3076,7 @@
       <c r="A10" s="52">
         <v>2</v>
       </c>
-      <c r="B10" s="163"/>
+      <c r="B10" s="56"/>
       <c r="C10" s="49" t="s">
         <v>30</v>
       </c>
@@ -3137,7 +3236,7 @@
       <c r="A11" s="52">
         <v>3</v>
       </c>
-      <c r="B11" s="163"/>
+      <c r="B11" s="56"/>
       <c r="C11" s="49" t="s">
         <v>30</v>
       </c>
@@ -3297,7 +3396,7 @@
       <c r="A12" s="52">
         <v>4</v>
       </c>
-      <c r="B12" s="163"/>
+      <c r="B12" s="74"/>
       <c r="C12" s="49" t="s">
         <v>30</v>
       </c>
@@ -3457,7 +3556,7 @@
       <c r="A13" s="52">
         <v>5</v>
       </c>
-      <c r="B13" s="163"/>
+      <c r="B13" s="56"/>
       <c r="C13" s="49" t="s">
         <v>30</v>
       </c>
@@ -3617,7 +3716,7 @@
       <c r="A14" s="52">
         <v>6</v>
       </c>
-      <c r="B14" s="163"/>
+      <c r="B14" s="56"/>
       <c r="C14" s="49" t="s">
         <v>30</v>
       </c>
@@ -3777,7 +3876,7 @@
       <c r="A15" s="52">
         <v>7</v>
       </c>
-      <c r="B15" s="163"/>
+      <c r="B15" s="56"/>
       <c r="C15" s="49" t="s">
         <v>30</v>
       </c>
@@ -3937,7 +4036,7 @@
       <c r="A16" s="52">
         <v>8</v>
       </c>
-      <c r="B16" s="163"/>
+      <c r="B16" s="56"/>
       <c r="C16" s="49" t="s">
         <v>30</v>
       </c>
@@ -4097,7 +4196,7 @@
       <c r="A17" s="52">
         <v>9</v>
       </c>
-      <c r="B17" s="163"/>
+      <c r="B17" s="56"/>
       <c r="C17" s="49" t="s">
         <v>30</v>
       </c>
@@ -4257,7 +4356,7 @@
       <c r="A18" s="52">
         <v>10</v>
       </c>
-      <c r="B18" s="163"/>
+      <c r="B18" s="56"/>
       <c r="C18" s="49" t="s">
         <v>30</v>
       </c>
@@ -4417,7 +4516,7 @@
       <c r="A19" s="52">
         <v>11</v>
       </c>
-      <c r="B19" s="163"/>
+      <c r="B19" s="56"/>
       <c r="C19" s="49" t="s">
         <v>30</v>
       </c>
@@ -4577,7 +4676,7 @@
       <c r="A20" s="52">
         <v>12</v>
       </c>
-      <c r="B20" s="163"/>
+      <c r="B20" s="56"/>
       <c r="C20" s="49" t="s">
         <v>30</v>
       </c>
@@ -4737,7 +4836,7 @@
       <c r="A21" s="52">
         <v>13</v>
       </c>
-      <c r="B21" s="163"/>
+      <c r="B21" s="74"/>
       <c r="C21" s="49" t="s">
         <v>30</v>
       </c>
@@ -4897,7 +4996,7 @@
       <c r="A22" s="52">
         <v>14</v>
       </c>
-      <c r="B22" s="163"/>
+      <c r="B22" s="56"/>
       <c r="C22" s="49" t="s">
         <v>30</v>
       </c>
@@ -5057,7 +5156,7 @@
       <c r="A23" s="52">
         <v>15</v>
       </c>
-      <c r="B23" s="163"/>
+      <c r="B23" s="56"/>
       <c r="C23" s="49" t="s">
         <v>30</v>
       </c>
@@ -5217,7 +5316,7 @@
       <c r="A24" s="52">
         <v>16</v>
       </c>
-      <c r="B24" s="163"/>
+      <c r="B24" s="56"/>
       <c r="C24" s="49" t="s">
         <v>30</v>
       </c>
@@ -5377,7 +5476,7 @@
       <c r="A25" s="52">
         <v>17</v>
       </c>
-      <c r="B25" s="163"/>
+      <c r="B25" s="56"/>
       <c r="C25" s="49" t="s">
         <v>30</v>
       </c>
@@ -5537,7 +5636,7 @@
       <c r="A26" s="52">
         <v>18</v>
       </c>
-      <c r="B26" s="163"/>
+      <c r="B26" s="74"/>
       <c r="C26" s="49" t="s">
         <v>30</v>
       </c>
@@ -5697,7 +5796,7 @@
       <c r="A27" s="52">
         <v>19</v>
       </c>
-      <c r="B27" s="164"/>
+      <c r="B27" s="55"/>
       <c r="C27" s="49" t="s">
         <v>30</v>
       </c>
@@ -5857,7 +5956,7 @@
       <c r="A28" s="52">
         <v>20</v>
       </c>
-      <c r="B28" s="165"/>
+      <c r="B28" s="19"/>
       <c r="C28" s="49" t="s">
         <v>30</v>
       </c>
@@ -6013,70 +6112,172 @@
       </c>
       <c r="BB28" s="56"/>
     </row>
-    <row r="29" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="166"/>
-    </row>
-    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="1:54" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A30" s="50"/>
-      <c r="B30" s="167"/>
-      <c r="C30" s="75"/>
-      <c r="D30" s="75"/>
-      <c r="E30" s="75"/>
-      <c r="F30" s="75"/>
-      <c r="G30" s="75"/>
-      <c r="H30" s="75"/>
-      <c r="I30" s="75"/>
-      <c r="J30" s="75"/>
-      <c r="K30" s="75"/>
-      <c r="L30" s="75"/>
-      <c r="M30" s="75"/>
-      <c r="N30" s="75"/>
-      <c r="O30" s="75"/>
-      <c r="P30" s="75"/>
-      <c r="Q30" s="75"/>
-      <c r="R30" s="75"/>
-      <c r="S30" s="75"/>
-      <c r="T30" s="75"/>
-      <c r="U30" s="75"/>
-      <c r="V30" s="75"/>
-      <c r="W30" s="75"/>
-      <c r="X30" s="75"/>
-      <c r="Y30" s="75"/>
-      <c r="Z30" s="75"/>
-      <c r="AA30" s="75"/>
-      <c r="AB30" s="75"/>
-      <c r="AC30" s="75"/>
-      <c r="AD30" s="75"/>
-      <c r="AE30" s="75"/>
-      <c r="AF30" s="75"/>
-      <c r="AG30" s="75"/>
-      <c r="AH30" s="75"/>
-      <c r="AI30" s="75"/>
-      <c r="AJ30" s="75"/>
-      <c r="AK30" s="75"/>
-      <c r="AL30" s="75"/>
-      <c r="AM30" s="75"/>
-      <c r="AN30" s="75"/>
-      <c r="AO30" s="75"/>
-      <c r="AP30" s="75"/>
-      <c r="AQ30" s="75"/>
-      <c r="AR30" s="75"/>
-      <c r="AS30" s="75"/>
-      <c r="AT30" s="75"/>
-      <c r="AU30" s="75"/>
-      <c r="AV30" s="75"/>
-      <c r="AW30" s="75"/>
-      <c r="AX30" s="75"/>
-      <c r="AY30" s="75"/>
-      <c r="AZ30" s="75"/>
-      <c r="BA30" s="76"/>
-      <c r="BB30" s="77"/>
+      <c r="B30" s="75" t="s">
+        <v>65</v>
+      </c>
+      <c r="C30" s="76">
+        <v>45698</v>
+      </c>
+      <c r="D30" s="76">
+        <v>45699</v>
+      </c>
+      <c r="E30" s="76">
+        <v>45700</v>
+      </c>
+      <c r="F30" s="76">
+        <v>45701</v>
+      </c>
+      <c r="G30" s="76">
+        <v>45702</v>
+      </c>
+      <c r="H30" s="76">
+        <v>45705</v>
+      </c>
+      <c r="I30" s="76">
+        <v>45706</v>
+      </c>
+      <c r="J30" s="76">
+        <v>45707</v>
+      </c>
+      <c r="K30" s="76">
+        <v>45708</v>
+      </c>
+      <c r="L30" s="76">
+        <v>45709</v>
+      </c>
+      <c r="M30" s="76">
+        <v>45712</v>
+      </c>
+      <c r="N30" s="76">
+        <v>45713</v>
+      </c>
+      <c r="O30" s="76">
+        <v>45714</v>
+      </c>
+      <c r="P30" s="76">
+        <v>45715</v>
+      </c>
+      <c r="Q30" s="76">
+        <v>45716</v>
+      </c>
+      <c r="R30" s="76">
+        <v>45722</v>
+      </c>
+      <c r="S30" s="76">
+        <v>45723</v>
+      </c>
+      <c r="T30" s="76">
+        <v>45726</v>
+      </c>
+      <c r="U30" s="76">
+        <v>45727</v>
+      </c>
+      <c r="V30" s="76">
+        <v>45728</v>
+      </c>
+      <c r="W30" s="76">
+        <v>45729</v>
+      </c>
+      <c r="X30" s="76">
+        <v>45730</v>
+      </c>
+      <c r="Y30" s="76">
+        <v>45733</v>
+      </c>
+      <c r="Z30" s="76">
+        <v>45734</v>
+      </c>
+      <c r="AA30" s="76">
+        <v>45735</v>
+      </c>
+      <c r="AB30" s="76">
+        <v>45736</v>
+      </c>
+      <c r="AC30" s="76">
+        <v>45737</v>
+      </c>
+      <c r="AD30" s="76">
+        <v>45740</v>
+      </c>
+      <c r="AE30" s="76">
+        <v>45741</v>
+      </c>
+      <c r="AF30" s="76">
+        <v>45742</v>
+      </c>
+      <c r="AG30" s="76">
+        <v>45743</v>
+      </c>
+      <c r="AH30" s="76">
+        <v>45744</v>
+      </c>
+      <c r="AI30" s="76">
+        <v>45747</v>
+      </c>
+      <c r="AJ30" s="76">
+        <v>45748</v>
+      </c>
+      <c r="AK30" s="76">
+        <v>45749</v>
+      </c>
+      <c r="AL30" s="76">
+        <v>45750</v>
+      </c>
+      <c r="AM30" s="76">
+        <v>45751</v>
+      </c>
+      <c r="AN30" s="76">
+        <v>45754</v>
+      </c>
+      <c r="AO30" s="76">
+        <v>45755</v>
+      </c>
+      <c r="AP30" s="76">
+        <v>45756</v>
+      </c>
+      <c r="AQ30" s="76">
+        <v>45757</v>
+      </c>
+      <c r="AR30" s="76">
+        <v>45758</v>
+      </c>
+      <c r="AS30" s="76">
+        <v>45761</v>
+      </c>
+      <c r="AT30" s="76">
+        <v>45762</v>
+      </c>
+      <c r="AU30" s="76">
+        <v>45763</v>
+      </c>
+      <c r="AV30" s="76">
+        <v>45764</v>
+      </c>
+      <c r="AW30" s="76">
+        <v>45769</v>
+      </c>
+      <c r="AX30" s="76">
+        <v>45770</v>
+      </c>
+      <c r="AY30" s="76">
+        <v>45771</v>
+      </c>
+      <c r="AZ30" s="76">
+        <v>45772</v>
+      </c>
+      <c r="BA30" s="77"/>
+      <c r="BB30" s="78"/>
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A31" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="B31" s="168"/>
+      <c r="B31" s="53" t="s">
+        <v>0</v>
+      </c>
       <c r="C31" s="48">
         <v>1</v>
       </c>
@@ -6230,13 +6431,15 @@
       <c r="BA31" s="1">
         <v>51</v>
       </c>
-      <c r="BB31" s="78"/>
+      <c r="BB31" s="79"/>
     </row>
     <row r="32" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A32" s="54">
         <v>1</v>
       </c>
-      <c r="B32" s="163"/>
+      <c r="B32" s="56" t="s">
+        <v>84</v>
+      </c>
       <c r="C32" s="49"/>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
@@ -6294,7 +6497,9 @@
       <c r="A33" s="52">
         <v>2</v>
       </c>
-      <c r="B33" s="163"/>
+      <c r="B33" s="56" t="s">
+        <v>96</v>
+      </c>
       <c r="C33" s="49"/>
       <c r="D33" s="6"/>
       <c r="E33" s="6"/>
@@ -6352,7 +6557,9 @@
       <c r="A34" s="52">
         <v>3</v>
       </c>
-      <c r="B34" s="163"/>
+      <c r="B34" s="56" t="s">
+        <v>85</v>
+      </c>
       <c r="C34" s="49"/>
       <c r="D34" s="6"/>
       <c r="E34" s="6"/>
@@ -6410,7 +6617,9 @@
       <c r="A35" s="52">
         <v>4</v>
       </c>
-      <c r="B35" s="163"/>
+      <c r="B35" s="74" t="s">
+        <v>83</v>
+      </c>
       <c r="C35" s="49"/>
       <c r="D35" s="6"/>
       <c r="E35" s="6"/>
@@ -6468,7 +6677,9 @@
       <c r="A36" s="52">
         <v>5</v>
       </c>
-      <c r="B36" s="163"/>
+      <c r="B36" s="56" t="s">
+        <v>86</v>
+      </c>
       <c r="C36" s="49"/>
       <c r="D36" s="6"/>
       <c r="E36" s="6"/>
@@ -6526,7 +6737,9 @@
       <c r="A37" s="52">
         <v>6</v>
       </c>
-      <c r="B37" s="163"/>
+      <c r="B37" s="56" t="s">
+        <v>87</v>
+      </c>
       <c r="C37" s="49"/>
       <c r="D37" s="6"/>
       <c r="E37" s="6"/>
@@ -6584,7 +6797,9 @@
       <c r="A38" s="52">
         <v>7</v>
       </c>
-      <c r="B38" s="163"/>
+      <c r="B38" s="56" t="s">
+        <v>88</v>
+      </c>
       <c r="C38" s="49"/>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
@@ -6642,7 +6857,9 @@
       <c r="A39" s="52">
         <v>8</v>
       </c>
-      <c r="B39" s="163"/>
+      <c r="B39" s="56" t="s">
+        <v>97</v>
+      </c>
       <c r="C39" s="49"/>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
@@ -6700,7 +6917,9 @@
       <c r="A40" s="52">
         <v>9</v>
       </c>
-      <c r="B40" s="163"/>
+      <c r="B40" s="56" t="s">
+        <v>89</v>
+      </c>
       <c r="C40" s="49"/>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
@@ -6758,7 +6977,9 @@
       <c r="A41" s="52">
         <v>10</v>
       </c>
-      <c r="B41" s="163"/>
+      <c r="B41" s="56" t="s">
+        <v>90</v>
+      </c>
       <c r="C41" s="49"/>
       <c r="D41" s="6"/>
       <c r="E41" s="6"/>
@@ -6816,7 +7037,9 @@
       <c r="A42" s="52">
         <v>11</v>
       </c>
-      <c r="B42" s="163"/>
+      <c r="B42" s="56" t="s">
+        <v>91</v>
+      </c>
       <c r="C42" s="49"/>
       <c r="D42" s="6"/>
       <c r="E42" s="6"/>
@@ -6874,7 +7097,9 @@
       <c r="A43" s="52">
         <v>12</v>
       </c>
-      <c r="B43" s="163"/>
+      <c r="B43" s="56" t="s">
+        <v>92</v>
+      </c>
       <c r="C43" s="49"/>
       <c r="D43" s="6"/>
       <c r="E43" s="6"/>
@@ -6932,7 +7157,9 @@
       <c r="A44" s="52">
         <v>13</v>
       </c>
-      <c r="B44" s="163"/>
+      <c r="B44" s="74" t="s">
+        <v>81</v>
+      </c>
       <c r="C44" s="49"/>
       <c r="D44" s="6"/>
       <c r="E44" s="6"/>
@@ -6990,7 +7217,9 @@
       <c r="A45" s="52">
         <v>14</v>
       </c>
-      <c r="B45" s="163"/>
+      <c r="B45" s="56" t="s">
+        <v>93</v>
+      </c>
       <c r="C45" s="49"/>
       <c r="D45" s="6"/>
       <c r="E45" s="6"/>
@@ -7048,7 +7277,9 @@
       <c r="A46" s="52">
         <v>15</v>
       </c>
-      <c r="B46" s="163"/>
+      <c r="B46" s="56" t="s">
+        <v>98</v>
+      </c>
       <c r="C46" s="49"/>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
@@ -7106,7 +7337,9 @@
       <c r="A47" s="52">
         <v>16</v>
       </c>
-      <c r="B47" s="163"/>
+      <c r="B47" s="56" t="s">
+        <v>94</v>
+      </c>
       <c r="C47" s="49"/>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
@@ -7164,7 +7397,9 @@
       <c r="A48" s="52">
         <v>17</v>
       </c>
-      <c r="B48" s="163"/>
+      <c r="B48" s="56" t="s">
+        <v>95</v>
+      </c>
       <c r="C48" s="49"/>
       <c r="D48" s="6"/>
       <c r="E48" s="6"/>
@@ -7222,7 +7457,9 @@
       <c r="A49" s="52">
         <v>18</v>
       </c>
-      <c r="B49" s="163"/>
+      <c r="B49" s="74" t="s">
+        <v>82</v>
+      </c>
       <c r="C49" s="49"/>
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
@@ -7311,10 +7548,10 @@
   <sheetData>
     <row r="2" spans="1:3" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C2" s="17"/>
     </row>
@@ -7323,7 +7560,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C3" s="17">
         <v>1</v>
@@ -7334,7 +7571,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C4" s="17"/>
     </row>
@@ -7343,7 +7580,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C5" s="17"/>
     </row>
@@ -7352,7 +7589,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C6" s="17"/>
     </row>
@@ -7361,7 +7598,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C7" s="17"/>
     </row>
@@ -7370,7 +7607,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C8" s="17"/>
     </row>
@@ -7379,7 +7616,7 @@
         <v>11</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C9" s="17"/>
     </row>
@@ -7388,7 +7625,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C10" s="17"/>
     </row>
@@ -7397,7 +7634,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C11" s="17"/>
     </row>
@@ -7406,7 +7643,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C12" s="17"/>
     </row>
@@ -7415,7 +7652,7 @@
         <v>5</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C13" s="17"/>
     </row>
@@ -7424,7 +7661,7 @@
         <v>1</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C14" s="17"/>
     </row>
@@ -7433,7 +7670,7 @@
         <v>2</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C15" s="17"/>
     </row>
@@ -7442,7 +7679,7 @@
         <v>2</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C16" s="17"/>
     </row>
@@ -7451,7 +7688,7 @@
         <v>2</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C17" s="17"/>
     </row>
@@ -7460,7 +7697,7 @@
         <v>2</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C18" s="17"/>
     </row>
@@ -7469,7 +7706,7 @@
         <v>2</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C19" s="17"/>
     </row>
@@ -7478,7 +7715,7 @@
         <v>1</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C20" s="17"/>
     </row>
@@ -7487,7 +7724,7 @@
         <v>1</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C21" s="17"/>
     </row>
@@ -7496,7 +7733,7 @@
         <v>1</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C22" s="17"/>
     </row>
@@ -7507,14 +7744,14 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="17"/>
-      <c r="B24" s="162" t="s">
-        <v>119</v>
+      <c r="B24" s="163" t="s">
+        <v>120</v>
       </c>
       <c r="C24" s="17"/>
     </row>
     <row r="25" spans="1:3" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="17"/>
-      <c r="B25" s="162"/>
+      <c r="B25" s="163"/>
       <c r="C25" s="17"/>
     </row>
   </sheetData>
@@ -7541,278 +7778,278 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:53" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="80" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="79"/>
-      <c r="O1" s="79"/>
-      <c r="P1" s="79"/>
-      <c r="Q1" s="79"/>
-      <c r="R1" s="79"/>
-      <c r="S1" s="79"/>
-      <c r="T1" s="79"/>
-      <c r="U1" s="79"/>
-      <c r="V1" s="79"/>
-      <c r="W1" s="79"/>
-      <c r="X1" s="79"/>
-      <c r="Y1" s="79"/>
-      <c r="Z1" s="79"/>
-      <c r="AA1" s="79"/>
-      <c r="AB1" s="79"/>
-      <c r="AC1" s="79"/>
-      <c r="AD1" s="79"/>
-      <c r="AE1" s="79"/>
-      <c r="AF1" s="79"/>
-      <c r="AG1" s="79"/>
-      <c r="AH1" s="79"/>
-      <c r="AI1" s="79"/>
-      <c r="AJ1" s="79"/>
-      <c r="AK1" s="79"/>
-      <c r="AL1" s="79"/>
-      <c r="AM1" s="79"/>
-      <c r="AN1" s="79"/>
-      <c r="AO1" s="79"/>
-      <c r="AP1" s="79"/>
-      <c r="AQ1" s="79"/>
-      <c r="AR1" s="79"/>
-      <c r="AS1" s="79"/>
-      <c r="AT1" s="79"/>
-      <c r="AU1" s="79"/>
-      <c r="AV1" s="79"/>
-      <c r="AW1" s="79"/>
-      <c r="AX1" s="79"/>
-      <c r="AY1" s="79"/>
-      <c r="AZ1" s="79"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="80"/>
+      <c r="L1" s="80"/>
+      <c r="M1" s="80"/>
+      <c r="N1" s="80"/>
+      <c r="O1" s="80"/>
+      <c r="P1" s="80"/>
+      <c r="Q1" s="80"/>
+      <c r="R1" s="80"/>
+      <c r="S1" s="80"/>
+      <c r="T1" s="80"/>
+      <c r="U1" s="80"/>
+      <c r="V1" s="80"/>
+      <c r="W1" s="80"/>
+      <c r="X1" s="80"/>
+      <c r="Y1" s="80"/>
+      <c r="Z1" s="80"/>
+      <c r="AA1" s="80"/>
+      <c r="AB1" s="80"/>
+      <c r="AC1" s="80"/>
+      <c r="AD1" s="80"/>
+      <c r="AE1" s="80"/>
+      <c r="AF1" s="80"/>
+      <c r="AG1" s="80"/>
+      <c r="AH1" s="80"/>
+      <c r="AI1" s="80"/>
+      <c r="AJ1" s="80"/>
+      <c r="AK1" s="80"/>
+      <c r="AL1" s="80"/>
+      <c r="AM1" s="80"/>
+      <c r="AN1" s="80"/>
+      <c r="AO1" s="80"/>
+      <c r="AP1" s="80"/>
+      <c r="AQ1" s="80"/>
+      <c r="AR1" s="80"/>
+      <c r="AS1" s="80"/>
+      <c r="AT1" s="80"/>
+      <c r="AU1" s="80"/>
+      <c r="AV1" s="80"/>
+      <c r="AW1" s="80"/>
+      <c r="AX1" s="80"/>
+      <c r="AY1" s="80"/>
+      <c r="AZ1" s="80"/>
     </row>
     <row r="2" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
-      <c r="M2" s="79"/>
-      <c r="N2" s="79"/>
-      <c r="O2" s="79"/>
-      <c r="P2" s="79"/>
-      <c r="Q2" s="79"/>
-      <c r="R2" s="79"/>
-      <c r="S2" s="79"/>
-      <c r="T2" s="79"/>
-      <c r="U2" s="79"/>
-      <c r="V2" s="79"/>
-      <c r="W2" s="79"/>
-      <c r="X2" s="79"/>
-      <c r="Y2" s="79"/>
-      <c r="Z2" s="79"/>
-      <c r="AA2" s="79"/>
-      <c r="AB2" s="79"/>
-      <c r="AC2" s="79"/>
-      <c r="AD2" s="79"/>
-      <c r="AE2" s="79"/>
-      <c r="AF2" s="79"/>
-      <c r="AG2" s="79"/>
-      <c r="AH2" s="79"/>
-      <c r="AI2" s="79"/>
-      <c r="AJ2" s="79"/>
-      <c r="AK2" s="79"/>
-      <c r="AL2" s="79"/>
-      <c r="AM2" s="79"/>
-      <c r="AN2" s="79"/>
-      <c r="AO2" s="79"/>
-      <c r="AP2" s="79"/>
-      <c r="AQ2" s="79"/>
-      <c r="AR2" s="79"/>
-      <c r="AS2" s="79"/>
-      <c r="AT2" s="79"/>
-      <c r="AU2" s="79"/>
-      <c r="AV2" s="79"/>
-      <c r="AW2" s="79"/>
-      <c r="AX2" s="79"/>
-      <c r="AY2" s="79"/>
-      <c r="AZ2" s="79"/>
+      <c r="A2" s="80"/>
+      <c r="B2" s="80"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="80"/>
+      <c r="K2" s="80"/>
+      <c r="L2" s="80"/>
+      <c r="M2" s="80"/>
+      <c r="N2" s="80"/>
+      <c r="O2" s="80"/>
+      <c r="P2" s="80"/>
+      <c r="Q2" s="80"/>
+      <c r="R2" s="80"/>
+      <c r="S2" s="80"/>
+      <c r="T2" s="80"/>
+      <c r="U2" s="80"/>
+      <c r="V2" s="80"/>
+      <c r="W2" s="80"/>
+      <c r="X2" s="80"/>
+      <c r="Y2" s="80"/>
+      <c r="Z2" s="80"/>
+      <c r="AA2" s="80"/>
+      <c r="AB2" s="80"/>
+      <c r="AC2" s="80"/>
+      <c r="AD2" s="80"/>
+      <c r="AE2" s="80"/>
+      <c r="AF2" s="80"/>
+      <c r="AG2" s="80"/>
+      <c r="AH2" s="80"/>
+      <c r="AI2" s="80"/>
+      <c r="AJ2" s="80"/>
+      <c r="AK2" s="80"/>
+      <c r="AL2" s="80"/>
+      <c r="AM2" s="80"/>
+      <c r="AN2" s="80"/>
+      <c r="AO2" s="80"/>
+      <c r="AP2" s="80"/>
+      <c r="AQ2" s="80"/>
+      <c r="AR2" s="80"/>
+      <c r="AS2" s="80"/>
+      <c r="AT2" s="80"/>
+      <c r="AU2" s="80"/>
+      <c r="AV2" s="80"/>
+      <c r="AW2" s="80"/>
+      <c r="AX2" s="80"/>
+      <c r="AY2" s="80"/>
+      <c r="AZ2" s="80"/>
     </row>
     <row r="3" spans="1:53" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="79"/>
-      <c r="B3" s="79"/>
-      <c r="C3" s="79"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="79"/>
-      <c r="J3" s="79"/>
-      <c r="K3" s="79"/>
-      <c r="L3" s="79"/>
-      <c r="M3" s="79"/>
-      <c r="N3" s="79"/>
-      <c r="O3" s="79"/>
-      <c r="P3" s="79"/>
-      <c r="Q3" s="79"/>
-      <c r="R3" s="79"/>
-      <c r="S3" s="79"/>
-      <c r="T3" s="79"/>
-      <c r="U3" s="79"/>
-      <c r="V3" s="79"/>
-      <c r="W3" s="79"/>
-      <c r="X3" s="79"/>
-      <c r="Y3" s="79"/>
-      <c r="Z3" s="79"/>
-      <c r="AA3" s="79"/>
-      <c r="AB3" s="79"/>
-      <c r="AC3" s="79"/>
-      <c r="AD3" s="79"/>
-      <c r="AE3" s="79"/>
-      <c r="AF3" s="79"/>
-      <c r="AG3" s="79"/>
-      <c r="AH3" s="79"/>
-      <c r="AI3" s="79"/>
-      <c r="AJ3" s="79"/>
-      <c r="AK3" s="79"/>
-      <c r="AL3" s="79"/>
-      <c r="AM3" s="79"/>
-      <c r="AN3" s="79"/>
-      <c r="AO3" s="79"/>
-      <c r="AP3" s="79"/>
-      <c r="AQ3" s="79"/>
-      <c r="AR3" s="79"/>
-      <c r="AS3" s="79"/>
-      <c r="AT3" s="79"/>
-      <c r="AU3" s="79"/>
-      <c r="AV3" s="79"/>
-      <c r="AW3" s="79"/>
-      <c r="AX3" s="79"/>
-      <c r="AY3" s="79"/>
-      <c r="AZ3" s="79"/>
+      <c r="A3" s="80"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="80"/>
+      <c r="K3" s="80"/>
+      <c r="L3" s="80"/>
+      <c r="M3" s="80"/>
+      <c r="N3" s="80"/>
+      <c r="O3" s="80"/>
+      <c r="P3" s="80"/>
+      <c r="Q3" s="80"/>
+      <c r="R3" s="80"/>
+      <c r="S3" s="80"/>
+      <c r="T3" s="80"/>
+      <c r="U3" s="80"/>
+      <c r="V3" s="80"/>
+      <c r="W3" s="80"/>
+      <c r="X3" s="80"/>
+      <c r="Y3" s="80"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
+      <c r="AB3" s="80"/>
+      <c r="AC3" s="80"/>
+      <c r="AD3" s="80"/>
+      <c r="AE3" s="80"/>
+      <c r="AF3" s="80"/>
+      <c r="AG3" s="80"/>
+      <c r="AH3" s="80"/>
+      <c r="AI3" s="80"/>
+      <c r="AJ3" s="80"/>
+      <c r="AK3" s="80"/>
+      <c r="AL3" s="80"/>
+      <c r="AM3" s="80"/>
+      <c r="AN3" s="80"/>
+      <c r="AO3" s="80"/>
+      <c r="AP3" s="80"/>
+      <c r="AQ3" s="80"/>
+      <c r="AR3" s="80"/>
+      <c r="AS3" s="80"/>
+      <c r="AT3" s="80"/>
+      <c r="AU3" s="80"/>
+      <c r="AV3" s="80"/>
+      <c r="AW3" s="80"/>
+      <c r="AX3" s="80"/>
+      <c r="AY3" s="80"/>
+      <c r="AZ3" s="80"/>
     </row>
     <row r="4" spans="1:53" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="79"/>
-      <c r="B4" s="79"/>
-      <c r="C4" s="79"/>
-      <c r="D4" s="79"/>
-      <c r="E4" s="79"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="79"/>
-      <c r="H4" s="79"/>
-      <c r="I4" s="79"/>
-      <c r="J4" s="79"/>
-      <c r="K4" s="79"/>
-      <c r="L4" s="79"/>
-      <c r="M4" s="79"/>
-      <c r="N4" s="79"/>
-      <c r="O4" s="79"/>
-      <c r="P4" s="79"/>
-      <c r="Q4" s="79"/>
-      <c r="R4" s="79"/>
-      <c r="S4" s="79"/>
-      <c r="T4" s="79"/>
-      <c r="U4" s="79"/>
-      <c r="V4" s="79"/>
-      <c r="W4" s="79"/>
-      <c r="X4" s="79"/>
-      <c r="Y4" s="79"/>
-      <c r="Z4" s="79"/>
-      <c r="AA4" s="79"/>
-      <c r="AB4" s="79"/>
-      <c r="AC4" s="79"/>
-      <c r="AD4" s="79"/>
-      <c r="AE4" s="79"/>
-      <c r="AF4" s="79"/>
-      <c r="AG4" s="79"/>
-      <c r="AH4" s="79"/>
-      <c r="AI4" s="79"/>
-      <c r="AJ4" s="79"/>
-      <c r="AK4" s="79"/>
-      <c r="AL4" s="79"/>
-      <c r="AM4" s="79"/>
-      <c r="AN4" s="79"/>
-      <c r="AO4" s="79"/>
-      <c r="AP4" s="79"/>
-      <c r="AQ4" s="79"/>
-      <c r="AR4" s="79"/>
-      <c r="AS4" s="79"/>
-      <c r="AT4" s="79"/>
-      <c r="AU4" s="79"/>
-      <c r="AV4" s="79"/>
-      <c r="AW4" s="79"/>
-      <c r="AX4" s="79"/>
-      <c r="AY4" s="79"/>
-      <c r="AZ4" s="79"/>
+      <c r="A4" s="80"/>
+      <c r="B4" s="80"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="80"/>
+      <c r="I4" s="80"/>
+      <c r="J4" s="80"/>
+      <c r="K4" s="80"/>
+      <c r="L4" s="80"/>
+      <c r="M4" s="80"/>
+      <c r="N4" s="80"/>
+      <c r="O4" s="80"/>
+      <c r="P4" s="80"/>
+      <c r="Q4" s="80"/>
+      <c r="R4" s="80"/>
+      <c r="S4" s="80"/>
+      <c r="T4" s="80"/>
+      <c r="U4" s="80"/>
+      <c r="V4" s="80"/>
+      <c r="W4" s="80"/>
+      <c r="X4" s="80"/>
+      <c r="Y4" s="80"/>
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="80"/>
+      <c r="AB4" s="80"/>
+      <c r="AC4" s="80"/>
+      <c r="AD4" s="80"/>
+      <c r="AE4" s="80"/>
+      <c r="AF4" s="80"/>
+      <c r="AG4" s="80"/>
+      <c r="AH4" s="80"/>
+      <c r="AI4" s="80"/>
+      <c r="AJ4" s="80"/>
+      <c r="AK4" s="80"/>
+      <c r="AL4" s="80"/>
+      <c r="AM4" s="80"/>
+      <c r="AN4" s="80"/>
+      <c r="AO4" s="80"/>
+      <c r="AP4" s="80"/>
+      <c r="AQ4" s="80"/>
+      <c r="AR4" s="80"/>
+      <c r="AS4" s="80"/>
+      <c r="AT4" s="80"/>
+      <c r="AU4" s="80"/>
+      <c r="AV4" s="80"/>
+      <c r="AW4" s="80"/>
+      <c r="AX4" s="80"/>
+      <c r="AY4" s="80"/>
+      <c r="AZ4" s="80"/>
     </row>
     <row r="5" spans="1:53" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="83" t="s">
-        <v>66</v>
-      </c>
-      <c r="B5" s="83"/>
-      <c r="C5" s="83"/>
-      <c r="D5" s="83"/>
-      <c r="E5" s="83"/>
-      <c r="F5" s="83"/>
-      <c r="G5" s="83"/>
-      <c r="H5" s="83"/>
-      <c r="I5" s="83"/>
-      <c r="J5" s="83"/>
-      <c r="K5" s="83"/>
-      <c r="L5" s="83"/>
-      <c r="M5" s="83"/>
-      <c r="N5" s="83"/>
-      <c r="O5" s="83"/>
-      <c r="P5" s="83"/>
-      <c r="Q5" s="83"/>
-      <c r="R5" s="83"/>
-      <c r="S5" s="83"/>
-      <c r="T5" s="83"/>
-      <c r="U5" s="83"/>
-      <c r="V5" s="83"/>
-      <c r="W5" s="83"/>
-      <c r="X5" s="83"/>
-      <c r="Y5" s="83"/>
-      <c r="Z5" s="83"/>
-      <c r="AA5" s="83"/>
-      <c r="AB5" s="83"/>
-      <c r="AC5" s="83"/>
-      <c r="AD5" s="83"/>
-      <c r="AE5" s="83"/>
-      <c r="AF5" s="83"/>
-      <c r="AG5" s="83"/>
-      <c r="AH5" s="83"/>
-      <c r="AI5" s="83"/>
-      <c r="AJ5" s="83"/>
-      <c r="AK5" s="83"/>
-      <c r="AL5" s="83"/>
-      <c r="AM5" s="83"/>
-      <c r="AN5" s="83"/>
-      <c r="AO5" s="83"/>
-      <c r="AP5" s="83"/>
-      <c r="AQ5" s="83"/>
-      <c r="AR5" s="83"/>
-      <c r="AS5" s="83"/>
-      <c r="AT5" s="83"/>
-      <c r="AU5" s="83"/>
-      <c r="AV5" s="83"/>
-      <c r="AW5" s="83"/>
-      <c r="AX5" s="83"/>
-      <c r="AY5" s="83"/>
-      <c r="AZ5" s="83"/>
+      <c r="A5" s="84" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" s="84"/>
+      <c r="C5" s="84"/>
+      <c r="D5" s="84"/>
+      <c r="E5" s="84"/>
+      <c r="F5" s="84"/>
+      <c r="G5" s="84"/>
+      <c r="H5" s="84"/>
+      <c r="I5" s="84"/>
+      <c r="J5" s="84"/>
+      <c r="K5" s="84"/>
+      <c r="L5" s="84"/>
+      <c r="M5" s="84"/>
+      <c r="N5" s="84"/>
+      <c r="O5" s="84"/>
+      <c r="P5" s="84"/>
+      <c r="Q5" s="84"/>
+      <c r="R5" s="84"/>
+      <c r="S5" s="84"/>
+      <c r="T5" s="84"/>
+      <c r="U5" s="84"/>
+      <c r="V5" s="84"/>
+      <c r="W5" s="84"/>
+      <c r="X5" s="84"/>
+      <c r="Y5" s="84"/>
+      <c r="Z5" s="84"/>
+      <c r="AA5" s="84"/>
+      <c r="AB5" s="84"/>
+      <c r="AC5" s="84"/>
+      <c r="AD5" s="84"/>
+      <c r="AE5" s="84"/>
+      <c r="AF5" s="84"/>
+      <c r="AG5" s="84"/>
+      <c r="AH5" s="84"/>
+      <c r="AI5" s="84"/>
+      <c r="AJ5" s="84"/>
+      <c r="AK5" s="84"/>
+      <c r="AL5" s="84"/>
+      <c r="AM5" s="84"/>
+      <c r="AN5" s="84"/>
+      <c r="AO5" s="84"/>
+      <c r="AP5" s="84"/>
+      <c r="AQ5" s="84"/>
+      <c r="AR5" s="84"/>
+      <c r="AS5" s="84"/>
+      <c r="AT5" s="84"/>
+      <c r="AU5" s="84"/>
+      <c r="AV5" s="84"/>
+      <c r="AW5" s="84"/>
+      <c r="AX5" s="84"/>
+      <c r="AY5" s="84"/>
+      <c r="AZ5" s="84"/>
     </row>
     <row r="6" spans="1:53" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
@@ -7820,19 +8057,19 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="4"/>
-      <c r="D6" s="81"/>
-      <c r="E6" s="81"/>
-      <c r="F6" s="81"/>
-      <c r="G6" s="81"/>
-      <c r="H6" s="81"/>
-      <c r="I6" s="81"/>
-      <c r="J6" s="81"/>
-      <c r="K6" s="81"/>
-      <c r="L6" s="81"/>
-      <c r="M6" s="81"/>
-      <c r="N6" s="81"/>
-      <c r="O6" s="81"/>
-      <c r="P6" s="81"/>
+      <c r="D6" s="82"/>
+      <c r="E6" s="82"/>
+      <c r="F6" s="82"/>
+      <c r="G6" s="82"/>
+      <c r="H6" s="82"/>
+      <c r="I6" s="82"/>
+      <c r="J6" s="82"/>
+      <c r="K6" s="82"/>
+      <c r="L6" s="82"/>
+      <c r="M6" s="82"/>
+      <c r="N6" s="82"/>
+      <c r="O6" s="82"/>
+      <c r="P6" s="82"/>
       <c r="Q6" s="5" t="s">
         <v>63</v>
       </c>
@@ -7868,20 +8105,20 @@
       <c r="AU6" s="4"/>
       <c r="AV6" s="4"/>
     </row>
-    <row r="7" spans="1:53" s="84" customFormat="1" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="1:53" s="85" customFormat="1" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="1:53" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="50"/>
       <c r="B8" s="51" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D8" s="59" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E8" s="59" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F8" s="59"/>
       <c r="G8" s="59"/>
@@ -8104,10 +8341,10 @@
         <v>46</v>
       </c>
       <c r="D10" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E10" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F10" s="67"/>
       <c r="G10" s="67"/>
@@ -8169,10 +8406,10 @@
         <v>50</v>
       </c>
       <c r="D11" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E11" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F11" s="67"/>
       <c r="G11" s="67"/>
@@ -8234,10 +8471,10 @@
         <v>40</v>
       </c>
       <c r="D12" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E12" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F12" s="67"/>
       <c r="G12" s="67"/>
@@ -8299,10 +8536,10 @@
         <v>49</v>
       </c>
       <c r="D13" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E13" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F13" s="67"/>
       <c r="G13" s="67"/>
@@ -8364,10 +8601,10 @@
         <v>39</v>
       </c>
       <c r="D14" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E14" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F14" s="67"/>
       <c r="G14" s="67"/>
@@ -8428,7 +8665,7 @@
       <c r="C15" s="66"/>
       <c r="D15" s="67"/>
       <c r="E15" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F15" s="67"/>
       <c r="G15" s="67"/>
@@ -8490,10 +8727,10 @@
         <v>48</v>
       </c>
       <c r="D16" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E16" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F16" s="67"/>
       <c r="G16" s="67"/>
@@ -8615,7 +8852,7 @@
       <c r="C18" s="66"/>
       <c r="D18" s="72"/>
       <c r="E18" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F18" s="67"/>
       <c r="G18" s="67"/>
@@ -8677,10 +8914,10 @@
         <v>50</v>
       </c>
       <c r="D19" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E19" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F19" s="67"/>
       <c r="G19" s="67"/>
@@ -8801,10 +9038,10 @@
         <v>46</v>
       </c>
       <c r="D21" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E21" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F21" s="67"/>
       <c r="G21" s="67"/>
@@ -8866,10 +9103,10 @@
         <v>50</v>
       </c>
       <c r="D22" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E22" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F22" s="67"/>
       <c r="G22" s="67"/>
@@ -8931,10 +9168,10 @@
         <v>50</v>
       </c>
       <c r="D23" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E23" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F23" s="67"/>
       <c r="G23" s="67"/>
@@ -8997,7 +9234,7 @@
       </c>
       <c r="D24" s="72"/>
       <c r="E24" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F24" s="67"/>
       <c r="G24" s="67"/>
@@ -9120,7 +9357,7 @@
         <v>49</v>
       </c>
       <c r="D26" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E26" s="72"/>
       <c r="F26" s="67"/>
@@ -9182,7 +9419,7 @@
       <c r="C27" s="66"/>
       <c r="D27" s="72"/>
       <c r="E27" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F27" s="67"/>
       <c r="G27" s="67"/>
@@ -9242,7 +9479,7 @@
       </c>
       <c r="C28" s="66"/>
       <c r="D28" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E28" s="67"/>
       <c r="F28" s="67"/>
@@ -9305,10 +9542,10 @@
         <v>20</v>
       </c>
       <c r="D29" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E29" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F29" s="67"/>
       <c r="G29" s="67"/>
@@ -9371,7 +9608,7 @@
       </c>
       <c r="D30" s="72"/>
       <c r="E30" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F30" s="67"/>
       <c r="G30" s="67"/>
@@ -9433,10 +9670,10 @@
         <v>40</v>
       </c>
       <c r="D31" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E31" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F31" s="67"/>
       <c r="G31" s="67"/>
@@ -9496,10 +9733,10 @@
       </c>
       <c r="C32" s="66"/>
       <c r="D32" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E32" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F32" s="67"/>
       <c r="G32" s="67"/>
@@ -9562,7 +9799,7 @@
       </c>
       <c r="D33" s="72"/>
       <c r="E33" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F33" s="67"/>
       <c r="G33" s="67"/>
@@ -9624,10 +9861,10 @@
         <v>49</v>
       </c>
       <c r="D34" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E34" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F34" s="67"/>
       <c r="G34" s="67"/>
@@ -9687,10 +9924,10 @@
       </c>
       <c r="C35" s="66"/>
       <c r="D35" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E35" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F35" s="67"/>
       <c r="G35" s="67"/>
@@ -9752,10 +9989,10 @@
         <v>24</v>
       </c>
       <c r="D36" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E36" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F36" s="67"/>
       <c r="G36" s="67"/>
@@ -9815,10 +10052,10 @@
       </c>
       <c r="C37" s="66"/>
       <c r="D37" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E37" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F37" s="67"/>
       <c r="G37" s="67"/>
@@ -9941,10 +10178,10 @@
         <v>42</v>
       </c>
       <c r="D39" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E39" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F39" s="67"/>
       <c r="G39" s="67"/>
@@ -10456,15 +10693,15 @@
     </row>
     <row r="4" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12"/>
-      <c r="B4" s="94" t="s">
+      <c r="B4" s="95" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="94"/>
-      <c r="D4" s="94"/>
-      <c r="E4" s="94"/>
-      <c r="F4" s="94"/>
-      <c r="G4" s="94"/>
-      <c r="H4" s="94"/>
+      <c r="C4" s="95"/>
+      <c r="D4" s="95"/>
+      <c r="E4" s="95"/>
+      <c r="F4" s="95"/>
+      <c r="G4" s="95"/>
+      <c r="H4" s="95"/>
       <c r="J4" s="13"/>
     </row>
     <row r="5" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10484,59 +10721,59 @@
     </row>
     <row r="7" spans="1:10" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12"/>
-      <c r="B7" s="94" t="s">
+      <c r="B7" s="95" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="94"/>
-      <c r="D7" s="94"/>
-      <c r="E7" s="94"/>
-      <c r="F7" s="94"/>
-      <c r="G7" s="94"/>
-      <c r="H7" s="94"/>
+      <c r="C7" s="95"/>
+      <c r="D7" s="95"/>
+      <c r="E7" s="95"/>
+      <c r="F7" s="95"/>
+      <c r="G7" s="95"/>
+      <c r="H7" s="95"/>
       <c r="J7" s="13"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="12"/>
-      <c r="B8" s="85"/>
-      <c r="C8" s="86"/>
-      <c r="D8" s="86"/>
-      <c r="E8" s="86"/>
-      <c r="F8" s="86"/>
-      <c r="G8" s="86"/>
-      <c r="H8" s="87"/>
+      <c r="B8" s="86"/>
+      <c r="C8" s="87"/>
+      <c r="D8" s="87"/>
+      <c r="E8" s="87"/>
+      <c r="F8" s="87"/>
+      <c r="G8" s="87"/>
+      <c r="H8" s="88"/>
       <c r="J8" s="13"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="12"/>
-      <c r="B9" s="88"/>
-      <c r="C9" s="89"/>
-      <c r="D9" s="89"/>
-      <c r="E9" s="89"/>
-      <c r="F9" s="89"/>
-      <c r="G9" s="89"/>
-      <c r="H9" s="90"/>
+      <c r="B9" s="89"/>
+      <c r="C9" s="90"/>
+      <c r="D9" s="90"/>
+      <c r="E9" s="90"/>
+      <c r="F9" s="90"/>
+      <c r="G9" s="90"/>
+      <c r="H9" s="91"/>
       <c r="J9" s="13"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="12"/>
-      <c r="B10" s="88"/>
-      <c r="C10" s="89"/>
-      <c r="D10" s="89"/>
-      <c r="E10" s="89"/>
-      <c r="F10" s="89"/>
-      <c r="G10" s="89"/>
-      <c r="H10" s="90"/>
+      <c r="B10" s="89"/>
+      <c r="C10" s="90"/>
+      <c r="D10" s="90"/>
+      <c r="E10" s="90"/>
+      <c r="F10" s="90"/>
+      <c r="G10" s="90"/>
+      <c r="H10" s="91"/>
       <c r="J10" s="13"/>
     </row>
     <row r="11" spans="1:10" ht="72" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="12"/>
-      <c r="B11" s="91"/>
-      <c r="C11" s="92"/>
-      <c r="D11" s="92"/>
-      <c r="E11" s="92"/>
-      <c r="F11" s="92"/>
-      <c r="G11" s="92"/>
-      <c r="H11" s="93"/>
+      <c r="B11" s="92"/>
+      <c r="C11" s="93"/>
+      <c r="D11" s="93"/>
+      <c r="E11" s="93"/>
+      <c r="F11" s="93"/>
+      <c r="G11" s="93"/>
+      <c r="H11" s="94"/>
       <c r="J11" s="13"/>
     </row>
     <row r="12" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -10956,135 +11193,135 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="108"/>
-      <c r="C1" s="108"/>
-      <c r="D1" s="108"/>
-      <c r="E1" s="108"/>
-      <c r="F1" s="108"/>
-      <c r="G1" s="108"/>
+      <c r="B1" s="99"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
+      <c r="F1" s="99"/>
+      <c r="G1" s="99"/>
       <c r="H1" s="27"/>
       <c r="I1" s="34"/>
-      <c r="J1" s="107" t="s">
+      <c r="J1" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="109"/>
+      <c r="K1" s="99"/>
+      <c r="L1" s="99"/>
+      <c r="M1" s="99"/>
+      <c r="N1" s="99"/>
+      <c r="O1" s="99"/>
+      <c r="P1" s="100"/>
     </row>
     <row r="2" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="110" t="s">
+      <c r="A2" s="101" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="111"/>
-      <c r="C2" s="111"/>
-      <c r="D2" s="111"/>
-      <c r="E2" s="111"/>
-      <c r="F2" s="112" t="s">
+      <c r="B2" s="102"/>
+      <c r="C2" s="102"/>
+      <c r="D2" s="102"/>
+      <c r="E2" s="102"/>
+      <c r="F2" s="96" t="s">
         <v>55</v>
       </c>
-      <c r="G2" s="113"/>
+      <c r="G2" s="97"/>
       <c r="H2" s="29"/>
-      <c r="J2" s="110" t="s">
+      <c r="J2" s="101" t="s">
         <v>48</v>
       </c>
-      <c r="K2" s="111"/>
-      <c r="L2" s="111"/>
-      <c r="M2" s="111"/>
-      <c r="N2" s="111"/>
-      <c r="O2" s="114" t="s">
+      <c r="K2" s="102"/>
+      <c r="L2" s="102"/>
+      <c r="M2" s="102"/>
+      <c r="N2" s="102"/>
+      <c r="O2" s="103" t="s">
         <v>55</v>
       </c>
-      <c r="P2" s="115"/>
+      <c r="P2" s="104"/>
     </row>
     <row r="3" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="95" t="s">
+      <c r="A3" s="105" t="s">
         <v>54</v>
       </c>
-      <c r="B3" s="96"/>
-      <c r="C3" s="96"/>
-      <c r="D3" s="96"/>
-      <c r="E3" s="96"/>
-      <c r="F3" s="96"/>
-      <c r="G3" s="96"/>
+      <c r="B3" s="106"/>
+      <c r="C3" s="106"/>
+      <c r="D3" s="106"/>
+      <c r="E3" s="106"/>
+      <c r="F3" s="106"/>
+      <c r="G3" s="106"/>
       <c r="H3" s="29"/>
-      <c r="J3" s="95" t="s">
+      <c r="J3" s="105" t="s">
         <v>54</v>
       </c>
-      <c r="K3" s="96"/>
-      <c r="L3" s="96"/>
-      <c r="M3" s="96"/>
-      <c r="N3" s="96"/>
-      <c r="O3" s="96"/>
-      <c r="P3" s="97"/>
+      <c r="K3" s="106"/>
+      <c r="L3" s="106"/>
+      <c r="M3" s="106"/>
+      <c r="N3" s="106"/>
+      <c r="O3" s="106"/>
+      <c r="P3" s="107"/>
     </row>
     <row r="4" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="95" t="s">
+      <c r="A4" s="105" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="96"/>
-      <c r="C4" s="96"/>
-      <c r="D4" s="96"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="96"/>
-      <c r="G4" s="96"/>
+      <c r="B4" s="106"/>
+      <c r="C4" s="106"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="106"/>
+      <c r="F4" s="106"/>
+      <c r="G4" s="106"/>
       <c r="H4" s="29"/>
-      <c r="J4" s="95" t="s">
+      <c r="J4" s="105" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="96"/>
-      <c r="L4" s="96"/>
-      <c r="M4" s="96"/>
-      <c r="N4" s="96"/>
-      <c r="O4" s="96"/>
-      <c r="P4" s="97"/>
+      <c r="K4" s="106"/>
+      <c r="L4" s="106"/>
+      <c r="M4" s="106"/>
+      <c r="N4" s="106"/>
+      <c r="O4" s="106"/>
+      <c r="P4" s="107"/>
     </row>
     <row r="5" spans="1:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="104" t="s">
+      <c r="A5" s="108" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="105"/>
-      <c r="C5" s="105"/>
-      <c r="D5" s="105"/>
-      <c r="E5" s="105"/>
-      <c r="F5" s="105"/>
-      <c r="G5" s="105"/>
+      <c r="B5" s="109"/>
+      <c r="C5" s="109"/>
+      <c r="D5" s="109"/>
+      <c r="E5" s="109"/>
+      <c r="F5" s="109"/>
+      <c r="G5" s="109"/>
       <c r="H5" s="29"/>
-      <c r="J5" s="104" t="s">
+      <c r="J5" s="108" t="s">
         <v>53</v>
       </c>
-      <c r="K5" s="105"/>
-      <c r="L5" s="105"/>
-      <c r="M5" s="105"/>
-      <c r="N5" s="105"/>
-      <c r="O5" s="105"/>
-      <c r="P5" s="106"/>
+      <c r="K5" s="109"/>
+      <c r="L5" s="109"/>
+      <c r="M5" s="109"/>
+      <c r="N5" s="109"/>
+      <c r="O5" s="109"/>
+      <c r="P5" s="110"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="95" t="s">
+      <c r="A6" s="105" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="96"/>
-      <c r="C6" s="96"/>
-      <c r="D6" s="96"/>
-      <c r="E6" s="96"/>
-      <c r="F6" s="96"/>
-      <c r="G6" s="96"/>
+      <c r="B6" s="106"/>
+      <c r="C6" s="106"/>
+      <c r="D6" s="106"/>
+      <c r="E6" s="106"/>
+      <c r="F6" s="106"/>
+      <c r="G6" s="106"/>
       <c r="H6" s="29"/>
-      <c r="J6" s="95" t="s">
+      <c r="J6" s="105" t="s">
         <v>50</v>
       </c>
-      <c r="K6" s="96"/>
-      <c r="L6" s="96"/>
-      <c r="M6" s="96"/>
-      <c r="N6" s="96"/>
-      <c r="O6" s="96"/>
-      <c r="P6" s="97"/>
+      <c r="K6" s="106"/>
+      <c r="L6" s="106"/>
+      <c r="M6" s="106"/>
+      <c r="N6" s="106"/>
+      <c r="O6" s="106"/>
+      <c r="P6" s="107"/>
     </row>
     <row r="7" spans="1:16" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="28"/>
@@ -11093,46 +11330,46 @@
       <c r="P7" s="29"/>
     </row>
     <row r="8" spans="1:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="98" t="s">
+      <c r="A8" s="113" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="99"/>
-      <c r="C8" s="99"/>
-      <c r="D8" s="99"/>
-      <c r="E8" s="99"/>
-      <c r="F8" s="99"/>
-      <c r="G8" s="99"/>
+      <c r="B8" s="114"/>
+      <c r="C8" s="114"/>
+      <c r="D8" s="114"/>
+      <c r="E8" s="114"/>
+      <c r="F8" s="114"/>
+      <c r="G8" s="114"/>
       <c r="H8" s="29"/>
-      <c r="J8" s="98" t="s">
+      <c r="J8" s="113" t="s">
         <v>51</v>
       </c>
-      <c r="K8" s="99"/>
-      <c r="L8" s="99"/>
-      <c r="M8" s="99"/>
-      <c r="N8" s="99"/>
-      <c r="O8" s="99"/>
-      <c r="P8" s="100"/>
+      <c r="K8" s="114"/>
+      <c r="L8" s="114"/>
+      <c r="M8" s="114"/>
+      <c r="N8" s="114"/>
+      <c r="O8" s="114"/>
+      <c r="P8" s="115"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="101" t="s">
+      <c r="A9" s="111" t="s">
         <v>57</v>
       </c>
-      <c r="B9" s="102"/>
-      <c r="C9" s="102"/>
-      <c r="D9" s="102"/>
-      <c r="E9" s="102"/>
-      <c r="F9" s="102"/>
-      <c r="G9" s="102"/>
+      <c r="B9" s="112"/>
+      <c r="C9" s="112"/>
+      <c r="D9" s="112"/>
+      <c r="E9" s="112"/>
+      <c r="F9" s="112"/>
+      <c r="G9" s="112"/>
       <c r="H9" s="29"/>
-      <c r="J9" s="101" t="s">
+      <c r="J9" s="111" t="s">
         <v>57</v>
       </c>
-      <c r="K9" s="102"/>
-      <c r="L9" s="102"/>
-      <c r="M9" s="102"/>
-      <c r="N9" s="102"/>
-      <c r="O9" s="102"/>
-      <c r="P9" s="103"/>
+      <c r="K9" s="112"/>
+      <c r="L9" s="112"/>
+      <c r="M9" s="112"/>
+      <c r="N9" s="112"/>
+      <c r="O9" s="112"/>
+      <c r="P9" s="116"/>
     </row>
     <row r="10" spans="1:16" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="30"/>
@@ -11153,135 +11390,135 @@
       <c r="P10" s="33"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="107" t="s">
+      <c r="A11" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="108"/>
-      <c r="C11" s="108"/>
-      <c r="D11" s="108"/>
-      <c r="E11" s="108"/>
-      <c r="F11" s="108"/>
-      <c r="G11" s="108"/>
+      <c r="B11" s="99"/>
+      <c r="C11" s="99"/>
+      <c r="D11" s="99"/>
+      <c r="E11" s="99"/>
+      <c r="F11" s="99"/>
+      <c r="G11" s="99"/>
       <c r="H11" s="27"/>
       <c r="I11" s="34"/>
-      <c r="J11" s="107" t="s">
+      <c r="J11" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="K11" s="108"/>
-      <c r="L11" s="108"/>
-      <c r="M11" s="108"/>
-      <c r="N11" s="108"/>
-      <c r="O11" s="108"/>
-      <c r="P11" s="109"/>
+      <c r="K11" s="99"/>
+      <c r="L11" s="99"/>
+      <c r="M11" s="99"/>
+      <c r="N11" s="99"/>
+      <c r="O11" s="99"/>
+      <c r="P11" s="100"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="110" t="s">
+      <c r="A12" s="101" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="111"/>
-      <c r="C12" s="111"/>
-      <c r="D12" s="111"/>
-      <c r="E12" s="111"/>
-      <c r="F12" s="112" t="s">
+      <c r="B12" s="102"/>
+      <c r="C12" s="102"/>
+      <c r="D12" s="102"/>
+      <c r="E12" s="102"/>
+      <c r="F12" s="96" t="s">
         <v>55</v>
       </c>
-      <c r="G12" s="113"/>
+      <c r="G12" s="97"/>
       <c r="H12" s="29"/>
-      <c r="J12" s="110" t="s">
+      <c r="J12" s="101" t="s">
         <v>48</v>
       </c>
-      <c r="K12" s="111"/>
-      <c r="L12" s="111"/>
-      <c r="M12" s="111"/>
-      <c r="N12" s="111"/>
-      <c r="O12" s="114" t="s">
+      <c r="K12" s="102"/>
+      <c r="L12" s="102"/>
+      <c r="M12" s="102"/>
+      <c r="N12" s="102"/>
+      <c r="O12" s="103" t="s">
         <v>55</v>
       </c>
-      <c r="P12" s="115"/>
+      <c r="P12" s="104"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="95" t="s">
+      <c r="A13" s="105" t="s">
         <v>54</v>
       </c>
-      <c r="B13" s="96"/>
-      <c r="C13" s="96"/>
-      <c r="D13" s="96"/>
-      <c r="E13" s="96"/>
-      <c r="F13" s="96"/>
-      <c r="G13" s="96"/>
+      <c r="B13" s="106"/>
+      <c r="C13" s="106"/>
+      <c r="D13" s="106"/>
+      <c r="E13" s="106"/>
+      <c r="F13" s="106"/>
+      <c r="G13" s="106"/>
       <c r="H13" s="29"/>
-      <c r="J13" s="95" t="s">
+      <c r="J13" s="105" t="s">
         <v>54</v>
       </c>
-      <c r="K13" s="96"/>
-      <c r="L13" s="96"/>
-      <c r="M13" s="96"/>
-      <c r="N13" s="96"/>
-      <c r="O13" s="96"/>
-      <c r="P13" s="97"/>
+      <c r="K13" s="106"/>
+      <c r="L13" s="106"/>
+      <c r="M13" s="106"/>
+      <c r="N13" s="106"/>
+      <c r="O13" s="106"/>
+      <c r="P13" s="107"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="95" t="s">
+      <c r="A14" s="105" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="96"/>
-      <c r="C14" s="96"/>
-      <c r="D14" s="96"/>
-      <c r="E14" s="96"/>
-      <c r="F14" s="96"/>
-      <c r="G14" s="96"/>
+      <c r="B14" s="106"/>
+      <c r="C14" s="106"/>
+      <c r="D14" s="106"/>
+      <c r="E14" s="106"/>
+      <c r="F14" s="106"/>
+      <c r="G14" s="106"/>
       <c r="H14" s="29"/>
-      <c r="J14" s="95" t="s">
+      <c r="J14" s="105" t="s">
         <v>49</v>
       </c>
-      <c r="K14" s="96"/>
-      <c r="L14" s="96"/>
-      <c r="M14" s="96"/>
-      <c r="N14" s="96"/>
-      <c r="O14" s="96"/>
-      <c r="P14" s="97"/>
+      <c r="K14" s="106"/>
+      <c r="L14" s="106"/>
+      <c r="M14" s="106"/>
+      <c r="N14" s="106"/>
+      <c r="O14" s="106"/>
+      <c r="P14" s="107"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" s="104" t="s">
+      <c r="A15" s="108" t="s">
         <v>53</v>
       </c>
-      <c r="B15" s="105"/>
-      <c r="C15" s="105"/>
-      <c r="D15" s="105"/>
-      <c r="E15" s="105"/>
-      <c r="F15" s="105"/>
-      <c r="G15" s="105"/>
+      <c r="B15" s="109"/>
+      <c r="C15" s="109"/>
+      <c r="D15" s="109"/>
+      <c r="E15" s="109"/>
+      <c r="F15" s="109"/>
+      <c r="G15" s="109"/>
       <c r="H15" s="29"/>
-      <c r="J15" s="104" t="s">
+      <c r="J15" s="108" t="s">
         <v>53</v>
       </c>
-      <c r="K15" s="105"/>
-      <c r="L15" s="105"/>
-      <c r="M15" s="105"/>
-      <c r="N15" s="105"/>
-      <c r="O15" s="105"/>
-      <c r="P15" s="106"/>
+      <c r="K15" s="109"/>
+      <c r="L15" s="109"/>
+      <c r="M15" s="109"/>
+      <c r="N15" s="109"/>
+      <c r="O15" s="109"/>
+      <c r="P15" s="110"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" s="95" t="s">
+      <c r="A16" s="105" t="s">
         <v>50</v>
       </c>
-      <c r="B16" s="96"/>
-      <c r="C16" s="96"/>
-      <c r="D16" s="96"/>
-      <c r="E16" s="96"/>
-      <c r="F16" s="96"/>
-      <c r="G16" s="96"/>
+      <c r="B16" s="106"/>
+      <c r="C16" s="106"/>
+      <c r="D16" s="106"/>
+      <c r="E16" s="106"/>
+      <c r="F16" s="106"/>
+      <c r="G16" s="106"/>
       <c r="H16" s="29"/>
-      <c r="J16" s="95" t="s">
+      <c r="J16" s="105" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="96"/>
-      <c r="L16" s="96"/>
-      <c r="M16" s="96"/>
-      <c r="N16" s="96"/>
-      <c r="O16" s="96"/>
-      <c r="P16" s="97"/>
+      <c r="K16" s="106"/>
+      <c r="L16" s="106"/>
+      <c r="M16" s="106"/>
+      <c r="N16" s="106"/>
+      <c r="O16" s="106"/>
+      <c r="P16" s="107"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="28"/>
@@ -11290,46 +11527,46 @@
       <c r="P17" s="29"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="98" t="s">
+      <c r="A18" s="113" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="99"/>
-      <c r="C18" s="99"/>
-      <c r="D18" s="99"/>
-      <c r="E18" s="99"/>
-      <c r="F18" s="99"/>
-      <c r="G18" s="99"/>
+      <c r="B18" s="114"/>
+      <c r="C18" s="114"/>
+      <c r="D18" s="114"/>
+      <c r="E18" s="114"/>
+      <c r="F18" s="114"/>
+      <c r="G18" s="114"/>
       <c r="H18" s="29"/>
-      <c r="J18" s="98" t="s">
+      <c r="J18" s="113" t="s">
         <v>51</v>
       </c>
-      <c r="K18" s="99"/>
-      <c r="L18" s="99"/>
-      <c r="M18" s="99"/>
-      <c r="N18" s="99"/>
-      <c r="O18" s="99"/>
-      <c r="P18" s="100"/>
+      <c r="K18" s="114"/>
+      <c r="L18" s="114"/>
+      <c r="M18" s="114"/>
+      <c r="N18" s="114"/>
+      <c r="O18" s="114"/>
+      <c r="P18" s="115"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="101" t="s">
+      <c r="A19" s="111" t="s">
         <v>57</v>
       </c>
-      <c r="B19" s="102"/>
-      <c r="C19" s="102"/>
-      <c r="D19" s="102"/>
-      <c r="E19" s="102"/>
-      <c r="F19" s="102"/>
-      <c r="G19" s="102"/>
+      <c r="B19" s="112"/>
+      <c r="C19" s="112"/>
+      <c r="D19" s="112"/>
+      <c r="E19" s="112"/>
+      <c r="F19" s="112"/>
+      <c r="G19" s="112"/>
       <c r="H19" s="29"/>
-      <c r="J19" s="101" t="s">
+      <c r="J19" s="111" t="s">
         <v>57</v>
       </c>
-      <c r="K19" s="102"/>
-      <c r="L19" s="102"/>
-      <c r="M19" s="102"/>
-      <c r="N19" s="102"/>
-      <c r="O19" s="102"/>
-      <c r="P19" s="103"/>
+      <c r="K19" s="112"/>
+      <c r="L19" s="112"/>
+      <c r="M19" s="112"/>
+      <c r="N19" s="112"/>
+      <c r="O19" s="112"/>
+      <c r="P19" s="116"/>
     </row>
     <row r="20" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="30"/>
@@ -11350,135 +11587,135 @@
       <c r="P20" s="33"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="107" t="s">
+      <c r="A21" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="108"/>
-      <c r="C21" s="108"/>
-      <c r="D21" s="108"/>
-      <c r="E21" s="108"/>
-      <c r="F21" s="108"/>
-      <c r="G21" s="108"/>
+      <c r="B21" s="99"/>
+      <c r="C21" s="99"/>
+      <c r="D21" s="99"/>
+      <c r="E21" s="99"/>
+      <c r="F21" s="99"/>
+      <c r="G21" s="99"/>
       <c r="H21" s="27"/>
       <c r="I21" s="34"/>
-      <c r="J21" s="107" t="s">
+      <c r="J21" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="K21" s="108"/>
-      <c r="L21" s="108"/>
-      <c r="M21" s="108"/>
-      <c r="N21" s="108"/>
-      <c r="O21" s="108"/>
-      <c r="P21" s="109"/>
+      <c r="K21" s="99"/>
+      <c r="L21" s="99"/>
+      <c r="M21" s="99"/>
+      <c r="N21" s="99"/>
+      <c r="O21" s="99"/>
+      <c r="P21" s="100"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" s="110" t="s">
+      <c r="A22" s="101" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="111"/>
-      <c r="C22" s="111"/>
-      <c r="D22" s="111"/>
-      <c r="E22" s="111"/>
-      <c r="F22" s="112" t="s">
+      <c r="B22" s="102"/>
+      <c r="C22" s="102"/>
+      <c r="D22" s="102"/>
+      <c r="E22" s="102"/>
+      <c r="F22" s="96" t="s">
         <v>55</v>
       </c>
-      <c r="G22" s="113"/>
+      <c r="G22" s="97"/>
       <c r="H22" s="29"/>
-      <c r="J22" s="110" t="s">
+      <c r="J22" s="101" t="s">
         <v>48</v>
       </c>
-      <c r="K22" s="111"/>
-      <c r="L22" s="111"/>
-      <c r="M22" s="111"/>
-      <c r="N22" s="111"/>
-      <c r="O22" s="114" t="s">
+      <c r="K22" s="102"/>
+      <c r="L22" s="102"/>
+      <c r="M22" s="102"/>
+      <c r="N22" s="102"/>
+      <c r="O22" s="103" t="s">
         <v>55</v>
       </c>
-      <c r="P22" s="115"/>
+      <c r="P22" s="104"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" s="95" t="s">
+      <c r="A23" s="105" t="s">
         <v>54</v>
       </c>
-      <c r="B23" s="96"/>
-      <c r="C23" s="96"/>
-      <c r="D23" s="96"/>
-      <c r="E23" s="96"/>
-      <c r="F23" s="96"/>
-      <c r="G23" s="96"/>
+      <c r="B23" s="106"/>
+      <c r="C23" s="106"/>
+      <c r="D23" s="106"/>
+      <c r="E23" s="106"/>
+      <c r="F23" s="106"/>
+      <c r="G23" s="106"/>
       <c r="H23" s="29"/>
-      <c r="J23" s="95" t="s">
+      <c r="J23" s="105" t="s">
         <v>54</v>
       </c>
-      <c r="K23" s="96"/>
-      <c r="L23" s="96"/>
-      <c r="M23" s="96"/>
-      <c r="N23" s="96"/>
-      <c r="O23" s="96"/>
-      <c r="P23" s="97"/>
+      <c r="K23" s="106"/>
+      <c r="L23" s="106"/>
+      <c r="M23" s="106"/>
+      <c r="N23" s="106"/>
+      <c r="O23" s="106"/>
+      <c r="P23" s="107"/>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" s="95" t="s">
+      <c r="A24" s="105" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="96"/>
-      <c r="C24" s="96"/>
-      <c r="D24" s="96"/>
-      <c r="E24" s="96"/>
-      <c r="F24" s="96"/>
-      <c r="G24" s="96"/>
+      <c r="B24" s="106"/>
+      <c r="C24" s="106"/>
+      <c r="D24" s="106"/>
+      <c r="E24" s="106"/>
+      <c r="F24" s="106"/>
+      <c r="G24" s="106"/>
       <c r="H24" s="29"/>
-      <c r="J24" s="95" t="s">
+      <c r="J24" s="105" t="s">
         <v>49</v>
       </c>
-      <c r="K24" s="96"/>
-      <c r="L24" s="96"/>
-      <c r="M24" s="96"/>
-      <c r="N24" s="96"/>
-      <c r="O24" s="96"/>
-      <c r="P24" s="97"/>
+      <c r="K24" s="106"/>
+      <c r="L24" s="106"/>
+      <c r="M24" s="106"/>
+      <c r="N24" s="106"/>
+      <c r="O24" s="106"/>
+      <c r="P24" s="107"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" s="104" t="s">
+      <c r="A25" s="108" t="s">
         <v>53</v>
       </c>
-      <c r="B25" s="105"/>
-      <c r="C25" s="105"/>
-      <c r="D25" s="105"/>
-      <c r="E25" s="105"/>
-      <c r="F25" s="105"/>
-      <c r="G25" s="105"/>
+      <c r="B25" s="109"/>
+      <c r="C25" s="109"/>
+      <c r="D25" s="109"/>
+      <c r="E25" s="109"/>
+      <c r="F25" s="109"/>
+      <c r="G25" s="109"/>
       <c r="H25" s="29"/>
-      <c r="J25" s="104" t="s">
+      <c r="J25" s="108" t="s">
         <v>53</v>
       </c>
-      <c r="K25" s="105"/>
-      <c r="L25" s="105"/>
-      <c r="M25" s="105"/>
-      <c r="N25" s="105"/>
-      <c r="O25" s="105"/>
-      <c r="P25" s="106"/>
+      <c r="K25" s="109"/>
+      <c r="L25" s="109"/>
+      <c r="M25" s="109"/>
+      <c r="N25" s="109"/>
+      <c r="O25" s="109"/>
+      <c r="P25" s="110"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" s="95" t="s">
+      <c r="A26" s="105" t="s">
         <v>50</v>
       </c>
-      <c r="B26" s="96"/>
-      <c r="C26" s="96"/>
-      <c r="D26" s="96"/>
-      <c r="E26" s="96"/>
-      <c r="F26" s="96"/>
-      <c r="G26" s="96"/>
+      <c r="B26" s="106"/>
+      <c r="C26" s="106"/>
+      <c r="D26" s="106"/>
+      <c r="E26" s="106"/>
+      <c r="F26" s="106"/>
+      <c r="G26" s="106"/>
       <c r="H26" s="29"/>
-      <c r="J26" s="95" t="s">
+      <c r="J26" s="105" t="s">
         <v>50</v>
       </c>
-      <c r="K26" s="96"/>
-      <c r="L26" s="96"/>
-      <c r="M26" s="96"/>
-      <c r="N26" s="96"/>
-      <c r="O26" s="96"/>
-      <c r="P26" s="97"/>
+      <c r="K26" s="106"/>
+      <c r="L26" s="106"/>
+      <c r="M26" s="106"/>
+      <c r="N26" s="106"/>
+      <c r="O26" s="106"/>
+      <c r="P26" s="107"/>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="28"/>
@@ -11487,46 +11724,46 @@
       <c r="P27" s="29"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" s="98" t="s">
+      <c r="A28" s="113" t="s">
         <v>51</v>
       </c>
-      <c r="B28" s="99"/>
-      <c r="C28" s="99"/>
-      <c r="D28" s="99"/>
-      <c r="E28" s="99"/>
-      <c r="F28" s="99"/>
-      <c r="G28" s="99"/>
+      <c r="B28" s="114"/>
+      <c r="C28" s="114"/>
+      <c r="D28" s="114"/>
+      <c r="E28" s="114"/>
+      <c r="F28" s="114"/>
+      <c r="G28" s="114"/>
       <c r="H28" s="29"/>
-      <c r="J28" s="98" t="s">
+      <c r="J28" s="113" t="s">
         <v>51</v>
       </c>
-      <c r="K28" s="99"/>
-      <c r="L28" s="99"/>
-      <c r="M28" s="99"/>
-      <c r="N28" s="99"/>
-      <c r="O28" s="99"/>
-      <c r="P28" s="100"/>
+      <c r="K28" s="114"/>
+      <c r="L28" s="114"/>
+      <c r="M28" s="114"/>
+      <c r="N28" s="114"/>
+      <c r="O28" s="114"/>
+      <c r="P28" s="115"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" s="101" t="s">
+      <c r="A29" s="111" t="s">
         <v>57</v>
       </c>
-      <c r="B29" s="102"/>
-      <c r="C29" s="102"/>
-      <c r="D29" s="102"/>
-      <c r="E29" s="102"/>
-      <c r="F29" s="102"/>
-      <c r="G29" s="102"/>
+      <c r="B29" s="112"/>
+      <c r="C29" s="112"/>
+      <c r="D29" s="112"/>
+      <c r="E29" s="112"/>
+      <c r="F29" s="112"/>
+      <c r="G29" s="112"/>
       <c r="H29" s="29"/>
-      <c r="J29" s="101" t="s">
+      <c r="J29" s="111" t="s">
         <v>57</v>
       </c>
-      <c r="K29" s="102"/>
-      <c r="L29" s="102"/>
-      <c r="M29" s="102"/>
-      <c r="N29" s="102"/>
-      <c r="O29" s="102"/>
-      <c r="P29" s="103"/>
+      <c r="K29" s="112"/>
+      <c r="L29" s="112"/>
+      <c r="M29" s="112"/>
+      <c r="N29" s="112"/>
+      <c r="O29" s="112"/>
+      <c r="P29" s="116"/>
     </row>
     <row r="30" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="30"/>
@@ -11547,135 +11784,135 @@
       <c r="P30" s="33"/>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31" s="107" t="s">
+      <c r="A31" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="B31" s="108"/>
-      <c r="C31" s="108"/>
-      <c r="D31" s="108"/>
-      <c r="E31" s="108"/>
-      <c r="F31" s="108"/>
-      <c r="G31" s="108"/>
+      <c r="B31" s="99"/>
+      <c r="C31" s="99"/>
+      <c r="D31" s="99"/>
+      <c r="E31" s="99"/>
+      <c r="F31" s="99"/>
+      <c r="G31" s="99"/>
       <c r="H31" s="27"/>
       <c r="I31" s="34"/>
-      <c r="J31" s="107" t="s">
+      <c r="J31" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="K31" s="108"/>
-      <c r="L31" s="108"/>
-      <c r="M31" s="108"/>
-      <c r="N31" s="108"/>
-      <c r="O31" s="108"/>
-      <c r="P31" s="109"/>
+      <c r="K31" s="99"/>
+      <c r="L31" s="99"/>
+      <c r="M31" s="99"/>
+      <c r="N31" s="99"/>
+      <c r="O31" s="99"/>
+      <c r="P31" s="100"/>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" s="110" t="s">
+      <c r="A32" s="101" t="s">
         <v>48</v>
       </c>
-      <c r="B32" s="111"/>
-      <c r="C32" s="111"/>
-      <c r="D32" s="111"/>
-      <c r="E32" s="111"/>
-      <c r="F32" s="112" t="s">
+      <c r="B32" s="102"/>
+      <c r="C32" s="102"/>
+      <c r="D32" s="102"/>
+      <c r="E32" s="102"/>
+      <c r="F32" s="96" t="s">
         <v>55</v>
       </c>
-      <c r="G32" s="113"/>
+      <c r="G32" s="97"/>
       <c r="H32" s="29"/>
-      <c r="J32" s="110" t="s">
+      <c r="J32" s="101" t="s">
         <v>48</v>
       </c>
-      <c r="K32" s="111"/>
-      <c r="L32" s="111"/>
-      <c r="M32" s="111"/>
-      <c r="N32" s="111"/>
-      <c r="O32" s="114" t="s">
+      <c r="K32" s="102"/>
+      <c r="L32" s="102"/>
+      <c r="M32" s="102"/>
+      <c r="N32" s="102"/>
+      <c r="O32" s="103" t="s">
         <v>55</v>
       </c>
-      <c r="P32" s="115"/>
+      <c r="P32" s="104"/>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" s="95" t="s">
+      <c r="A33" s="105" t="s">
         <v>54</v>
       </c>
-      <c r="B33" s="96"/>
-      <c r="C33" s="96"/>
-      <c r="D33" s="96"/>
-      <c r="E33" s="96"/>
-      <c r="F33" s="96"/>
-      <c r="G33" s="96"/>
+      <c r="B33" s="106"/>
+      <c r="C33" s="106"/>
+      <c r="D33" s="106"/>
+      <c r="E33" s="106"/>
+      <c r="F33" s="106"/>
+      <c r="G33" s="106"/>
       <c r="H33" s="29"/>
-      <c r="J33" s="95" t="s">
+      <c r="J33" s="105" t="s">
         <v>54</v>
       </c>
-      <c r="K33" s="96"/>
-      <c r="L33" s="96"/>
-      <c r="M33" s="96"/>
-      <c r="N33" s="96"/>
-      <c r="O33" s="96"/>
-      <c r="P33" s="97"/>
+      <c r="K33" s="106"/>
+      <c r="L33" s="106"/>
+      <c r="M33" s="106"/>
+      <c r="N33" s="106"/>
+      <c r="O33" s="106"/>
+      <c r="P33" s="107"/>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34" s="95" t="s">
+      <c r="A34" s="105" t="s">
         <v>49</v>
       </c>
-      <c r="B34" s="96"/>
-      <c r="C34" s="96"/>
-      <c r="D34" s="96"/>
-      <c r="E34" s="96"/>
-      <c r="F34" s="96"/>
-      <c r="G34" s="96"/>
+      <c r="B34" s="106"/>
+      <c r="C34" s="106"/>
+      <c r="D34" s="106"/>
+      <c r="E34" s="106"/>
+      <c r="F34" s="106"/>
+      <c r="G34" s="106"/>
       <c r="H34" s="29"/>
-      <c r="J34" s="95" t="s">
+      <c r="J34" s="105" t="s">
         <v>49</v>
       </c>
-      <c r="K34" s="96"/>
-      <c r="L34" s="96"/>
-      <c r="M34" s="96"/>
-      <c r="N34" s="96"/>
-      <c r="O34" s="96"/>
-      <c r="P34" s="97"/>
+      <c r="K34" s="106"/>
+      <c r="L34" s="106"/>
+      <c r="M34" s="106"/>
+      <c r="N34" s="106"/>
+      <c r="O34" s="106"/>
+      <c r="P34" s="107"/>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A35" s="104" t="s">
+      <c r="A35" s="108" t="s">
         <v>53</v>
       </c>
-      <c r="B35" s="105"/>
-      <c r="C35" s="105"/>
-      <c r="D35" s="105"/>
-      <c r="E35" s="105"/>
-      <c r="F35" s="105"/>
-      <c r="G35" s="105"/>
+      <c r="B35" s="109"/>
+      <c r="C35" s="109"/>
+      <c r="D35" s="109"/>
+      <c r="E35" s="109"/>
+      <c r="F35" s="109"/>
+      <c r="G35" s="109"/>
       <c r="H35" s="29"/>
-      <c r="J35" s="104" t="s">
+      <c r="J35" s="108" t="s">
         <v>53</v>
       </c>
-      <c r="K35" s="105"/>
-      <c r="L35" s="105"/>
-      <c r="M35" s="105"/>
-      <c r="N35" s="105"/>
-      <c r="O35" s="105"/>
-      <c r="P35" s="106"/>
+      <c r="K35" s="109"/>
+      <c r="L35" s="109"/>
+      <c r="M35" s="109"/>
+      <c r="N35" s="109"/>
+      <c r="O35" s="109"/>
+      <c r="P35" s="110"/>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A36" s="95" t="s">
+      <c r="A36" s="105" t="s">
         <v>50</v>
       </c>
-      <c r="B36" s="96"/>
-      <c r="C36" s="96"/>
-      <c r="D36" s="96"/>
-      <c r="E36" s="96"/>
-      <c r="F36" s="96"/>
-      <c r="G36" s="96"/>
+      <c r="B36" s="106"/>
+      <c r="C36" s="106"/>
+      <c r="D36" s="106"/>
+      <c r="E36" s="106"/>
+      <c r="F36" s="106"/>
+      <c r="G36" s="106"/>
       <c r="H36" s="29"/>
-      <c r="J36" s="95" t="s">
+      <c r="J36" s="105" t="s">
         <v>50</v>
       </c>
-      <c r="K36" s="96"/>
-      <c r="L36" s="96"/>
-      <c r="M36" s="96"/>
-      <c r="N36" s="96"/>
-      <c r="O36" s="96"/>
-      <c r="P36" s="97"/>
+      <c r="K36" s="106"/>
+      <c r="L36" s="106"/>
+      <c r="M36" s="106"/>
+      <c r="N36" s="106"/>
+      <c r="O36" s="106"/>
+      <c r="P36" s="107"/>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="28"/>
@@ -11684,46 +11921,46 @@
       <c r="P37" s="29"/>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A38" s="98" t="s">
+      <c r="A38" s="113" t="s">
         <v>51</v>
       </c>
-      <c r="B38" s="99"/>
-      <c r="C38" s="99"/>
-      <c r="D38" s="99"/>
-      <c r="E38" s="99"/>
-      <c r="F38" s="99"/>
-      <c r="G38" s="99"/>
+      <c r="B38" s="114"/>
+      <c r="C38" s="114"/>
+      <c r="D38" s="114"/>
+      <c r="E38" s="114"/>
+      <c r="F38" s="114"/>
+      <c r="G38" s="114"/>
       <c r="H38" s="29"/>
-      <c r="J38" s="98" t="s">
+      <c r="J38" s="113" t="s">
         <v>51</v>
       </c>
-      <c r="K38" s="99"/>
-      <c r="L38" s="99"/>
-      <c r="M38" s="99"/>
-      <c r="N38" s="99"/>
-      <c r="O38" s="99"/>
-      <c r="P38" s="100"/>
+      <c r="K38" s="114"/>
+      <c r="L38" s="114"/>
+      <c r="M38" s="114"/>
+      <c r="N38" s="114"/>
+      <c r="O38" s="114"/>
+      <c r="P38" s="115"/>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" s="101" t="s">
+      <c r="A39" s="111" t="s">
         <v>57</v>
       </c>
-      <c r="B39" s="102"/>
-      <c r="C39" s="102"/>
-      <c r="D39" s="102"/>
-      <c r="E39" s="102"/>
-      <c r="F39" s="102"/>
-      <c r="G39" s="102"/>
+      <c r="B39" s="112"/>
+      <c r="C39" s="112"/>
+      <c r="D39" s="112"/>
+      <c r="E39" s="112"/>
+      <c r="F39" s="112"/>
+      <c r="G39" s="112"/>
       <c r="H39" s="29"/>
-      <c r="J39" s="101" t="s">
+      <c r="J39" s="111" t="s">
         <v>52</v>
       </c>
-      <c r="K39" s="102"/>
-      <c r="L39" s="102"/>
-      <c r="M39" s="102"/>
-      <c r="N39" s="102"/>
-      <c r="O39" s="102"/>
-      <c r="P39" s="103"/>
+      <c r="K39" s="112"/>
+      <c r="L39" s="112"/>
+      <c r="M39" s="112"/>
+      <c r="N39" s="112"/>
+      <c r="O39" s="112"/>
+      <c r="P39" s="116"/>
     </row>
     <row r="40" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="30"/>
@@ -11744,135 +11981,135 @@
       <c r="P40" s="33"/>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A41" s="107" t="s">
+      <c r="A41" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="B41" s="108"/>
-      <c r="C41" s="108"/>
-      <c r="D41" s="108"/>
-      <c r="E41" s="108"/>
-      <c r="F41" s="108"/>
-      <c r="G41" s="108"/>
+      <c r="B41" s="99"/>
+      <c r="C41" s="99"/>
+      <c r="D41" s="99"/>
+      <c r="E41" s="99"/>
+      <c r="F41" s="99"/>
+      <c r="G41" s="99"/>
       <c r="H41" s="27"/>
       <c r="I41" s="34"/>
-      <c r="J41" s="107" t="s">
+      <c r="J41" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="K41" s="108"/>
-      <c r="L41" s="108"/>
-      <c r="M41" s="108"/>
-      <c r="N41" s="108"/>
-      <c r="O41" s="108"/>
-      <c r="P41" s="109"/>
+      <c r="K41" s="99"/>
+      <c r="L41" s="99"/>
+      <c r="M41" s="99"/>
+      <c r="N41" s="99"/>
+      <c r="O41" s="99"/>
+      <c r="P41" s="100"/>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42" s="110" t="s">
+      <c r="A42" s="101" t="s">
         <v>48</v>
       </c>
-      <c r="B42" s="111"/>
-      <c r="C42" s="111"/>
-      <c r="D42" s="111"/>
-      <c r="E42" s="111"/>
-      <c r="F42" s="112" t="s">
+      <c r="B42" s="102"/>
+      <c r="C42" s="102"/>
+      <c r="D42" s="102"/>
+      <c r="E42" s="102"/>
+      <c r="F42" s="96" t="s">
         <v>55</v>
       </c>
-      <c r="G42" s="113"/>
+      <c r="G42" s="97"/>
       <c r="H42" s="29"/>
-      <c r="J42" s="110" t="s">
+      <c r="J42" s="101" t="s">
         <v>48</v>
       </c>
-      <c r="K42" s="111"/>
-      <c r="L42" s="111"/>
-      <c r="M42" s="111"/>
-      <c r="N42" s="111"/>
-      <c r="O42" s="114" t="s">
+      <c r="K42" s="102"/>
+      <c r="L42" s="102"/>
+      <c r="M42" s="102"/>
+      <c r="N42" s="102"/>
+      <c r="O42" s="103" t="s">
         <v>55</v>
       </c>
-      <c r="P42" s="115"/>
+      <c r="P42" s="104"/>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43" s="95" t="s">
+      <c r="A43" s="105" t="s">
         <v>54</v>
       </c>
-      <c r="B43" s="96"/>
-      <c r="C43" s="96"/>
-      <c r="D43" s="96"/>
-      <c r="E43" s="96"/>
-      <c r="F43" s="96"/>
-      <c r="G43" s="96"/>
+      <c r="B43" s="106"/>
+      <c r="C43" s="106"/>
+      <c r="D43" s="106"/>
+      <c r="E43" s="106"/>
+      <c r="F43" s="106"/>
+      <c r="G43" s="106"/>
       <c r="H43" s="29"/>
-      <c r="J43" s="95" t="s">
+      <c r="J43" s="105" t="s">
         <v>54</v>
       </c>
-      <c r="K43" s="96"/>
-      <c r="L43" s="96"/>
-      <c r="M43" s="96"/>
-      <c r="N43" s="96"/>
-      <c r="O43" s="96"/>
-      <c r="P43" s="97"/>
+      <c r="K43" s="106"/>
+      <c r="L43" s="106"/>
+      <c r="M43" s="106"/>
+      <c r="N43" s="106"/>
+      <c r="O43" s="106"/>
+      <c r="P43" s="107"/>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44" s="95" t="s">
+      <c r="A44" s="105" t="s">
         <v>49</v>
       </c>
-      <c r="B44" s="96"/>
-      <c r="C44" s="96"/>
-      <c r="D44" s="96"/>
-      <c r="E44" s="96"/>
-      <c r="F44" s="96"/>
-      <c r="G44" s="96"/>
+      <c r="B44" s="106"/>
+      <c r="C44" s="106"/>
+      <c r="D44" s="106"/>
+      <c r="E44" s="106"/>
+      <c r="F44" s="106"/>
+      <c r="G44" s="106"/>
       <c r="H44" s="29"/>
-      <c r="J44" s="95" t="s">
+      <c r="J44" s="105" t="s">
         <v>49</v>
       </c>
-      <c r="K44" s="96"/>
-      <c r="L44" s="96"/>
-      <c r="M44" s="96"/>
-      <c r="N44" s="96"/>
-      <c r="O44" s="96"/>
-      <c r="P44" s="97"/>
+      <c r="K44" s="106"/>
+      <c r="L44" s="106"/>
+      <c r="M44" s="106"/>
+      <c r="N44" s="106"/>
+      <c r="O44" s="106"/>
+      <c r="P44" s="107"/>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A45" s="104" t="s">
+      <c r="A45" s="108" t="s">
         <v>53</v>
       </c>
-      <c r="B45" s="105"/>
-      <c r="C45" s="105"/>
-      <c r="D45" s="105"/>
-      <c r="E45" s="105"/>
-      <c r="F45" s="105"/>
-      <c r="G45" s="105"/>
+      <c r="B45" s="109"/>
+      <c r="C45" s="109"/>
+      <c r="D45" s="109"/>
+      <c r="E45" s="109"/>
+      <c r="F45" s="109"/>
+      <c r="G45" s="109"/>
       <c r="H45" s="29"/>
-      <c r="J45" s="104" t="s">
+      <c r="J45" s="108" t="s">
         <v>53</v>
       </c>
-      <c r="K45" s="105"/>
-      <c r="L45" s="105"/>
-      <c r="M45" s="105"/>
-      <c r="N45" s="105"/>
-      <c r="O45" s="105"/>
-      <c r="P45" s="106"/>
+      <c r="K45" s="109"/>
+      <c r="L45" s="109"/>
+      <c r="M45" s="109"/>
+      <c r="N45" s="109"/>
+      <c r="O45" s="109"/>
+      <c r="P45" s="110"/>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A46" s="95" t="s">
+      <c r="A46" s="105" t="s">
         <v>50</v>
       </c>
-      <c r="B46" s="96"/>
-      <c r="C46" s="96"/>
-      <c r="D46" s="96"/>
-      <c r="E46" s="96"/>
-      <c r="F46" s="96"/>
-      <c r="G46" s="96"/>
+      <c r="B46" s="106"/>
+      <c r="C46" s="106"/>
+      <c r="D46" s="106"/>
+      <c r="E46" s="106"/>
+      <c r="F46" s="106"/>
+      <c r="G46" s="106"/>
       <c r="H46" s="29"/>
-      <c r="J46" s="95" t="s">
+      <c r="J46" s="105" t="s">
         <v>50</v>
       </c>
-      <c r="K46" s="96"/>
-      <c r="L46" s="96"/>
-      <c r="M46" s="96"/>
-      <c r="N46" s="96"/>
-      <c r="O46" s="96"/>
-      <c r="P46" s="97"/>
+      <c r="K46" s="106"/>
+      <c r="L46" s="106"/>
+      <c r="M46" s="106"/>
+      <c r="N46" s="106"/>
+      <c r="O46" s="106"/>
+      <c r="P46" s="107"/>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" s="28"/>
@@ -11881,46 +12118,46 @@
       <c r="P47" s="29"/>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A48" s="98" t="s">
+      <c r="A48" s="113" t="s">
         <v>51</v>
       </c>
-      <c r="B48" s="99"/>
-      <c r="C48" s="99"/>
-      <c r="D48" s="99"/>
-      <c r="E48" s="99"/>
-      <c r="F48" s="99"/>
-      <c r="G48" s="99"/>
+      <c r="B48" s="114"/>
+      <c r="C48" s="114"/>
+      <c r="D48" s="114"/>
+      <c r="E48" s="114"/>
+      <c r="F48" s="114"/>
+      <c r="G48" s="114"/>
       <c r="H48" s="29"/>
-      <c r="J48" s="98" t="s">
+      <c r="J48" s="113" t="s">
         <v>51</v>
       </c>
-      <c r="K48" s="99"/>
-      <c r="L48" s="99"/>
-      <c r="M48" s="99"/>
-      <c r="N48" s="99"/>
-      <c r="O48" s="99"/>
-      <c r="P48" s="100"/>
+      <c r="K48" s="114"/>
+      <c r="L48" s="114"/>
+      <c r="M48" s="114"/>
+      <c r="N48" s="114"/>
+      <c r="O48" s="114"/>
+      <c r="P48" s="115"/>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A49" s="101" t="s">
+      <c r="A49" s="111" t="s">
         <v>57</v>
       </c>
-      <c r="B49" s="102"/>
-      <c r="C49" s="102"/>
-      <c r="D49" s="102"/>
-      <c r="E49" s="102"/>
-      <c r="F49" s="102"/>
-      <c r="G49" s="102"/>
+      <c r="B49" s="112"/>
+      <c r="C49" s="112"/>
+      <c r="D49" s="112"/>
+      <c r="E49" s="112"/>
+      <c r="F49" s="112"/>
+      <c r="G49" s="112"/>
       <c r="H49" s="29"/>
-      <c r="J49" s="101" t="s">
+      <c r="J49" s="111" t="s">
         <v>57</v>
       </c>
-      <c r="K49" s="102"/>
-      <c r="L49" s="102"/>
-      <c r="M49" s="102"/>
-      <c r="N49" s="102"/>
-      <c r="O49" s="102"/>
-      <c r="P49" s="103"/>
+      <c r="K49" s="112"/>
+      <c r="L49" s="112"/>
+      <c r="M49" s="112"/>
+      <c r="N49" s="112"/>
+      <c r="O49" s="112"/>
+      <c r="P49" s="116"/>
     </row>
     <row r="50" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="30"/>
@@ -11941,135 +12178,135 @@
       <c r="P50" s="33"/>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A51" s="107" t="s">
+      <c r="A51" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="B51" s="108"/>
-      <c r="C51" s="108"/>
-      <c r="D51" s="108"/>
-      <c r="E51" s="108"/>
-      <c r="F51" s="108"/>
-      <c r="G51" s="108"/>
+      <c r="B51" s="99"/>
+      <c r="C51" s="99"/>
+      <c r="D51" s="99"/>
+      <c r="E51" s="99"/>
+      <c r="F51" s="99"/>
+      <c r="G51" s="99"/>
       <c r="H51" s="27"/>
       <c r="I51" s="34"/>
-      <c r="J51" s="107" t="s">
+      <c r="J51" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="K51" s="108"/>
-      <c r="L51" s="108"/>
-      <c r="M51" s="108"/>
-      <c r="N51" s="108"/>
-      <c r="O51" s="108"/>
-      <c r="P51" s="109"/>
+      <c r="K51" s="99"/>
+      <c r="L51" s="99"/>
+      <c r="M51" s="99"/>
+      <c r="N51" s="99"/>
+      <c r="O51" s="99"/>
+      <c r="P51" s="100"/>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A52" s="110" t="s">
+      <c r="A52" s="101" t="s">
         <v>48</v>
       </c>
-      <c r="B52" s="111"/>
-      <c r="C52" s="111"/>
-      <c r="D52" s="111"/>
-      <c r="E52" s="111"/>
-      <c r="F52" s="112" t="s">
+      <c r="B52" s="102"/>
+      <c r="C52" s="102"/>
+      <c r="D52" s="102"/>
+      <c r="E52" s="102"/>
+      <c r="F52" s="96" t="s">
         <v>55</v>
       </c>
-      <c r="G52" s="113"/>
+      <c r="G52" s="97"/>
       <c r="H52" s="29"/>
-      <c r="J52" s="110" t="s">
+      <c r="J52" s="101" t="s">
         <v>48</v>
       </c>
-      <c r="K52" s="111"/>
-      <c r="L52" s="111"/>
-      <c r="M52" s="111"/>
-      <c r="N52" s="111"/>
-      <c r="O52" s="114" t="s">
+      <c r="K52" s="102"/>
+      <c r="L52" s="102"/>
+      <c r="M52" s="102"/>
+      <c r="N52" s="102"/>
+      <c r="O52" s="103" t="s">
         <v>55</v>
       </c>
-      <c r="P52" s="115"/>
+      <c r="P52" s="104"/>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A53" s="95" t="s">
+      <c r="A53" s="105" t="s">
         <v>54</v>
       </c>
-      <c r="B53" s="96"/>
-      <c r="C53" s="96"/>
-      <c r="D53" s="96"/>
-      <c r="E53" s="96"/>
-      <c r="F53" s="96"/>
-      <c r="G53" s="96"/>
+      <c r="B53" s="106"/>
+      <c r="C53" s="106"/>
+      <c r="D53" s="106"/>
+      <c r="E53" s="106"/>
+      <c r="F53" s="106"/>
+      <c r="G53" s="106"/>
       <c r="H53" s="29"/>
-      <c r="J53" s="95" t="s">
+      <c r="J53" s="105" t="s">
         <v>54</v>
       </c>
-      <c r="K53" s="96"/>
-      <c r="L53" s="96"/>
-      <c r="M53" s="96"/>
-      <c r="N53" s="96"/>
-      <c r="O53" s="96"/>
-      <c r="P53" s="97"/>
+      <c r="K53" s="106"/>
+      <c r="L53" s="106"/>
+      <c r="M53" s="106"/>
+      <c r="N53" s="106"/>
+      <c r="O53" s="106"/>
+      <c r="P53" s="107"/>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A54" s="95" t="s">
+      <c r="A54" s="105" t="s">
         <v>49</v>
       </c>
-      <c r="B54" s="96"/>
-      <c r="C54" s="96"/>
-      <c r="D54" s="96"/>
-      <c r="E54" s="96"/>
-      <c r="F54" s="96"/>
-      <c r="G54" s="96"/>
+      <c r="B54" s="106"/>
+      <c r="C54" s="106"/>
+      <c r="D54" s="106"/>
+      <c r="E54" s="106"/>
+      <c r="F54" s="106"/>
+      <c r="G54" s="106"/>
       <c r="H54" s="29"/>
-      <c r="J54" s="95" t="s">
+      <c r="J54" s="105" t="s">
         <v>49</v>
       </c>
-      <c r="K54" s="96"/>
-      <c r="L54" s="96"/>
-      <c r="M54" s="96"/>
-      <c r="N54" s="96"/>
-      <c r="O54" s="96"/>
-      <c r="P54" s="97"/>
+      <c r="K54" s="106"/>
+      <c r="L54" s="106"/>
+      <c r="M54" s="106"/>
+      <c r="N54" s="106"/>
+      <c r="O54" s="106"/>
+      <c r="P54" s="107"/>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A55" s="104" t="s">
+      <c r="A55" s="108" t="s">
         <v>53</v>
       </c>
-      <c r="B55" s="105"/>
-      <c r="C55" s="105"/>
-      <c r="D55" s="105"/>
-      <c r="E55" s="105"/>
-      <c r="F55" s="105"/>
-      <c r="G55" s="105"/>
+      <c r="B55" s="109"/>
+      <c r="C55" s="109"/>
+      <c r="D55" s="109"/>
+      <c r="E55" s="109"/>
+      <c r="F55" s="109"/>
+      <c r="G55" s="109"/>
       <c r="H55" s="29"/>
-      <c r="J55" s="104" t="s">
+      <c r="J55" s="108" t="s">
         <v>53</v>
       </c>
-      <c r="K55" s="105"/>
-      <c r="L55" s="105"/>
-      <c r="M55" s="105"/>
-      <c r="N55" s="105"/>
-      <c r="O55" s="105"/>
-      <c r="P55" s="106"/>
+      <c r="K55" s="109"/>
+      <c r="L55" s="109"/>
+      <c r="M55" s="109"/>
+      <c r="N55" s="109"/>
+      <c r="O55" s="109"/>
+      <c r="P55" s="110"/>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A56" s="95" t="s">
+      <c r="A56" s="105" t="s">
         <v>50</v>
       </c>
-      <c r="B56" s="96"/>
-      <c r="C56" s="96"/>
-      <c r="D56" s="96"/>
-      <c r="E56" s="96"/>
-      <c r="F56" s="96"/>
-      <c r="G56" s="96"/>
+      <c r="B56" s="106"/>
+      <c r="C56" s="106"/>
+      <c r="D56" s="106"/>
+      <c r="E56" s="106"/>
+      <c r="F56" s="106"/>
+      <c r="G56" s="106"/>
       <c r="H56" s="29"/>
-      <c r="J56" s="95" t="s">
+      <c r="J56" s="105" t="s">
         <v>50</v>
       </c>
-      <c r="K56" s="96"/>
-      <c r="L56" s="96"/>
-      <c r="M56" s="96"/>
-      <c r="N56" s="96"/>
-      <c r="O56" s="96"/>
-      <c r="P56" s="97"/>
+      <c r="K56" s="106"/>
+      <c r="L56" s="106"/>
+      <c r="M56" s="106"/>
+      <c r="N56" s="106"/>
+      <c r="O56" s="106"/>
+      <c r="P56" s="107"/>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57" s="28"/>
@@ -12078,46 +12315,46 @@
       <c r="P57" s="29"/>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A58" s="98" t="s">
+      <c r="A58" s="113" t="s">
         <v>51</v>
       </c>
-      <c r="B58" s="99"/>
-      <c r="C58" s="99"/>
-      <c r="D58" s="99"/>
-      <c r="E58" s="99"/>
-      <c r="F58" s="99"/>
-      <c r="G58" s="99"/>
+      <c r="B58" s="114"/>
+      <c r="C58" s="114"/>
+      <c r="D58" s="114"/>
+      <c r="E58" s="114"/>
+      <c r="F58" s="114"/>
+      <c r="G58" s="114"/>
       <c r="H58" s="29"/>
-      <c r="J58" s="98" t="s">
+      <c r="J58" s="113" t="s">
         <v>51</v>
       </c>
-      <c r="K58" s="99"/>
-      <c r="L58" s="99"/>
-      <c r="M58" s="99"/>
-      <c r="N58" s="99"/>
-      <c r="O58" s="99"/>
-      <c r="P58" s="100"/>
+      <c r="K58" s="114"/>
+      <c r="L58" s="114"/>
+      <c r="M58" s="114"/>
+      <c r="N58" s="114"/>
+      <c r="O58" s="114"/>
+      <c r="P58" s="115"/>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A59" s="101" t="s">
+      <c r="A59" s="111" t="s">
         <v>57</v>
       </c>
-      <c r="B59" s="102"/>
-      <c r="C59" s="102"/>
-      <c r="D59" s="102"/>
-      <c r="E59" s="102"/>
-      <c r="F59" s="102"/>
-      <c r="G59" s="102"/>
+      <c r="B59" s="112"/>
+      <c r="C59" s="112"/>
+      <c r="D59" s="112"/>
+      <c r="E59" s="112"/>
+      <c r="F59" s="112"/>
+      <c r="G59" s="112"/>
       <c r="H59" s="29"/>
-      <c r="J59" s="101" t="s">
+      <c r="J59" s="111" t="s">
         <v>57</v>
       </c>
-      <c r="K59" s="102"/>
-      <c r="L59" s="102"/>
-      <c r="M59" s="102"/>
-      <c r="N59" s="102"/>
-      <c r="O59" s="102"/>
-      <c r="P59" s="103"/>
+      <c r="K59" s="112"/>
+      <c r="L59" s="112"/>
+      <c r="M59" s="112"/>
+      <c r="N59" s="112"/>
+      <c r="O59" s="112"/>
+      <c r="P59" s="116"/>
     </row>
     <row r="60" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="30"/>
@@ -12138,135 +12375,135 @@
       <c r="P60" s="33"/>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A61" s="107" t="s">
+      <c r="A61" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="B61" s="108"/>
-      <c r="C61" s="108"/>
-      <c r="D61" s="108"/>
-      <c r="E61" s="108"/>
-      <c r="F61" s="108"/>
-      <c r="G61" s="108"/>
+      <c r="B61" s="99"/>
+      <c r="C61" s="99"/>
+      <c r="D61" s="99"/>
+      <c r="E61" s="99"/>
+      <c r="F61" s="99"/>
+      <c r="G61" s="99"/>
       <c r="H61" s="27"/>
       <c r="I61" s="34"/>
-      <c r="J61" s="107" t="s">
+      <c r="J61" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="K61" s="108"/>
-      <c r="L61" s="108"/>
-      <c r="M61" s="108"/>
-      <c r="N61" s="108"/>
-      <c r="O61" s="108"/>
-      <c r="P61" s="109"/>
+      <c r="K61" s="99"/>
+      <c r="L61" s="99"/>
+      <c r="M61" s="99"/>
+      <c r="N61" s="99"/>
+      <c r="O61" s="99"/>
+      <c r="P61" s="100"/>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A62" s="110" t="s">
+      <c r="A62" s="101" t="s">
         <v>48</v>
       </c>
-      <c r="B62" s="111"/>
-      <c r="C62" s="111"/>
-      <c r="D62" s="111"/>
-      <c r="E62" s="111"/>
-      <c r="F62" s="112" t="s">
+      <c r="B62" s="102"/>
+      <c r="C62" s="102"/>
+      <c r="D62" s="102"/>
+      <c r="E62" s="102"/>
+      <c r="F62" s="96" t="s">
         <v>55</v>
       </c>
-      <c r="G62" s="113"/>
+      <c r="G62" s="97"/>
       <c r="H62" s="29"/>
-      <c r="J62" s="110" t="s">
+      <c r="J62" s="101" t="s">
         <v>48</v>
       </c>
-      <c r="K62" s="111"/>
-      <c r="L62" s="111"/>
-      <c r="M62" s="111"/>
-      <c r="N62" s="111"/>
-      <c r="O62" s="114" t="s">
+      <c r="K62" s="102"/>
+      <c r="L62" s="102"/>
+      <c r="M62" s="102"/>
+      <c r="N62" s="102"/>
+      <c r="O62" s="103" t="s">
         <v>55</v>
       </c>
-      <c r="P62" s="115"/>
+      <c r="P62" s="104"/>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A63" s="95" t="s">
+      <c r="A63" s="105" t="s">
         <v>54</v>
       </c>
-      <c r="B63" s="96"/>
-      <c r="C63" s="96"/>
-      <c r="D63" s="96"/>
-      <c r="E63" s="96"/>
-      <c r="F63" s="96"/>
-      <c r="G63" s="96"/>
+      <c r="B63" s="106"/>
+      <c r="C63" s="106"/>
+      <c r="D63" s="106"/>
+      <c r="E63" s="106"/>
+      <c r="F63" s="106"/>
+      <c r="G63" s="106"/>
       <c r="H63" s="29"/>
-      <c r="J63" s="95" t="s">
+      <c r="J63" s="105" t="s">
         <v>54</v>
       </c>
-      <c r="K63" s="96"/>
-      <c r="L63" s="96"/>
-      <c r="M63" s="96"/>
-      <c r="N63" s="96"/>
-      <c r="O63" s="96"/>
-      <c r="P63" s="97"/>
+      <c r="K63" s="106"/>
+      <c r="L63" s="106"/>
+      <c r="M63" s="106"/>
+      <c r="N63" s="106"/>
+      <c r="O63" s="106"/>
+      <c r="P63" s="107"/>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A64" s="95" t="s">
+      <c r="A64" s="105" t="s">
         <v>49</v>
       </c>
-      <c r="B64" s="96"/>
-      <c r="C64" s="96"/>
-      <c r="D64" s="96"/>
-      <c r="E64" s="96"/>
-      <c r="F64" s="96"/>
-      <c r="G64" s="96"/>
+      <c r="B64" s="106"/>
+      <c r="C64" s="106"/>
+      <c r="D64" s="106"/>
+      <c r="E64" s="106"/>
+      <c r="F64" s="106"/>
+      <c r="G64" s="106"/>
       <c r="H64" s="29"/>
-      <c r="J64" s="95" t="s">
+      <c r="J64" s="105" t="s">
         <v>49</v>
       </c>
-      <c r="K64" s="96"/>
-      <c r="L64" s="96"/>
-      <c r="M64" s="96"/>
-      <c r="N64" s="96"/>
-      <c r="O64" s="96"/>
-      <c r="P64" s="97"/>
+      <c r="K64" s="106"/>
+      <c r="L64" s="106"/>
+      <c r="M64" s="106"/>
+      <c r="N64" s="106"/>
+      <c r="O64" s="106"/>
+      <c r="P64" s="107"/>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A65" s="104" t="s">
+      <c r="A65" s="108" t="s">
         <v>53</v>
       </c>
-      <c r="B65" s="105"/>
-      <c r="C65" s="105"/>
-      <c r="D65" s="105"/>
-      <c r="E65" s="105"/>
-      <c r="F65" s="105"/>
-      <c r="G65" s="105"/>
+      <c r="B65" s="109"/>
+      <c r="C65" s="109"/>
+      <c r="D65" s="109"/>
+      <c r="E65" s="109"/>
+      <c r="F65" s="109"/>
+      <c r="G65" s="109"/>
       <c r="H65" s="29"/>
-      <c r="J65" s="104" t="s">
+      <c r="J65" s="108" t="s">
         <v>53</v>
       </c>
-      <c r="K65" s="105"/>
-      <c r="L65" s="105"/>
-      <c r="M65" s="105"/>
-      <c r="N65" s="105"/>
-      <c r="O65" s="105"/>
-      <c r="P65" s="106"/>
+      <c r="K65" s="109"/>
+      <c r="L65" s="109"/>
+      <c r="M65" s="109"/>
+      <c r="N65" s="109"/>
+      <c r="O65" s="109"/>
+      <c r="P65" s="110"/>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A66" s="95" t="s">
+      <c r="A66" s="105" t="s">
         <v>50</v>
       </c>
-      <c r="B66" s="96"/>
-      <c r="C66" s="96"/>
-      <c r="D66" s="96"/>
-      <c r="E66" s="96"/>
-      <c r="F66" s="96"/>
-      <c r="G66" s="96"/>
+      <c r="B66" s="106"/>
+      <c r="C66" s="106"/>
+      <c r="D66" s="106"/>
+      <c r="E66" s="106"/>
+      <c r="F66" s="106"/>
+      <c r="G66" s="106"/>
       <c r="H66" s="29"/>
-      <c r="J66" s="95" t="s">
+      <c r="J66" s="105" t="s">
         <v>50</v>
       </c>
-      <c r="K66" s="96"/>
-      <c r="L66" s="96"/>
-      <c r="M66" s="96"/>
-      <c r="N66" s="96"/>
-      <c r="O66" s="96"/>
-      <c r="P66" s="97"/>
+      <c r="K66" s="106"/>
+      <c r="L66" s="106"/>
+      <c r="M66" s="106"/>
+      <c r="N66" s="106"/>
+      <c r="O66" s="106"/>
+      <c r="P66" s="107"/>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" s="28"/>
@@ -12275,46 +12512,46 @@
       <c r="P67" s="29"/>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A68" s="98" t="s">
+      <c r="A68" s="113" t="s">
         <v>51</v>
       </c>
-      <c r="B68" s="99"/>
-      <c r="C68" s="99"/>
-      <c r="D68" s="99"/>
-      <c r="E68" s="99"/>
-      <c r="F68" s="99"/>
-      <c r="G68" s="99"/>
+      <c r="B68" s="114"/>
+      <c r="C68" s="114"/>
+      <c r="D68" s="114"/>
+      <c r="E68" s="114"/>
+      <c r="F68" s="114"/>
+      <c r="G68" s="114"/>
       <c r="H68" s="29"/>
-      <c r="J68" s="98" t="s">
+      <c r="J68" s="113" t="s">
         <v>51</v>
       </c>
-      <c r="K68" s="99"/>
-      <c r="L68" s="99"/>
-      <c r="M68" s="99"/>
-      <c r="N68" s="99"/>
-      <c r="O68" s="99"/>
-      <c r="P68" s="100"/>
+      <c r="K68" s="114"/>
+      <c r="L68" s="114"/>
+      <c r="M68" s="114"/>
+      <c r="N68" s="114"/>
+      <c r="O68" s="114"/>
+      <c r="P68" s="115"/>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A69" s="101" t="s">
+      <c r="A69" s="111" t="s">
         <v>56</v>
       </c>
-      <c r="B69" s="102"/>
-      <c r="C69" s="102"/>
-      <c r="D69" s="102"/>
-      <c r="E69" s="102"/>
-      <c r="F69" s="102"/>
-      <c r="G69" s="102"/>
+      <c r="B69" s="112"/>
+      <c r="C69" s="112"/>
+      <c r="D69" s="112"/>
+      <c r="E69" s="112"/>
+      <c r="F69" s="112"/>
+      <c r="G69" s="112"/>
       <c r="H69" s="29"/>
-      <c r="J69" s="101" t="s">
+      <c r="J69" s="111" t="s">
         <v>57</v>
       </c>
-      <c r="K69" s="102"/>
-      <c r="L69" s="102"/>
-      <c r="M69" s="102"/>
-      <c r="N69" s="102"/>
-      <c r="O69" s="102"/>
-      <c r="P69" s="103"/>
+      <c r="K69" s="112"/>
+      <c r="L69" s="112"/>
+      <c r="M69" s="112"/>
+      <c r="N69" s="112"/>
+      <c r="O69" s="112"/>
+      <c r="P69" s="116"/>
     </row>
     <row r="70" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="30"/>
@@ -12336,6 +12573,116 @@
     </row>
   </sheetData>
   <mergeCells count="126">
+    <mergeCell ref="A66:G66"/>
+    <mergeCell ref="J66:P66"/>
+    <mergeCell ref="A68:G68"/>
+    <mergeCell ref="J68:P68"/>
+    <mergeCell ref="A69:G69"/>
+    <mergeCell ref="J69:P69"/>
+    <mergeCell ref="A63:G63"/>
+    <mergeCell ref="J63:P63"/>
+    <mergeCell ref="A64:G64"/>
+    <mergeCell ref="J64:P64"/>
+    <mergeCell ref="A65:G65"/>
+    <mergeCell ref="J65:P65"/>
+    <mergeCell ref="A61:G61"/>
+    <mergeCell ref="J61:P61"/>
+    <mergeCell ref="A62:E62"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="J62:N62"/>
+    <mergeCell ref="O62:P62"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="J56:P56"/>
+    <mergeCell ref="A58:G58"/>
+    <mergeCell ref="J58:P58"/>
+    <mergeCell ref="A59:G59"/>
+    <mergeCell ref="J59:P59"/>
+    <mergeCell ref="A53:G53"/>
+    <mergeCell ref="J53:P53"/>
+    <mergeCell ref="A54:G54"/>
+    <mergeCell ref="J54:P54"/>
+    <mergeCell ref="A55:G55"/>
+    <mergeCell ref="J55:P55"/>
+    <mergeCell ref="A51:G51"/>
+    <mergeCell ref="J51:P51"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="J52:N52"/>
+    <mergeCell ref="O52:P52"/>
+    <mergeCell ref="A46:G46"/>
+    <mergeCell ref="J46:P46"/>
+    <mergeCell ref="A48:G48"/>
+    <mergeCell ref="J48:P48"/>
+    <mergeCell ref="A49:G49"/>
+    <mergeCell ref="J49:P49"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="J43:P43"/>
+    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="J44:P44"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="J45:P45"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="J41:P41"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="J42:N42"/>
+    <mergeCell ref="O42:P42"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="J36:P36"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="J38:P38"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="J39:P39"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="J33:P33"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="J34:P34"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="J35:P35"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="J32:N32"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="J22:N22"/>
+    <mergeCell ref="O22:P22"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="J12:N12"/>
+    <mergeCell ref="O12:P12"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="J2:N2"/>
@@ -12352,116 +12699,6 @@
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="J12:N12"/>
-    <mergeCell ref="O12:P12"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="J22:N22"/>
-    <mergeCell ref="O22:P22"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="J33:P33"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="J34:P34"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="J35:P35"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="A32:E32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="J32:N32"/>
-    <mergeCell ref="O32:P32"/>
-    <mergeCell ref="A41:G41"/>
-    <mergeCell ref="J41:P41"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="J42:N42"/>
-    <mergeCell ref="O42:P42"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="J36:P36"/>
-    <mergeCell ref="A38:G38"/>
-    <mergeCell ref="J38:P38"/>
-    <mergeCell ref="A39:G39"/>
-    <mergeCell ref="J39:P39"/>
-    <mergeCell ref="A46:G46"/>
-    <mergeCell ref="J46:P46"/>
-    <mergeCell ref="A48:G48"/>
-    <mergeCell ref="J48:P48"/>
-    <mergeCell ref="A49:G49"/>
-    <mergeCell ref="J49:P49"/>
-    <mergeCell ref="A43:G43"/>
-    <mergeCell ref="J43:P43"/>
-    <mergeCell ref="A44:G44"/>
-    <mergeCell ref="J44:P44"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="J45:P45"/>
-    <mergeCell ref="A53:G53"/>
-    <mergeCell ref="J53:P53"/>
-    <mergeCell ref="A54:G54"/>
-    <mergeCell ref="J54:P54"/>
-    <mergeCell ref="A55:G55"/>
-    <mergeCell ref="J55:P55"/>
-    <mergeCell ref="A51:G51"/>
-    <mergeCell ref="J51:P51"/>
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="J52:N52"/>
-    <mergeCell ref="O52:P52"/>
-    <mergeCell ref="A61:G61"/>
-    <mergeCell ref="J61:P61"/>
-    <mergeCell ref="A62:E62"/>
-    <mergeCell ref="F62:G62"/>
-    <mergeCell ref="J62:N62"/>
-    <mergeCell ref="O62:P62"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="J56:P56"/>
-    <mergeCell ref="A58:G58"/>
-    <mergeCell ref="J58:P58"/>
-    <mergeCell ref="A59:G59"/>
-    <mergeCell ref="J59:P59"/>
-    <mergeCell ref="A66:G66"/>
-    <mergeCell ref="J66:P66"/>
-    <mergeCell ref="A68:G68"/>
-    <mergeCell ref="J68:P68"/>
-    <mergeCell ref="A69:G69"/>
-    <mergeCell ref="J69:P69"/>
-    <mergeCell ref="A63:G63"/>
-    <mergeCell ref="J63:P63"/>
-    <mergeCell ref="A64:G64"/>
-    <mergeCell ref="J64:P64"/>
-    <mergeCell ref="A65:G65"/>
-    <mergeCell ref="J65:P65"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="70" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -12486,61 +12723,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
-      <c r="J1" s="134"/>
-      <c r="K1" s="134"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
     </row>
     <row r="2" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="134"/>
-      <c r="C2" s="134"/>
-      <c r="D2" s="134"/>
-      <c r="E2" s="134"/>
-      <c r="F2" s="134"/>
-      <c r="G2" s="134"/>
-      <c r="H2" s="134"/>
-      <c r="I2" s="134"/>
-      <c r="J2" s="134"/>
-      <c r="K2" s="134"/>
+      <c r="B2" s="117"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="117"/>
+      <c r="E2" s="117"/>
+      <c r="F2" s="117"/>
+      <c r="G2" s="117"/>
+      <c r="H2" s="117"/>
+      <c r="I2" s="117"/>
+      <c r="J2" s="117"/>
+      <c r="K2" s="117"/>
     </row>
     <row r="3" spans="2:11" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="134"/>
-      <c r="C3" s="134"/>
-      <c r="D3" s="134"/>
-      <c r="E3" s="134"/>
-      <c r="F3" s="134"/>
-      <c r="G3" s="134"/>
-      <c r="H3" s="134"/>
-      <c r="I3" s="134"/>
-      <c r="J3" s="134"/>
-      <c r="K3" s="134"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="117"/>
+      <c r="D3" s="117"/>
+      <c r="E3" s="117"/>
+      <c r="F3" s="117"/>
+      <c r="G3" s="117"/>
+      <c r="H3" s="117"/>
+      <c r="I3" s="117"/>
+      <c r="J3" s="117"/>
+      <c r="K3" s="117"/>
     </row>
     <row r="4" spans="2:11" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="134"/>
-      <c r="C4" s="134"/>
-      <c r="D4" s="134"/>
-      <c r="E4" s="134"/>
-      <c r="F4" s="134"/>
-      <c r="G4" s="134"/>
-      <c r="H4" s="134"/>
-      <c r="I4" s="134"/>
-      <c r="J4" s="134"/>
-      <c r="K4" s="134"/>
+      <c r="B4" s="117"/>
+      <c r="C4" s="117"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="117"/>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B5" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="132">
+      <c r="C5" s="135">
         <v>43509</v>
       </c>
-      <c r="D5" s="133"/>
+      <c r="D5" s="136"/>
       <c r="E5" s="40" t="s">
         <v>1</v>
       </c>
@@ -12550,10 +12787,10 @@
       <c r="G5" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="H5" s="132">
+      <c r="H5" s="135">
         <v>43516</v>
       </c>
-      <c r="I5" s="133"/>
+      <c r="I5" s="136"/>
       <c r="J5" s="40" t="s">
         <v>1</v>
       </c>
@@ -12562,129 +12799,129 @@
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B6" s="124" t="s">
+      <c r="B6" s="118" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="125"/>
-      <c r="D6" s="125"/>
-      <c r="E6" s="126"/>
-      <c r="F6" s="126"/>
-      <c r="G6" s="125" t="s">
+      <c r="C6" s="119"/>
+      <c r="D6" s="119"/>
+      <c r="E6" s="120"/>
+      <c r="F6" s="120"/>
+      <c r="G6" s="119" t="s">
         <v>59</v>
       </c>
-      <c r="H6" s="125"/>
-      <c r="I6" s="125"/>
-      <c r="J6" s="126"/>
-      <c r="K6" s="127"/>
+      <c r="H6" s="119"/>
+      <c r="I6" s="119"/>
+      <c r="J6" s="120"/>
+      <c r="K6" s="130"/>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B7" s="135" t="s">
+      <c r="B7" s="121" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="136"/>
-      <c r="D7" s="136"/>
-      <c r="E7" s="136"/>
-      <c r="F7" s="137"/>
-      <c r="G7" s="144" t="s">
+      <c r="C7" s="122"/>
+      <c r="D7" s="122"/>
+      <c r="E7" s="122"/>
+      <c r="F7" s="123"/>
+      <c r="G7" s="131" t="s">
         <v>62</v>
       </c>
-      <c r="H7" s="144"/>
-      <c r="I7" s="144"/>
-      <c r="J7" s="144"/>
-      <c r="K7" s="145"/>
+      <c r="H7" s="131"/>
+      <c r="I7" s="131"/>
+      <c r="J7" s="131"/>
+      <c r="K7" s="132"/>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B8" s="138"/>
-      <c r="C8" s="139"/>
-      <c r="D8" s="139"/>
-      <c r="E8" s="139"/>
-      <c r="F8" s="140"/>
-      <c r="G8" s="144"/>
-      <c r="H8" s="144"/>
-      <c r="I8" s="144"/>
-      <c r="J8" s="144"/>
-      <c r="K8" s="145"/>
+      <c r="B8" s="124"/>
+      <c r="C8" s="125"/>
+      <c r="D8" s="125"/>
+      <c r="E8" s="125"/>
+      <c r="F8" s="126"/>
+      <c r="G8" s="131"/>
+      <c r="H8" s="131"/>
+      <c r="I8" s="131"/>
+      <c r="J8" s="131"/>
+      <c r="K8" s="132"/>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B9" s="138"/>
-      <c r="C9" s="139"/>
-      <c r="D9" s="139"/>
-      <c r="E9" s="139"/>
-      <c r="F9" s="140"/>
-      <c r="G9" s="144"/>
-      <c r="H9" s="144"/>
-      <c r="I9" s="144"/>
-      <c r="J9" s="144"/>
-      <c r="K9" s="145"/>
+      <c r="B9" s="124"/>
+      <c r="C9" s="125"/>
+      <c r="D9" s="125"/>
+      <c r="E9" s="125"/>
+      <c r="F9" s="126"/>
+      <c r="G9" s="131"/>
+      <c r="H9" s="131"/>
+      <c r="I9" s="131"/>
+      <c r="J9" s="131"/>
+      <c r="K9" s="132"/>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B10" s="138"/>
-      <c r="C10" s="139"/>
-      <c r="D10" s="139"/>
-      <c r="E10" s="139"/>
-      <c r="F10" s="140"/>
-      <c r="G10" s="144"/>
-      <c r="H10" s="144"/>
-      <c r="I10" s="144"/>
-      <c r="J10" s="144"/>
-      <c r="K10" s="145"/>
+      <c r="B10" s="124"/>
+      <c r="C10" s="125"/>
+      <c r="D10" s="125"/>
+      <c r="E10" s="125"/>
+      <c r="F10" s="126"/>
+      <c r="G10" s="131"/>
+      <c r="H10" s="131"/>
+      <c r="I10" s="131"/>
+      <c r="J10" s="131"/>
+      <c r="K10" s="132"/>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B11" s="138"/>
-      <c r="C11" s="139"/>
-      <c r="D11" s="139"/>
-      <c r="E11" s="139"/>
-      <c r="F11" s="140"/>
-      <c r="G11" s="144"/>
-      <c r="H11" s="144"/>
-      <c r="I11" s="144"/>
-      <c r="J11" s="144"/>
-      <c r="K11" s="145"/>
+      <c r="B11" s="124"/>
+      <c r="C11" s="125"/>
+      <c r="D11" s="125"/>
+      <c r="E11" s="125"/>
+      <c r="F11" s="126"/>
+      <c r="G11" s="131"/>
+      <c r="H11" s="131"/>
+      <c r="I11" s="131"/>
+      <c r="J11" s="131"/>
+      <c r="K11" s="132"/>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B12" s="138"/>
-      <c r="C12" s="139"/>
-      <c r="D12" s="139"/>
-      <c r="E12" s="139"/>
-      <c r="F12" s="140"/>
-      <c r="G12" s="144"/>
-      <c r="H12" s="144"/>
-      <c r="I12" s="144"/>
-      <c r="J12" s="144"/>
-      <c r="K12" s="145"/>
+      <c r="B12" s="124"/>
+      <c r="C12" s="125"/>
+      <c r="D12" s="125"/>
+      <c r="E12" s="125"/>
+      <c r="F12" s="126"/>
+      <c r="G12" s="131"/>
+      <c r="H12" s="131"/>
+      <c r="I12" s="131"/>
+      <c r="J12" s="131"/>
+      <c r="K12" s="132"/>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B13" s="138"/>
-      <c r="C13" s="139"/>
-      <c r="D13" s="139"/>
-      <c r="E13" s="139"/>
-      <c r="F13" s="140"/>
-      <c r="G13" s="144"/>
-      <c r="H13" s="144"/>
-      <c r="I13" s="144"/>
-      <c r="J13" s="144"/>
-      <c r="K13" s="145"/>
+      <c r="B13" s="124"/>
+      <c r="C13" s="125"/>
+      <c r="D13" s="125"/>
+      <c r="E13" s="125"/>
+      <c r="F13" s="126"/>
+      <c r="G13" s="131"/>
+      <c r="H13" s="131"/>
+      <c r="I13" s="131"/>
+      <c r="J13" s="131"/>
+      <c r="K13" s="132"/>
     </row>
     <row r="14" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="141"/>
-      <c r="C14" s="142"/>
-      <c r="D14" s="142"/>
-      <c r="E14" s="142"/>
-      <c r="F14" s="143"/>
-      <c r="G14" s="144"/>
-      <c r="H14" s="144"/>
-      <c r="I14" s="144"/>
-      <c r="J14" s="146"/>
-      <c r="K14" s="147"/>
+      <c r="B14" s="127"/>
+      <c r="C14" s="128"/>
+      <c r="D14" s="128"/>
+      <c r="E14" s="128"/>
+      <c r="F14" s="129"/>
+      <c r="G14" s="131"/>
+      <c r="H14" s="131"/>
+      <c r="I14" s="131"/>
+      <c r="J14" s="133"/>
+      <c r="K14" s="134"/>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" s="44" t="s">
         <v>58</v>
       </c>
-      <c r="C15" s="130">
+      <c r="C15" s="137">
         <v>43523</v>
       </c>
-      <c r="D15" s="131"/>
+      <c r="D15" s="138"/>
       <c r="E15" s="35" t="s">
         <v>1</v>
       </c>
@@ -12694,10 +12931,10 @@
       <c r="G15" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="H15" s="122">
+      <c r="H15" s="139">
         <v>43530</v>
       </c>
-      <c r="I15" s="123"/>
+      <c r="I15" s="140"/>
       <c r="J15" s="35" t="s">
         <v>1</v>
       </c>
@@ -12706,127 +12943,127 @@
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B16" s="124" t="s">
+      <c r="B16" s="118" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="125"/>
-      <c r="D16" s="125"/>
-      <c r="E16" s="126"/>
-      <c r="F16" s="126"/>
-      <c r="G16" s="125" t="s">
+      <c r="C16" s="119"/>
+      <c r="D16" s="119"/>
+      <c r="E16" s="120"/>
+      <c r="F16" s="120"/>
+      <c r="G16" s="119" t="s">
         <v>59</v>
       </c>
-      <c r="H16" s="125"/>
-      <c r="I16" s="125"/>
-      <c r="J16" s="126"/>
-      <c r="K16" s="127"/>
+      <c r="H16" s="119"/>
+      <c r="I16" s="119"/>
+      <c r="J16" s="120"/>
+      <c r="K16" s="130"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B17" s="128" t="s">
+      <c r="B17" s="144" t="s">
         <v>60</v>
       </c>
-      <c r="C17" s="129"/>
-      <c r="D17" s="129"/>
-      <c r="E17" s="129"/>
-      <c r="F17" s="129"/>
-      <c r="G17" s="117"/>
-      <c r="H17" s="117"/>
-      <c r="I17" s="117"/>
-      <c r="J17" s="117"/>
-      <c r="K17" s="120"/>
+      <c r="C17" s="145"/>
+      <c r="D17" s="145"/>
+      <c r="E17" s="145"/>
+      <c r="F17" s="145"/>
+      <c r="G17" s="142"/>
+      <c r="H17" s="142"/>
+      <c r="I17" s="142"/>
+      <c r="J17" s="142"/>
+      <c r="K17" s="143"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B18" s="128"/>
-      <c r="C18" s="129"/>
-      <c r="D18" s="129"/>
-      <c r="E18" s="129"/>
-      <c r="F18" s="129"/>
-      <c r="G18" s="117"/>
-      <c r="H18" s="117"/>
-      <c r="I18" s="117"/>
-      <c r="J18" s="117"/>
-      <c r="K18" s="120"/>
+      <c r="B18" s="144"/>
+      <c r="C18" s="145"/>
+      <c r="D18" s="145"/>
+      <c r="E18" s="145"/>
+      <c r="F18" s="145"/>
+      <c r="G18" s="142"/>
+      <c r="H18" s="142"/>
+      <c r="I18" s="142"/>
+      <c r="J18" s="142"/>
+      <c r="K18" s="143"/>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B19" s="128"/>
-      <c r="C19" s="129"/>
-      <c r="D19" s="129"/>
-      <c r="E19" s="129"/>
-      <c r="F19" s="129"/>
-      <c r="G19" s="117"/>
-      <c r="H19" s="117"/>
-      <c r="I19" s="117"/>
-      <c r="J19" s="117"/>
-      <c r="K19" s="120"/>
+      <c r="B19" s="144"/>
+      <c r="C19" s="145"/>
+      <c r="D19" s="145"/>
+      <c r="E19" s="145"/>
+      <c r="F19" s="145"/>
+      <c r="G19" s="142"/>
+      <c r="H19" s="142"/>
+      <c r="I19" s="142"/>
+      <c r="J19" s="142"/>
+      <c r="K19" s="143"/>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B20" s="128"/>
-      <c r="C20" s="129"/>
-      <c r="D20" s="129"/>
-      <c r="E20" s="129"/>
-      <c r="F20" s="129"/>
-      <c r="G20" s="117"/>
-      <c r="H20" s="117"/>
-      <c r="I20" s="117"/>
-      <c r="J20" s="117"/>
-      <c r="K20" s="120"/>
+      <c r="B20" s="144"/>
+      <c r="C20" s="145"/>
+      <c r="D20" s="145"/>
+      <c r="E20" s="145"/>
+      <c r="F20" s="145"/>
+      <c r="G20" s="142"/>
+      <c r="H20" s="142"/>
+      <c r="I20" s="142"/>
+      <c r="J20" s="142"/>
+      <c r="K20" s="143"/>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B21" s="128"/>
-      <c r="C21" s="129"/>
-      <c r="D21" s="129"/>
-      <c r="E21" s="129"/>
-      <c r="F21" s="129"/>
-      <c r="G21" s="117"/>
-      <c r="H21" s="117"/>
-      <c r="I21" s="117"/>
-      <c r="J21" s="117"/>
-      <c r="K21" s="120"/>
+      <c r="B21" s="144"/>
+      <c r="C21" s="145"/>
+      <c r="D21" s="145"/>
+      <c r="E21" s="145"/>
+      <c r="F21" s="145"/>
+      <c r="G21" s="142"/>
+      <c r="H21" s="142"/>
+      <c r="I21" s="142"/>
+      <c r="J21" s="142"/>
+      <c r="K21" s="143"/>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B22" s="128"/>
-      <c r="C22" s="129"/>
-      <c r="D22" s="129"/>
-      <c r="E22" s="129"/>
-      <c r="F22" s="129"/>
-      <c r="G22" s="117"/>
-      <c r="H22" s="117"/>
-      <c r="I22" s="117"/>
-      <c r="J22" s="117"/>
-      <c r="K22" s="120"/>
+      <c r="B22" s="144"/>
+      <c r="C22" s="145"/>
+      <c r="D22" s="145"/>
+      <c r="E22" s="145"/>
+      <c r="F22" s="145"/>
+      <c r="G22" s="142"/>
+      <c r="H22" s="142"/>
+      <c r="I22" s="142"/>
+      <c r="J22" s="142"/>
+      <c r="K22" s="143"/>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B23" s="128"/>
-      <c r="C23" s="129"/>
-      <c r="D23" s="129"/>
-      <c r="E23" s="129"/>
-      <c r="F23" s="129"/>
-      <c r="G23" s="117"/>
-      <c r="H23" s="117"/>
-      <c r="I23" s="117"/>
-      <c r="J23" s="117"/>
-      <c r="K23" s="120"/>
+      <c r="B23" s="144"/>
+      <c r="C23" s="145"/>
+      <c r="D23" s="145"/>
+      <c r="E23" s="145"/>
+      <c r="F23" s="145"/>
+      <c r="G23" s="142"/>
+      <c r="H23" s="142"/>
+      <c r="I23" s="142"/>
+      <c r="J23" s="142"/>
+      <c r="K23" s="143"/>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B24" s="128"/>
-      <c r="C24" s="129"/>
-      <c r="D24" s="129"/>
-      <c r="E24" s="129"/>
-      <c r="F24" s="129"/>
-      <c r="G24" s="117"/>
-      <c r="H24" s="117"/>
-      <c r="I24" s="117"/>
-      <c r="J24" s="117"/>
-      <c r="K24" s="120"/>
+      <c r="B24" s="144"/>
+      <c r="C24" s="145"/>
+      <c r="D24" s="145"/>
+      <c r="E24" s="145"/>
+      <c r="F24" s="145"/>
+      <c r="G24" s="142"/>
+      <c r="H24" s="142"/>
+      <c r="I24" s="142"/>
+      <c r="J24" s="142"/>
+      <c r="K24" s="143"/>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B25" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="C25" s="122">
+      <c r="C25" s="139">
         <v>43537</v>
       </c>
-      <c r="D25" s="123"/>
+      <c r="D25" s="140"/>
       <c r="E25" s="35" t="s">
         <v>1</v>
       </c>
@@ -12836,10 +13073,10 @@
       <c r="G25" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="H25" s="122">
+      <c r="H25" s="139">
         <v>43544</v>
       </c>
-      <c r="I25" s="123"/>
+      <c r="I25" s="140"/>
       <c r="J25" s="35" t="s">
         <v>1</v>
       </c>
@@ -12848,125 +13085,125 @@
       </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B26" s="124" t="s">
+      <c r="B26" s="118" t="s">
         <v>59</v>
       </c>
-      <c r="C26" s="125"/>
-      <c r="D26" s="125"/>
-      <c r="E26" s="126"/>
-      <c r="F26" s="126"/>
-      <c r="G26" s="125" t="s">
+      <c r="C26" s="119"/>
+      <c r="D26" s="119"/>
+      <c r="E26" s="120"/>
+      <c r="F26" s="120"/>
+      <c r="G26" s="119" t="s">
         <v>59</v>
       </c>
-      <c r="H26" s="125"/>
-      <c r="I26" s="125"/>
-      <c r="J26" s="126"/>
-      <c r="K26" s="127"/>
+      <c r="H26" s="119"/>
+      <c r="I26" s="119"/>
+      <c r="J26" s="120"/>
+      <c r="K26" s="130"/>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B27" s="116"/>
-      <c r="C27" s="117"/>
-      <c r="D27" s="117"/>
-      <c r="E27" s="117"/>
-      <c r="F27" s="117"/>
-      <c r="G27" s="117"/>
-      <c r="H27" s="117"/>
-      <c r="I27" s="117"/>
-      <c r="J27" s="117"/>
-      <c r="K27" s="120"/>
+      <c r="B27" s="141"/>
+      <c r="C27" s="142"/>
+      <c r="D27" s="142"/>
+      <c r="E27" s="142"/>
+      <c r="F27" s="142"/>
+      <c r="G27" s="142"/>
+      <c r="H27" s="142"/>
+      <c r="I27" s="142"/>
+      <c r="J27" s="142"/>
+      <c r="K27" s="143"/>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B28" s="116"/>
-      <c r="C28" s="117"/>
-      <c r="D28" s="117"/>
-      <c r="E28" s="117"/>
-      <c r="F28" s="117"/>
-      <c r="G28" s="117"/>
-      <c r="H28" s="117"/>
-      <c r="I28" s="117"/>
-      <c r="J28" s="117"/>
-      <c r="K28" s="120"/>
+      <c r="B28" s="141"/>
+      <c r="C28" s="142"/>
+      <c r="D28" s="142"/>
+      <c r="E28" s="142"/>
+      <c r="F28" s="142"/>
+      <c r="G28" s="142"/>
+      <c r="H28" s="142"/>
+      <c r="I28" s="142"/>
+      <c r="J28" s="142"/>
+      <c r="K28" s="143"/>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B29" s="116"/>
-      <c r="C29" s="117"/>
-      <c r="D29" s="117"/>
-      <c r="E29" s="117"/>
-      <c r="F29" s="117"/>
-      <c r="G29" s="117"/>
-      <c r="H29" s="117"/>
-      <c r="I29" s="117"/>
-      <c r="J29" s="117"/>
-      <c r="K29" s="120"/>
+      <c r="B29" s="141"/>
+      <c r="C29" s="142"/>
+      <c r="D29" s="142"/>
+      <c r="E29" s="142"/>
+      <c r="F29" s="142"/>
+      <c r="G29" s="142"/>
+      <c r="H29" s="142"/>
+      <c r="I29" s="142"/>
+      <c r="J29" s="142"/>
+      <c r="K29" s="143"/>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B30" s="116"/>
-      <c r="C30" s="117"/>
-      <c r="D30" s="117"/>
-      <c r="E30" s="117"/>
-      <c r="F30" s="117"/>
-      <c r="G30" s="117"/>
-      <c r="H30" s="117"/>
-      <c r="I30" s="117"/>
-      <c r="J30" s="117"/>
-      <c r="K30" s="120"/>
+      <c r="B30" s="141"/>
+      <c r="C30" s="142"/>
+      <c r="D30" s="142"/>
+      <c r="E30" s="142"/>
+      <c r="F30" s="142"/>
+      <c r="G30" s="142"/>
+      <c r="H30" s="142"/>
+      <c r="I30" s="142"/>
+      <c r="J30" s="142"/>
+      <c r="K30" s="143"/>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B31" s="116"/>
-      <c r="C31" s="117"/>
-      <c r="D31" s="117"/>
-      <c r="E31" s="117"/>
-      <c r="F31" s="117"/>
-      <c r="G31" s="117"/>
-      <c r="H31" s="117"/>
-      <c r="I31" s="117"/>
-      <c r="J31" s="117"/>
-      <c r="K31" s="120"/>
+      <c r="B31" s="141"/>
+      <c r="C31" s="142"/>
+      <c r="D31" s="142"/>
+      <c r="E31" s="142"/>
+      <c r="F31" s="142"/>
+      <c r="G31" s="142"/>
+      <c r="H31" s="142"/>
+      <c r="I31" s="142"/>
+      <c r="J31" s="142"/>
+      <c r="K31" s="143"/>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B32" s="116"/>
-      <c r="C32" s="117"/>
-      <c r="D32" s="117"/>
-      <c r="E32" s="117"/>
-      <c r="F32" s="117"/>
-      <c r="G32" s="117"/>
-      <c r="H32" s="117"/>
-      <c r="I32" s="117"/>
-      <c r="J32" s="117"/>
-      <c r="K32" s="120"/>
+      <c r="B32" s="141"/>
+      <c r="C32" s="142"/>
+      <c r="D32" s="142"/>
+      <c r="E32" s="142"/>
+      <c r="F32" s="142"/>
+      <c r="G32" s="142"/>
+      <c r="H32" s="142"/>
+      <c r="I32" s="142"/>
+      <c r="J32" s="142"/>
+      <c r="K32" s="143"/>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B33" s="116"/>
-      <c r="C33" s="117"/>
-      <c r="D33" s="117"/>
-      <c r="E33" s="117"/>
-      <c r="F33" s="117"/>
-      <c r="G33" s="117"/>
-      <c r="H33" s="117"/>
-      <c r="I33" s="117"/>
-      <c r="J33" s="117"/>
-      <c r="K33" s="120"/>
+      <c r="B33" s="141"/>
+      <c r="C33" s="142"/>
+      <c r="D33" s="142"/>
+      <c r="E33" s="142"/>
+      <c r="F33" s="142"/>
+      <c r="G33" s="142"/>
+      <c r="H33" s="142"/>
+      <c r="I33" s="142"/>
+      <c r="J33" s="142"/>
+      <c r="K33" s="143"/>
     </row>
     <row r="34" spans="2:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="116"/>
-      <c r="C34" s="117"/>
-      <c r="D34" s="117"/>
-      <c r="E34" s="117"/>
-      <c r="F34" s="117"/>
-      <c r="G34" s="117"/>
-      <c r="H34" s="117"/>
-      <c r="I34" s="117"/>
-      <c r="J34" s="117"/>
-      <c r="K34" s="120"/>
+      <c r="B34" s="141"/>
+      <c r="C34" s="142"/>
+      <c r="D34" s="142"/>
+      <c r="E34" s="142"/>
+      <c r="F34" s="142"/>
+      <c r="G34" s="142"/>
+      <c r="H34" s="142"/>
+      <c r="I34" s="142"/>
+      <c r="J34" s="142"/>
+      <c r="K34" s="143"/>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="C35" s="122">
+      <c r="C35" s="139">
         <v>43551</v>
       </c>
-      <c r="D35" s="123"/>
+      <c r="D35" s="140"/>
       <c r="E35" s="35" t="s">
         <v>1</v>
       </c>
@@ -12976,10 +13213,10 @@
       <c r="G35" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="H35" s="122">
+      <c r="H35" s="139">
         <v>43558</v>
       </c>
-      <c r="I35" s="123"/>
+      <c r="I35" s="140"/>
       <c r="J35" s="35" t="s">
         <v>1</v>
       </c>
@@ -12988,126 +13225,126 @@
       </c>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B36" s="124" t="s">
+      <c r="B36" s="118" t="s">
         <v>59</v>
       </c>
-      <c r="C36" s="125"/>
-      <c r="D36" s="125"/>
-      <c r="E36" s="126"/>
-      <c r="F36" s="126"/>
-      <c r="G36" s="125" t="s">
+      <c r="C36" s="119"/>
+      <c r="D36" s="119"/>
+      <c r="E36" s="120"/>
+      <c r="F36" s="120"/>
+      <c r="G36" s="119" t="s">
         <v>59</v>
       </c>
-      <c r="H36" s="125"/>
-      <c r="I36" s="125"/>
-      <c r="J36" s="126"/>
-      <c r="K36" s="127"/>
+      <c r="H36" s="119"/>
+      <c r="I36" s="119"/>
+      <c r="J36" s="120"/>
+      <c r="K36" s="130"/>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B37" s="116"/>
-      <c r="C37" s="117"/>
-      <c r="D37" s="117"/>
-      <c r="E37" s="117"/>
-      <c r="F37" s="117"/>
-      <c r="G37" s="117"/>
-      <c r="H37" s="117"/>
-      <c r="I37" s="117"/>
-      <c r="J37" s="117"/>
-      <c r="K37" s="120"/>
+      <c r="B37" s="141"/>
+      <c r="C37" s="142"/>
+      <c r="D37" s="142"/>
+      <c r="E37" s="142"/>
+      <c r="F37" s="142"/>
+      <c r="G37" s="142"/>
+      <c r="H37" s="142"/>
+      <c r="I37" s="142"/>
+      <c r="J37" s="142"/>
+      <c r="K37" s="143"/>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B38" s="116"/>
-      <c r="C38" s="117"/>
-      <c r="D38" s="117"/>
-      <c r="E38" s="117"/>
-      <c r="F38" s="117"/>
-      <c r="G38" s="117"/>
-      <c r="H38" s="117"/>
-      <c r="I38" s="117"/>
-      <c r="J38" s="117"/>
-      <c r="K38" s="120"/>
+      <c r="B38" s="141"/>
+      <c r="C38" s="142"/>
+      <c r="D38" s="142"/>
+      <c r="E38" s="142"/>
+      <c r="F38" s="142"/>
+      <c r="G38" s="142"/>
+      <c r="H38" s="142"/>
+      <c r="I38" s="142"/>
+      <c r="J38" s="142"/>
+      <c r="K38" s="143"/>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B39" s="116"/>
-      <c r="C39" s="117"/>
-      <c r="D39" s="117"/>
-      <c r="E39" s="117"/>
-      <c r="F39" s="117"/>
-      <c r="G39" s="117"/>
-      <c r="H39" s="117"/>
-      <c r="I39" s="117"/>
-      <c r="J39" s="117"/>
-      <c r="K39" s="120"/>
+      <c r="B39" s="141"/>
+      <c r="C39" s="142"/>
+      <c r="D39" s="142"/>
+      <c r="E39" s="142"/>
+      <c r="F39" s="142"/>
+      <c r="G39" s="142"/>
+      <c r="H39" s="142"/>
+      <c r="I39" s="142"/>
+      <c r="J39" s="142"/>
+      <c r="K39" s="143"/>
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B40" s="116"/>
-      <c r="C40" s="117"/>
-      <c r="D40" s="117"/>
-      <c r="E40" s="117"/>
-      <c r="F40" s="117"/>
-      <c r="G40" s="117"/>
-      <c r="H40" s="117"/>
-      <c r="I40" s="117"/>
-      <c r="J40" s="117"/>
-      <c r="K40" s="120"/>
+      <c r="B40" s="141"/>
+      <c r="C40" s="142"/>
+      <c r="D40" s="142"/>
+      <c r="E40" s="142"/>
+      <c r="F40" s="142"/>
+      <c r="G40" s="142"/>
+      <c r="H40" s="142"/>
+      <c r="I40" s="142"/>
+      <c r="J40" s="142"/>
+      <c r="K40" s="143"/>
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B41" s="116"/>
-      <c r="C41" s="117"/>
-      <c r="D41" s="117"/>
-      <c r="E41" s="117"/>
-      <c r="F41" s="117"/>
-      <c r="G41" s="117"/>
-      <c r="H41" s="117"/>
-      <c r="I41" s="117"/>
-      <c r="J41" s="117"/>
-      <c r="K41" s="120"/>
+      <c r="B41" s="141"/>
+      <c r="C41" s="142"/>
+      <c r="D41" s="142"/>
+      <c r="E41" s="142"/>
+      <c r="F41" s="142"/>
+      <c r="G41" s="142"/>
+      <c r="H41" s="142"/>
+      <c r="I41" s="142"/>
+      <c r="J41" s="142"/>
+      <c r="K41" s="143"/>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B42" s="116"/>
-      <c r="C42" s="117"/>
-      <c r="D42" s="117"/>
-      <c r="E42" s="117"/>
-      <c r="F42" s="117"/>
-      <c r="G42" s="117"/>
-      <c r="H42" s="117"/>
-      <c r="I42" s="117"/>
-      <c r="J42" s="117"/>
-      <c r="K42" s="120"/>
+      <c r="B42" s="141"/>
+      <c r="C42" s="142"/>
+      <c r="D42" s="142"/>
+      <c r="E42" s="142"/>
+      <c r="F42" s="142"/>
+      <c r="G42" s="142"/>
+      <c r="H42" s="142"/>
+      <c r="I42" s="142"/>
+      <c r="J42" s="142"/>
+      <c r="K42" s="143"/>
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B43" s="116"/>
-      <c r="C43" s="117"/>
-      <c r="D43" s="117"/>
-      <c r="E43" s="117"/>
-      <c r="F43" s="117"/>
-      <c r="G43" s="117"/>
-      <c r="H43" s="117"/>
-      <c r="I43" s="117"/>
-      <c r="J43" s="117"/>
-      <c r="K43" s="120"/>
+      <c r="B43" s="141"/>
+      <c r="C43" s="142"/>
+      <c r="D43" s="142"/>
+      <c r="E43" s="142"/>
+      <c r="F43" s="142"/>
+      <c r="G43" s="142"/>
+      <c r="H43" s="142"/>
+      <c r="I43" s="142"/>
+      <c r="J43" s="142"/>
+      <c r="K43" s="143"/>
     </row>
     <row r="44" spans="2:11" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="118"/>
-      <c r="C44" s="119"/>
-      <c r="D44" s="119"/>
-      <c r="E44" s="119"/>
-      <c r="F44" s="119"/>
-      <c r="G44" s="119"/>
-      <c r="H44" s="119"/>
-      <c r="I44" s="119"/>
-      <c r="J44" s="119"/>
-      <c r="K44" s="121"/>
+      <c r="B44" s="146"/>
+      <c r="C44" s="147"/>
+      <c r="D44" s="147"/>
+      <c r="E44" s="147"/>
+      <c r="F44" s="147"/>
+      <c r="G44" s="147"/>
+      <c r="H44" s="147"/>
+      <c r="I44" s="147"/>
+      <c r="J44" s="147"/>
+      <c r="K44" s="148"/>
     </row>
     <row r="45" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B46" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="C46" s="132">
+      <c r="C46" s="135">
         <v>43782</v>
       </c>
-      <c r="D46" s="133"/>
+      <c r="D46" s="136"/>
       <c r="E46" s="40" t="s">
         <v>1</v>
       </c>
@@ -13117,10 +13354,10 @@
       <c r="G46" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="H46" s="132">
+      <c r="H46" s="135">
         <v>43789</v>
       </c>
-      <c r="I46" s="133"/>
+      <c r="I46" s="136"/>
       <c r="J46" s="40" t="s">
         <v>1</v>
       </c>
@@ -13129,125 +13366,125 @@
       </c>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B47" s="124" t="s">
+      <c r="B47" s="118" t="s">
         <v>59</v>
       </c>
-      <c r="C47" s="125"/>
-      <c r="D47" s="125"/>
-      <c r="E47" s="126"/>
-      <c r="F47" s="126"/>
-      <c r="G47" s="125" t="s">
+      <c r="C47" s="119"/>
+      <c r="D47" s="119"/>
+      <c r="E47" s="120"/>
+      <c r="F47" s="120"/>
+      <c r="G47" s="119" t="s">
         <v>59</v>
       </c>
-      <c r="H47" s="125"/>
-      <c r="I47" s="125"/>
-      <c r="J47" s="126"/>
-      <c r="K47" s="127"/>
+      <c r="H47" s="119"/>
+      <c r="I47" s="119"/>
+      <c r="J47" s="120"/>
+      <c r="K47" s="130"/>
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B48" s="116"/>
-      <c r="C48" s="117"/>
-      <c r="D48" s="117"/>
-      <c r="E48" s="117"/>
-      <c r="F48" s="117"/>
-      <c r="G48" s="117"/>
-      <c r="H48" s="117"/>
-      <c r="I48" s="117"/>
-      <c r="J48" s="117"/>
-      <c r="K48" s="120"/>
+      <c r="B48" s="141"/>
+      <c r="C48" s="142"/>
+      <c r="D48" s="142"/>
+      <c r="E48" s="142"/>
+      <c r="F48" s="142"/>
+      <c r="G48" s="142"/>
+      <c r="H48" s="142"/>
+      <c r="I48" s="142"/>
+      <c r="J48" s="142"/>
+      <c r="K48" s="143"/>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B49" s="116"/>
-      <c r="C49" s="117"/>
-      <c r="D49" s="117"/>
-      <c r="E49" s="117"/>
-      <c r="F49" s="117"/>
-      <c r="G49" s="117"/>
-      <c r="H49" s="117"/>
-      <c r="I49" s="117"/>
-      <c r="J49" s="117"/>
-      <c r="K49" s="120"/>
+      <c r="B49" s="141"/>
+      <c r="C49" s="142"/>
+      <c r="D49" s="142"/>
+      <c r="E49" s="142"/>
+      <c r="F49" s="142"/>
+      <c r="G49" s="142"/>
+      <c r="H49" s="142"/>
+      <c r="I49" s="142"/>
+      <c r="J49" s="142"/>
+      <c r="K49" s="143"/>
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B50" s="116"/>
-      <c r="C50" s="117"/>
-      <c r="D50" s="117"/>
-      <c r="E50" s="117"/>
-      <c r="F50" s="117"/>
-      <c r="G50" s="117"/>
-      <c r="H50" s="117"/>
-      <c r="I50" s="117"/>
-      <c r="J50" s="117"/>
-      <c r="K50" s="120"/>
+      <c r="B50" s="141"/>
+      <c r="C50" s="142"/>
+      <c r="D50" s="142"/>
+      <c r="E50" s="142"/>
+      <c r="F50" s="142"/>
+      <c r="G50" s="142"/>
+      <c r="H50" s="142"/>
+      <c r="I50" s="142"/>
+      <c r="J50" s="142"/>
+      <c r="K50" s="143"/>
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B51" s="116"/>
-      <c r="C51" s="117"/>
-      <c r="D51" s="117"/>
-      <c r="E51" s="117"/>
-      <c r="F51" s="117"/>
-      <c r="G51" s="117"/>
-      <c r="H51" s="117"/>
-      <c r="I51" s="117"/>
-      <c r="J51" s="117"/>
-      <c r="K51" s="120"/>
+      <c r="B51" s="141"/>
+      <c r="C51" s="142"/>
+      <c r="D51" s="142"/>
+      <c r="E51" s="142"/>
+      <c r="F51" s="142"/>
+      <c r="G51" s="142"/>
+      <c r="H51" s="142"/>
+      <c r="I51" s="142"/>
+      <c r="J51" s="142"/>
+      <c r="K51" s="143"/>
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B52" s="116"/>
-      <c r="C52" s="117"/>
-      <c r="D52" s="117"/>
-      <c r="E52" s="117"/>
-      <c r="F52" s="117"/>
-      <c r="G52" s="117"/>
-      <c r="H52" s="117"/>
-      <c r="I52" s="117"/>
-      <c r="J52" s="117"/>
-      <c r="K52" s="120"/>
+      <c r="B52" s="141"/>
+      <c r="C52" s="142"/>
+      <c r="D52" s="142"/>
+      <c r="E52" s="142"/>
+      <c r="F52" s="142"/>
+      <c r="G52" s="142"/>
+      <c r="H52" s="142"/>
+      <c r="I52" s="142"/>
+      <c r="J52" s="142"/>
+      <c r="K52" s="143"/>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B53" s="116"/>
-      <c r="C53" s="117"/>
-      <c r="D53" s="117"/>
-      <c r="E53" s="117"/>
-      <c r="F53" s="117"/>
-      <c r="G53" s="117"/>
-      <c r="H53" s="117"/>
-      <c r="I53" s="117"/>
-      <c r="J53" s="117"/>
-      <c r="K53" s="120"/>
+      <c r="B53" s="141"/>
+      <c r="C53" s="142"/>
+      <c r="D53" s="142"/>
+      <c r="E53" s="142"/>
+      <c r="F53" s="142"/>
+      <c r="G53" s="142"/>
+      <c r="H53" s="142"/>
+      <c r="I53" s="142"/>
+      <c r="J53" s="142"/>
+      <c r="K53" s="143"/>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B54" s="116"/>
-      <c r="C54" s="117"/>
-      <c r="D54" s="117"/>
-      <c r="E54" s="117"/>
-      <c r="F54" s="117"/>
-      <c r="G54" s="117"/>
-      <c r="H54" s="117"/>
-      <c r="I54" s="117"/>
-      <c r="J54" s="117"/>
-      <c r="K54" s="120"/>
+      <c r="B54" s="141"/>
+      <c r="C54" s="142"/>
+      <c r="D54" s="142"/>
+      <c r="E54" s="142"/>
+      <c r="F54" s="142"/>
+      <c r="G54" s="142"/>
+      <c r="H54" s="142"/>
+      <c r="I54" s="142"/>
+      <c r="J54" s="142"/>
+      <c r="K54" s="143"/>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B55" s="116"/>
-      <c r="C55" s="117"/>
-      <c r="D55" s="117"/>
-      <c r="E55" s="117"/>
-      <c r="F55" s="117"/>
-      <c r="G55" s="117"/>
-      <c r="H55" s="117"/>
-      <c r="I55" s="117"/>
-      <c r="J55" s="117"/>
-      <c r="K55" s="120"/>
+      <c r="B55" s="141"/>
+      <c r="C55" s="142"/>
+      <c r="D55" s="142"/>
+      <c r="E55" s="142"/>
+      <c r="F55" s="142"/>
+      <c r="G55" s="142"/>
+      <c r="H55" s="142"/>
+      <c r="I55" s="142"/>
+      <c r="J55" s="142"/>
+      <c r="K55" s="143"/>
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B56" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="C56" s="122">
+      <c r="C56" s="139">
         <v>43796</v>
       </c>
-      <c r="D56" s="123"/>
+      <c r="D56" s="140"/>
       <c r="E56" s="35" t="s">
         <v>1</v>
       </c>
@@ -13257,10 +13494,10 @@
       <c r="G56" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="H56" s="122">
+      <c r="H56" s="139">
         <v>43803</v>
       </c>
-      <c r="I56" s="123"/>
+      <c r="I56" s="140"/>
       <c r="J56" s="35" t="s">
         <v>1</v>
       </c>
@@ -13269,125 +13506,125 @@
       </c>
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B57" s="124" t="s">
+      <c r="B57" s="118" t="s">
         <v>59</v>
       </c>
-      <c r="C57" s="125"/>
-      <c r="D57" s="125"/>
-      <c r="E57" s="126"/>
-      <c r="F57" s="126"/>
-      <c r="G57" s="125" t="s">
+      <c r="C57" s="119"/>
+      <c r="D57" s="119"/>
+      <c r="E57" s="120"/>
+      <c r="F57" s="120"/>
+      <c r="G57" s="119" t="s">
         <v>59</v>
       </c>
-      <c r="H57" s="125"/>
-      <c r="I57" s="125"/>
-      <c r="J57" s="126"/>
-      <c r="K57" s="127"/>
+      <c r="H57" s="119"/>
+      <c r="I57" s="119"/>
+      <c r="J57" s="120"/>
+      <c r="K57" s="130"/>
     </row>
     <row r="58" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="116"/>
-      <c r="C58" s="117"/>
-      <c r="D58" s="117"/>
-      <c r="E58" s="117"/>
-      <c r="F58" s="117"/>
-      <c r="G58" s="117"/>
-      <c r="H58" s="117"/>
-      <c r="I58" s="117"/>
-      <c r="J58" s="117"/>
-      <c r="K58" s="120"/>
+      <c r="B58" s="141"/>
+      <c r="C58" s="142"/>
+      <c r="D58" s="142"/>
+      <c r="E58" s="142"/>
+      <c r="F58" s="142"/>
+      <c r="G58" s="142"/>
+      <c r="H58" s="142"/>
+      <c r="I58" s="142"/>
+      <c r="J58" s="142"/>
+      <c r="K58" s="143"/>
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B59" s="116"/>
-      <c r="C59" s="117"/>
-      <c r="D59" s="117"/>
-      <c r="E59" s="117"/>
-      <c r="F59" s="117"/>
-      <c r="G59" s="117"/>
-      <c r="H59" s="117"/>
-      <c r="I59" s="117"/>
-      <c r="J59" s="117"/>
-      <c r="K59" s="120"/>
+      <c r="B59" s="141"/>
+      <c r="C59" s="142"/>
+      <c r="D59" s="142"/>
+      <c r="E59" s="142"/>
+      <c r="F59" s="142"/>
+      <c r="G59" s="142"/>
+      <c r="H59" s="142"/>
+      <c r="I59" s="142"/>
+      <c r="J59" s="142"/>
+      <c r="K59" s="143"/>
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B60" s="116"/>
-      <c r="C60" s="117"/>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="120"/>
+      <c r="B60" s="141"/>
+      <c r="C60" s="142"/>
+      <c r="D60" s="142"/>
+      <c r="E60" s="142"/>
+      <c r="F60" s="142"/>
+      <c r="G60" s="142"/>
+      <c r="H60" s="142"/>
+      <c r="I60" s="142"/>
+      <c r="J60" s="142"/>
+      <c r="K60" s="143"/>
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B61" s="116"/>
-      <c r="C61" s="117"/>
-      <c r="D61" s="117"/>
-      <c r="E61" s="117"/>
-      <c r="F61" s="117"/>
-      <c r="G61" s="117"/>
-      <c r="H61" s="117"/>
-      <c r="I61" s="117"/>
-      <c r="J61" s="117"/>
-      <c r="K61" s="120"/>
+      <c r="B61" s="141"/>
+      <c r="C61" s="142"/>
+      <c r="D61" s="142"/>
+      <c r="E61" s="142"/>
+      <c r="F61" s="142"/>
+      <c r="G61" s="142"/>
+      <c r="H61" s="142"/>
+      <c r="I61" s="142"/>
+      <c r="J61" s="142"/>
+      <c r="K61" s="143"/>
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B62" s="116"/>
-      <c r="C62" s="117"/>
-      <c r="D62" s="117"/>
-      <c r="E62" s="117"/>
-      <c r="F62" s="117"/>
-      <c r="G62" s="117"/>
-      <c r="H62" s="117"/>
-      <c r="I62" s="117"/>
-      <c r="J62" s="117"/>
-      <c r="K62" s="120"/>
+      <c r="B62" s="141"/>
+      <c r="C62" s="142"/>
+      <c r="D62" s="142"/>
+      <c r="E62" s="142"/>
+      <c r="F62" s="142"/>
+      <c r="G62" s="142"/>
+      <c r="H62" s="142"/>
+      <c r="I62" s="142"/>
+      <c r="J62" s="142"/>
+      <c r="K62" s="143"/>
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B63" s="116"/>
-      <c r="C63" s="117"/>
-      <c r="D63" s="117"/>
-      <c r="E63" s="117"/>
-      <c r="F63" s="117"/>
-      <c r="G63" s="117"/>
-      <c r="H63" s="117"/>
-      <c r="I63" s="117"/>
-      <c r="J63" s="117"/>
-      <c r="K63" s="120"/>
+      <c r="B63" s="141"/>
+      <c r="C63" s="142"/>
+      <c r="D63" s="142"/>
+      <c r="E63" s="142"/>
+      <c r="F63" s="142"/>
+      <c r="G63" s="142"/>
+      <c r="H63" s="142"/>
+      <c r="I63" s="142"/>
+      <c r="J63" s="142"/>
+      <c r="K63" s="143"/>
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B64" s="116"/>
-      <c r="C64" s="117"/>
-      <c r="D64" s="117"/>
-      <c r="E64" s="117"/>
-      <c r="F64" s="117"/>
-      <c r="G64" s="117"/>
-      <c r="H64" s="117"/>
-      <c r="I64" s="117"/>
-      <c r="J64" s="117"/>
-      <c r="K64" s="120"/>
+      <c r="B64" s="141"/>
+      <c r="C64" s="142"/>
+      <c r="D64" s="142"/>
+      <c r="E64" s="142"/>
+      <c r="F64" s="142"/>
+      <c r="G64" s="142"/>
+      <c r="H64" s="142"/>
+      <c r="I64" s="142"/>
+      <c r="J64" s="142"/>
+      <c r="K64" s="143"/>
     </row>
     <row r="65" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B65" s="116"/>
-      <c r="C65" s="117"/>
-      <c r="D65" s="117"/>
-      <c r="E65" s="117"/>
-      <c r="F65" s="117"/>
-      <c r="G65" s="117"/>
-      <c r="H65" s="117"/>
-      <c r="I65" s="117"/>
-      <c r="J65" s="117"/>
-      <c r="K65" s="120"/>
+      <c r="B65" s="141"/>
+      <c r="C65" s="142"/>
+      <c r="D65" s="142"/>
+      <c r="E65" s="142"/>
+      <c r="F65" s="142"/>
+      <c r="G65" s="142"/>
+      <c r="H65" s="142"/>
+      <c r="I65" s="142"/>
+      <c r="J65" s="142"/>
+      <c r="K65" s="143"/>
     </row>
     <row r="66" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B66" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="C66" s="122">
+      <c r="C66" s="139">
         <v>43810</v>
       </c>
-      <c r="D66" s="123"/>
+      <c r="D66" s="140"/>
       <c r="E66" s="35" t="s">
         <v>1</v>
       </c>
@@ -13397,10 +13634,10 @@
       <c r="G66" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="H66" s="122">
+      <c r="H66" s="139">
         <v>43817</v>
       </c>
-      <c r="I66" s="123"/>
+      <c r="I66" s="140"/>
       <c r="J66" s="35" t="s">
         <v>1</v>
       </c>
@@ -13409,125 +13646,125 @@
       </c>
     </row>
     <row r="67" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B67" s="124" t="s">
+      <c r="B67" s="118" t="s">
         <v>59</v>
       </c>
-      <c r="C67" s="125"/>
-      <c r="D67" s="125"/>
-      <c r="E67" s="126"/>
-      <c r="F67" s="126"/>
-      <c r="G67" s="125" t="s">
+      <c r="C67" s="119"/>
+      <c r="D67" s="119"/>
+      <c r="E67" s="120"/>
+      <c r="F67" s="120"/>
+      <c r="G67" s="119" t="s">
         <v>59</v>
       </c>
-      <c r="H67" s="125"/>
-      <c r="I67" s="125"/>
-      <c r="J67" s="126"/>
-      <c r="K67" s="127"/>
+      <c r="H67" s="119"/>
+      <c r="I67" s="119"/>
+      <c r="J67" s="120"/>
+      <c r="K67" s="130"/>
     </row>
     <row r="68" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B68" s="116"/>
-      <c r="C68" s="117"/>
-      <c r="D68" s="117"/>
-      <c r="E68" s="117"/>
-      <c r="F68" s="117"/>
-      <c r="G68" s="117"/>
-      <c r="H68" s="117"/>
-      <c r="I68" s="117"/>
-      <c r="J68" s="117"/>
-      <c r="K68" s="120"/>
+      <c r="B68" s="141"/>
+      <c r="C68" s="142"/>
+      <c r="D68" s="142"/>
+      <c r="E68" s="142"/>
+      <c r="F68" s="142"/>
+      <c r="G68" s="142"/>
+      <c r="H68" s="142"/>
+      <c r="I68" s="142"/>
+      <c r="J68" s="142"/>
+      <c r="K68" s="143"/>
     </row>
     <row r="69" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B69" s="116"/>
-      <c r="C69" s="117"/>
-      <c r="D69" s="117"/>
-      <c r="E69" s="117"/>
-      <c r="F69" s="117"/>
-      <c r="G69" s="117"/>
-      <c r="H69" s="117"/>
-      <c r="I69" s="117"/>
-      <c r="J69" s="117"/>
-      <c r="K69" s="120"/>
+      <c r="B69" s="141"/>
+      <c r="C69" s="142"/>
+      <c r="D69" s="142"/>
+      <c r="E69" s="142"/>
+      <c r="F69" s="142"/>
+      <c r="G69" s="142"/>
+      <c r="H69" s="142"/>
+      <c r="I69" s="142"/>
+      <c r="J69" s="142"/>
+      <c r="K69" s="143"/>
     </row>
     <row r="70" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B70" s="116"/>
-      <c r="C70" s="117"/>
-      <c r="D70" s="117"/>
-      <c r="E70" s="117"/>
-      <c r="F70" s="117"/>
-      <c r="G70" s="117"/>
-      <c r="H70" s="117"/>
-      <c r="I70" s="117"/>
-      <c r="J70" s="117"/>
-      <c r="K70" s="120"/>
+      <c r="B70" s="141"/>
+      <c r="C70" s="142"/>
+      <c r="D70" s="142"/>
+      <c r="E70" s="142"/>
+      <c r="F70" s="142"/>
+      <c r="G70" s="142"/>
+      <c r="H70" s="142"/>
+      <c r="I70" s="142"/>
+      <c r="J70" s="142"/>
+      <c r="K70" s="143"/>
     </row>
     <row r="71" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B71" s="116"/>
-      <c r="C71" s="117"/>
-      <c r="D71" s="117"/>
-      <c r="E71" s="117"/>
-      <c r="F71" s="117"/>
-      <c r="G71" s="117"/>
-      <c r="H71" s="117"/>
-      <c r="I71" s="117"/>
-      <c r="J71" s="117"/>
-      <c r="K71" s="120"/>
+      <c r="B71" s="141"/>
+      <c r="C71" s="142"/>
+      <c r="D71" s="142"/>
+      <c r="E71" s="142"/>
+      <c r="F71" s="142"/>
+      <c r="G71" s="142"/>
+      <c r="H71" s="142"/>
+      <c r="I71" s="142"/>
+      <c r="J71" s="142"/>
+      <c r="K71" s="143"/>
     </row>
     <row r="72" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B72" s="116"/>
-      <c r="C72" s="117"/>
-      <c r="D72" s="117"/>
-      <c r="E72" s="117"/>
-      <c r="F72" s="117"/>
-      <c r="G72" s="117"/>
-      <c r="H72" s="117"/>
-      <c r="I72" s="117"/>
-      <c r="J72" s="117"/>
-      <c r="K72" s="120"/>
+      <c r="B72" s="141"/>
+      <c r="C72" s="142"/>
+      <c r="D72" s="142"/>
+      <c r="E72" s="142"/>
+      <c r="F72" s="142"/>
+      <c r="G72" s="142"/>
+      <c r="H72" s="142"/>
+      <c r="I72" s="142"/>
+      <c r="J72" s="142"/>
+      <c r="K72" s="143"/>
     </row>
     <row r="73" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B73" s="116"/>
-      <c r="C73" s="117"/>
-      <c r="D73" s="117"/>
-      <c r="E73" s="117"/>
-      <c r="F73" s="117"/>
-      <c r="G73" s="117"/>
-      <c r="H73" s="117"/>
-      <c r="I73" s="117"/>
-      <c r="J73" s="117"/>
-      <c r="K73" s="120"/>
+      <c r="B73" s="141"/>
+      <c r="C73" s="142"/>
+      <c r="D73" s="142"/>
+      <c r="E73" s="142"/>
+      <c r="F73" s="142"/>
+      <c r="G73" s="142"/>
+      <c r="H73" s="142"/>
+      <c r="I73" s="142"/>
+      <c r="J73" s="142"/>
+      <c r="K73" s="143"/>
     </row>
     <row r="74" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B74" s="116"/>
-      <c r="C74" s="117"/>
-      <c r="D74" s="117"/>
-      <c r="E74" s="117"/>
-      <c r="F74" s="117"/>
-      <c r="G74" s="117"/>
-      <c r="H74" s="117"/>
-      <c r="I74" s="117"/>
-      <c r="J74" s="117"/>
-      <c r="K74" s="120"/>
+      <c r="B74" s="141"/>
+      <c r="C74" s="142"/>
+      <c r="D74" s="142"/>
+      <c r="E74" s="142"/>
+      <c r="F74" s="142"/>
+      <c r="G74" s="142"/>
+      <c r="H74" s="142"/>
+      <c r="I74" s="142"/>
+      <c r="J74" s="142"/>
+      <c r="K74" s="143"/>
     </row>
     <row r="75" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B75" s="116"/>
-      <c r="C75" s="117"/>
-      <c r="D75" s="117"/>
-      <c r="E75" s="117"/>
-      <c r="F75" s="117"/>
-      <c r="G75" s="117"/>
-      <c r="H75" s="117"/>
-      <c r="I75" s="117"/>
-      <c r="J75" s="117"/>
-      <c r="K75" s="120"/>
+      <c r="B75" s="141"/>
+      <c r="C75" s="142"/>
+      <c r="D75" s="142"/>
+      <c r="E75" s="142"/>
+      <c r="F75" s="142"/>
+      <c r="G75" s="142"/>
+      <c r="H75" s="142"/>
+      <c r="I75" s="142"/>
+      <c r="J75" s="142"/>
+      <c r="K75" s="143"/>
     </row>
     <row r="76" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B76" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="C76" s="122">
+      <c r="C76" s="139">
         <v>43747</v>
       </c>
-      <c r="D76" s="123"/>
+      <c r="D76" s="140"/>
       <c r="E76" s="35" t="s">
         <v>1</v>
       </c>
@@ -13537,10 +13774,10 @@
       <c r="G76" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="H76" s="122">
+      <c r="H76" s="139">
         <v>43761</v>
       </c>
-      <c r="I76" s="123"/>
+      <c r="I76" s="140"/>
       <c r="J76" s="35" t="s">
         <v>1</v>
       </c>
@@ -13549,125 +13786,125 @@
       </c>
     </row>
     <row r="77" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B77" s="124" t="s">
+      <c r="B77" s="118" t="s">
         <v>59</v>
       </c>
-      <c r="C77" s="125"/>
-      <c r="D77" s="125"/>
-      <c r="E77" s="126"/>
-      <c r="F77" s="126"/>
-      <c r="G77" s="125" t="s">
+      <c r="C77" s="119"/>
+      <c r="D77" s="119"/>
+      <c r="E77" s="120"/>
+      <c r="F77" s="120"/>
+      <c r="G77" s="119" t="s">
         <v>59</v>
       </c>
-      <c r="H77" s="125"/>
-      <c r="I77" s="125"/>
-      <c r="J77" s="126"/>
-      <c r="K77" s="127"/>
+      <c r="H77" s="119"/>
+      <c r="I77" s="119"/>
+      <c r="J77" s="120"/>
+      <c r="K77" s="130"/>
     </row>
     <row r="78" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B78" s="116"/>
-      <c r="C78" s="117"/>
-      <c r="D78" s="117"/>
-      <c r="E78" s="117"/>
-      <c r="F78" s="117"/>
-      <c r="G78" s="117"/>
-      <c r="H78" s="117"/>
-      <c r="I78" s="117"/>
-      <c r="J78" s="117"/>
-      <c r="K78" s="120"/>
+      <c r="B78" s="141"/>
+      <c r="C78" s="142"/>
+      <c r="D78" s="142"/>
+      <c r="E78" s="142"/>
+      <c r="F78" s="142"/>
+      <c r="G78" s="142"/>
+      <c r="H78" s="142"/>
+      <c r="I78" s="142"/>
+      <c r="J78" s="142"/>
+      <c r="K78" s="143"/>
     </row>
     <row r="79" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B79" s="116"/>
-      <c r="C79" s="117"/>
-      <c r="D79" s="117"/>
-      <c r="E79" s="117"/>
-      <c r="F79" s="117"/>
-      <c r="G79" s="117"/>
-      <c r="H79" s="117"/>
-      <c r="I79" s="117"/>
-      <c r="J79" s="117"/>
-      <c r="K79" s="120"/>
+      <c r="B79" s="141"/>
+      <c r="C79" s="142"/>
+      <c r="D79" s="142"/>
+      <c r="E79" s="142"/>
+      <c r="F79" s="142"/>
+      <c r="G79" s="142"/>
+      <c r="H79" s="142"/>
+      <c r="I79" s="142"/>
+      <c r="J79" s="142"/>
+      <c r="K79" s="143"/>
     </row>
     <row r="80" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B80" s="116"/>
-      <c r="C80" s="117"/>
-      <c r="D80" s="117"/>
-      <c r="E80" s="117"/>
-      <c r="F80" s="117"/>
-      <c r="G80" s="117"/>
-      <c r="H80" s="117"/>
-      <c r="I80" s="117"/>
-      <c r="J80" s="117"/>
-      <c r="K80" s="120"/>
+      <c r="B80" s="141"/>
+      <c r="C80" s="142"/>
+      <c r="D80" s="142"/>
+      <c r="E80" s="142"/>
+      <c r="F80" s="142"/>
+      <c r="G80" s="142"/>
+      <c r="H80" s="142"/>
+      <c r="I80" s="142"/>
+      <c r="J80" s="142"/>
+      <c r="K80" s="143"/>
     </row>
     <row r="81" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B81" s="116"/>
-      <c r="C81" s="117"/>
-      <c r="D81" s="117"/>
-      <c r="E81" s="117"/>
-      <c r="F81" s="117"/>
-      <c r="G81" s="117"/>
-      <c r="H81" s="117"/>
-      <c r="I81" s="117"/>
-      <c r="J81" s="117"/>
-      <c r="K81" s="120"/>
+      <c r="B81" s="141"/>
+      <c r="C81" s="142"/>
+      <c r="D81" s="142"/>
+      <c r="E81" s="142"/>
+      <c r="F81" s="142"/>
+      <c r="G81" s="142"/>
+      <c r="H81" s="142"/>
+      <c r="I81" s="142"/>
+      <c r="J81" s="142"/>
+      <c r="K81" s="143"/>
     </row>
     <row r="82" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B82" s="116"/>
-      <c r="C82" s="117"/>
-      <c r="D82" s="117"/>
-      <c r="E82" s="117"/>
-      <c r="F82" s="117"/>
-      <c r="G82" s="117"/>
-      <c r="H82" s="117"/>
-      <c r="I82" s="117"/>
-      <c r="J82" s="117"/>
-      <c r="K82" s="120"/>
+      <c r="B82" s="141"/>
+      <c r="C82" s="142"/>
+      <c r="D82" s="142"/>
+      <c r="E82" s="142"/>
+      <c r="F82" s="142"/>
+      <c r="G82" s="142"/>
+      <c r="H82" s="142"/>
+      <c r="I82" s="142"/>
+      <c r="J82" s="142"/>
+      <c r="K82" s="143"/>
     </row>
     <row r="83" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B83" s="116"/>
-      <c r="C83" s="117"/>
-      <c r="D83" s="117"/>
-      <c r="E83" s="117"/>
-      <c r="F83" s="117"/>
-      <c r="G83" s="117"/>
-      <c r="H83" s="117"/>
-      <c r="I83" s="117"/>
-      <c r="J83" s="117"/>
-      <c r="K83" s="120"/>
+      <c r="B83" s="141"/>
+      <c r="C83" s="142"/>
+      <c r="D83" s="142"/>
+      <c r="E83" s="142"/>
+      <c r="F83" s="142"/>
+      <c r="G83" s="142"/>
+      <c r="H83" s="142"/>
+      <c r="I83" s="142"/>
+      <c r="J83" s="142"/>
+      <c r="K83" s="143"/>
     </row>
     <row r="84" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B84" s="116"/>
-      <c r="C84" s="117"/>
-      <c r="D84" s="117"/>
-      <c r="E84" s="117"/>
-      <c r="F84" s="117"/>
-      <c r="G84" s="117"/>
-      <c r="H84" s="117"/>
-      <c r="I84" s="117"/>
-      <c r="J84" s="117"/>
-      <c r="K84" s="120"/>
+      <c r="B84" s="141"/>
+      <c r="C84" s="142"/>
+      <c r="D84" s="142"/>
+      <c r="E84" s="142"/>
+      <c r="F84" s="142"/>
+      <c r="G84" s="142"/>
+      <c r="H84" s="142"/>
+      <c r="I84" s="142"/>
+      <c r="J84" s="142"/>
+      <c r="K84" s="143"/>
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B85" s="116"/>
-      <c r="C85" s="117"/>
-      <c r="D85" s="117"/>
-      <c r="E85" s="117"/>
-      <c r="F85" s="117"/>
-      <c r="G85" s="117"/>
-      <c r="H85" s="117"/>
-      <c r="I85" s="117"/>
-      <c r="J85" s="117"/>
-      <c r="K85" s="120"/>
+      <c r="B85" s="141"/>
+      <c r="C85" s="142"/>
+      <c r="D85" s="142"/>
+      <c r="E85" s="142"/>
+      <c r="F85" s="142"/>
+      <c r="G85" s="142"/>
+      <c r="H85" s="142"/>
+      <c r="I85" s="142"/>
+      <c r="J85" s="142"/>
+      <c r="K85" s="143"/>
     </row>
     <row r="86" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B86" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="C86" s="122">
+      <c r="C86" s="139">
         <v>43768</v>
       </c>
-      <c r="D86" s="123"/>
+      <c r="D86" s="140"/>
       <c r="E86" s="35" t="s">
         <v>1</v>
       </c>
@@ -13677,10 +13914,10 @@
       <c r="G86" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="H86" s="122">
+      <c r="H86" s="139">
         <v>43775</v>
       </c>
-      <c r="I86" s="123"/>
+      <c r="I86" s="140"/>
       <c r="J86" s="35" t="s">
         <v>1</v>
       </c>
@@ -13689,127 +13926,153 @@
       </c>
     </row>
     <row r="87" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B87" s="124" t="s">
+      <c r="B87" s="118" t="s">
         <v>59</v>
       </c>
-      <c r="C87" s="125"/>
-      <c r="D87" s="125"/>
-      <c r="E87" s="126"/>
-      <c r="F87" s="126"/>
-      <c r="G87" s="125" t="s">
+      <c r="C87" s="119"/>
+      <c r="D87" s="119"/>
+      <c r="E87" s="120"/>
+      <c r="F87" s="120"/>
+      <c r="G87" s="119" t="s">
         <v>59</v>
       </c>
-      <c r="H87" s="125"/>
-      <c r="I87" s="125"/>
-      <c r="J87" s="126"/>
-      <c r="K87" s="127"/>
+      <c r="H87" s="119"/>
+      <c r="I87" s="119"/>
+      <c r="J87" s="120"/>
+      <c r="K87" s="130"/>
     </row>
     <row r="88" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B88" s="116"/>
-      <c r="C88" s="117"/>
-      <c r="D88" s="117"/>
-      <c r="E88" s="117"/>
-      <c r="F88" s="117"/>
-      <c r="G88" s="117"/>
-      <c r="H88" s="117"/>
-      <c r="I88" s="117"/>
-      <c r="J88" s="117"/>
-      <c r="K88" s="120"/>
+      <c r="B88" s="141"/>
+      <c r="C88" s="142"/>
+      <c r="D88" s="142"/>
+      <c r="E88" s="142"/>
+      <c r="F88" s="142"/>
+      <c r="G88" s="142"/>
+      <c r="H88" s="142"/>
+      <c r="I88" s="142"/>
+      <c r="J88" s="142"/>
+      <c r="K88" s="143"/>
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B89" s="116"/>
-      <c r="C89" s="117"/>
-      <c r="D89" s="117"/>
-      <c r="E89" s="117"/>
-      <c r="F89" s="117"/>
-      <c r="G89" s="117"/>
-      <c r="H89" s="117"/>
-      <c r="I89" s="117"/>
-      <c r="J89" s="117"/>
-      <c r="K89" s="120"/>
+      <c r="B89" s="141"/>
+      <c r="C89" s="142"/>
+      <c r="D89" s="142"/>
+      <c r="E89" s="142"/>
+      <c r="F89" s="142"/>
+      <c r="G89" s="142"/>
+      <c r="H89" s="142"/>
+      <c r="I89" s="142"/>
+      <c r="J89" s="142"/>
+      <c r="K89" s="143"/>
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B90" s="116"/>
-      <c r="C90" s="117"/>
-      <c r="D90" s="117"/>
-      <c r="E90" s="117"/>
-      <c r="F90" s="117"/>
-      <c r="G90" s="117"/>
-      <c r="H90" s="117"/>
-      <c r="I90" s="117"/>
-      <c r="J90" s="117"/>
-      <c r="K90" s="120"/>
+      <c r="B90" s="141"/>
+      <c r="C90" s="142"/>
+      <c r="D90" s="142"/>
+      <c r="E90" s="142"/>
+      <c r="F90" s="142"/>
+      <c r="G90" s="142"/>
+      <c r="H90" s="142"/>
+      <c r="I90" s="142"/>
+      <c r="J90" s="142"/>
+      <c r="K90" s="143"/>
     </row>
     <row r="91" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B91" s="116"/>
-      <c r="C91" s="117"/>
-      <c r="D91" s="117"/>
-      <c r="E91" s="117"/>
-      <c r="F91" s="117"/>
-      <c r="G91" s="117"/>
-      <c r="H91" s="117"/>
-      <c r="I91" s="117"/>
-      <c r="J91" s="117"/>
-      <c r="K91" s="120"/>
+      <c r="B91" s="141"/>
+      <c r="C91" s="142"/>
+      <c r="D91" s="142"/>
+      <c r="E91" s="142"/>
+      <c r="F91" s="142"/>
+      <c r="G91" s="142"/>
+      <c r="H91" s="142"/>
+      <c r="I91" s="142"/>
+      <c r="J91" s="142"/>
+      <c r="K91" s="143"/>
     </row>
     <row r="92" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B92" s="116"/>
-      <c r="C92" s="117"/>
-      <c r="D92" s="117"/>
-      <c r="E92" s="117"/>
-      <c r="F92" s="117"/>
-      <c r="G92" s="117"/>
-      <c r="H92" s="117"/>
-      <c r="I92" s="117"/>
-      <c r="J92" s="117"/>
-      <c r="K92" s="120"/>
+      <c r="B92" s="141"/>
+      <c r="C92" s="142"/>
+      <c r="D92" s="142"/>
+      <c r="E92" s="142"/>
+      <c r="F92" s="142"/>
+      <c r="G92" s="142"/>
+      <c r="H92" s="142"/>
+      <c r="I92" s="142"/>
+      <c r="J92" s="142"/>
+      <c r="K92" s="143"/>
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B93" s="116"/>
-      <c r="C93" s="117"/>
-      <c r="D93" s="117"/>
-      <c r="E93" s="117"/>
-      <c r="F93" s="117"/>
-      <c r="G93" s="117"/>
-      <c r="H93" s="117"/>
-      <c r="I93" s="117"/>
-      <c r="J93" s="117"/>
-      <c r="K93" s="120"/>
+      <c r="B93" s="141"/>
+      <c r="C93" s="142"/>
+      <c r="D93" s="142"/>
+      <c r="E93" s="142"/>
+      <c r="F93" s="142"/>
+      <c r="G93" s="142"/>
+      <c r="H93" s="142"/>
+      <c r="I93" s="142"/>
+      <c r="J93" s="142"/>
+      <c r="K93" s="143"/>
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B94" s="116"/>
-      <c r="C94" s="117"/>
-      <c r="D94" s="117"/>
-      <c r="E94" s="117"/>
-      <c r="F94" s="117"/>
-      <c r="G94" s="117"/>
-      <c r="H94" s="117"/>
-      <c r="I94" s="117"/>
-      <c r="J94" s="117"/>
-      <c r="K94" s="120"/>
+      <c r="B94" s="141"/>
+      <c r="C94" s="142"/>
+      <c r="D94" s="142"/>
+      <c r="E94" s="142"/>
+      <c r="F94" s="142"/>
+      <c r="G94" s="142"/>
+      <c r="H94" s="142"/>
+      <c r="I94" s="142"/>
+      <c r="J94" s="142"/>
+      <c r="K94" s="143"/>
     </row>
     <row r="95" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B95" s="118"/>
-      <c r="C95" s="119"/>
-      <c r="D95" s="119"/>
-      <c r="E95" s="119"/>
-      <c r="F95" s="119"/>
-      <c r="G95" s="119"/>
-      <c r="H95" s="119"/>
-      <c r="I95" s="119"/>
-      <c r="J95" s="119"/>
-      <c r="K95" s="121"/>
+      <c r="B95" s="146"/>
+      <c r="C95" s="147"/>
+      <c r="D95" s="147"/>
+      <c r="E95" s="147"/>
+      <c r="F95" s="147"/>
+      <c r="G95" s="147"/>
+      <c r="H95" s="147"/>
+      <c r="I95" s="147"/>
+      <c r="J95" s="147"/>
+      <c r="K95" s="148"/>
     </row>
   </sheetData>
   <mergeCells count="56">
-    <mergeCell ref="B1:K3"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B7:F14"/>
-    <mergeCell ref="G6:K6"/>
-    <mergeCell ref="G7:K14"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="B4:K4"/>
+    <mergeCell ref="B88:F95"/>
+    <mergeCell ref="G88:K95"/>
+    <mergeCell ref="B78:F85"/>
+    <mergeCell ref="G78:K85"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="H86:I86"/>
+    <mergeCell ref="B87:F87"/>
+    <mergeCell ref="G87:K87"/>
+    <mergeCell ref="B68:F75"/>
+    <mergeCell ref="G68:K75"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="H76:I76"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="G77:K77"/>
+    <mergeCell ref="B58:F65"/>
+    <mergeCell ref="G58:K65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="H66:I66"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="G67:K67"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="G57:K57"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="G16:K16"/>
+    <mergeCell ref="B17:F24"/>
+    <mergeCell ref="G17:K24"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="G26:K26"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="B48:F55"/>
+    <mergeCell ref="G48:K55"/>
+    <mergeCell ref="B37:F44"/>
+    <mergeCell ref="G37:K44"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="C46:D46"/>
@@ -13824,40 +14087,14 @@
     <mergeCell ref="G36:K36"/>
     <mergeCell ref="C35:D35"/>
     <mergeCell ref="H35:I35"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="G57:K57"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="G16:K16"/>
-    <mergeCell ref="B17:F24"/>
-    <mergeCell ref="G17:K24"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="G26:K26"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="B48:F55"/>
-    <mergeCell ref="G48:K55"/>
-    <mergeCell ref="B37:F44"/>
-    <mergeCell ref="G37:K44"/>
-    <mergeCell ref="B58:F65"/>
-    <mergeCell ref="G58:K65"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="H66:I66"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="G67:K67"/>
-    <mergeCell ref="B68:F75"/>
-    <mergeCell ref="G68:K75"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="H76:I76"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="G77:K77"/>
-    <mergeCell ref="B88:F95"/>
-    <mergeCell ref="G88:K95"/>
-    <mergeCell ref="B78:F85"/>
-    <mergeCell ref="G78:K85"/>
-    <mergeCell ref="C86:D86"/>
-    <mergeCell ref="H86:I86"/>
-    <mergeCell ref="B87:F87"/>
-    <mergeCell ref="G87:K87"/>
+    <mergeCell ref="B1:K3"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B7:F14"/>
+    <mergeCell ref="G6:K6"/>
+    <mergeCell ref="G7:K14"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="B4:K4"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -13878,7 +14115,7 @@
   <sheetData>
     <row r="1" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="149" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C1" s="149"/>
       <c r="D1" s="149"/>
@@ -13906,7 +14143,7 @@
     </row>
     <row r="3" spans="2:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="150" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3" s="151"/>
       <c r="D3" s="151"/>
@@ -13934,51 +14171,51 @@
     </row>
     <row r="5" spans="2:13" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="154" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C5" s="155"/>
-      <c r="D5" s="148"/>
-      <c r="E5" s="148"/>
-      <c r="F5" s="148"/>
-      <c r="G5" s="148"/>
-      <c r="H5" s="148"/>
-      <c r="I5" s="148"/>
-      <c r="J5" s="117"/>
-      <c r="K5" s="117"/>
-      <c r="L5" s="117"/>
-      <c r="M5" s="117"/>
+      <c r="D5" s="159"/>
+      <c r="E5" s="159"/>
+      <c r="F5" s="159"/>
+      <c r="G5" s="159"/>
+      <c r="H5" s="159"/>
+      <c r="I5" s="159"/>
+      <c r="J5" s="142"/>
+      <c r="K5" s="142"/>
+      <c r="L5" s="142"/>
+      <c r="M5" s="142"/>
     </row>
     <row r="6" spans="2:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="156" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6" s="157"/>
-      <c r="D6" s="148"/>
-      <c r="E6" s="148"/>
-      <c r="F6" s="148"/>
-      <c r="G6" s="148"/>
-      <c r="H6" s="148"/>
-      <c r="I6" s="148"/>
-      <c r="J6" s="117"/>
-      <c r="K6" s="117"/>
-      <c r="L6" s="117"/>
-      <c r="M6" s="117"/>
+      <c r="D6" s="159"/>
+      <c r="E6" s="159"/>
+      <c r="F6" s="159"/>
+      <c r="G6" s="159"/>
+      <c r="H6" s="159"/>
+      <c r="I6" s="159"/>
+      <c r="J6" s="142"/>
+      <c r="K6" s="142"/>
+      <c r="L6" s="142"/>
+      <c r="M6" s="142"/>
     </row>
     <row r="7" spans="2:13" s="62" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="152" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C7" s="153"/>
-      <c r="D7" s="148"/>
-      <c r="E7" s="148"/>
-      <c r="F7" s="148"/>
-      <c r="G7" s="148"/>
-      <c r="H7" s="148"/>
-      <c r="I7" s="148"/>
-      <c r="J7" s="117"/>
-      <c r="K7" s="117"/>
-      <c r="L7" s="117"/>
-      <c r="M7" s="117"/>
+      <c r="D7" s="159"/>
+      <c r="E7" s="159"/>
+      <c r="F7" s="159"/>
+      <c r="G7" s="159"/>
+      <c r="H7" s="159"/>
+      <c r="I7" s="159"/>
+      <c r="J7" s="142"/>
+      <c r="K7" s="142"/>
+      <c r="L7" s="142"/>
+      <c r="M7" s="142"/>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B8" s="2">
@@ -14650,6 +14887,14 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="M5:M7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="H5:H7"/>
+    <mergeCell ref="I5:I7"/>
+    <mergeCell ref="J5:J7"/>
     <mergeCell ref="B1:L2"/>
     <mergeCell ref="B3:L3"/>
     <mergeCell ref="B7:C7"/>
@@ -14658,14 +14903,6 @@
     <mergeCell ref="B4:L4"/>
     <mergeCell ref="K5:K7"/>
     <mergeCell ref="L5:L7"/>
-    <mergeCell ref="M5:M7"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="F5:F7"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="H5:H7"/>
-    <mergeCell ref="I5:I7"/>
-    <mergeCell ref="J5:J7"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="90" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -14679,569 +14916,602 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:12" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="161" t="s">
-        <v>75</v>
-      </c>
-      <c r="B2" s="161"/>
-      <c r="C2" s="161"/>
-      <c r="D2" s="161"/>
-      <c r="E2" s="161"/>
-      <c r="F2" s="161"/>
-      <c r="G2" s="161"/>
-      <c r="H2" s="161"/>
-      <c r="I2" s="161"/>
-      <c r="J2" s="161"/>
-      <c r="K2" s="161"/>
-      <c r="L2" s="161"/>
+      <c r="A2" s="160" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" s="160"/>
+      <c r="C2" s="160"/>
+      <c r="D2" s="160"/>
+      <c r="E2" s="160"/>
+      <c r="F2" s="160"/>
+      <c r="G2" s="160"/>
+      <c r="H2" s="160"/>
+      <c r="I2" s="160"/>
+      <c r="J2" s="160"/>
+      <c r="K2" s="160"/>
+      <c r="L2" s="160"/>
     </row>
     <row r="3" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="159" t="s">
-        <v>72</v>
-      </c>
-      <c r="B5" s="159"/>
-      <c r="C5" s="159"/>
-      <c r="D5" s="117" t="s">
+      <c r="A5" s="161" t="s">
         <v>73</v>
       </c>
-      <c r="E5" s="117"/>
-      <c r="F5" s="117"/>
-      <c r="G5" s="117"/>
-      <c r="H5" s="117"/>
-      <c r="I5" s="117"/>
-      <c r="J5" s="117"/>
-      <c r="K5" s="117"/>
-      <c r="L5" s="117"/>
+      <c r="B5" s="161"/>
+      <c r="C5" s="161"/>
+      <c r="D5" s="142" t="s">
+        <v>74</v>
+      </c>
+      <c r="E5" s="142"/>
+      <c r="F5" s="142"/>
+      <c r="G5" s="142"/>
+      <c r="H5" s="142"/>
+      <c r="I5" s="142"/>
+      <c r="J5" s="142"/>
+      <c r="K5" s="142"/>
+      <c r="L5" s="142"/>
     </row>
     <row r="6" spans="1:12" s="62" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="159"/>
-      <c r="B6" s="159"/>
-      <c r="C6" s="159"/>
-      <c r="D6" s="160" t="s">
+      <c r="A6" s="161"/>
+      <c r="B6" s="161"/>
+      <c r="C6" s="161"/>
+      <c r="D6" s="162" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" s="162"/>
+      <c r="F6" s="162"/>
+      <c r="G6" s="162"/>
+      <c r="H6" s="162"/>
+      <c r="I6" s="162"/>
+      <c r="J6" s="162"/>
+      <c r="K6" s="162"/>
+      <c r="L6" s="162"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="161" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="161"/>
+      <c r="C8" s="161"/>
+      <c r="D8" s="142" t="s">
         <v>74</v>
       </c>
-      <c r="E6" s="160"/>
-      <c r="F6" s="160"/>
-      <c r="G6" s="160"/>
-      <c r="H6" s="160"/>
-      <c r="I6" s="160"/>
-      <c r="J6" s="160"/>
-      <c r="K6" s="160"/>
-      <c r="L6" s="160"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="159" t="s">
-        <v>72</v>
-      </c>
-      <c r="B8" s="159"/>
-      <c r="C8" s="159"/>
-      <c r="D8" s="117" t="s">
+      <c r="E8" s="142"/>
+      <c r="F8" s="142"/>
+      <c r="G8" s="142"/>
+      <c r="H8" s="142"/>
+      <c r="I8" s="142"/>
+      <c r="J8" s="142"/>
+      <c r="K8" s="142"/>
+      <c r="L8" s="142"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="161"/>
+      <c r="B9" s="161"/>
+      <c r="C9" s="161"/>
+      <c r="D9" s="162" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" s="162"/>
+      <c r="F9" s="162"/>
+      <c r="G9" s="162"/>
+      <c r="H9" s="162"/>
+      <c r="I9" s="162"/>
+      <c r="J9" s="162"/>
+      <c r="K9" s="162"/>
+      <c r="L9" s="162"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="161" t="s">
         <v>73</v>
       </c>
-      <c r="E8" s="117"/>
-      <c r="F8" s="117"/>
-      <c r="G8" s="117"/>
-      <c r="H8" s="117"/>
-      <c r="I8" s="117"/>
-      <c r="J8" s="117"/>
-      <c r="K8" s="117"/>
-      <c r="L8" s="117"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="159"/>
-      <c r="B9" s="159"/>
-      <c r="C9" s="159"/>
-      <c r="D9" s="160" t="s">
+      <c r="B11" s="161"/>
+      <c r="C11" s="161"/>
+      <c r="D11" s="142" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="160"/>
-      <c r="F9" s="160"/>
-      <c r="G9" s="160"/>
-      <c r="H9" s="160"/>
-      <c r="I9" s="160"/>
-      <c r="J9" s="160"/>
-      <c r="K9" s="160"/>
-      <c r="L9" s="160"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="159" t="s">
-        <v>72</v>
-      </c>
-      <c r="B11" s="159"/>
-      <c r="C11" s="159"/>
-      <c r="D11" s="117" t="s">
+      <c r="E11" s="142"/>
+      <c r="F11" s="142"/>
+      <c r="G11" s="142"/>
+      <c r="H11" s="142"/>
+      <c r="I11" s="142"/>
+      <c r="J11" s="142"/>
+      <c r="K11" s="142"/>
+      <c r="L11" s="142"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="161"/>
+      <c r="B12" s="161"/>
+      <c r="C12" s="161"/>
+      <c r="D12" s="162" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" s="162"/>
+      <c r="F12" s="162"/>
+      <c r="G12" s="162"/>
+      <c r="H12" s="162"/>
+      <c r="I12" s="162"/>
+      <c r="J12" s="162"/>
+      <c r="K12" s="162"/>
+      <c r="L12" s="162"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="161" t="s">
         <v>73</v>
       </c>
-      <c r="E11" s="117"/>
-      <c r="F11" s="117"/>
-      <c r="G11" s="117"/>
-      <c r="H11" s="117"/>
-      <c r="I11" s="117"/>
-      <c r="J11" s="117"/>
-      <c r="K11" s="117"/>
-      <c r="L11" s="117"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="159"/>
-      <c r="B12" s="159"/>
-      <c r="C12" s="159"/>
-      <c r="D12" s="160" t="s">
+      <c r="B14" s="161"/>
+      <c r="C14" s="161"/>
+      <c r="D14" s="142" t="s">
         <v>74</v>
       </c>
-      <c r="E12" s="160"/>
-      <c r="F12" s="160"/>
-      <c r="G12" s="160"/>
-      <c r="H12" s="160"/>
-      <c r="I12" s="160"/>
-      <c r="J12" s="160"/>
-      <c r="K12" s="160"/>
-      <c r="L12" s="160"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="159" t="s">
-        <v>72</v>
-      </c>
-      <c r="B14" s="159"/>
-      <c r="C14" s="159"/>
-      <c r="D14" s="117" t="s">
+      <c r="E14" s="142"/>
+      <c r="F14" s="142"/>
+      <c r="G14" s="142"/>
+      <c r="H14" s="142"/>
+      <c r="I14" s="142"/>
+      <c r="J14" s="142"/>
+      <c r="K14" s="142"/>
+      <c r="L14" s="142"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="161"/>
+      <c r="B15" s="161"/>
+      <c r="C15" s="161"/>
+      <c r="D15" s="162" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" s="162"/>
+      <c r="F15" s="162"/>
+      <c r="G15" s="162"/>
+      <c r="H15" s="162"/>
+      <c r="I15" s="162"/>
+      <c r="J15" s="162"/>
+      <c r="K15" s="162"/>
+      <c r="L15" s="162"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="161" t="s">
         <v>73</v>
       </c>
-      <c r="E14" s="117"/>
-      <c r="F14" s="117"/>
-      <c r="G14" s="117"/>
-      <c r="H14" s="117"/>
-      <c r="I14" s="117"/>
-      <c r="J14" s="117"/>
-      <c r="K14" s="117"/>
-      <c r="L14" s="117"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="159"/>
-      <c r="B15" s="159"/>
-      <c r="C15" s="159"/>
-      <c r="D15" s="160" t="s">
+      <c r="B17" s="161"/>
+      <c r="C17" s="161"/>
+      <c r="D17" s="142" t="s">
         <v>74</v>
       </c>
-      <c r="E15" s="160"/>
-      <c r="F15" s="160"/>
-      <c r="G15" s="160"/>
-      <c r="H15" s="160"/>
-      <c r="I15" s="160"/>
-      <c r="J15" s="160"/>
-      <c r="K15" s="160"/>
-      <c r="L15" s="160"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="159" t="s">
-        <v>72</v>
-      </c>
-      <c r="B17" s="159"/>
-      <c r="C17" s="159"/>
-      <c r="D17" s="117" t="s">
+      <c r="E17" s="142"/>
+      <c r="F17" s="142"/>
+      <c r="G17" s="142"/>
+      <c r="H17" s="142"/>
+      <c r="I17" s="142"/>
+      <c r="J17" s="142"/>
+      <c r="K17" s="142"/>
+      <c r="L17" s="142"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="161"/>
+      <c r="B18" s="161"/>
+      <c r="C18" s="161"/>
+      <c r="D18" s="162" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" s="162"/>
+      <c r="F18" s="162"/>
+      <c r="G18" s="162"/>
+      <c r="H18" s="162"/>
+      <c r="I18" s="162"/>
+      <c r="J18" s="162"/>
+      <c r="K18" s="162"/>
+      <c r="L18" s="162"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="161" t="s">
         <v>73</v>
       </c>
-      <c r="E17" s="117"/>
-      <c r="F17" s="117"/>
-      <c r="G17" s="117"/>
-      <c r="H17" s="117"/>
-      <c r="I17" s="117"/>
-      <c r="J17" s="117"/>
-      <c r="K17" s="117"/>
-      <c r="L17" s="117"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="159"/>
-      <c r="B18" s="159"/>
-      <c r="C18" s="159"/>
-      <c r="D18" s="160" t="s">
+      <c r="B20" s="161"/>
+      <c r="C20" s="161"/>
+      <c r="D20" s="142" t="s">
         <v>74</v>
       </c>
-      <c r="E18" s="160"/>
-      <c r="F18" s="160"/>
-      <c r="G18" s="160"/>
-      <c r="H18" s="160"/>
-      <c r="I18" s="160"/>
-      <c r="J18" s="160"/>
-      <c r="K18" s="160"/>
-      <c r="L18" s="160"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="159" t="s">
-        <v>72</v>
-      </c>
-      <c r="B20" s="159"/>
-      <c r="C20" s="159"/>
-      <c r="D20" s="117" t="s">
+      <c r="E20" s="142"/>
+      <c r="F20" s="142"/>
+      <c r="G20" s="142"/>
+      <c r="H20" s="142"/>
+      <c r="I20" s="142"/>
+      <c r="J20" s="142"/>
+      <c r="K20" s="142"/>
+      <c r="L20" s="142"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="161"/>
+      <c r="B21" s="161"/>
+      <c r="C21" s="161"/>
+      <c r="D21" s="162" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" s="162"/>
+      <c r="F21" s="162"/>
+      <c r="G21" s="162"/>
+      <c r="H21" s="162"/>
+      <c r="I21" s="162"/>
+      <c r="J21" s="162"/>
+      <c r="K21" s="162"/>
+      <c r="L21" s="162"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="161" t="s">
         <v>73</v>
       </c>
-      <c r="E20" s="117"/>
-      <c r="F20" s="117"/>
-      <c r="G20" s="117"/>
-      <c r="H20" s="117"/>
-      <c r="I20" s="117"/>
-      <c r="J20" s="117"/>
-      <c r="K20" s="117"/>
-      <c r="L20" s="117"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="159"/>
-      <c r="B21" s="159"/>
-      <c r="C21" s="159"/>
-      <c r="D21" s="160" t="s">
+      <c r="B23" s="161"/>
+      <c r="C23" s="161"/>
+      <c r="D23" s="142" t="s">
         <v>74</v>
       </c>
-      <c r="E21" s="160"/>
-      <c r="F21" s="160"/>
-      <c r="G21" s="160"/>
-      <c r="H21" s="160"/>
-      <c r="I21" s="160"/>
-      <c r="J21" s="160"/>
-      <c r="K21" s="160"/>
-      <c r="L21" s="160"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="159" t="s">
-        <v>72</v>
-      </c>
-      <c r="B23" s="159"/>
-      <c r="C23" s="159"/>
-      <c r="D23" s="117" t="s">
+      <c r="E23" s="142"/>
+      <c r="F23" s="142"/>
+      <c r="G23" s="142"/>
+      <c r="H23" s="142"/>
+      <c r="I23" s="142"/>
+      <c r="J23" s="142"/>
+      <c r="K23" s="142"/>
+      <c r="L23" s="142"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="161"/>
+      <c r="B24" s="161"/>
+      <c r="C24" s="161"/>
+      <c r="D24" s="162" t="s">
+        <v>75</v>
+      </c>
+      <c r="E24" s="162"/>
+      <c r="F24" s="162"/>
+      <c r="G24" s="162"/>
+      <c r="H24" s="162"/>
+      <c r="I24" s="162"/>
+      <c r="J24" s="162"/>
+      <c r="K24" s="162"/>
+      <c r="L24" s="162"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="161" t="s">
         <v>73</v>
       </c>
-      <c r="E23" s="117"/>
-      <c r="F23" s="117"/>
-      <c r="G23" s="117"/>
-      <c r="H23" s="117"/>
-      <c r="I23" s="117"/>
-      <c r="J23" s="117"/>
-      <c r="K23" s="117"/>
-      <c r="L23" s="117"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="159"/>
-      <c r="B24" s="159"/>
-      <c r="C24" s="159"/>
-      <c r="D24" s="160" t="s">
+      <c r="B26" s="161"/>
+      <c r="C26" s="161"/>
+      <c r="D26" s="142" t="s">
         <v>74</v>
       </c>
-      <c r="E24" s="160"/>
-      <c r="F24" s="160"/>
-      <c r="G24" s="160"/>
-      <c r="H24" s="160"/>
-      <c r="I24" s="160"/>
-      <c r="J24" s="160"/>
-      <c r="K24" s="160"/>
-      <c r="L24" s="160"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="159" t="s">
-        <v>72</v>
-      </c>
-      <c r="B26" s="159"/>
-      <c r="C26" s="159"/>
-      <c r="D26" s="117" t="s">
+      <c r="E26" s="142"/>
+      <c r="F26" s="142"/>
+      <c r="G26" s="142"/>
+      <c r="H26" s="142"/>
+      <c r="I26" s="142"/>
+      <c r="J26" s="142"/>
+      <c r="K26" s="142"/>
+      <c r="L26" s="142"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="161"/>
+      <c r="B27" s="161"/>
+      <c r="C27" s="161"/>
+      <c r="D27" s="162" t="s">
+        <v>75</v>
+      </c>
+      <c r="E27" s="162"/>
+      <c r="F27" s="162"/>
+      <c r="G27" s="162"/>
+      <c r="H27" s="162"/>
+      <c r="I27" s="162"/>
+      <c r="J27" s="162"/>
+      <c r="K27" s="162"/>
+      <c r="L27" s="162"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="161" t="s">
         <v>73</v>
       </c>
-      <c r="E26" s="117"/>
-      <c r="F26" s="117"/>
-      <c r="G26" s="117"/>
-      <c r="H26" s="117"/>
-      <c r="I26" s="117"/>
-      <c r="J26" s="117"/>
-      <c r="K26" s="117"/>
-      <c r="L26" s="117"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="159"/>
-      <c r="B27" s="159"/>
-      <c r="C27" s="159"/>
-      <c r="D27" s="160" t="s">
+      <c r="B29" s="161"/>
+      <c r="C29" s="161"/>
+      <c r="D29" s="142" t="s">
         <v>74</v>
       </c>
-      <c r="E27" s="160"/>
-      <c r="F27" s="160"/>
-      <c r="G27" s="160"/>
-      <c r="H27" s="160"/>
-      <c r="I27" s="160"/>
-      <c r="J27" s="160"/>
-      <c r="K27" s="160"/>
-      <c r="L27" s="160"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="159" t="s">
-        <v>72</v>
-      </c>
-      <c r="B29" s="159"/>
-      <c r="C29" s="159"/>
-      <c r="D29" s="117" t="s">
+      <c r="E29" s="142"/>
+      <c r="F29" s="142"/>
+      <c r="G29" s="142"/>
+      <c r="H29" s="142"/>
+      <c r="I29" s="142"/>
+      <c r="J29" s="142"/>
+      <c r="K29" s="142"/>
+      <c r="L29" s="142"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="161"/>
+      <c r="B30" s="161"/>
+      <c r="C30" s="161"/>
+      <c r="D30" s="162" t="s">
+        <v>75</v>
+      </c>
+      <c r="E30" s="162"/>
+      <c r="F30" s="162"/>
+      <c r="G30" s="162"/>
+      <c r="H30" s="162"/>
+      <c r="I30" s="162"/>
+      <c r="J30" s="162"/>
+      <c r="K30" s="162"/>
+      <c r="L30" s="162"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="161" t="s">
         <v>73</v>
       </c>
-      <c r="E29" s="117"/>
-      <c r="F29" s="117"/>
-      <c r="G29" s="117"/>
-      <c r="H29" s="117"/>
-      <c r="I29" s="117"/>
-      <c r="J29" s="117"/>
-      <c r="K29" s="117"/>
-      <c r="L29" s="117"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="159"/>
-      <c r="B30" s="159"/>
-      <c r="C30" s="159"/>
-      <c r="D30" s="160" t="s">
+      <c r="B32" s="161"/>
+      <c r="C32" s="161"/>
+      <c r="D32" s="142" t="s">
         <v>74</v>
       </c>
-      <c r="E30" s="160"/>
-      <c r="F30" s="160"/>
-      <c r="G30" s="160"/>
-      <c r="H30" s="160"/>
-      <c r="I30" s="160"/>
-      <c r="J30" s="160"/>
-      <c r="K30" s="160"/>
-      <c r="L30" s="160"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="159" t="s">
-        <v>72</v>
-      </c>
-      <c r="B32" s="159"/>
-      <c r="C32" s="159"/>
-      <c r="D32" s="117" t="s">
+      <c r="E32" s="142"/>
+      <c r="F32" s="142"/>
+      <c r="G32" s="142"/>
+      <c r="H32" s="142"/>
+      <c r="I32" s="142"/>
+      <c r="J32" s="142"/>
+      <c r="K32" s="142"/>
+      <c r="L32" s="142"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="161"/>
+      <c r="B33" s="161"/>
+      <c r="C33" s="161"/>
+      <c r="D33" s="162" t="s">
+        <v>75</v>
+      </c>
+      <c r="E33" s="162"/>
+      <c r="F33" s="162"/>
+      <c r="G33" s="162"/>
+      <c r="H33" s="162"/>
+      <c r="I33" s="162"/>
+      <c r="J33" s="162"/>
+      <c r="K33" s="162"/>
+      <c r="L33" s="162"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" s="161" t="s">
         <v>73</v>
       </c>
-      <c r="E32" s="117"/>
-      <c r="F32" s="117"/>
-      <c r="G32" s="117"/>
-      <c r="H32" s="117"/>
-      <c r="I32" s="117"/>
-      <c r="J32" s="117"/>
-      <c r="K32" s="117"/>
-      <c r="L32" s="117"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="159"/>
-      <c r="B33" s="159"/>
-      <c r="C33" s="159"/>
-      <c r="D33" s="160" t="s">
+      <c r="B35" s="161"/>
+      <c r="C35" s="161"/>
+      <c r="D35" s="142" t="s">
         <v>74</v>
       </c>
-      <c r="E33" s="160"/>
-      <c r="F33" s="160"/>
-      <c r="G33" s="160"/>
-      <c r="H33" s="160"/>
-      <c r="I33" s="160"/>
-      <c r="J33" s="160"/>
-      <c r="K33" s="160"/>
-      <c r="L33" s="160"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="159" t="s">
-        <v>72</v>
-      </c>
-      <c r="B35" s="159"/>
-      <c r="C35" s="159"/>
-      <c r="D35" s="117" t="s">
+      <c r="E35" s="142"/>
+      <c r="F35" s="142"/>
+      <c r="G35" s="142"/>
+      <c r="H35" s="142"/>
+      <c r="I35" s="142"/>
+      <c r="J35" s="142"/>
+      <c r="K35" s="142"/>
+      <c r="L35" s="142"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" s="161"/>
+      <c r="B36" s="161"/>
+      <c r="C36" s="161"/>
+      <c r="D36" s="162" t="s">
+        <v>75</v>
+      </c>
+      <c r="E36" s="162"/>
+      <c r="F36" s="162"/>
+      <c r="G36" s="162"/>
+      <c r="H36" s="162"/>
+      <c r="I36" s="162"/>
+      <c r="J36" s="162"/>
+      <c r="K36" s="162"/>
+      <c r="L36" s="162"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" s="161" t="s">
         <v>73</v>
       </c>
-      <c r="E35" s="117"/>
-      <c r="F35" s="117"/>
-      <c r="G35" s="117"/>
-      <c r="H35" s="117"/>
-      <c r="I35" s="117"/>
-      <c r="J35" s="117"/>
-      <c r="K35" s="117"/>
-      <c r="L35" s="117"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="159"/>
-      <c r="B36" s="159"/>
-      <c r="C36" s="159"/>
-      <c r="D36" s="160" t="s">
+      <c r="B38" s="161"/>
+      <c r="C38" s="161"/>
+      <c r="D38" s="142" t="s">
         <v>74</v>
       </c>
-      <c r="E36" s="160"/>
-      <c r="F36" s="160"/>
-      <c r="G36" s="160"/>
-      <c r="H36" s="160"/>
-      <c r="I36" s="160"/>
-      <c r="J36" s="160"/>
-      <c r="K36" s="160"/>
-      <c r="L36" s="160"/>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" s="159" t="s">
-        <v>72</v>
-      </c>
-      <c r="B38" s="159"/>
-      <c r="C38" s="159"/>
-      <c r="D38" s="117" t="s">
+      <c r="E38" s="142"/>
+      <c r="F38" s="142"/>
+      <c r="G38" s="142"/>
+      <c r="H38" s="142"/>
+      <c r="I38" s="142"/>
+      <c r="J38" s="142"/>
+      <c r="K38" s="142"/>
+      <c r="L38" s="142"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" s="161"/>
+      <c r="B39" s="161"/>
+      <c r="C39" s="161"/>
+      <c r="D39" s="162" t="s">
+        <v>75</v>
+      </c>
+      <c r="E39" s="162"/>
+      <c r="F39" s="162"/>
+      <c r="G39" s="162"/>
+      <c r="H39" s="162"/>
+      <c r="I39" s="162"/>
+      <c r="J39" s="162"/>
+      <c r="K39" s="162"/>
+      <c r="L39" s="162"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" s="161" t="s">
         <v>73</v>
       </c>
-      <c r="E38" s="117"/>
-      <c r="F38" s="117"/>
-      <c r="G38" s="117"/>
-      <c r="H38" s="117"/>
-      <c r="I38" s="117"/>
-      <c r="J38" s="117"/>
-      <c r="K38" s="117"/>
-      <c r="L38" s="117"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="159"/>
-      <c r="B39" s="159"/>
-      <c r="C39" s="159"/>
-      <c r="D39" s="160" t="s">
+      <c r="B41" s="161"/>
+      <c r="C41" s="161"/>
+      <c r="D41" s="142" t="s">
         <v>74</v>
       </c>
-      <c r="E39" s="160"/>
-      <c r="F39" s="160"/>
-      <c r="G39" s="160"/>
-      <c r="H39" s="160"/>
-      <c r="I39" s="160"/>
-      <c r="J39" s="160"/>
-      <c r="K39" s="160"/>
-      <c r="L39" s="160"/>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41" s="159" t="s">
-        <v>72</v>
-      </c>
-      <c r="B41" s="159"/>
-      <c r="C41" s="159"/>
-      <c r="D41" s="117" t="s">
+      <c r="E41" s="142"/>
+      <c r="F41" s="142"/>
+      <c r="G41" s="142"/>
+      <c r="H41" s="142"/>
+      <c r="I41" s="142"/>
+      <c r="J41" s="142"/>
+      <c r="K41" s="142"/>
+      <c r="L41" s="142"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A42" s="161"/>
+      <c r="B42" s="161"/>
+      <c r="C42" s="161"/>
+      <c r="D42" s="162" t="s">
+        <v>75</v>
+      </c>
+      <c r="E42" s="162"/>
+      <c r="F42" s="162"/>
+      <c r="G42" s="162"/>
+      <c r="H42" s="162"/>
+      <c r="I42" s="162"/>
+      <c r="J42" s="162"/>
+      <c r="K42" s="162"/>
+      <c r="L42" s="162"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A44" s="161" t="s">
         <v>73</v>
       </c>
-      <c r="E41" s="117"/>
-      <c r="F41" s="117"/>
-      <c r="G41" s="117"/>
-      <c r="H41" s="117"/>
-      <c r="I41" s="117"/>
-      <c r="J41" s="117"/>
-      <c r="K41" s="117"/>
-      <c r="L41" s="117"/>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="159"/>
-      <c r="B42" s="159"/>
-      <c r="C42" s="159"/>
-      <c r="D42" s="160" t="s">
+      <c r="B44" s="161"/>
+      <c r="C44" s="161"/>
+      <c r="D44" s="142" t="s">
         <v>74</v>
       </c>
-      <c r="E42" s="160"/>
-      <c r="F42" s="160"/>
-      <c r="G42" s="160"/>
-      <c r="H42" s="160"/>
-      <c r="I42" s="160"/>
-      <c r="J42" s="160"/>
-      <c r="K42" s="160"/>
-      <c r="L42" s="160"/>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A44" s="159" t="s">
-        <v>72</v>
-      </c>
-      <c r="B44" s="159"/>
-      <c r="C44" s="159"/>
-      <c r="D44" s="117" t="s">
+      <c r="E44" s="142"/>
+      <c r="F44" s="142"/>
+      <c r="G44" s="142"/>
+      <c r="H44" s="142"/>
+      <c r="I44" s="142"/>
+      <c r="J44" s="142"/>
+      <c r="K44" s="142"/>
+      <c r="L44" s="142"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A45" s="161"/>
+      <c r="B45" s="161"/>
+      <c r="C45" s="161"/>
+      <c r="D45" s="162" t="s">
+        <v>75</v>
+      </c>
+      <c r="E45" s="162"/>
+      <c r="F45" s="162"/>
+      <c r="G45" s="162"/>
+      <c r="H45" s="162"/>
+      <c r="I45" s="162"/>
+      <c r="J45" s="162"/>
+      <c r="K45" s="162"/>
+      <c r="L45" s="162"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A47" s="161" t="s">
         <v>73</v>
       </c>
-      <c r="E44" s="117"/>
-      <c r="F44" s="117"/>
-      <c r="G44" s="117"/>
-      <c r="H44" s="117"/>
-      <c r="I44" s="117"/>
-      <c r="J44" s="117"/>
-      <c r="K44" s="117"/>
-      <c r="L44" s="117"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45" s="159"/>
-      <c r="B45" s="159"/>
-      <c r="C45" s="159"/>
-      <c r="D45" s="160" t="s">
+      <c r="B47" s="161"/>
+      <c r="C47" s="161"/>
+      <c r="D47" s="142" t="s">
         <v>74</v>
       </c>
-      <c r="E45" s="160"/>
-      <c r="F45" s="160"/>
-      <c r="G45" s="160"/>
-      <c r="H45" s="160"/>
-      <c r="I45" s="160"/>
-      <c r="J45" s="160"/>
-      <c r="K45" s="160"/>
-      <c r="L45" s="160"/>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="159" t="s">
-        <v>72</v>
-      </c>
-      <c r="B47" s="159"/>
-      <c r="C47" s="159"/>
-      <c r="D47" s="117" t="s">
+      <c r="E47" s="142"/>
+      <c r="F47" s="142"/>
+      <c r="G47" s="142"/>
+      <c r="H47" s="142"/>
+      <c r="I47" s="142"/>
+      <c r="J47" s="142"/>
+      <c r="K47" s="142"/>
+      <c r="L47" s="142"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A48" s="161"/>
+      <c r="B48" s="161"/>
+      <c r="C48" s="161"/>
+      <c r="D48" s="162" t="s">
+        <v>75</v>
+      </c>
+      <c r="E48" s="162"/>
+      <c r="F48" s="162"/>
+      <c r="G48" s="162"/>
+      <c r="H48" s="162"/>
+      <c r="I48" s="162"/>
+      <c r="J48" s="162"/>
+      <c r="K48" s="162"/>
+      <c r="L48" s="162"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" s="161" t="s">
         <v>73</v>
       </c>
-      <c r="E47" s="117"/>
-      <c r="F47" s="117"/>
-      <c r="G47" s="117"/>
-      <c r="H47" s="117"/>
-      <c r="I47" s="117"/>
-      <c r="J47" s="117"/>
-      <c r="K47" s="117"/>
-      <c r="L47" s="117"/>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48" s="159"/>
-      <c r="B48" s="159"/>
-      <c r="C48" s="159"/>
-      <c r="D48" s="160" t="s">
+      <c r="B50" s="161"/>
+      <c r="C50" s="161"/>
+      <c r="D50" s="142" t="s">
         <v>74</v>
       </c>
-      <c r="E48" s="160"/>
-      <c r="F48" s="160"/>
-      <c r="G48" s="160"/>
-      <c r="H48" s="160"/>
-      <c r="I48" s="160"/>
-      <c r="J48" s="160"/>
-      <c r="K48" s="160"/>
-      <c r="L48" s="160"/>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50" s="159" t="s">
-        <v>72</v>
-      </c>
-      <c r="B50" s="159"/>
-      <c r="C50" s="159"/>
-      <c r="D50" s="117" t="s">
-        <v>73</v>
-      </c>
-      <c r="E50" s="117"/>
-      <c r="F50" s="117"/>
-      <c r="G50" s="117"/>
-      <c r="H50" s="117"/>
-      <c r="I50" s="117"/>
-      <c r="J50" s="117"/>
-      <c r="K50" s="117"/>
-      <c r="L50" s="117"/>
+      <c r="E50" s="142"/>
+      <c r="F50" s="142"/>
+      <c r="G50" s="142"/>
+      <c r="H50" s="142"/>
+      <c r="I50" s="142"/>
+      <c r="J50" s="142"/>
+      <c r="K50" s="142"/>
+      <c r="L50" s="142"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A51" s="159"/>
-      <c r="B51" s="159"/>
-      <c r="C51" s="159"/>
-      <c r="D51" s="160" t="s">
-        <v>74</v>
-      </c>
-      <c r="E51" s="160"/>
-      <c r="F51" s="160"/>
-      <c r="G51" s="160"/>
-      <c r="H51" s="160"/>
-      <c r="I51" s="160"/>
-      <c r="J51" s="160"/>
-      <c r="K51" s="160"/>
-      <c r="L51" s="160"/>
+      <c r="A51" s="161"/>
+      <c r="B51" s="161"/>
+      <c r="C51" s="161"/>
+      <c r="D51" s="162" t="s">
+        <v>75</v>
+      </c>
+      <c r="E51" s="162"/>
+      <c r="F51" s="162"/>
+      <c r="G51" s="162"/>
+      <c r="H51" s="162"/>
+      <c r="I51" s="162"/>
+      <c r="J51" s="162"/>
+      <c r="K51" s="162"/>
+      <c r="L51" s="162"/>
     </row>
   </sheetData>
   <mergeCells count="49">
+    <mergeCell ref="A50:C51"/>
+    <mergeCell ref="D50:L50"/>
+    <mergeCell ref="D51:L51"/>
+    <mergeCell ref="D47:L47"/>
+    <mergeCell ref="D11:L11"/>
+    <mergeCell ref="A44:C45"/>
+    <mergeCell ref="D45:L45"/>
+    <mergeCell ref="A47:C48"/>
+    <mergeCell ref="D48:L48"/>
+    <mergeCell ref="D41:L41"/>
+    <mergeCell ref="D44:L44"/>
+    <mergeCell ref="A38:C39"/>
+    <mergeCell ref="D39:L39"/>
+    <mergeCell ref="A41:C42"/>
+    <mergeCell ref="D42:L42"/>
+    <mergeCell ref="D35:L35"/>
+    <mergeCell ref="D38:L38"/>
+    <mergeCell ref="A32:C33"/>
+    <mergeCell ref="D33:L33"/>
+    <mergeCell ref="A35:C36"/>
+    <mergeCell ref="D36:L36"/>
+    <mergeCell ref="D29:L29"/>
+    <mergeCell ref="D32:L32"/>
+    <mergeCell ref="A26:C27"/>
+    <mergeCell ref="D27:L27"/>
+    <mergeCell ref="A29:C30"/>
+    <mergeCell ref="D30:L30"/>
+    <mergeCell ref="D23:L23"/>
+    <mergeCell ref="D26:L26"/>
+    <mergeCell ref="A20:C21"/>
+    <mergeCell ref="D21:L21"/>
+    <mergeCell ref="A23:C24"/>
+    <mergeCell ref="D24:L24"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="D5:L5"/>
     <mergeCell ref="D8:L8"/>
@@ -15258,39 +15528,6 @@
     <mergeCell ref="D9:L9"/>
     <mergeCell ref="A11:C12"/>
     <mergeCell ref="D12:L12"/>
-    <mergeCell ref="D23:L23"/>
-    <mergeCell ref="D26:L26"/>
-    <mergeCell ref="A20:C21"/>
-    <mergeCell ref="D21:L21"/>
-    <mergeCell ref="A23:C24"/>
-    <mergeCell ref="D24:L24"/>
-    <mergeCell ref="D29:L29"/>
-    <mergeCell ref="D32:L32"/>
-    <mergeCell ref="A26:C27"/>
-    <mergeCell ref="D27:L27"/>
-    <mergeCell ref="A29:C30"/>
-    <mergeCell ref="D30:L30"/>
-    <mergeCell ref="D38:L38"/>
-    <mergeCell ref="A32:C33"/>
-    <mergeCell ref="D33:L33"/>
-    <mergeCell ref="A35:C36"/>
-    <mergeCell ref="D36:L36"/>
-    <mergeCell ref="A50:C51"/>
-    <mergeCell ref="D50:L50"/>
-    <mergeCell ref="D51:L51"/>
-    <mergeCell ref="D47:L47"/>
-    <mergeCell ref="D11:L11"/>
-    <mergeCell ref="A44:C45"/>
-    <mergeCell ref="D45:L45"/>
-    <mergeCell ref="A47:C48"/>
-    <mergeCell ref="D48:L48"/>
-    <mergeCell ref="D41:L41"/>
-    <mergeCell ref="D44:L44"/>
-    <mergeCell ref="A38:C39"/>
-    <mergeCell ref="D39:L39"/>
-    <mergeCell ref="A41:C42"/>
-    <mergeCell ref="D42:L42"/>
-    <mergeCell ref="D35:L35"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="90" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -15308,92 +15545,92 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="73" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="73" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="73" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
